--- a/JsonConverter/ExcelFiles/MainDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/MainDialogue.xlsx
@@ -16,466 +16,466 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="154">
   <x:si>
+    <x:t>시끄러워.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>좋은 저녁.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>길...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하아...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>당연하지!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그게 뭔데?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>글쎄. 뭣 좀 사러 밖에 나갔...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>별거 아니야 조금 생각할게 있어서.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SelectionNameList</x:t>
+  </x:si>
+  <x:si>
+    <x:t>우선 슈가 러쉬부터 시작해보자.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>내가 너를 쥴스라고 부를 수 있게 허락해줄 때 쯤.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>character_jill_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>칵테일 조합법에 있는 탐색 막대를 이용해 레시피를 확인해 봐. 왼쪽 상단에 표시될거야.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(아, 그러고 보니 내 아파트 방바닥에 맥주 캔들이 엄청나게 널브러져 있었지. 또...)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(게다가 포어에게 중성화 수술을 시켜주느라 지갑 속 마지막 동전 하나까지 다써버렸지. 월세를 한번만 더 미뤘다간 쫒겨날거야...)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>했어. 너, 역시 딴 생각에 빠져 있는 것 같아. 그것도 아주 심하게.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(어제는 1시간 동안 혼자 떠들었다고 오해받는 일이 생기질않나.)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오른쪽 가운데에 있는 셰이커에 재료를 원하는 양만큼 클릭해서 넣어.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아, 만약 제조에 실패했다면 리셋 버튼을 눌러서 다시 시도할 수 있어.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>다 끝나면 서빙하기 버튼을 눌러서 손님에게 전해주면 돼. 그게 다야.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>음, 매월 30일에 월세를 내는게 엄청 스트레스거든, 그리고-</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(이틀 전에는 이곳이 폐쇄될 위기에 처했다는 것까지 알게됐지)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>네가 피아노 맨을 만들 수 있을 정도 상태면, 나머지 과정은 생략할게. 그래도 웬만하면 잠ᄁᆞᆫ 참고 나랑 어울려줘, 괜찮지?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>또 맛이나 종류 기준으로 검색할 수 있어. "달콤한" 술이나 "남성적인" 술을 정렬시켜 볼 수 있다는 거야.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>리셋 버튼은 아무 때나 누를 수 있어. 셰이커가 움직이고 있을 때도 말이지. 부담 가지지 말고 원할 때 눌러.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>character_gillian_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그러고 난 다음, 섞기 버튼을 누르면 돼. 다시 눌러서 섞는 걸 멈출 수 있고.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그럼 우리 기초 과정부터 한번 다시 확인해 보자고. 괜찮지? 혹시 모르니까 말야</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>길이 슈가 러쉬나 피아노 맨을 달라는군. 만약에 망쳤다면, 재시도 버튼을 눌러서 다시 하면 되겠지.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아, 안녕 존.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>보스는 어디 있어?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>무슨 말 했어?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TexturePath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VoicePath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string[]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>길리안, 나 공식적인 BTC 교육을 받고 여기 온 거거든?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대체 언제쯤이면 네가 존같이 생겼다는 걸 인정할거야, 길?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>질!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아! 어서 와, 질.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(삶의 기반도 흔들리게 됐는데, 정신까지 나가버릴 지경이라고.)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_018</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_015</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_019</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_096</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_017</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_013</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_014</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_012</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_016</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_033</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_029</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_039</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_021</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_031</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_024</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_030</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_020</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_023</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_022</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_032</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_037</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_028</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_027</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_040</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_034</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_048</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_046</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_035</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_049</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_043</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_045</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_050</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_041</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_054</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_047</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_042</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_036</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_038</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_044</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_052</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_056</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_062</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_065</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_072</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_057</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_058</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_059</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_064</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_061</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_066</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_051</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_063</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_053</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_055</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_060</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_074</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_076</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_083</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_071</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_069</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_068</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_084</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_077</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_078</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_085</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_080</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_079</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_073</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_070</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_067</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_075</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_087</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_086</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_089</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_092</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_082</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_088</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_091</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_095</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_094</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_010</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_081</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_093</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_090</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainstream_1_1_300</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_008</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainstream_1_1_200</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_009</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_007</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_006</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_011</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NextDialogueId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CharacterDataId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>내가 방금 한 말 들었어?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>미안, 무슨 말 했어?</x:t>
+  </x:si>
+  <x:si>
     <x:t>...정말 오늘 일할 수 있는 거 맞아?</x:t>
   </x:si>
   <x:si>
-    <x:t>보스는 어디 있어?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>내가 방금 한 말 들었어?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>당연하지!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아, 안녕 존.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(삶의 기반도 흔들리게 됐는데, 정신ᄁᆞ지 나가버릴 지경이라고.)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아, 만약 제조에 실패했다면 리셋 버튼을 눌러서 다시 시도할 수 있어.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>다 끝나면 서빙하기 버튼을 눌러서 손님에게 전해주면 돼. 그게 다야.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>음, 매월 30일에 월세를 내는게 엄청 스트레스거든, 그리고-</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(이틀 전에는 이곳이 폐쇄될 위기에 처했다는 것까지 알게됐지)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>길리안, 나 공식적인 BTC 교육을 받고 여기 온 거거든?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(게다가 포어에게 중성화 수술을 시켜주느라 지갑 속 마지막 동전 하나ᄁᆞ지 다써버렸지. 월세를 한번만 더 미뤘다간 쫒겨날거야...)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>글쎄. 뭣 좀 사러 밖에 나갔...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>별거 아니야 조금 생각할게 있어서.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>칵테일 조합법에 있는 탐색 막대를 이용해 레시피를 확인해 봐. 왼쪽 상단에 표시될거야.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(아, 그러고 보니 내 아파트 방바닥에 맥주 캔들이 엄청나게 널브러져 있었지. 또...)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>좋은 저녁.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CharacterDataId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NextDialogueId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대체 언제쯤이면 네가 존같이 생겼다는 걸 인정할거야, 길?</x:t>
+    <x:t>괜찮아? 생각이 다른데 가있는 것 같은데.</x:t>
   </x:si>
   <x:si>
     <x:t>SelectionDialogueIdList</x:t>
   </x:si>
   <x:si>
-    <x:t>무슨 말 했어?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SelectionNameList</x:t>
-  </x:si>
-  <x:si>
-    <x:t>...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그러고 난 다음, 섞기 버튼을 누르면 돼. 다시 눌러서 섞는 걸 멈출 수 있고.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>jill_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>네가 피아노 맨을 만들 수 있을 정도 상태면, 나머지 과정은 생략할게. 그래도 웬만하면 잠ᄁᆞᆫ 참고 나랑 어울려줘, 괜찮지?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>내가 너를 쥴스라고 부를 수 있게 허락해줄 때 쯤.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그럼 우리 기초 과정부터 한번 다시 확인해 보자고. 괜찮지? 혹시 모르니까 말야</x:t>
-  </x:si>
-  <x:si>
-    <x:t>길이 슈가 러쉬나 피아노 맨을 달라는군. 만약에 망쳤다면, 재시도 버튼을 눌러서 다시 하면 되겠지.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>했어. 너, 역시 딴 생각에 빠져 있는 것 같아. 그것도 아주 심하게.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VoicePath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TexturePath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string[]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>미안, 무슨 말 했어?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>또 맛이나 종류 기준으로 검색할 수 있어. "달콤한" 술이나 "남성적인" 술을 정렬시켜 볼 수 있다는 거야.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>리셋 버튼은 아무 때나 누를 수 있어. 셰이커가 움직이고 있을 때도 말이지. 부담 가지지 말고 원할 때 눌러.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_096</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_013</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_014</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_015</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_012</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_017</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_019</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_016</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_018</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_023</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_024</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_021</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_022</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_020</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_028</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_031</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_032</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_033</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_027</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_029</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_030</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_037</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_039</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_040</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_038</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_041</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_035</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_043</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_034</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_042</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_036</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_046</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_047</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_049</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_045</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_044</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_048</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_050</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_054</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_052</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_053</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_056</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_057</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_051</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_055</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_066</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_060</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_062</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_059</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_063</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_065</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_058</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_061</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_064</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_072</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_073</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_074</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_071</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_070</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_068</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_075</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_067</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_069</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_080</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_083</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_076</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_077</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_084</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_085</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_079</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_078</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_081</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_082</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_086</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_087</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_088</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_089</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_095</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_094</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_090</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_093</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_091</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_092</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_010</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_011</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_007</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_009</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_005</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_006</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_008</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainstream_1_1_300</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainstream_1_1_200</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시끄러워.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>gillian_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>우선 슈가 러쉬부터 시작해보자.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>질!</x:t>
-  </x:si>
-  <x:si>
     <x:t>그럼 문제없이 만들어 낼 수 있겠네!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(어제는 1시간 동안 혼자 떠들었다고 오해받는 일이 생기질않나.)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아! 어서 와, 질.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>괜찮아? 생각이 다른데 가있는 것 같은데.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그게 뭔데?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하아...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>길...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>오른쪽 가운데에 있는 셰이커에 재료를 원하는 양만큼 클릭해서 넣어.</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -566,7 +566,7 @@
       </x:patternFill>
     </x:fill>
   </x:fills>
-  <x:borders count="2">
+  <x:borders count="3">
     <x:border diagonalUp="1" diagonalDown="1">
       <x:left>
         <x:color rgb="ff000000"/>
@@ -596,6 +596,23 @@
       </x:top>
       <x:bottom style="thin">
         <x:color rgb="ff000000"/>
+      </x:bottom>
+      <x:diagonal>
+        <x:color indexed="64"/>
+      </x:diagonal>
+    </x:border>
+    <x:border diagonalUp="1" diagonalDown="1">
+      <x:left style="thin">
+        <x:color indexed="64"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color indexed="64"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color indexed="64"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color indexed="64"/>
       </x:bottom>
       <x:diagonal>
         <x:color indexed="64"/>
@@ -649,7 +666,7 @@
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="14">
+  <x:cellXfs count="16">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
@@ -691,6 +708,12 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="bottom"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="bottom" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -1361,7 +1384,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>140</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1"/>
@@ -1373,68 +1396,68 @@
     </x:row>
     <x:row r="2" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>141</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>141</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>141</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>141</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>141</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A3" s="2" t="s">
-        <x:v>25</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
-        <x:v>18</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="C3" s="2" t="s">
-        <x:v>33</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D3" s="2" t="s">
-        <x:v>19</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="E3" s="2" t="s">
-        <x:v>23</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F3" s="2" t="s">
-        <x:v>21</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="G3" s="2" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="H3" s="2" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A4" s="4" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="B4" s="12" t="s">
-        <x:v>27</x:v>
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="B4" s="14" t="s">
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C4" s="4" t="s">
-        <x:v>17</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D4" s="4" t="s">
-        <x:v>138</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="G4" s="4"/>
       <x:c r="H4" s="4"/>
@@ -1451,13 +1474,13 @@
     </x:row>
     <x:row r="5" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A5" s="4" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="B5" s="13" t="s">
-        <x:v>143</x:v>
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="B5" s="15" t="s">
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C5" s="4" t="s">
-        <x:v>148</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D5" s="4" t="s">
         <x:v>137</x:v>
@@ -1479,13 +1502,13 @@
     </x:row>
     <x:row r="6" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A6" s="4" t="s">
-        <x:v>127</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="B6" s="12" t="s">
-        <x:v>27</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C6" s="4" t="s">
-        <x:v>24</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D6" s="4"/>
       <x:c r="E6" s="4"/>
@@ -1505,13 +1528,13 @@
     </x:row>
     <x:row r="7" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A7" s="4" t="s">
-        <x:v>130</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="B7" s="12" t="s">
-        <x:v>27</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C7" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D7" s="4"/>
       <x:c r="E7" s="4"/>
@@ -1531,13 +1554,13 @@
     </x:row>
     <x:row r="8" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A8" s="4" t="s">
-        <x:v>129</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="B8" s="13" t="s">
-        <x:v>143</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C8" s="6" t="s">
-        <x:v>24</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D8" s="6"/>
       <x:c r="E8" s="6"/>
@@ -1557,13 +1580,13 @@
     </x:row>
     <x:row r="9" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A9" s="4" t="s">
-        <x:v>134</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B9" s="12" t="s">
-        <x:v>27</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C9" s="6" t="s">
-        <x:v>20</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D9" s="6"/>
       <x:c r="E9" s="6"/>
@@ -1583,13 +1606,13 @@
     </x:row>
     <x:row r="10" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A10" s="4" t="s">
-        <x:v>135</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="B10" s="13" t="s">
-        <x:v>143</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C10" s="7" t="s">
-        <x:v>29</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D10" s="7"/>
       <x:c r="E10" s="7"/>
@@ -1609,13 +1632,13 @@
     </x:row>
     <x:row r="11" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A11" s="4" t="s">
-        <x:v>132</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="B11" s="12" t="s">
-        <x:v>27</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C11" s="7" t="s">
-        <x:v>139</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D11" s="7"/>
       <x:c r="E11" s="7"/>
@@ -1635,13 +1658,13 @@
     </x:row>
     <x:row r="12" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A12" s="4" t="s">
-        <x:v>136</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="B12" s="13" t="s">
-        <x:v>143</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C12" s="6" t="s">
-        <x:v>149</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="D12" s="6"/>
       <x:c r="E12" s="6"/>
@@ -1661,13 +1684,13 @@
     </x:row>
     <x:row r="13" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A13" s="4" t="s">
-        <x:v>133</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="B13" s="12" t="s">
-        <x:v>27</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C13" s="4" t="s">
-        <x:v>1</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D13" s="4"/>
       <x:c r="E13" s="4"/>
@@ -1687,13 +1710,13 @@
     </x:row>
     <x:row r="14" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A14" s="4" t="s">
-        <x:v>128</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B14" s="13" t="s">
-        <x:v>143</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C14" s="7" t="s">
-        <x:v>13</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D14" s="7"/>
       <x:c r="E14" s="7"/>
@@ -1713,13 +1736,13 @@
     </x:row>
     <x:row r="15" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A15" s="4" t="s">
-        <x:v>131</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="B15" s="13" t="s">
-        <x:v>143</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C15" s="7" t="s">
-        <x:v>3</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="D15" s="7"/>
       <x:c r="E15" s="7"/>
@@ -1739,13 +1762,13 @@
     </x:row>
     <x:row r="16" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A16" s="4" t="s">
-        <x:v>44</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B16" s="12" t="s">
-        <x:v>27</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C16" s="8" t="s">
-        <x:v>22</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D16" s="8"/>
       <x:c r="E16" s="8"/>
@@ -1755,13 +1778,13 @@
     </x:row>
     <x:row r="17" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A17" s="4" t="s">
-        <x:v>41</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B17" s="13" t="s">
-        <x:v>143</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C17" s="9" t="s">
-        <x:v>32</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D17" s="8"/>
       <x:c r="E17" s="8"/>
@@ -1771,13 +1794,13 @@
     </x:row>
     <x:row r="18" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A18" s="4" t="s">
-        <x:v>42</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B18" s="12" t="s">
-        <x:v>27</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C18" s="9" t="s">
-        <x:v>14</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D18" s="8"/>
       <x:c r="E18" s="8"/>
@@ -1787,13 +1810,13 @@
     </x:row>
     <x:row r="19" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A19" s="4" t="s">
-        <x:v>43</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B19" s="13" t="s">
-        <x:v>143</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C19" s="9" t="s">
-        <x:v>150</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D19" s="8"/>
       <x:c r="E19" s="8"/>
@@ -1803,13 +1826,13 @@
     </x:row>
     <x:row r="20" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A20" s="4" t="s">
-        <x:v>47</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B20" s="12" t="s">
-        <x:v>27</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C20" s="9" t="s">
-        <x:v>9</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D20" s="8"/>
       <x:c r="E20" s="8"/>
@@ -1819,13 +1842,13 @@
     </x:row>
     <x:row r="21" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A21" s="4" t="s">
-        <x:v>45</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B21" s="13" t="s">
-        <x:v>143</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C21" s="9" t="s">
-        <x:v>2</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D21" s="8"/>
       <x:c r="E21" s="8"/>
@@ -1835,13 +1858,13 @@
     </x:row>
     <x:row r="22" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A22" s="4" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B22" s="12" t="s">
-        <x:v>27</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C22" s="9" t="s">
-        <x:v>147</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D22" s="8"/>
       <x:c r="E22" s="8"/>
@@ -1851,13 +1874,13 @@
     </x:row>
     <x:row r="23" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A23" s="4" t="s">
-        <x:v>46</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B23" s="12" t="s">
-        <x:v>27</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C23" s="9" t="s">
-        <x:v>10</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D23" s="8"/>
       <x:c r="E23" s="8"/>
@@ -1867,13 +1890,13 @@
     </x:row>
     <x:row r="24" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A24" s="4" t="s">
-        <x:v>55</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B24" s="12" t="s">
-        <x:v>27</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C24" s="9" t="s">
-        <x:v>6</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D24" s="8"/>
       <x:c r="E24" s="8"/>
@@ -1883,13 +1906,13 @@
     </x:row>
     <x:row r="25" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A25" s="4" t="s">
-        <x:v>52</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B25" s="12" t="s">
-        <x:v>27</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C25" s="9" t="s">
-        <x:v>12</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D25" s="8"/>
       <x:c r="E25" s="8"/>
@@ -1899,13 +1922,13 @@
     </x:row>
     <x:row r="26" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A26" s="4" t="s">
-        <x:v>53</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B26" s="12" t="s">
-        <x:v>27</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C26" s="10" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D26" s="10"/>
       <x:c r="E26" s="10"/>
@@ -1915,13 +1938,13 @@
     </x:row>
     <x:row r="27" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A27" s="4" t="s">
-        <x:v>50</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B27" s="13" t="s">
-        <x:v>143</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C27" s="10" t="s">
-        <x:v>145</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D27" s="10"/>
       <x:c r="E27" s="10"/>
@@ -1931,13 +1954,13 @@
     </x:row>
     <x:row r="28" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A28" s="4" t="s">
-        <x:v>51</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B28" s="12" t="s">
-        <x:v>27</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C28" s="10" t="s">
-        <x:v>37</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="D28" s="10"/>
       <x:c r="E28" s="10"/>
@@ -1947,13 +1970,13 @@
     </x:row>
     <x:row r="29" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A29" s="4" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B29" s="13" t="s">
-        <x:v>143</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C29" s="10" t="s">
-        <x:v>0</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="D29" s="10"/>
       <x:c r="E29" s="10"/>
@@ -1963,10 +1986,10 @@
     </x:row>
     <x:row r="30" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A30" s="4" t="s">
-        <x:v>56</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B30" s="12" t="s">
-        <x:v>27</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C30" s="10" t="s">
         <x:v>4</x:v>
@@ -1979,13 +2002,13 @@
     </x:row>
     <x:row r="31" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A31" s="4" t="s">
-        <x:v>61</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B31" s="13" t="s">
-        <x:v>143</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C31" s="10" t="s">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D31" s="10"/>
       <x:c r="E31" s="10"/>
@@ -1995,13 +2018,13 @@
     </x:row>
     <x:row r="32" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A32" s="4" t="s">
-        <x:v>57</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B32" s="12" t="s">
-        <x:v>27</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C32" s="11" t="s">
-        <x:v>24</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D32" s="11"/>
       <x:c r="E32" s="11"/>
@@ -2011,13 +2034,13 @@
     </x:row>
     <x:row r="33" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A33" s="4" t="s">
-        <x:v>62</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B33" s="13" t="s">
-        <x:v>143</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C33" s="11" t="s">
-        <x:v>28</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D33" s="11"/>
       <x:c r="E33" s="11"/>
@@ -2030,10 +2053,10 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="B34" s="12" t="s">
-        <x:v>27</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C34" s="11" t="s">
-        <x:v>24</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D34" s="11"/>
       <x:c r="E34" s="11"/>
@@ -2043,13 +2066,13 @@
     </x:row>
     <x:row r="35" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A35" s="4" t="s">
-        <x:v>58</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B35" s="13" t="s">
-        <x:v>143</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C35" s="11" t="s">
-        <x:v>144</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D35" s="11"/>
       <x:c r="E35" s="11"/>
@@ -2059,301 +2082,301 @@
     </x:row>
     <x:row r="36" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A36" s="4" t="s">
-        <x:v>59</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B36" s="13" t="s">
-        <x:v>143</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C36" t="s">
-        <x:v>15</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A37" s="4" t="s">
-        <x:v>60</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B37" s="13" t="s">
-        <x:v>143</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C37" t="s">
-        <x:v>38</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A38" s="4" t="s">
-        <x:v>71</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B38" s="13" t="s">
-        <x:v>143</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C38" t="s">
-        <x:v>153</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A39" s="4" t="s">
-        <x:v>69</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B39" s="12" t="s">
-        <x:v>27</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C39" t="s">
-        <x:v>152</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A40" s="4" t="s">
-        <x:v>73</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B40" s="13" t="s">
-        <x:v>143</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C40" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A41" s="4" t="s">
-        <x:v>64</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B41" s="13" t="s">
-        <x:v>143</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C41" t="s">
-        <x:v>8</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A42" s="4" t="s">
-        <x:v>67</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B42" s="13" t="s">
-        <x:v>143</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C42" t="s">
-        <x:v>7</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A43" s="4" t="s">
-        <x:v>65</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B43" s="13" t="s">
-        <x:v>143</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C43" t="s">
-        <x:v>39</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A44" s="4" t="s">
-        <x:v>66</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B44" s="12" t="s">
-        <x:v>27</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C44" t="s">
-        <x:v>11</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A45" s="4" t="s">
-        <x:v>68</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B45" s="13" t="s">
-        <x:v>143</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C45" t="s">
-        <x:v>146</x:v>
+        <x:v>153</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A46" s="4" t="s">
-        <x:v>72</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B46" s="12" t="s">
-        <x:v>27</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C46" t="s">
-        <x:v>151</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A47" s="4" t="s">
-        <x:v>70</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C47" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A48" s="4" t="s">
-        <x:v>78</x:v>
+        <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A49" s="4" t="s">
-        <x:v>77</x:v>
+        <x:v>80</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A50" s="4" t="s">
-        <x:v>74</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A51" s="4" t="s">
-        <x:v>75</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A52" s="4" t="s">
-        <x:v>79</x:v>
+        <x:v>75</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A53" s="4" t="s">
-        <x:v>76</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A54" s="4" t="s">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A55" s="4" t="s">
-        <x:v>86</x:v>
+        <x:v>100</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A56" s="4" t="s">
-        <x:v>82</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A57" s="4" t="s">
-        <x:v>83</x:v>
+        <x:v>102</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A58" s="4" t="s">
-        <x:v>81</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A59" s="4" t="s">
-        <x:v>87</x:v>
+        <x:v>103</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A60" s="4" t="s">
-        <x:v>84</x:v>
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A61" s="4" t="s">
-        <x:v>85</x:v>
+        <x:v>94</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A62" s="4" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A63" s="4" t="s">
-        <x:v>91</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A64" s="4" t="s">
-        <x:v>89</x:v>
+        <x:v>104</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A65" s="4" t="s">
-        <x:v>95</x:v>
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A66" s="4" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A67" s="4" t="s">
-        <x:v>92</x:v>
+        <x:v>101</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A68" s="4" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A69" s="4" t="s">
-        <x:v>93</x:v>
+        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A70" s="4" t="s">
-        <x:v>88</x:v>
+        <x:v>99</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A71" s="4" t="s">
-        <x:v>104</x:v>
+        <x:v>119</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A72" s="4" t="s">
-        <x:v>102</x:v>
+        <x:v>110</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A73" s="4" t="s">
-        <x:v>105</x:v>
+        <x:v>109</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A74" s="4" t="s">
-        <x:v>101</x:v>
+        <x:v>118</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A75" s="4" t="s">
-        <x:v>100</x:v>
+        <x:v>108</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A76" s="4" t="s">
-        <x:v>97</x:v>
+        <x:v>93</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A77" s="4" t="s">
-        <x:v>98</x:v>
+        <x:v>117</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A78" s="4" t="s">
-        <x:v>99</x:v>
+        <x:v>105</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A79" s="4" t="s">
-        <x:v>103</x:v>
+        <x:v>120</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A80" s="4" t="s">
-        <x:v>108</x:v>
+        <x:v>106</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A81" s="4" t="s">
-        <x:v>109</x:v>
+        <x:v>112</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:1" ht="15.75" customHeight="1">
@@ -2363,22 +2386,22 @@
     </x:row>
     <x:row r="83" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A83" s="4" t="s">
-        <x:v>112</x:v>
+        <x:v>116</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A84" s="4" t="s">
-        <x:v>106</x:v>
+        <x:v>115</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A85" s="4" t="s">
-        <x:v>114</x:v>
+        <x:v>133</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A86" s="4" t="s">
-        <x:v>115</x:v>
+        <x:v>125</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:1" ht="15.75" customHeight="1">
@@ -2388,67 +2411,67 @@
     </x:row>
     <x:row r="88" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A88" s="4" t="s">
-        <x:v>110</x:v>
+        <x:v>111</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A89" s="4" t="s">
-        <x:v>111</x:v>
+        <x:v>114</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A90" s="4" t="s">
-        <x:v>116</x:v>
+        <x:v>122</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A91" s="4" t="s">
-        <x:v>117</x:v>
+        <x:v>121</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A92" s="4" t="s">
-        <x:v>118</x:v>
+        <x:v>126</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A93" s="4" t="s">
-        <x:v>119</x:v>
+        <x:v>123</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A94" s="4" t="s">
-        <x:v>122</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A95" s="4" t="s">
-        <x:v>124</x:v>
+        <x:v>127</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A96" s="4" t="s">
-        <x:v>125</x:v>
+        <x:v>124</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A97" s="4" t="s">
-        <x:v>123</x:v>
+        <x:v>134</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A98" s="4" t="s">
-        <x:v>121</x:v>
+        <x:v>130</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A99" s="4" t="s">
-        <x:v>120</x:v>
+        <x:v>128</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A100" s="4" t="s">
-        <x:v>40</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="101" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/MainDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/MainDialogue.xlsx
@@ -14,468 +14,462 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="154">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="152">
+  <x:si>
+    <x:t>했어. 너, 역시 딴 생각에 빠져 있는 것 같아. 그것도 아주 심하게.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(어제는 1시간 동안 혼자 떠들었다고 오해받는 일이 생기질않나.)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오른쪽 가운데에 있는 셰이커에 재료를 원하는 양만큼 클릭해서 넣어.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>다 끝나면 서빙하기 버튼을 눌러서 손님에게 전해주면 돼. 그게 다야.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아, 만약 제조에 실패했다면 리셋 버튼을 눌러서 다시 시도할 수 있어.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>별거 아니야 조금 생각할게 있어서.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>글쎄. 뭣 좀 사러 밖에 나갔...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>character_jill_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SelectionNameList</x:t>
+  </x:si>
+  <x:si>
+    <x:t>우선 슈가 러쉬부터 시작해보자.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>미안, 무슨 말 했어?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CharacterDataId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NextDialogueId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>내가 방금 한 말 들었어?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string[]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(이틀 전에는 이곳이 폐쇄될 위기에 처했다는 것까지 알게됐지)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>길리안, 나 공식적인 BTC 교육을 받고 여기 온 거거든?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>음, 매월 30일에 월세를 내는게 엄청 스트레스거든, 그리고-</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대체 언제쯤이면 네가 존같이 생겼다는 걸 인정할거야, 길?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(삶의 기반도 흔들리게 됐는데, 정신까지 나가버릴 지경이라고.)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>질!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>네가 피아노 맨을 만들 수 있을 정도 상태면, 나머지 과정은 생략할게. 그래도 웬만하면 잠ᄁᆞᆫ 참고 나랑 어울려줘, 괜찮지?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>또 맛이나 종류 기준으로 검색할 수 있어. "달콤한" 술이나 "남성적인" 술을 정렬시켜 볼 수 있다는 거야.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>리셋 버튼은 아무 때나 누를 수 있어. 셰이커가 움직이고 있을 때도 말이지. 부담 가지지 말고 원할 때 눌러.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>칵테일 조합법에 있는 탐색 막대를 이용해 레시피를 확인해 봐. 왼쪽 상단에 표시될거야.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(아, 그러고 보니 내 아파트 방바닥에 맥주 캔들이 엄청나게 널브러져 있었지. 또...)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(게다가 포어에게 중성화 수술을 시켜주느라 지갑 속 마지막 동전 하나까지 다써버렸지. 월세를 한번만 더 미뤘다간 쫒겨날거야...)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>내가 너를 쥴스라고 부를 수 있게 허락해줄 때 쯤.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>길이 슈가 러쉬나 피아노 맨을 달라는군. 만약에 망쳤다면, 재시도 버튼을 눌러서 다시 하면 되겠지.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그러고 난 다음, 섞기 버튼을 누르면 돼. 다시 눌러서 섞는 걸 멈출 수 있고.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그럼 우리 기초 과정부터 한번 다시 확인해 보자고. 괜찮지? 혹시 모르니까 말야</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>보스는 어디 있어?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아! 어서 와, 질.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VoicePath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아, 안녕 존.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>무슨 말 했어?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TexturePath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하아...</x:t>
+  </x:si>
   <x:si>
     <x:t>시끄러워.</x:t>
   </x:si>
   <x:si>
+    <x:t>당연하지!</x:t>
+  </x:si>
+  <x:si>
     <x:t>좋은 저녁.</x:t>
   </x:si>
   <x:si>
     <x:t>길...</x:t>
   </x:si>
   <x:si>
-    <x:t>하아...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>당연하지!</x:t>
-  </x:si>
-  <x:si>
     <x:t>그게 뭔데?</x:t>
   </x:si>
   <x:si>
-    <x:t>고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>글쎄. 뭣 좀 사러 밖에 나갔...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>별거 아니야 조금 생각할게 있어서.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SelectionNameList</x:t>
-  </x:si>
-  <x:si>
-    <x:t>우선 슈가 러쉬부터 시작해보자.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>내가 너를 쥴스라고 부를 수 있게 허락해줄 때 쯤.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>character_jill_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>칵테일 조합법에 있는 탐색 막대를 이용해 레시피를 확인해 봐. 왼쪽 상단에 표시될거야.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(아, 그러고 보니 내 아파트 방바닥에 맥주 캔들이 엄청나게 널브러져 있었지. 또...)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(게다가 포어에게 중성화 수술을 시켜주느라 지갑 속 마지막 동전 하나까지 다써버렸지. 월세를 한번만 더 미뤘다간 쫒겨날거야...)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>했어. 너, 역시 딴 생각에 빠져 있는 것 같아. 그것도 아주 심하게.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(어제는 1시간 동안 혼자 떠들었다고 오해받는 일이 생기질않나.)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>오른쪽 가운데에 있는 셰이커에 재료를 원하는 양만큼 클릭해서 넣어.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아, 만약 제조에 실패했다면 리셋 버튼을 눌러서 다시 시도할 수 있어.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>다 끝나면 서빙하기 버튼을 눌러서 손님에게 전해주면 돼. 그게 다야.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>음, 매월 30일에 월세를 내는게 엄청 스트레스거든, 그리고-</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(이틀 전에는 이곳이 폐쇄될 위기에 처했다는 것까지 알게됐지)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>네가 피아노 맨을 만들 수 있을 정도 상태면, 나머지 과정은 생략할게. 그래도 웬만하면 잠ᄁᆞᆫ 참고 나랑 어울려줘, 괜찮지?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>또 맛이나 종류 기준으로 검색할 수 있어. "달콤한" 술이나 "남성적인" 술을 정렬시켜 볼 수 있다는 거야.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>리셋 버튼은 아무 때나 누를 수 있어. 셰이커가 움직이고 있을 때도 말이지. 부담 가지지 말고 원할 때 눌러.</x:t>
+    <x:t>dialogue_tutorial_1_1_019</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_096</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_014</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_012</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_015</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_013</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_018</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_017</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_039</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_031</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_037</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_033</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_021</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_028</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_022</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_027</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_024</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_030</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_016</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_020</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_023</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_032</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_029</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_038</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_034</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_050</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_040</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_041</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_045</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_047</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_043</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_049</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_054</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_046</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_048</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_035</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_042</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_036</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_055</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_056</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_059</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_064</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_058</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_065</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_052</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_057</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_062</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_061</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_066</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_051</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_044</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_072</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_063</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_053</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_070</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_067</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_060</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_074</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_069</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_077</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_078</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_085</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_076</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_079</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_068</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_080</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_073</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_084</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_083</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_071</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_094</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_010</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_081</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_093</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_090</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_086</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_089</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_092</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_095</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_091</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_087</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_075</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_082</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_088</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_009</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_006</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_011</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_007</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_008</x:t>
+  </x:si>
+  <x:si>
+    <x:t>괜찮아? 생각이 다른데 가있는 것 같은데.</x:t>
   </x:si>
   <x:si>
     <x:t>character_gillian_01</x:t>
   </x:si>
   <x:si>
-    <x:t>그러고 난 다음, 섞기 버튼을 누르면 돼. 다시 눌러서 섞는 걸 멈출 수 있고.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그럼 우리 기초 과정부터 한번 다시 확인해 보자고. 괜찮지? 혹시 모르니까 말야</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>길이 슈가 러쉬나 피아노 맨을 달라는군. 만약에 망쳤다면, 재시도 버튼을 눌러서 다시 하면 되겠지.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아, 안녕 존.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>보스는 어디 있어?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>무슨 말 했어?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TexturePath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VoicePath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string[]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>길리안, 나 공식적인 BTC 교육을 받고 여기 온 거거든?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대체 언제쯤이면 네가 존같이 생겼다는 걸 인정할거야, 길?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>질!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아! 어서 와, 질.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(삶의 기반도 흔들리게 됐는데, 정신까지 나가버릴 지경이라고.)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_018</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_015</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_019</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_096</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_017</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_013</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_014</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_012</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_016</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_033</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_029</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_039</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_021</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_031</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_024</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_030</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_020</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_023</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_022</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_032</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_037</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_028</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_027</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_040</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_034</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_048</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_046</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_035</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_049</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_043</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_045</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_050</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_041</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_054</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_047</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_042</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_036</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_038</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_044</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_052</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_056</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_062</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_065</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_072</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_057</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_058</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_059</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_064</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_061</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_066</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_051</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_063</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_053</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_055</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_060</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_074</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_076</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_083</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_071</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_069</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_068</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_084</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_077</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_078</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_085</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_080</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_079</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_073</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_070</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_067</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_075</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_087</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_086</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_089</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_092</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_082</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_088</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_091</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_095</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_094</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_010</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_081</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_093</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_090</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainstream_1_1_300</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_008</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainstream_1_1_200</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_005</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_009</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_007</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_006</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_011</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NextDialogueId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CharacterDataId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>내가 방금 한 말 들었어?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>미안, 무슨 말 했어?</x:t>
+    <x:t>SelectionDialogueIdList</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그럼 문제없이 만들어 낼 수 있겠네!</x:t>
   </x:si>
   <x:si>
     <x:t>...정말 오늘 일할 수 있는 거 맞아?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>괜찮아? 생각이 다른데 가있는 것 같은데.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SelectionDialogueIdList</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그럼 문제없이 만들어 낼 수 있겠네!</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1373,7 +1367,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:R100"/>
+  <x:dimension ref="A1:R101"/>
   <x:sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1"/>
   <x:cols>
     <x:col min="1" max="1" width="26.36328125" customWidth="1"/>
@@ -1384,7 +1378,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1"/>
@@ -1396,69 +1390,70 @@
     </x:row>
     <x:row r="2" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B2" s="1" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="B2" s="1" t="s">
-        <x:v>30</x:v>
-      </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A3" s="2" t="s">
-        <x:v>21</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
-        <x:v>147</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C3" s="2" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="D3" s="2" t="s">
-        <x:v>146</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E3" s="2" t="s">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F3" s="2" t="s">
-        <x:v>152</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="G3" s="2" t="s">
-        <x:v>36</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="H3" s="2" t="s">
-        <x:v>38</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A4" s="4" t="s">
-        <x:v>72</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B4" s="14" t="s">
-        <x:v>12</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C4" s="4" t="s">
-        <x:v>1</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D4" s="4" t="s">
-        <x:v>139</x:v>
-      </x:c>
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="E4" s="12"/>
       <x:c r="G4" s="4"/>
       <x:c r="H4" s="4"/>
       <x:c r="I4" s="3"/>
@@ -1474,16 +1469,16 @@
     </x:row>
     <x:row r="5" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A5" s="4" t="s">
-        <x:v>129</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="B5" s="15" t="s">
-        <x:v>27</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C5" s="4" t="s">
-        <x:v>45</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D5" s="4" t="s">
-        <x:v>137</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="E5" s="4"/>
       <x:c r="F5" s="4"/>
@@ -1502,15 +1497,17 @@
     </x:row>
     <x:row r="6" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A6" s="4" t="s">
-        <x:v>131</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B6" s="12" t="s">
-        <x:v>12</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C6" s="4" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="D6" s="4"/>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="D6" s="4" t="s">
+        <x:v>143</x:v>
+      </x:c>
       <x:c r="E6" s="4"/>
       <x:c r="F6" s="4"/>
       <x:c r="G6" s="4"/>
@@ -1531,12 +1528,14 @@
         <x:v>143</x:v>
       </x:c>
       <x:c r="B7" s="12" t="s">
-        <x:v>12</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C7" s="4" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="D7" s="4"/>
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D7" s="4" t="s">
+        <x:v>139</x:v>
+      </x:c>
       <x:c r="E7" s="4"/>
       <x:c r="F7" s="4"/>
       <x:c r="G7" s="4"/>
@@ -1554,15 +1553,17 @@
     </x:row>
     <x:row r="8" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A8" s="4" t="s">
-        <x:v>136</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="B8" s="13" t="s">
-        <x:v>27</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C8" s="6" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="D8" s="6"/>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="D8" s="4" t="s">
+        <x:v>145</x:v>
+      </x:c>
       <x:c r="E8" s="6"/>
       <x:c r="F8" s="6"/>
       <x:c r="G8" s="6"/>
@@ -1580,15 +1581,17 @@
     </x:row>
     <x:row r="9" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A9" s="4" t="s">
-        <x:v>140</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="B9" s="12" t="s">
-        <x:v>12</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C9" s="6" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="D9" s="6"/>
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D9" s="4" t="s">
+        <x:v>141</x:v>
+      </x:c>
       <x:c r="E9" s="6"/>
       <x:c r="F9" s="6"/>
       <x:c r="G9" s="6"/>
@@ -1606,15 +1609,17 @@
     </x:row>
     <x:row r="10" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A10" s="4" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="B10" s="13" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="C10" s="7" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="D10" s="4" t="s">
         <x:v>144</x:v>
       </x:c>
-      <x:c r="B10" s="13" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C10" s="7" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D10" s="7"/>
       <x:c r="E10" s="7"/>
       <x:c r="F10" s="7"/>
       <x:c r="G10" s="7"/>
@@ -1632,15 +1637,17 @@
     </x:row>
     <x:row r="11" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A11" s="4" t="s">
-        <x:v>142</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="B11" s="12" t="s">
-        <x:v>12</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C11" s="7" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D11" s="7"/>
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="D11" s="4" t="s">
+        <x:v>146</x:v>
+      </x:c>
       <x:c r="E11" s="7"/>
       <x:c r="F11" s="7"/>
       <x:c r="G11" s="7"/>
@@ -1658,15 +1665,17 @@
     </x:row>
     <x:row r="12" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A12" s="4" t="s">
-        <x:v>138</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="B12" s="13" t="s">
-        <x:v>27</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C12" s="6" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="D12" s="6"/>
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="D12" s="4" t="s">
+        <x:v>140</x:v>
+      </x:c>
       <x:c r="E12" s="6"/>
       <x:c r="F12" s="6"/>
       <x:c r="G12" s="6"/>
@@ -1684,15 +1693,17 @@
     </x:row>
     <x:row r="13" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A13" s="4" t="s">
-        <x:v>141</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B13" s="12" t="s">
-        <x:v>12</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C13" s="4" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="D13" s="4"/>
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="D13" s="4" t="s">
+        <x:v>125</x:v>
+      </x:c>
       <x:c r="E13" s="4"/>
       <x:c r="F13" s="4"/>
       <x:c r="G13" s="4"/>
@@ -1710,15 +1721,17 @@
     </x:row>
     <x:row r="14" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A14" s="4" t="s">
-        <x:v>132</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B14" s="13" t="s">
-        <x:v>27</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C14" s="7" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D14" s="7"/>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D14" s="4" t="s">
+        <x:v>142</x:v>
+      </x:c>
       <x:c r="E14" s="7"/>
       <x:c r="F14" s="7"/>
       <x:c r="G14" s="7"/>
@@ -1736,15 +1749,17 @@
     </x:row>
     <x:row r="15" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A15" s="4" t="s">
-        <x:v>145</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="B15" s="13" t="s">
-        <x:v>27</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C15" s="7" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="D15" s="7"/>
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D15" s="4" t="s">
+        <x:v>53</x:v>
+      </x:c>
       <x:c r="E15" s="7"/>
       <x:c r="F15" s="7"/>
       <x:c r="G15" s="7"/>
@@ -1762,15 +1777,17 @@
     </x:row>
     <x:row r="16" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A16" s="4" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B16" s="12" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C16" s="8" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D16" s="4" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="B16" s="12" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C16" s="8" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D16" s="8"/>
       <x:c r="E16" s="8"/>
       <x:c r="F16" s="8"/>
       <x:c r="G16" s="8"/>
@@ -1778,15 +1795,17 @@
     </x:row>
     <x:row r="17" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A17" s="4" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B17" s="13" t="s">
-        <x:v>27</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C17" s="9" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D17" s="8"/>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D17" s="4" t="s">
+        <x:v>52</x:v>
+      </x:c>
       <x:c r="E17" s="8"/>
       <x:c r="F17" s="8"/>
       <x:c r="G17" s="9"/>
@@ -1794,15 +1813,17 @@
     </x:row>
     <x:row r="18" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A18" s="4" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B18" s="12" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C18" s="9" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D18" s="4" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="B18" s="12" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C18" s="9" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D18" s="8"/>
       <x:c r="E18" s="8"/>
       <x:c r="F18" s="8"/>
       <x:c r="G18" s="9"/>
@@ -1810,15 +1831,17 @@
     </x:row>
     <x:row r="19" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A19" s="4" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B19" s="13" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="C19" s="9" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="B19" s="13" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C19" s="9" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D19" s="8"/>
+      <x:c r="D19" s="4" t="s">
+        <x:v>70</x:v>
+      </x:c>
       <x:c r="E19" s="8"/>
       <x:c r="F19" s="8"/>
       <x:c r="G19" s="9"/>
@@ -1826,15 +1849,17 @@
     </x:row>
     <x:row r="20" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A20" s="4" t="s">
-        <x:v>56</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B20" s="12" t="s">
-        <x:v>12</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C20" s="9" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="D20" s="8"/>
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D20" s="4" t="s">
+        <x:v>58</x:v>
+      </x:c>
       <x:c r="E20" s="8"/>
       <x:c r="F20" s="8"/>
       <x:c r="G20" s="9"/>
@@ -1842,15 +1867,17 @@
     </x:row>
     <x:row r="21" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A21" s="4" t="s">
-        <x:v>52</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B21" s="13" t="s">
-        <x:v>27</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C21" s="9" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="D21" s="8"/>
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D21" s="4" t="s">
+        <x:v>57</x:v>
+      </x:c>
       <x:c r="E21" s="8"/>
       <x:c r="F21" s="8"/>
       <x:c r="G21" s="9"/>
@@ -1858,15 +1885,17 @@
     </x:row>
     <x:row r="22" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A22" s="4" t="s">
-        <x:v>47</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B22" s="12" t="s">
-        <x:v>12</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C22" s="9" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D22" s="8"/>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D22" s="4" t="s">
+        <x:v>50</x:v>
+      </x:c>
       <x:c r="E22" s="8"/>
       <x:c r="F22" s="8"/>
       <x:c r="G22" s="9"/>
@@ -1877,12 +1906,14 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B23" s="12" t="s">
-        <x:v>12</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C23" s="9" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D23" s="8"/>
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D23" s="4" t="s">
+        <x:v>71</x:v>
+      </x:c>
       <x:c r="E23" s="8"/>
       <x:c r="F23" s="8"/>
       <x:c r="G23" s="9"/>
@@ -1890,15 +1921,17 @@
     </x:row>
     <x:row r="24" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A24" s="4" t="s">
-        <x:v>64</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B24" s="12" t="s">
-        <x:v>12</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C24" s="9" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="D24" s="8"/>
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D24" s="4" t="s">
+        <x:v>63</x:v>
+      </x:c>
       <x:c r="E24" s="8"/>
       <x:c r="F24" s="8"/>
       <x:c r="G24" s="9"/>
@@ -1906,15 +1939,17 @@
     </x:row>
     <x:row r="25" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A25" s="4" t="s">
-        <x:v>60</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B25" s="12" t="s">
-        <x:v>12</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C25" s="9" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D25" s="8"/>
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="D25" s="4" t="s">
+        <x:v>65</x:v>
+      </x:c>
       <x:c r="E25" s="8"/>
       <x:c r="F25" s="8"/>
       <x:c r="G25" s="9"/>
@@ -1922,15 +1957,17 @@
     </x:row>
     <x:row r="26" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A26" s="4" t="s">
-        <x:v>66</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B26" s="12" t="s">
-        <x:v>12</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C26" s="10" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D26" s="10"/>
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D26" s="4" t="s">
+        <x:v>72</x:v>
+      </x:c>
       <x:c r="E26" s="10"/>
       <x:c r="F26" s="10"/>
       <x:c r="G26" s="10"/>
@@ -1938,15 +1975,17 @@
     </x:row>
     <x:row r="27" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A27" s="4" t="s">
-        <x:v>65</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B27" s="13" t="s">
-        <x:v>27</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C27" s="10" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="D27" s="10"/>
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D27" s="4" t="s">
+        <x:v>68</x:v>
+      </x:c>
       <x:c r="E27" s="10"/>
       <x:c r="F27" s="10"/>
       <x:c r="G27" s="10"/>
@@ -1954,15 +1993,17 @@
     </x:row>
     <x:row r="28" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A28" s="4" t="s">
-        <x:v>62</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B28" s="12" t="s">
-        <x:v>12</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C28" s="10" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="D28" s="10"/>
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D28" s="4" t="s">
+        <x:v>56</x:v>
+      </x:c>
       <x:c r="E28" s="10"/>
       <x:c r="F28" s="10"/>
       <x:c r="G28" s="10"/>
@@ -1970,15 +2011,17 @@
     </x:row>
     <x:row r="29" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A29" s="4" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B29" s="13" t="s">
-        <x:v>27</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C29" s="10" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="D29" s="10"/>
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="D29" s="4" t="s">
+        <x:v>66</x:v>
+      </x:c>
       <x:c r="E29" s="10"/>
       <x:c r="F29" s="10"/>
       <x:c r="G29" s="10"/>
@@ -1986,15 +2029,17 @@
     </x:row>
     <x:row r="30" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A30" s="4" t="s">
-        <x:v>70</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B30" s="12" t="s">
-        <x:v>12</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C30" s="10" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D30" s="10"/>
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D30" s="4" t="s">
+        <x:v>67</x:v>
+      </x:c>
       <x:c r="E30" s="10"/>
       <x:c r="F30" s="10"/>
       <x:c r="G30" s="10"/>
@@ -2002,15 +2047,17 @@
     </x:row>
     <x:row r="31" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A31" s="4" t="s">
-        <x:v>71</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B31" s="13" t="s">
-        <x:v>27</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C31" s="10" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="D31" s="10"/>
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D31" s="4" t="s">
+        <x:v>64</x:v>
+      </x:c>
       <x:c r="E31" s="10"/>
       <x:c r="F31" s="10"/>
       <x:c r="G31" s="10"/>
@@ -2018,15 +2065,17 @@
     </x:row>
     <x:row r="32" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A32" s="4" t="s">
-        <x:v>69</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B32" s="12" t="s">
-        <x:v>12</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C32" s="11" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="D32" s="11"/>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="D32" s="4" t="s">
+        <x:v>74</x:v>
+      </x:c>
       <x:c r="E32" s="11"/>
       <x:c r="F32" s="11"/>
       <x:c r="G32" s="11"/>
@@ -2034,15 +2083,17 @@
     </x:row>
     <x:row r="33" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A33" s="4" t="s">
-        <x:v>58</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B33" s="13" t="s">
-        <x:v>27</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C33" s="11" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="D33" s="11"/>
+      <x:c r="D33" s="4" t="s">
+        <x:v>69</x:v>
+      </x:c>
       <x:c r="E33" s="11"/>
       <x:c r="F33" s="11"/>
       <x:c r="G33" s="11"/>
@@ -2050,15 +2101,17 @@
     </x:row>
     <x:row r="34" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A34" s="4" t="s">
-        <x:v>63</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B34" s="12" t="s">
-        <x:v>12</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C34" s="11" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="D34" s="11"/>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="D34" s="4" t="s">
+        <x:v>60</x:v>
+      </x:c>
       <x:c r="E34" s="11"/>
       <x:c r="F34" s="11"/>
       <x:c r="G34" s="11"/>
@@ -2066,152 +2119,188 @@
     </x:row>
     <x:row r="35" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A35" s="4" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B35" s="13" t="s">
-        <x:v>27</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C35" s="11" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D35" s="11"/>
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D35" s="4" t="s">
+        <x:v>73</x:v>
+      </x:c>
       <x:c r="E35" s="11"/>
       <x:c r="F35" s="11"/>
       <x:c r="G35" s="11"/>
       <x:c r="H35" s="11"/>
     </x:row>
-    <x:row r="36" spans="1:3" ht="15.75" customHeight="1">
+    <x:row r="36" spans="1:4" ht="15.75" customHeight="1">
       <x:c r="A36" s="4" t="s">
-        <x:v>67</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B36" s="13" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="C36" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="C36" t="s">
-        <x:v>13</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="D36" s="4" t="s">
+        <x:v>62</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:4" ht="15.75" customHeight="1">
       <x:c r="A37" s="4" t="s">
-        <x:v>57</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B37" s="13" t="s">
-        <x:v>27</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C37" t="s">
         <x:v>25</x:v>
       </x:c>
-    </x:row>
-    <x:row r="38" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="D37" s="4" t="s">
+        <x:v>76</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:4" ht="15.75" customHeight="1">
       <x:c r="A38" s="4" t="s">
-        <x:v>74</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B38" s="13" t="s">
-        <x:v>27</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C38" t="s">
-        <x:v>18</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:3" ht="15.75" customHeight="1">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D38" s="4" t="s">
+        <x:v>88</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:4" ht="15.75" customHeight="1">
       <x:c r="A39" s="4" t="s">
-        <x:v>77</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B39" s="12" t="s">
-        <x:v>12</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C39" t="s">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:3" ht="15.75" customHeight="1">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D39" s="4" t="s">
+        <x:v>90</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:4" ht="15.75" customHeight="1">
       <x:c r="A40" s="4" t="s">
-        <x:v>86</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B40" s="13" t="s">
-        <x:v>27</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C40" t="s">
-        <x:v>28</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="1:3" ht="15.75" customHeight="1">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D40" s="4" t="s">
+        <x:v>61</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:4" ht="15.75" customHeight="1">
       <x:c r="A41" s="4" t="s">
-        <x:v>68</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B41" s="13" t="s">
-        <x:v>27</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C41" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" spans="1:3" ht="15.75" customHeight="1">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D41" s="4" t="s">
+        <x:v>75</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:4" ht="15.75" customHeight="1">
       <x:c r="A42" s="4" t="s">
-        <x:v>87</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B42" s="13" t="s">
-        <x:v>27</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C42" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" spans="1:3" ht="15.75" customHeight="1">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D42" s="4" t="s">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:4" ht="15.75" customHeight="1">
       <x:c r="A43" s="4" t="s">
         <x:v>59</x:v>
       </x:c>
       <x:c r="B43" s="13" t="s">
-        <x:v>27</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C43" t="s">
         <x:v>26</x:v>
       </x:c>
-    </x:row>
-    <x:row r="44" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="D43" s="4" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:4" ht="15.75" customHeight="1">
       <x:c r="A44" s="4" t="s">
-        <x:v>73</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B44" s="12" t="s">
-        <x:v>12</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C44" t="s">
-        <x:v>40</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" spans="1:3" ht="15.75" customHeight="1">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D44" s="4" t="s">
+        <x:v>79</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:4" ht="15.75" customHeight="1">
       <x:c r="A45" s="4" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="B45" s="13" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="C45" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="D45" s="4" t="s">
+        <x:v>89</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:4" ht="15.75" customHeight="1">
+      <x:c r="A46" s="4" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="B46" s="12" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C46" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="D46" s="4" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="B45" s="13" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C45" t="s">
-        <x:v>153</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A46" s="4" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="B46" s="12" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C46" t="s">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47" spans="1:3" ht="15.75" customHeight="1">
+    </x:row>
+    <x:row r="47" spans="1:4" ht="15.75" customHeight="1">
       <x:c r="A47" s="4" t="s">
-        <x:v>79</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C47" t="s">
-        <x:v>32</x:v>
-      </x:c>
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D47" s="4"/>
     </x:row>
     <x:row r="48" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A48" s="4" t="s">
-        <x:v>88</x:v>
+        <x:v>103</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:1" ht="15.75" customHeight="1">
@@ -2221,62 +2310,62 @@
     </x:row>
     <x:row r="50" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A50" s="4" t="s">
-        <x:v>76</x:v>
+        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A51" s="4" t="s">
-        <x:v>84</x:v>
+        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A52" s="4" t="s">
-        <x:v>75</x:v>
+        <x:v>87</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A53" s="4" t="s">
-        <x:v>78</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A54" s="4" t="s">
-        <x:v>81</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A55" s="4" t="s">
-        <x:v>100</x:v>
+        <x:v>102</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A56" s="4" t="s">
-        <x:v>89</x:v>
+        <x:v>97</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A57" s="4" t="s">
-        <x:v>102</x:v>
+        <x:v>106</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A58" s="4" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A59" s="4" t="s">
-        <x:v>103</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A60" s="4" t="s">
-        <x:v>90</x:v>
+        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A61" s="4" t="s">
-        <x:v>94</x:v>
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:1" ht="15.75" customHeight="1">
@@ -2286,92 +2375,92 @@
     </x:row>
     <x:row r="63" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A63" s="4" t="s">
-        <x:v>96</x:v>
+        <x:v>93</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A64" s="4" t="s">
-        <x:v>104</x:v>
+        <x:v>109</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A65" s="4" t="s">
-        <x:v>98</x:v>
+        <x:v>100</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A66" s="4" t="s">
-        <x:v>91</x:v>
+        <x:v>99</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A67" s="4" t="s">
-        <x:v>101</x:v>
+        <x:v>105</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A68" s="4" t="s">
-        <x:v>97</x:v>
+        <x:v>94</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A69" s="4" t="s">
-        <x:v>92</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A70" s="4" t="s">
-        <x:v>99</x:v>
+        <x:v>101</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A71" s="4" t="s">
-        <x:v>119</x:v>
+        <x:v>108</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A72" s="4" t="s">
-        <x:v>110</x:v>
+        <x:v>117</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A73" s="4" t="s">
-        <x:v>109</x:v>
+        <x:v>111</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A74" s="4" t="s">
-        <x:v>118</x:v>
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A75" s="4" t="s">
-        <x:v>108</x:v>
+        <x:v>122</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A76" s="4" t="s">
-        <x:v>93</x:v>
+        <x:v>104</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A77" s="4" t="s">
-        <x:v>117</x:v>
+        <x:v>119</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A78" s="4" t="s">
-        <x:v>105</x:v>
+        <x:v>110</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A79" s="4" t="s">
-        <x:v>120</x:v>
+        <x:v>136</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A80" s="4" t="s">
-        <x:v>106</x:v>
+        <x:v>115</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:1" ht="15.75" customHeight="1">
@@ -2391,27 +2480,27 @@
     </x:row>
     <x:row r="84" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A84" s="4" t="s">
-        <x:v>115</x:v>
+        <x:v>118</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A85" s="4" t="s">
-        <x:v>133</x:v>
+        <x:v>126</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A86" s="4" t="s">
-        <x:v>125</x:v>
+        <x:v>137</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A87" s="4" t="s">
-        <x:v>107</x:v>
+        <x:v>121</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A88" s="4" t="s">
-        <x:v>111</x:v>
+        <x:v>120</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:1" ht="15.75" customHeight="1">
@@ -2421,52 +2510,52 @@
     </x:row>
     <x:row r="90" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A90" s="4" t="s">
-        <x:v>122</x:v>
+        <x:v>129</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A91" s="4" t="s">
-        <x:v>121</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A92" s="4" t="s">
-        <x:v>126</x:v>
+        <x:v>138</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A93" s="4" t="s">
-        <x:v>123</x:v>
+        <x:v>130</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A94" s="4" t="s">
-        <x:v>135</x:v>
+        <x:v>128</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A95" s="4" t="s">
-        <x:v>127</x:v>
+        <x:v>134</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A96" s="4" t="s">
-        <x:v>124</x:v>
+        <x:v>131</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A97" s="4" t="s">
-        <x:v>134</x:v>
+        <x:v>127</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A98" s="4" t="s">
-        <x:v>130</x:v>
+        <x:v>123</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A99" s="4" t="s">
-        <x:v>128</x:v>
+        <x:v>132</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:1" ht="15.75" customHeight="1">
@@ -2474,7 +2563,9 @@
         <x:v>51</x:v>
       </x:c>
     </x:row>
-    <x:row r="101" ht="15.75" customHeight="1"/>
+    <x:row r="101" spans="1:1" ht="15.75" customHeight="1">
+      <x:c r="A101" s="12"/>
+    </x:row>
     <x:row r="102" ht="15.75" customHeight="1"/>
     <x:row r="103" ht="15.75" customHeight="1"/>
     <x:row r="104" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/MainDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/MainDialogue.xlsx
@@ -88,9 +88,6 @@
     <x:t>...</x:t>
   </x:si>
   <x:si>
-    <x:t>네가 피아노 맨을 만들 수 있을 정도 상태면, 나머지 과정은 생략할게. 그래도 웬만하면 잠ᄁᆞᆫ 참고 나랑 어울려줘, 괜찮지?</x:t>
-  </x:si>
-  <x:si>
     <x:t>또 맛이나 종류 기준으로 검색할 수 있어. "달콤한" 술이나 "남성적인" 술을 정렬시켜 볼 수 있다는 거야.</x:t>
   </x:si>
   <x:si>
@@ -470,6 +467,9 @@
   </x:si>
   <x:si>
     <x:t>...정말 오늘 일할 수 있는 거 맞아?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>네가 피아노 맨을 만들 수 있을 정도 상태면, 나머지 과정은 생략할게. 그래도 웬만하면 잠깐참고 나랑 어울려줘, 괜찮지?</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1378,7 +1378,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1"/>
@@ -1390,16 +1390,16 @@
     </x:row>
     <x:row r="2" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
         <x:v>15</x:v>
@@ -1408,10 +1408,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:8" ht="15.75" customHeight="1">
@@ -1422,7 +1422,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="C3" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D3" s="2" t="s">
         <x:v>13</x:v>
@@ -1431,27 +1431,27 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="F3" s="2" t="s">
-        <x:v>149</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="G3" s="2" t="s">
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H3" s="2" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A4" s="4" t="s">
-        <x:v>85</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B4" s="14" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="C4" s="4" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D4" s="4" t="s">
-        <x:v>133</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="E4" s="12"/>
       <x:c r="G4" s="4"/>
@@ -1469,16 +1469,16 @@
     </x:row>
     <x:row r="5" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A5" s="4" t="s">
-        <x:v>133</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B5" s="15" t="s">
-        <x:v>148</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="C5" s="4" t="s">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D5" s="4" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="E5" s="4"/>
       <x:c r="F5" s="4"/>
@@ -1497,7 +1497,7 @@
     </x:row>
     <x:row r="6" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A6" s="4" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B6" s="12" t="s">
         <x:v>7</x:v>
@@ -1506,7 +1506,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="D6" s="4" t="s">
-        <x:v>143</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="E6" s="4"/>
       <x:c r="F6" s="4"/>
@@ -1525,16 +1525,16 @@
     </x:row>
     <x:row r="7" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A7" s="4" t="s">
-        <x:v>143</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="B7" s="12" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="C7" s="4" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D7" s="4" t="s">
-        <x:v>139</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="E7" s="4"/>
       <x:c r="F7" s="4"/>
@@ -1553,16 +1553,16 @@
     </x:row>
     <x:row r="8" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A8" s="4" t="s">
-        <x:v>139</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="B8" s="13" t="s">
-        <x:v>148</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="C8" s="6" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="D8" s="4" t="s">
-        <x:v>145</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="E8" s="6"/>
       <x:c r="F8" s="6"/>
@@ -1581,7 +1581,7 @@
     </x:row>
     <x:row r="9" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A9" s="4" t="s">
-        <x:v>145</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="B9" s="12" t="s">
         <x:v>7</x:v>
@@ -1590,7 +1590,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="D9" s="4" t="s">
-        <x:v>141</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="E9" s="6"/>
       <x:c r="F9" s="6"/>
@@ -1609,16 +1609,16 @@
     </x:row>
     <x:row r="10" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A10" s="4" t="s">
-        <x:v>141</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B10" s="13" t="s">
-        <x:v>148</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="C10" s="7" t="s">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D10" s="4" t="s">
-        <x:v>144</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="E10" s="7"/>
       <x:c r="F10" s="7"/>
@@ -1637,16 +1637,16 @@
     </x:row>
     <x:row r="11" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A11" s="4" t="s">
-        <x:v>144</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="B11" s="12" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="C11" s="7" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D11" s="4" t="s">
-        <x:v>146</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E11" s="7"/>
       <x:c r="F11" s="7"/>
@@ -1665,16 +1665,16 @@
     </x:row>
     <x:row r="12" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A12" s="4" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="B12" s="13" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="C12" s="6" t="s">
         <x:v>146</x:v>
       </x:c>
-      <x:c r="B12" s="13" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="C12" s="6" t="s">
-        <x:v>147</x:v>
-      </x:c>
       <x:c r="D12" s="4" t="s">
-        <x:v>140</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="E12" s="6"/>
       <x:c r="F12" s="6"/>
@@ -1693,16 +1693,16 @@
     </x:row>
     <x:row r="13" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A13" s="4" t="s">
-        <x:v>140</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="B13" s="12" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="C13" s="4" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D13" s="4" t="s">
-        <x:v>125</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="E13" s="4"/>
       <x:c r="F13" s="4"/>
@@ -1721,16 +1721,16 @@
     </x:row>
     <x:row r="14" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A14" s="4" t="s">
-        <x:v>125</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B14" s="13" t="s">
-        <x:v>148</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="C14" s="7" t="s">
         <x:v>6</x:v>
       </x:c>
       <x:c r="D14" s="4" t="s">
-        <x:v>142</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="E14" s="7"/>
       <x:c r="F14" s="7"/>
@@ -1749,16 +1749,16 @@
     </x:row>
     <x:row r="15" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A15" s="4" t="s">
-        <x:v>142</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="B15" s="13" t="s">
-        <x:v>148</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="C15" s="7" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="D15" s="4" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E15" s="7"/>
       <x:c r="F15" s="7"/>
@@ -1777,16 +1777,16 @@
     </x:row>
     <x:row r="16" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A16" s="4" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B16" s="12" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="C16" s="8" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D16" s="4" t="s">
-        <x:v>55</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E16" s="8"/>
       <x:c r="F16" s="8"/>
@@ -1795,16 +1795,16 @@
     </x:row>
     <x:row r="17" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A17" s="4" t="s">
-        <x:v>55</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B17" s="13" t="s">
-        <x:v>148</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="C17" s="9" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D17" s="4" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E17" s="8"/>
       <x:c r="F17" s="8"/>
@@ -1813,7 +1813,7 @@
     </x:row>
     <x:row r="18" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A18" s="4" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B18" s="12" t="s">
         <x:v>7</x:v>
@@ -1822,7 +1822,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="D18" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E18" s="8"/>
       <x:c r="F18" s="8"/>
@@ -1831,16 +1831,16 @@
     </x:row>
     <x:row r="19" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A19" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B19" s="13" t="s">
-        <x:v>148</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="C19" s="9" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D19" s="4" t="s">
-        <x:v>70</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E19" s="8"/>
       <x:c r="F19" s="8"/>
@@ -1849,7 +1849,7 @@
     </x:row>
     <x:row r="20" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A20" s="4" t="s">
-        <x:v>70</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B20" s="12" t="s">
         <x:v>7</x:v>
@@ -1858,7 +1858,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="D20" s="4" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E20" s="8"/>
       <x:c r="F20" s="8"/>
@@ -1867,16 +1867,16 @@
     </x:row>
     <x:row r="21" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A21" s="4" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B21" s="13" t="s">
-        <x:v>148</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="C21" s="9" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D21" s="4" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E21" s="8"/>
       <x:c r="F21" s="8"/>
@@ -1885,7 +1885,7 @@
     </x:row>
     <x:row r="22" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A22" s="4" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B22" s="12" t="s">
         <x:v>7</x:v>
@@ -1894,7 +1894,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="D22" s="4" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E22" s="8"/>
       <x:c r="F22" s="8"/>
@@ -1903,7 +1903,7 @@
     </x:row>
     <x:row r="23" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A23" s="4" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B23" s="12" t="s">
         <x:v>7</x:v>
@@ -1912,7 +1912,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="D23" s="4" t="s">
-        <x:v>71</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E23" s="8"/>
       <x:c r="F23" s="8"/>
@@ -1921,7 +1921,7 @@
     </x:row>
     <x:row r="24" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A24" s="4" t="s">
-        <x:v>71</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B24" s="12" t="s">
         <x:v>7</x:v>
@@ -1930,7 +1930,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="D24" s="4" t="s">
-        <x:v>63</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E24" s="8"/>
       <x:c r="F24" s="8"/>
@@ -1939,16 +1939,16 @@
     </x:row>
     <x:row r="25" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A25" s="4" t="s">
-        <x:v>63</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B25" s="12" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="C25" s="9" t="s">
-        <x:v>29</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D25" s="4" t="s">
-        <x:v>65</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E25" s="8"/>
       <x:c r="F25" s="8"/>
@@ -1957,16 +1957,16 @@
     </x:row>
     <x:row r="26" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A26" s="4" t="s">
-        <x:v>65</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B26" s="12" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="C26" s="10" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D26" s="4" t="s">
-        <x:v>72</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E26" s="10"/>
       <x:c r="F26" s="10"/>
@@ -1975,16 +1975,16 @@
     </x:row>
     <x:row r="27" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A27" s="4" t="s">
-        <x:v>72</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B27" s="13" t="s">
-        <x:v>148</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="C27" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="D27" s="4" t="s">
-        <x:v>68</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E27" s="10"/>
       <x:c r="F27" s="10"/>
@@ -1993,7 +1993,7 @@
     </x:row>
     <x:row r="28" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A28" s="4" t="s">
-        <x:v>68</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B28" s="12" t="s">
         <x:v>7</x:v>
@@ -2002,7 +2002,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="D28" s="4" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E28" s="10"/>
       <x:c r="F28" s="10"/>
@@ -2011,16 +2011,16 @@
     </x:row>
     <x:row r="29" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A29" s="4" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B29" s="13" t="s">
-        <x:v>148</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="C29" s="10" t="s">
-        <x:v>151</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="D29" s="4" t="s">
-        <x:v>66</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E29" s="10"/>
       <x:c r="F29" s="10"/>
@@ -2029,16 +2029,16 @@
     </x:row>
     <x:row r="30" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A30" s="4" t="s">
-        <x:v>66</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B30" s="12" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="C30" s="10" t="s">
-        <x:v>46</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D30" s="4" t="s">
-        <x:v>67</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E30" s="10"/>
       <x:c r="F30" s="10"/>
@@ -2047,16 +2047,16 @@
     </x:row>
     <x:row r="31" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A31" s="4" t="s">
-        <x:v>67</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B31" s="13" t="s">
-        <x:v>148</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="C31" s="10" t="s">
-        <x:v>36</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D31" s="4" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E31" s="10"/>
       <x:c r="F31" s="10"/>
@@ -2065,7 +2065,7 @@
     </x:row>
     <x:row r="32" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A32" s="4" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B32" s="12" t="s">
         <x:v>7</x:v>
@@ -2074,7 +2074,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="D32" s="4" t="s">
-        <x:v>74</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E32" s="11"/>
       <x:c r="F32" s="11"/>
@@ -2083,16 +2083,16 @@
     </x:row>
     <x:row r="33" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A33" s="4" t="s">
-        <x:v>74</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B33" s="13" t="s">
-        <x:v>148</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="C33" s="11" t="s">
-        <x:v>24</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="D33" s="4" t="s">
-        <x:v>69</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E33" s="11"/>
       <x:c r="F33" s="11"/>
@@ -2101,7 +2101,7 @@
     </x:row>
     <x:row r="34" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A34" s="4" t="s">
-        <x:v>69</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B34" s="12" t="s">
         <x:v>7</x:v>
@@ -2110,7 +2110,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="D34" s="4" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E34" s="11"/>
       <x:c r="F34" s="11"/>
@@ -2119,16 +2119,16 @@
     </x:row>
     <x:row r="35" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A35" s="4" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B35" s="13" t="s">
-        <x:v>148</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="C35" s="11" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D35" s="4" t="s">
-        <x:v>73</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E35" s="11"/>
       <x:c r="F35" s="11"/>
@@ -2137,119 +2137,119 @@
     </x:row>
     <x:row r="36" spans="1:4" ht="15.75" customHeight="1">
       <x:c r="A36" s="4" t="s">
-        <x:v>73</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B36" s="13" t="s">
-        <x:v>148</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="C36" t="s">
-        <x:v>27</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D36" s="4" t="s">
-        <x:v>62</x:v>
+        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:4" ht="15.75" customHeight="1">
       <x:c r="A37" s="4" t="s">
-        <x:v>62</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B37" s="13" t="s">
-        <x:v>148</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="C37" t="s">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D37" s="4" t="s">
-        <x:v>76</x:v>
+        <x:v>75</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:4" ht="15.75" customHeight="1">
       <x:c r="A38" s="4" t="s">
-        <x:v>76</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B38" s="13" t="s">
-        <x:v>148</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="C38" t="s">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D38" s="4" t="s">
-        <x:v>88</x:v>
+        <x:v>87</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:4" ht="15.75" customHeight="1">
       <x:c r="A39" s="4" t="s">
-        <x:v>88</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B39" s="12" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="C39" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D39" s="4" t="s">
-        <x:v>90</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:4" ht="15.75" customHeight="1">
       <x:c r="A40" s="4" t="s">
-        <x:v>90</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B40" s="13" t="s">
-        <x:v>148</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="C40" t="s">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D40" s="4" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:4" ht="15.75" customHeight="1">
       <x:c r="A41" s="4" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B41" s="13" t="s">
-        <x:v>148</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="C41" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D41" s="4" t="s">
-        <x:v>75</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:4" ht="15.75" customHeight="1">
       <x:c r="A42" s="4" t="s">
-        <x:v>75</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B42" s="13" t="s">
-        <x:v>148</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="C42" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D42" s="4" t="s">
-        <x:v>59</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:4" ht="15.75" customHeight="1">
       <x:c r="A43" s="4" t="s">
-        <x:v>59</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B43" s="13" t="s">
-        <x:v>148</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="C43" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D43" s="4" t="s">
-        <x:v>78</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:4" ht="15.75" customHeight="1">
       <x:c r="A44" s="4" t="s">
-        <x:v>78</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B44" s="12" t="s">
         <x:v>7</x:v>
@@ -2258,309 +2258,309 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="D44" s="4" t="s">
-        <x:v>79</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:4" ht="15.75" customHeight="1">
       <x:c r="A45" s="4" t="s">
-        <x:v>79</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B45" s="13" t="s">
-        <x:v>148</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="C45" t="s">
-        <x:v>150</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="D45" s="4" t="s">
-        <x:v>89</x:v>
+        <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:4" ht="15.75" customHeight="1">
       <x:c r="A46" s="4" t="s">
-        <x:v>89</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B46" s="12" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="C46" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D46" s="4" t="s">
-        <x:v>82</x:v>
+        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:4" ht="15.75" customHeight="1">
       <x:c r="A47" s="4" t="s">
-        <x:v>82</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C47" t="s">
-        <x:v>34</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D47" s="4"/>
     </x:row>
     <x:row r="48" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A48" s="4" t="s">
-        <x:v>103</x:v>
+        <x:v>102</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A49" s="4" t="s">
-        <x:v>80</x:v>
+        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A50" s="4" t="s">
-        <x:v>86</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A51" s="4" t="s">
-        <x:v>81</x:v>
+        <x:v>80</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A52" s="4" t="s">
-        <x:v>87</x:v>
+        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A53" s="4" t="s">
-        <x:v>83</x:v>
+        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A54" s="4" t="s">
-        <x:v>77</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A55" s="4" t="s">
-        <x:v>102</x:v>
+        <x:v>101</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A56" s="4" t="s">
-        <x:v>97</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A57" s="4" t="s">
-        <x:v>106</x:v>
+        <x:v>105</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A58" s="4" t="s">
-        <x:v>84</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A59" s="4" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A60" s="4" t="s">
-        <x:v>92</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A61" s="4" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A62" s="4" t="s">
-        <x:v>95</x:v>
+        <x:v>94</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A63" s="4" t="s">
-        <x:v>93</x:v>
+        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A64" s="4" t="s">
-        <x:v>109</x:v>
+        <x:v>108</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A65" s="4" t="s">
-        <x:v>100</x:v>
+        <x:v>99</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A66" s="4" t="s">
-        <x:v>99</x:v>
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A67" s="4" t="s">
-        <x:v>105</x:v>
+        <x:v>104</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A68" s="4" t="s">
-        <x:v>94</x:v>
+        <x:v>93</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A69" s="4" t="s">
-        <x:v>96</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A70" s="4" t="s">
-        <x:v>101</x:v>
+        <x:v>100</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A71" s="4" t="s">
-        <x:v>108</x:v>
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A72" s="4" t="s">
-        <x:v>117</x:v>
+        <x:v>116</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A73" s="4" t="s">
-        <x:v>111</x:v>
+        <x:v>110</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A74" s="4" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A75" s="4" t="s">
-        <x:v>122</x:v>
+        <x:v>121</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A76" s="4" t="s">
-        <x:v>104</x:v>
+        <x:v>103</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A77" s="4" t="s">
-        <x:v>119</x:v>
+        <x:v>118</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A78" s="4" t="s">
-        <x:v>110</x:v>
+        <x:v>109</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A79" s="4" t="s">
-        <x:v>136</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A80" s="4" t="s">
-        <x:v>115</x:v>
+        <x:v>114</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A81" s="4" t="s">
-        <x:v>112</x:v>
+        <x:v>111</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A82" s="4" t="s">
-        <x:v>113</x:v>
+        <x:v>112</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A83" s="4" t="s">
-        <x:v>116</x:v>
+        <x:v>115</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A84" s="4" t="s">
-        <x:v>118</x:v>
+        <x:v>117</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A85" s="4" t="s">
-        <x:v>126</x:v>
+        <x:v>125</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A86" s="4" t="s">
-        <x:v>137</x:v>
+        <x:v>136</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A87" s="4" t="s">
-        <x:v>121</x:v>
+        <x:v>120</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A88" s="4" t="s">
-        <x:v>120</x:v>
+        <x:v>119</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A89" s="4" t="s">
-        <x:v>114</x:v>
+        <x:v>113</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A90" s="4" t="s">
-        <x:v>129</x:v>
+        <x:v>128</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A91" s="4" t="s">
-        <x:v>135</x:v>
+        <x:v>134</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A92" s="4" t="s">
-        <x:v>138</x:v>
+        <x:v>137</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A93" s="4" t="s">
-        <x:v>130</x:v>
+        <x:v>129</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A94" s="4" t="s">
-        <x:v>128</x:v>
+        <x:v>127</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A95" s="4" t="s">
-        <x:v>134</x:v>
+        <x:v>133</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A96" s="4" t="s">
-        <x:v>131</x:v>
+        <x:v>130</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A97" s="4" t="s">
-        <x:v>127</x:v>
+        <x:v>126</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A98" s="4" t="s">
-        <x:v>123</x:v>
+        <x:v>122</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A99" s="4" t="s">
-        <x:v>132</x:v>
+        <x:v>131</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A100" s="4" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:1" ht="15.75" customHeight="1">

--- a/JsonConverter/ExcelFiles/MainDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/MainDialogue.xlsx
@@ -4,7 +4,7 @@
   <x:fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="24240" windowHeight="13680"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="24240" windowHeight="11190"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="DNTable_Weapon" sheetId="1" r:id="rId4"/>
@@ -14,469 +14,316 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="152">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="101">
+  <x:si>
+    <x:t>TexturePath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Texture2D/Character_Gillian_Basic</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Texture2D/Character_Gillian_Dismay</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CharacterDataId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>내가 방금 한 말 들었어?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>미안, 무슨 말 했어?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NextDialogueId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>질!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>character_gillian_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>...정말 오늘 일할 수 있는 거 맞아?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SelectionDialogueIdList</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그럼 문제없이 만들어 낼 수 있겠네!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>괜찮아? 생각이 다른데 가있는 것 같은데.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(아, 그러고 보니 내 아파트 방바닥에 맥주 캔들이 엄청나게 널브러져 있었지. 또...)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>칵테일 조합법에 있는 탐색 막대를 이용해 레시피를 확인해 봐. 왼쪽 상단에 표시될거야.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그럼 우리 기초 과정부터 한번 다시 확인해 보자고. 괜찮지? 혹시 모르니까 말야</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그러고 난 다음, 섞기 버튼을 누르면 돼. 다시 눌러서 섞는 걸 멈출 수 있고.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>내가 너를 쥴스라고 부를 수 있게 허락해줄 때 쯤.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대체 언제쯤이면 네가 존같이 생겼다는 걸 인정할거야, 길?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(이틀 전에는 이곳이 폐쇄될 위기에 처했다는 것까지 알게됐지)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>음, 매월 30일에 월세를 내는게 엄청 스트레스거든, 그리고-</x:t>
+  </x:si>
+  <x:si>
+    <x:t>길리안, 나 공식적인 BTC 교육을 받고 여기 온 거거든?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(삶의 기반도 흔들리게 됐는데, 정신까지 나가버릴 지경이라고.)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(게다가 포어에게 중성화 수술을 시켜주느라 지갑 속 마지막 동전 하나까지 다써버렸지. 월세를 한번만 더 미뤘다간 쫒겨날거야...)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>길이 슈가 러쉬나 피아노 맨을 달라는군. 만약에 망쳤다면, 재시도 버튼을 눌러서 다시 하면 되겠지.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>리셋 버튼은 아무 때나 누를 수 있어. 셰이커가 움직이고 있을 때도 말이지. 부담 가지지 말고 원할 때 눌러.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>또 맛이나 종류 기준으로 검색할 수 있어. "달콤한" 술이나 "남성적인" 술을 정렬시켜 볼 수 있다는 거야.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>네가 피아노 맨을 만들 수 있을 정도 상태면, 나머지 과정은 생략할게. 그래도 웬만하면 잠깐참고 나랑 어울려줘, 괜찮지?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string[]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VoicePath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아! 어서 와, 질.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아, 안녕 존.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>무슨 말 했어?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>보스는 어디 있어?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오른쪽 가운데에 있는 셰이커에 재료를 원하는 양만큼 클릭해서 넣어.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아, 만약 제조에 실패했다면 리셋 버튼을 눌러서 다시 시도할 수 있어.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(어제는 1시간 동안 혼자 떠들었다고 오해받는 일이 생기질않나.)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>다 끝나면 서빙하기 버튼을 눌러서 손님에게 전해주면 돼. 그게 다야.</x:t>
+  </x:si>
   <x:si>
     <x:t>했어. 너, 역시 딴 생각에 빠져 있는 것 같아. 그것도 아주 심하게.</x:t>
   </x:si>
   <x:si>
-    <x:t>(어제는 1시간 동안 혼자 떠들었다고 오해받는 일이 생기질않나.)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>오른쪽 가운데에 있는 셰이커에 재료를 원하는 양만큼 클릭해서 넣어.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>다 끝나면 서빙하기 버튼을 눌러서 손님에게 전해주면 돼. 그게 다야.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아, 만약 제조에 실패했다면 리셋 버튼을 눌러서 다시 시도할 수 있어.</x:t>
+    <x:t>character_jill_01</x:t>
   </x:si>
   <x:si>
     <x:t>별거 아니야 조금 생각할게 있어서.</x:t>
   </x:si>
   <x:si>
+    <x:t>SelectionNameList</x:t>
+  </x:si>
+  <x:si>
+    <x:t>우선 슈가 러쉬부터 시작해보자.</x:t>
+  </x:si>
+  <x:si>
     <x:t>글쎄. 뭣 좀 사러 밖에 나갔...</x:t>
   </x:si>
   <x:si>
-    <x:t>character_jill_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SelectionNameList</x:t>
-  </x:si>
-  <x:si>
-    <x:t>우선 슈가 러쉬부터 시작해보자.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>미안, 무슨 말 했어?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CharacterDataId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NextDialogueId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>내가 방금 한 말 들었어?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string[]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(이틀 전에는 이곳이 폐쇄될 위기에 처했다는 것까지 알게됐지)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>길리안, 나 공식적인 BTC 교육을 받고 여기 온 거거든?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>음, 매월 30일에 월세를 내는게 엄청 스트레스거든, 그리고-</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대체 언제쯤이면 네가 존같이 생겼다는 걸 인정할거야, 길?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(삶의 기반도 흔들리게 됐는데, 정신까지 나가버릴 지경이라고.)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>질!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>또 맛이나 종류 기준으로 검색할 수 있어. "달콤한" 술이나 "남성적인" 술을 정렬시켜 볼 수 있다는 거야.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>리셋 버튼은 아무 때나 누를 수 있어. 셰이커가 움직이고 있을 때도 말이지. 부담 가지지 말고 원할 때 눌러.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>칵테일 조합법에 있는 탐색 막대를 이용해 레시피를 확인해 봐. 왼쪽 상단에 표시될거야.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(아, 그러고 보니 내 아파트 방바닥에 맥주 캔들이 엄청나게 널브러져 있었지. 또...)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(게다가 포어에게 중성화 수술을 시켜주느라 지갑 속 마지막 동전 하나까지 다써버렸지. 월세를 한번만 더 미뤘다간 쫒겨날거야...)</x:t>
+    <x:t>dialogue_tutorial_1_1_012</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_015</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_019</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_014</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_018</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_030</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_031</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_016</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_033</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_027</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_037</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_021</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_013</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_017</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_039</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_028</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_022</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_024</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_029</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_023</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_020</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_041</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_040</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_038</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_034</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_032</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_043</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_042</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_035</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_036</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_010</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_008</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_009</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_006</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_011</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_007</x:t>
+  </x:si>
+  <x:si>
+    <x:t>길...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시끄러워.</x:t>
   </x:si>
   <x:si>
     <x:t>고유 ID</x:t>
   </x:si>
   <x:si>
+    <x:t>하아...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그게 뭔데?</x:t>
+  </x:si>
+  <x:si>
     <x:t>string</x:t>
   </x:si>
   <x:si>
+    <x:t>좋은 저녁.</x:t>
+  </x:si>
+  <x:si>
     <x:t>(name)</x:t>
   </x:si>
   <x:si>
-    <x:t>내가 너를 쥴스라고 부를 수 있게 허락해줄 때 쯤.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>길이 슈가 러쉬나 피아노 맨을 달라는군. 만약에 망쳤다면, 재시도 버튼을 눌러서 다시 하면 되겠지.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그러고 난 다음, 섞기 버튼을 누르면 돼. 다시 눌러서 섞는 걸 멈출 수 있고.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그럼 우리 기초 과정부터 한번 다시 확인해 보자고. 괜찮지? 혹시 모르니까 말야</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>보스는 어디 있어?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아! 어서 와, 질.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VoicePath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아, 안녕 존.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>무슨 말 했어?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TexturePath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하아...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시끄러워.</x:t>
-  </x:si>
-  <x:si>
     <x:t>당연하지!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>좋은 저녁.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>길...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그게 뭔데?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_019</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_096</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_014</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_012</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_015</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_013</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_018</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_017</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_039</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_031</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_037</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_033</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_021</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_028</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_022</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_027</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_024</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_030</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_016</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_020</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_023</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_032</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_029</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_038</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_034</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_050</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_040</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_041</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_045</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_047</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_043</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_049</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_054</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_046</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_048</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_035</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_042</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_036</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_055</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_056</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_059</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_064</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_058</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_065</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_052</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_057</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_062</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_061</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_066</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_051</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_044</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_072</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_063</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_053</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_070</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_067</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_060</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_074</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_069</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_077</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_078</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_085</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_076</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_079</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_068</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_080</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_073</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_084</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_083</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_071</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_094</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_010</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_081</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_093</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_090</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_086</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_089</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_092</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_095</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_091</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_087</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_075</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_082</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_088</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_009</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_006</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_011</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_007</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_005</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_008</x:t>
-  </x:si>
-  <x:si>
-    <x:t>괜찮아? 생각이 다른데 가있는 것 같은데.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>character_gillian_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SelectionDialogueIdList</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그럼 문제없이 만들어 낼 수 있겠네!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>...정말 오늘 일할 수 있는 거 맞아?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>네가 피아노 맨을 만들 수 있을 정도 상태면, 나머지 과정은 생략할게. 그래도 웬만하면 잠깐참고 나랑 어울려줘, 괜찮지?</x:t>
   </x:si>
 </x:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="9">
+  <x:fonts count="10">
     <x:font>
       <x:name val="Arial"/>
       <x:sz val="10"/>
@@ -521,6 +368,12 @@
       <x:name val="&quot;맑은 고딕&quot;"/>
       <x:sz val="11"/>
       <x:color rgb="ff008000"/>
+    </x:font>
+    <x:font>
+      <x:name val="Arial"/>
+      <x:sz val="10"/>
+      <x:color rgb="ff000000"/>
+      <x:b val="1"/>
     </x:font>
   </x:fonts>
   <x:fills count="7">
@@ -660,7 +513,7 @@
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="16">
+  <x:cellXfs count="18">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
@@ -708,6 +561,12 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -1378,7 +1237,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1"/>
@@ -1390,71 +1249,72 @@
     </x:row>
     <x:row r="2" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="B2" s="1" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="C2" s="1" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="D2" s="1" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="E2" s="1" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="B2" s="1" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D2" s="1" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E2" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>97</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A3" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C3" s="2" t="s">
         <x:v>36</x:v>
       </x:c>
       <x:c r="D3" s="2" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="E3" s="2" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F3" s="2" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="E3" s="2" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F3" s="2" t="s">
-        <x:v>148</x:v>
-      </x:c>
       <x:c r="G3" s="2" t="s">
-        <x:v>42</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H3" s="2" t="s">
-        <x:v>39</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A4" s="4" t="s">
-        <x:v>84</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B4" s="14" t="s">
-        <x:v>7</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C4" s="4" t="s">
-        <x:v>46</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D4" s="4" t="s">
-        <x:v>132</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E4" s="12"/>
-      <x:c r="G4" s="4"/>
+      <x:c r="F4" s="16"/>
+      <x:c r="G4" s="12"/>
       <x:c r="H4" s="4"/>
       <x:c r="I4" s="3"/>
       <x:c r="J4" s="3"/>
@@ -1469,20 +1329,22 @@
     </x:row>
     <x:row r="5" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A5" s="4" t="s">
-        <x:v>132</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B5" s="15" t="s">
-        <x:v>147</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C5" s="4" t="s">
-        <x:v>38</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D5" s="4" t="s">
-        <x:v>123</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E5" s="4"/>
       <x:c r="F5" s="4"/>
-      <x:c r="G5" s="4"/>
+      <x:c r="G5" s="4" t="s">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="H5" s="4"/>
       <x:c r="I5" s="3"/>
       <x:c r="J5" s="3"/>
@@ -1497,20 +1359,22 @@
     </x:row>
     <x:row r="6" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A6" s="4" t="s">
-        <x:v>123</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B6" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C6" s="4" t="s">
-        <x:v>23</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D6" s="4" t="s">
-        <x:v>142</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E6" s="4"/>
       <x:c r="F6" s="4"/>
-      <x:c r="G6" s="4"/>
+      <x:c r="G6" s="4" t="s">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="H6" s="4"/>
       <x:c r="I6" s="3"/>
       <x:c r="J6" s="3"/>
@@ -1525,20 +1389,22 @@
     </x:row>
     <x:row r="7" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A7" s="4" t="s">
-        <x:v>142</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B7" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C7" s="4" t="s">
-        <x:v>40</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D7" s="4" t="s">
-        <x:v>138</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E7" s="4"/>
       <x:c r="F7" s="4"/>
-      <x:c r="G7" s="4"/>
+      <x:c r="G7" s="4" t="s">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="H7" s="4"/>
       <x:c r="I7" s="3"/>
       <x:c r="J7" s="3"/>
@@ -1553,20 +1419,22 @@
     </x:row>
     <x:row r="8" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A8" s="4" t="s">
-        <x:v>138</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B8" s="13" t="s">
-        <x:v>147</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C8" s="6" t="s">
-        <x:v>23</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D8" s="4" t="s">
-        <x:v>144</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E8" s="6"/>
       <x:c r="F8" s="6"/>
-      <x:c r="G8" s="6"/>
+      <x:c r="G8" s="6" t="s">
+        <x:v>2</x:v>
+      </x:c>
       <x:c r="H8" s="6"/>
       <x:c r="I8" s="3"/>
       <x:c r="J8" s="3"/>
@@ -1581,20 +1449,22 @@
     </x:row>
     <x:row r="9" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A9" s="4" t="s">
-        <x:v>144</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B9" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C9" s="6" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D9" s="4" t="s">
-        <x:v>140</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E9" s="6"/>
       <x:c r="F9" s="6"/>
-      <x:c r="G9" s="6"/>
+      <x:c r="G9" s="6" t="s">
+        <x:v>2</x:v>
+      </x:c>
       <x:c r="H9" s="4"/>
       <x:c r="I9" s="3"/>
       <x:c r="J9" s="3"/>
@@ -1609,20 +1479,22 @@
     </x:row>
     <x:row r="10" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A10" s="4" t="s">
-        <x:v>140</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B10" s="13" t="s">
-        <x:v>147</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C10" s="7" t="s">
-        <x:v>32</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D10" s="4" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="E10" s="7"/>
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="E10" s="4"/>
       <x:c r="F10" s="7"/>
-      <x:c r="G10" s="7"/>
+      <x:c r="G10" s="4" t="s">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="H10" s="7"/>
       <x:c r="I10" s="3"/>
       <x:c r="J10" s="3"/>
@@ -1637,20 +1509,22 @@
     </x:row>
     <x:row r="11" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A11" s="4" t="s">
-        <x:v>143</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B11" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C11" s="7" t="s">
-        <x:v>44</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D11" s="4" t="s">
-        <x:v>145</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E11" s="7"/>
       <x:c r="F11" s="7"/>
-      <x:c r="G11" s="7"/>
+      <x:c r="G11" s="4" t="s">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="H11" s="7"/>
       <x:c r="I11" s="3"/>
       <x:c r="J11" s="3"/>
@@ -1665,20 +1539,22 @@
     </x:row>
     <x:row r="12" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A12" s="4" t="s">
-        <x:v>145</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B12" s="13" t="s">
-        <x:v>147</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C12" s="6" t="s">
-        <x:v>146</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D12" s="4" t="s">
-        <x:v>139</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="E12" s="6"/>
       <x:c r="F12" s="6"/>
-      <x:c r="G12" s="6"/>
+      <x:c r="G12" s="4" t="s">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="H12" s="6"/>
       <x:c r="I12" s="3"/>
       <x:c r="J12" s="3"/>
@@ -1693,20 +1569,22 @@
     </x:row>
     <x:row r="13" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A13" s="4" t="s">
-        <x:v>139</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B13" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C13" s="4" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="D13" s="4" t="s">
-        <x:v>124</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E13" s="4"/>
       <x:c r="F13" s="4"/>
-      <x:c r="G13" s="4"/>
+      <x:c r="G13" s="4" t="s">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="H13" s="4"/>
       <x:c r="I13" s="3"/>
       <x:c r="J13" s="3"/>
@@ -1721,20 +1599,22 @@
     </x:row>
     <x:row r="14" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A14" s="4" t="s">
-        <x:v>124</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B14" s="13" t="s">
-        <x:v>147</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C14" s="7" t="s">
-        <x:v>6</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D14" s="4" t="s">
-        <x:v>141</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="E14" s="7"/>
       <x:c r="F14" s="7"/>
-      <x:c r="G14" s="7"/>
+      <x:c r="G14" s="4" t="s">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="H14" s="7"/>
       <x:c r="I14" s="3"/>
       <x:c r="J14" s="3"/>
@@ -1749,20 +1629,22 @@
     </x:row>
     <x:row r="15" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A15" s="4" t="s">
-        <x:v>141</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B15" s="13" t="s">
-        <x:v>147</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C15" s="7" t="s">
-        <x:v>14</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D15" s="4" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E15" s="7"/>
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="E15" s="6"/>
       <x:c r="F15" s="7"/>
-      <x:c r="G15" s="7"/>
+      <x:c r="G15" s="6" t="s">
+        <x:v>2</x:v>
+      </x:c>
       <x:c r="H15" s="7"/>
       <x:c r="I15" s="3"/>
       <x:c r="J15" s="3"/>
@@ -1777,38 +1659,42 @@
     </x:row>
     <x:row r="16" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A16" s="4" t="s">
-        <x:v>52</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B16" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C16" s="8" t="s">
-        <x:v>41</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D16" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E16" s="8"/>
       <x:c r="F16" s="8"/>
-      <x:c r="G16" s="8"/>
+      <x:c r="G16" s="6" t="s">
+        <x:v>2</x:v>
+      </x:c>
       <x:c r="H16" s="8"/>
     </x:row>
     <x:row r="17" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A17" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B17" s="13" t="s">
-        <x:v>147</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C17" s="9" t="s">
-        <x:v>0</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D17" s="4" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="E17" s="8"/>
+      <x:c r="E17" s="4"/>
       <x:c r="F17" s="8"/>
-      <x:c r="G17" s="9"/>
+      <x:c r="G17" s="4" t="s">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="H17" s="9"/>
     </x:row>
     <x:row r="18" spans="1:8" ht="15.75" customHeight="1">
@@ -1816,107 +1702,119 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B18" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C18" s="9" t="s">
-        <x:v>5</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D18" s="4" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E18" s="8"/>
       <x:c r="F18" s="8"/>
-      <x:c r="G18" s="9"/>
+      <x:c r="G18" s="4" t="s">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="H18" s="9"/>
     </x:row>
     <x:row r="19" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A19" s="4" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B19" s="13" t="s">
-        <x:v>147</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C19" s="9" t="s">
-        <x:v>48</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D19" s="4" t="s">
-        <x:v>69</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E19" s="8"/>
       <x:c r="F19" s="8"/>
-      <x:c r="G19" s="9"/>
+      <x:c r="G19" s="4" t="s">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="H19" s="9"/>
     </x:row>
     <x:row r="20" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A20" s="4" t="s">
-        <x:v>69</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B20" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C20" s="9" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D20" s="4" t="s">
-        <x:v>57</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E20" s="8"/>
       <x:c r="F20" s="8"/>
-      <x:c r="G20" s="9"/>
+      <x:c r="G20" s="4" t="s">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="H20" s="9"/>
     </x:row>
     <x:row r="21" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A21" s="4" t="s">
-        <x:v>57</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B21" s="13" t="s">
-        <x:v>147</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C21" s="9" t="s">
-        <x:v>21</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D21" s="4" t="s">
-        <x:v>56</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E21" s="8"/>
       <x:c r="F21" s="8"/>
-      <x:c r="G21" s="9"/>
+      <x:c r="G21" s="4" t="s">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="H21" s="9"/>
     </x:row>
     <x:row r="22" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A22" s="4" t="s">
-        <x:v>56</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B22" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C22" s="9" t="s">
-        <x:v>1</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D22" s="4" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E22" s="8"/>
       <x:c r="F22" s="8"/>
-      <x:c r="G22" s="9"/>
+      <x:c r="G22" s="4" t="s">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="H22" s="9"/>
     </x:row>
     <x:row r="23" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A23" s="4" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B23" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C23" s="9" t="s">
-        <x:v>16</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D23" s="4" t="s">
         <x:v>70</x:v>
       </x:c>
       <x:c r="E23" s="8"/>
       <x:c r="F23" s="8"/>
-      <x:c r="G23" s="9"/>
+      <x:c r="G23" s="4" t="s">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="H23" s="9"/>
     </x:row>
     <x:row r="24" spans="1:8" ht="15.75" customHeight="1">
@@ -1924,71 +1822,79 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="B24" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C24" s="9" t="s">
-        <x:v>20</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D24" s="4" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E24" s="8"/>
       <x:c r="F24" s="8"/>
-      <x:c r="G24" s="9"/>
+      <x:c r="G24" s="4" t="s">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="H24" s="9"/>
     </x:row>
     <x:row r="25" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A25" s="4" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B25" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C25" s="9" t="s">
-        <x:v>28</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D25" s="4" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E25" s="8"/>
       <x:c r="F25" s="8"/>
-      <x:c r="G25" s="9"/>
+      <x:c r="G25" s="4" t="s">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="H25" s="9"/>
     </x:row>
     <x:row r="26" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A26" s="4" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B26" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C26" s="10" t="s">
-        <x:v>27</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D26" s="4" t="s">
-        <x:v>71</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E26" s="10"/>
       <x:c r="F26" s="10"/>
-      <x:c r="G26" s="10"/>
+      <x:c r="G26" s="4" t="s">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="H26" s="10"/>
     </x:row>
     <x:row r="27" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A27" s="4" t="s">
-        <x:v>71</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B27" s="13" t="s">
-        <x:v>147</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C27" s="10" t="s">
-        <x:v>22</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D27" s="4" t="s">
         <x:v>67</x:v>
       </x:c>
       <x:c r="E27" s="10"/>
       <x:c r="F27" s="10"/>
-      <x:c r="G27" s="10"/>
+      <x:c r="G27" s="4" t="s">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="H27" s="10"/>
     </x:row>
     <x:row r="28" spans="1:8" ht="15.75" customHeight="1">
@@ -1996,71 +1902,79 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="B28" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C28" s="10" t="s">
-        <x:v>11</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D28" s="4" t="s">
-        <x:v>55</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E28" s="10"/>
       <x:c r="F28" s="10"/>
-      <x:c r="G28" s="10"/>
+      <x:c r="G28" s="4" t="s">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="H28" s="10"/>
     </x:row>
     <x:row r="29" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A29" s="4" t="s">
-        <x:v>55</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B29" s="13" t="s">
-        <x:v>147</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C29" s="10" t="s">
-        <x:v>150</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D29" s="4" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="E29" s="10"/>
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E29" s="6"/>
       <x:c r="F29" s="10"/>
-      <x:c r="G29" s="10"/>
+      <x:c r="G29" s="6" t="s">
+        <x:v>2</x:v>
+      </x:c>
       <x:c r="H29" s="10"/>
     </x:row>
     <x:row r="30" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A30" s="4" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B30" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C30" s="10" t="s">
-        <x:v>45</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D30" s="4" t="s">
-        <x:v>66</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E30" s="10"/>
       <x:c r="F30" s="10"/>
-      <x:c r="G30" s="10"/>
+      <x:c r="G30" s="6" t="s">
+        <x:v>2</x:v>
+      </x:c>
       <x:c r="H30" s="10"/>
     </x:row>
     <x:row r="31" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A31" s="4" t="s">
-        <x:v>66</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B31" s="13" t="s">
-        <x:v>147</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C31" s="10" t="s">
-        <x:v>35</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D31" s="4" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="E31" s="10"/>
+      <x:c r="E31" s="4"/>
       <x:c r="F31" s="10"/>
-      <x:c r="G31" s="10"/>
+      <x:c r="G31" s="4" t="s">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="H31" s="10"/>
     </x:row>
     <x:row r="32" spans="1:8" ht="15.75" customHeight="1">
@@ -2068,500 +1982,438 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="B32" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C32" s="11" t="s">
-        <x:v>23</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D32" s="4" t="s">
-        <x:v>73</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E32" s="11"/>
       <x:c r="F32" s="11"/>
-      <x:c r="G32" s="11"/>
+      <x:c r="G32" s="4" t="s">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="H32" s="11"/>
     </x:row>
     <x:row r="33" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A33" s="4" t="s">
-        <x:v>73</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B33" s="13" t="s">
-        <x:v>147</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C33" s="11" t="s">
-        <x:v>151</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D33" s="4" t="s">
-        <x:v>68</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E33" s="11"/>
       <x:c r="F33" s="11"/>
-      <x:c r="G33" s="11"/>
+      <x:c r="G33" s="4" t="s">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="H33" s="11"/>
     </x:row>
     <x:row r="34" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A34" s="4" t="s">
-        <x:v>68</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B34" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C34" s="11" t="s">
-        <x:v>23</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D34" s="4" t="s">
-        <x:v>59</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E34" s="11"/>
       <x:c r="F34" s="11"/>
-      <x:c r="G34" s="11"/>
+      <x:c r="G34" s="4" t="s">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="H34" s="11"/>
     </x:row>
     <x:row r="35" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A35" s="4" t="s">
-        <x:v>59</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B35" s="13" t="s">
-        <x:v>147</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C35" s="11" t="s">
-        <x:v>9</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D35" s="4" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="E35" s="11"/>
+      <x:c r="F35" s="17"/>
+      <x:c r="G35" s="4" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H35" s="11"/>
+    </x:row>
+    <x:row r="36" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A36" s="4" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B36" s="13" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C36" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D36" s="4" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="G36" s="4" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A37" s="4" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B37" s="13" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C37" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="D37" s="4" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="G37" s="4" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A38" s="4" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="B38" s="13" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C38" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="D38" s="4" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="G38" s="4" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A39" s="4" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="B39" s="12" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C39" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D39" s="4" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="G39" s="4" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A40" s="4" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="B40" s="13" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C40" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D40" s="4" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="G40" s="4" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A41" s="4" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B41" s="13" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C41" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D41" s="4" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="G41" s="4" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A42" s="4" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B42" s="13" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C42" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D42" s="4" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="G42" s="4" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A43" s="4" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B43" s="13" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C43" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D43" s="4" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="E35" s="11"/>
-      <x:c r="F35" s="11"/>
-      <x:c r="G35" s="11"/>
-      <x:c r="H35" s="11"/>
-    </x:row>
-    <x:row r="36" spans="1:4" ht="15.75" customHeight="1">
-      <x:c r="A36" s="4" t="s">
+      <x:c r="G43" s="4" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A44" s="4" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="B36" s="13" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="C36" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D36" s="4" t="s">
-        <x:v>61</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:4" ht="15.75" customHeight="1">
-      <x:c r="A37" s="4" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="B37" s="13" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="C37" t="s">
+      <x:c r="B44" s="12" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C44" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="D37" s="4" t="s">
-        <x:v>75</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:4" ht="15.75" customHeight="1">
-      <x:c r="A38" s="4" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="B38" s="13" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="C38" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D38" s="4" t="s">
-        <x:v>87</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:4" ht="15.75" customHeight="1">
-      <x:c r="A39" s="4" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="B39" s="12" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C39" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="D39" s="4" t="s">
-        <x:v>89</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:4" ht="15.75" customHeight="1">
-      <x:c r="A40" s="4" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="B40" s="13" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="C40" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="D40" s="4" t="s">
-        <x:v>60</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="1:4" ht="15.75" customHeight="1">
-      <x:c r="A41" s="4" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="B41" s="13" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="C41" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D41" s="4" t="s">
-        <x:v>74</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" spans="1:4" ht="15.75" customHeight="1">
-      <x:c r="A42" s="4" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="B42" s="13" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="C42" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D42" s="4" t="s">
-        <x:v>58</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" spans="1:4" ht="15.75" customHeight="1">
-      <x:c r="A43" s="4" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="B43" s="13" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="C43" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="D43" s="4" t="s">
-        <x:v>77</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" spans="1:4" ht="15.75" customHeight="1">
-      <x:c r="A44" s="4" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="B44" s="12" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C44" t="s">
-        <x:v>17</x:v>
-      </x:c>
       <x:c r="D44" s="4" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="G44" s="4" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A45" s="4" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="B45" s="13" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C45" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D45" s="4" t="s">
         <x:v>78</x:v>
       </x:c>
-    </x:row>
-    <x:row r="45" spans="1:4" ht="15.75" customHeight="1">
-      <x:c r="A45" s="4" t="s">
+      <x:c r="G45" s="4" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A46" s="4" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="B45" s="13" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="C45" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="D45" s="4" t="s">
-        <x:v>88</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" spans="1:4" ht="15.75" customHeight="1">
-      <x:c r="A46" s="4" t="s">
-        <x:v>88</x:v>
-      </x:c>
       <x:c r="B46" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C46" t="s">
-        <x:v>43</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D46" s="4" t="s">
-        <x:v>81</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47" spans="1:4" ht="15.75" customHeight="1">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="G46" s="4" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A47" s="4" t="s">
-        <x:v>81</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C47" t="s">
-        <x:v>33</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D47" s="4"/>
+      <x:c r="G47" s="4" t="s">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="48" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A48" s="4" t="s">
-        <x:v>102</x:v>
-      </x:c>
+      <x:c r="A48" s="4"/>
     </x:row>
     <x:row r="49" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A49" s="4" t="s">
-        <x:v>79</x:v>
-      </x:c>
+      <x:c r="A49" s="4"/>
     </x:row>
     <x:row r="50" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A50" s="4" t="s">
-        <x:v>85</x:v>
-      </x:c>
+      <x:c r="A50" s="4"/>
     </x:row>
     <x:row r="51" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A51" s="4" t="s">
-        <x:v>80</x:v>
-      </x:c>
+      <x:c r="A51" s="4"/>
     </x:row>
     <x:row r="52" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A52" s="4" t="s">
-        <x:v>86</x:v>
-      </x:c>
+      <x:c r="A52" s="4"/>
     </x:row>
     <x:row r="53" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A53" s="4" t="s">
-        <x:v>82</x:v>
-      </x:c>
+      <x:c r="A53" s="4"/>
     </x:row>
     <x:row r="54" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A54" s="4" t="s">
-        <x:v>76</x:v>
-      </x:c>
+      <x:c r="A54" s="4"/>
     </x:row>
     <x:row r="55" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A55" s="4" t="s">
-        <x:v>101</x:v>
-      </x:c>
+      <x:c r="A55" s="4"/>
     </x:row>
     <x:row r="56" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A56" s="4" t="s">
-        <x:v>96</x:v>
-      </x:c>
+      <x:c r="A56" s="4"/>
     </x:row>
     <x:row r="57" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A57" s="4" t="s">
-        <x:v>105</x:v>
-      </x:c>
+      <x:c r="A57" s="4"/>
     </x:row>
     <x:row r="58" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A58" s="4" t="s">
-        <x:v>83</x:v>
-      </x:c>
+      <x:c r="A58" s="4"/>
     </x:row>
     <x:row r="59" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A59" s="4" t="s">
-        <x:v>90</x:v>
-      </x:c>
+      <x:c r="A59" s="4"/>
     </x:row>
     <x:row r="60" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A60" s="4" t="s">
-        <x:v>91</x:v>
-      </x:c>
+      <x:c r="A60" s="4"/>
     </x:row>
     <x:row r="61" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A61" s="4" t="s">
-        <x:v>97</x:v>
-      </x:c>
+      <x:c r="A61" s="4"/>
     </x:row>
     <x:row r="62" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A62" s="4" t="s">
-        <x:v>94</x:v>
-      </x:c>
+      <x:c r="A62" s="4"/>
     </x:row>
     <x:row r="63" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A63" s="4" t="s">
-        <x:v>92</x:v>
-      </x:c>
+      <x:c r="A63" s="4"/>
     </x:row>
     <x:row r="64" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A64" s="4" t="s">
-        <x:v>108</x:v>
-      </x:c>
+      <x:c r="A64" s="4"/>
     </x:row>
     <x:row r="65" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A65" s="4" t="s">
-        <x:v>99</x:v>
-      </x:c>
+      <x:c r="A65" s="4"/>
     </x:row>
     <x:row r="66" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A66" s="4" t="s">
-        <x:v>98</x:v>
-      </x:c>
+      <x:c r="A66" s="4"/>
     </x:row>
     <x:row r="67" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A67" s="4" t="s">
-        <x:v>104</x:v>
-      </x:c>
+      <x:c r="A67" s="4"/>
     </x:row>
     <x:row r="68" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A68" s="4" t="s">
-        <x:v>93</x:v>
-      </x:c>
+      <x:c r="A68" s="4"/>
     </x:row>
     <x:row r="69" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A69" s="4" t="s">
-        <x:v>95</x:v>
-      </x:c>
+      <x:c r="A69" s="4"/>
     </x:row>
     <x:row r="70" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A70" s="4" t="s">
-        <x:v>100</x:v>
-      </x:c>
+      <x:c r="A70" s="4"/>
     </x:row>
     <x:row r="71" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A71" s="4" t="s">
-        <x:v>107</x:v>
-      </x:c>
+      <x:c r="A71" s="4"/>
     </x:row>
     <x:row r="72" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A72" s="4" t="s">
-        <x:v>116</x:v>
-      </x:c>
+      <x:c r="A72" s="4"/>
     </x:row>
     <x:row r="73" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A73" s="4" t="s">
-        <x:v>110</x:v>
-      </x:c>
+      <x:c r="A73" s="4"/>
     </x:row>
     <x:row r="74" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A74" s="4" t="s">
-        <x:v>106</x:v>
-      </x:c>
+      <x:c r="A74" s="4"/>
     </x:row>
     <x:row r="75" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A75" s="4" t="s">
-        <x:v>121</x:v>
-      </x:c>
+      <x:c r="A75" s="4"/>
     </x:row>
     <x:row r="76" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A76" s="4" t="s">
-        <x:v>103</x:v>
-      </x:c>
+      <x:c r="A76" s="4"/>
     </x:row>
     <x:row r="77" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A77" s="4" t="s">
-        <x:v>118</x:v>
-      </x:c>
+      <x:c r="A77" s="4"/>
     </x:row>
     <x:row r="78" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A78" s="4" t="s">
-        <x:v>109</x:v>
-      </x:c>
+      <x:c r="A78" s="4"/>
     </x:row>
     <x:row r="79" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A79" s="4" t="s">
-        <x:v>135</x:v>
-      </x:c>
+      <x:c r="A79" s="4"/>
     </x:row>
     <x:row r="80" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A80" s="4" t="s">
-        <x:v>114</x:v>
-      </x:c>
+      <x:c r="A80" s="4"/>
     </x:row>
     <x:row r="81" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A81" s="4" t="s">
-        <x:v>111</x:v>
-      </x:c>
+      <x:c r="A81" s="4"/>
     </x:row>
     <x:row r="82" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A82" s="4" t="s">
-        <x:v>112</x:v>
-      </x:c>
+      <x:c r="A82" s="4"/>
     </x:row>
     <x:row r="83" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A83" s="4" t="s">
-        <x:v>115</x:v>
-      </x:c>
+      <x:c r="A83" s="4"/>
     </x:row>
     <x:row r="84" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A84" s="4" t="s">
-        <x:v>117</x:v>
-      </x:c>
+      <x:c r="A84" s="4"/>
     </x:row>
     <x:row r="85" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A85" s="4" t="s">
-        <x:v>125</x:v>
-      </x:c>
+      <x:c r="A85" s="4"/>
     </x:row>
     <x:row r="86" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A86" s="4" t="s">
-        <x:v>136</x:v>
-      </x:c>
+      <x:c r="A86" s="4"/>
     </x:row>
     <x:row r="87" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A87" s="4" t="s">
-        <x:v>120</x:v>
-      </x:c>
+      <x:c r="A87" s="4"/>
     </x:row>
     <x:row r="88" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A88" s="4" t="s">
-        <x:v>119</x:v>
-      </x:c>
+      <x:c r="A88" s="4"/>
     </x:row>
     <x:row r="89" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A89" s="4" t="s">
-        <x:v>113</x:v>
-      </x:c>
+      <x:c r="A89" s="4"/>
     </x:row>
     <x:row r="90" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A90" s="4" t="s">
-        <x:v>128</x:v>
-      </x:c>
+      <x:c r="A90" s="4"/>
     </x:row>
     <x:row r="91" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A91" s="4" t="s">
-        <x:v>134</x:v>
-      </x:c>
+      <x:c r="A91" s="4"/>
     </x:row>
     <x:row r="92" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A92" s="4" t="s">
-        <x:v>137</x:v>
-      </x:c>
+      <x:c r="A92" s="4"/>
     </x:row>
     <x:row r="93" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A93" s="4" t="s">
-        <x:v>129</x:v>
-      </x:c>
+      <x:c r="A93" s="4"/>
     </x:row>
     <x:row r="94" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A94" s="4" t="s">
-        <x:v>127</x:v>
-      </x:c>
+      <x:c r="A94" s="4"/>
     </x:row>
     <x:row r="95" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A95" s="4" t="s">
-        <x:v>133</x:v>
-      </x:c>
+      <x:c r="A95" s="4"/>
     </x:row>
     <x:row r="96" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A96" s="4" t="s">
-        <x:v>130</x:v>
-      </x:c>
+      <x:c r="A96" s="4"/>
     </x:row>
     <x:row r="97" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A97" s="4" t="s">
-        <x:v>126</x:v>
-      </x:c>
+      <x:c r="A97" s="4"/>
     </x:row>
     <x:row r="98" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A98" s="4" t="s">
-        <x:v>122</x:v>
-      </x:c>
+      <x:c r="A98" s="4"/>
     </x:row>
     <x:row r="99" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A99" s="4" t="s">
-        <x:v>131</x:v>
-      </x:c>
+      <x:c r="A99" s="4"/>
     </x:row>
     <x:row r="100" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A100" s="4" t="s">
-        <x:v>50</x:v>
-      </x:c>
+      <x:c r="A100" s="4"/>
     </x:row>
     <x:row r="101" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A101" s="12"/>

--- a/JsonConverter/ExcelFiles/MainDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/MainDialogue.xlsx
@@ -4,7 +4,7 @@
   <x:fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="24240" windowHeight="11190"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="20610" windowHeight="11190"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="DNTable_Weapon" sheetId="1" r:id="rId4"/>

--- a/JsonConverter/ExcelFiles/MainDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/MainDialogue.xlsx
@@ -4,7 +4,7 @@
   <x:fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="20610" windowHeight="11190"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="25440" windowHeight="11190"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="DNTable_Weapon" sheetId="1" r:id="rId4"/>
@@ -14,7 +14,16 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="101">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="149">
+  <x:si>
+    <x:t>측면에 있는 얼음과 숙성 버튼 중 필요한 걸 선택하면 돼.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>알았다, 알았어...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이건...내가 원하던게 아니야.</x:t>
+  </x:si>
   <x:si>
     <x:t>TexturePath</x:t>
   </x:si>
@@ -25,6 +34,15 @@
     <x:t>Texture2D/Character_Gillian_Dismay</x:t>
   </x:si>
   <x:si>
+    <x:t>자 그럼 시작해볼까?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이제 설명 끝났어?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>음..다른걸 만들어보자</x:t>
+  </x:si>
+  <x:si>
     <x:t>CharacterDataId</x:t>
   </x:si>
   <x:si>
@@ -37,6 +55,12 @@
     <x:t>NextDialogueId</x:t>
   </x:si>
   <x:si>
+    <x:t>Texture2D/Character_Gillian_Surprise</x:t>
+  </x:si>
+  <x:si>
+    <x:t>길에게 다시 슈가러쉬나 피아노 맨을 주자고. 이번엔 정확히 섞어보자.</x:t>
+  </x:si>
+  <x:si>
     <x:t>Id</x:t>
   </x:si>
   <x:si>
@@ -64,6 +88,9 @@
     <x:t>괜찮아? 생각이 다른데 가있는 것 같은데.</x:t>
   </x:si>
   <x:si>
+    <x:t>아, 그래! 잊기 전에 하나만 더!</x:t>
+  </x:si>
+  <x:si>
     <x:t>(아, 그러고 보니 내 아파트 방바닥에 맥주 캔들이 엄청나게 널브러져 있었지. 또...)</x:t>
   </x:si>
   <x:si>
@@ -317,6 +344,123 @@
   </x:si>
   <x:si>
     <x:t>당연하지!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>만약에 레시피에 "카모트린 추가 가능"이라고 써져 있다면, 아예 넣지 않을 수도 잔 끝까지 채워 넣을 수도 있다는 의미야.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>카모트린은 음료의 알콜 도수를 결정하지. 맛은 변화시키지 못하지만, 알콜의 효과는 그대로 가지고 있어.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그래.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>내가 말했던 것들을 잘 떠올리면서 만들어!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>음료는 "온더록스" 혹은 숙성을 요구하는지 확인해야 해.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>혹시 용어를 모를 수도 있으니 하는 말인데, "온더록스"는 "얼음"버튼을 눌러서 얼음을 넣어야 한다는 걸 의미해</x:t>
+  </x:si>
+  <x:si>
+    <x:t>응?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_2_000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아, 마지막 문장은 그렇게 신경쓰지 않아도 돼. 그냥 재밌는 뒷이야기 같은 거니까.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_3_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_3_009</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_3_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_3_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_3_004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_3_010</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_3_006</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_3_007</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_3_008</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_3_005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_3_011</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_3_000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_2_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_2_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_2_004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_2_011</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_2_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_2_006</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_2_005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_2_007</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_2_010</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_2_008</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_2_009</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그럼 이제 일을 시작하자고.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자, 충분히 오래 놀아줬지?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그래. 잡아둬서 미안.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이렇게 버튼을 누르면, 재료를 섞은 뒤에 기기가 자동으로 얼음을 추가시켜주지.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>나한테 다시 슈가러쉬나 피아노 맨을 만들어주면 더는 귀찮게 굴지 않을게.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그래, 이제 막 끝났어.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그러니 너무 많이 넣으면, 손님이 빨리 취해버리게 될거야 잘 생각해서 넣어.</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -513,7 +657,7 @@
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="18">
+  <x:cellXfs count="19">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
@@ -567,6 +711,9 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="bottom" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -1231,13 +1378,17 @@
   <x:cols>
     <x:col min="1" max="1" width="26.36328125" customWidth="1"/>
     <x:col min="2" max="2" width="19.54296875" customWidth="1"/>
-    <x:col min="3" max="6" width="77.08984375" customWidth="1"/>
-    <x:col min="7" max="8" width="50.7265625" customWidth="1"/>
+    <x:col min="3" max="3" width="31.5703125" customWidth="1"/>
+    <x:col min="4" max="4" width="27.5703125" customWidth="1"/>
+    <x:col min="5" max="5" width="22.85546875" customWidth="1"/>
+    <x:col min="6" max="6" width="24.85546875" customWidth="1"/>
+    <x:col min="7" max="7" width="36.85546875" customWidth="1"/>
+    <x:col min="8" max="8" width="50.7265625" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1"/>
@@ -1249,68 +1400,68 @@
     </x:row>
     <x:row r="2" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>106</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A3" s="2" t="s">
-        <x:v>7</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C3" s="2" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="D3" s="2" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E3" s="2" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="F3" s="2" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="G3" s="2" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="D3" s="2" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="E3" s="2" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="F3" s="2" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="G3" s="2" t="s">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="H3" s="2" t="s">
-        <x:v>32</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A4" s="4" t="s">
-        <x:v>77</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B4" s="14" t="s">
-        <x:v>43</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C4" s="4" t="s">
-        <x:v>98</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D4" s="4" t="s">
-        <x:v>81</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E4" s="12"/>
       <x:c r="F4" s="16"/>
@@ -1329,21 +1480,21 @@
     </x:row>
     <x:row r="5" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A5" s="4" t="s">
-        <x:v>81</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B5" s="15" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C5" s="4" t="s">
-        <x:v>33</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D5" s="4" t="s">
-        <x:v>82</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E5" s="4"/>
       <x:c r="F5" s="4"/>
       <x:c r="G5" s="4" t="s">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H5" s="4"/>
       <x:c r="I5" s="3"/>
@@ -1359,21 +1510,21 @@
     </x:row>
     <x:row r="6" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A6" s="4" t="s">
-        <x:v>82</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B6" s="12" t="s">
-        <x:v>43</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C6" s="4" t="s">
-        <x:v>9</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D6" s="4" t="s">
-        <x:v>88</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="E6" s="4"/>
       <x:c r="F6" s="4"/>
       <x:c r="G6" s="4" t="s">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H6" s="4"/>
       <x:c r="I6" s="3"/>
@@ -1389,21 +1540,21 @@
     </x:row>
     <x:row r="7" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A7" s="4" t="s">
-        <x:v>88</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B7" s="12" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C7" s="4" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="C7" s="4" t="s">
-        <x:v>34</x:v>
-      </x:c>
       <x:c r="D7" s="4" t="s">
-        <x:v>90</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="E7" s="4"/>
       <x:c r="F7" s="4"/>
       <x:c r="G7" s="4" t="s">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H7" s="4"/>
       <x:c r="I7" s="3"/>
@@ -1419,21 +1570,21 @@
     </x:row>
     <x:row r="8" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A8" s="4" t="s">
-        <x:v>90</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B8" s="13" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C8" s="6" t="s">
-        <x:v>9</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D8" s="4" t="s">
-        <x:v>89</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="E8" s="6"/>
       <x:c r="F8" s="6"/>
       <x:c r="G8" s="6" t="s">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H8" s="6"/>
       <x:c r="I8" s="3"/>
@@ -1449,21 +1600,21 @@
     </x:row>
     <x:row r="9" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A9" s="4" t="s">
-        <x:v>89</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B9" s="12" t="s">
-        <x:v>43</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C9" s="6" t="s">
-        <x:v>21</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D9" s="4" t="s">
-        <x:v>86</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E9" s="6"/>
       <x:c r="F9" s="6"/>
       <x:c r="G9" s="6" t="s">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H9" s="4"/>
       <x:c r="I9" s="3"/>
@@ -1479,21 +1630,21 @@
     </x:row>
     <x:row r="10" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A10" s="4" t="s">
-        <x:v>86</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B10" s="13" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C10" s="7" t="s">
-        <x:v>20</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D10" s="4" t="s">
-        <x:v>91</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E10" s="4"/>
       <x:c r="F10" s="7"/>
       <x:c r="G10" s="4" t="s">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H10" s="7"/>
       <x:c r="I10" s="3"/>
@@ -1509,21 +1660,21 @@
     </x:row>
     <x:row r="11" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A11" s="4" t="s">
-        <x:v>91</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B11" s="12" t="s">
-        <x:v>43</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C11" s="7" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="D11" s="4" t="s">
         <x:v>93</x:v>
-      </x:c>
-      <x:c r="D11" s="4" t="s">
-        <x:v>84</x:v>
       </x:c>
       <x:c r="E11" s="7"/>
       <x:c r="F11" s="7"/>
       <x:c r="G11" s="4" t="s">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H11" s="7"/>
       <x:c r="I11" s="3"/>
@@ -1539,21 +1690,21 @@
     </x:row>
     <x:row r="12" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A12" s="4" t="s">
-        <x:v>84</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B12" s="13" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C12" s="6" t="s">
-        <x:v>15</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D12" s="4" t="s">
-        <x:v>85</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="E12" s="6"/>
       <x:c r="F12" s="6"/>
       <x:c r="G12" s="4" t="s">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H12" s="6"/>
       <x:c r="I12" s="3"/>
@@ -1569,21 +1720,21 @@
     </x:row>
     <x:row r="13" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A13" s="4" t="s">
-        <x:v>85</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B13" s="12" t="s">
-        <x:v>43</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C13" s="4" t="s">
-        <x:v>37</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D13" s="4" t="s">
-        <x:v>83</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E13" s="4"/>
       <x:c r="F13" s="4"/>
       <x:c r="G13" s="4" t="s">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H13" s="4"/>
       <x:c r="I13" s="3"/>
@@ -1599,21 +1750,21 @@
     </x:row>
     <x:row r="14" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A14" s="4" t="s">
-        <x:v>83</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B14" s="13" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C14" s="7" t="s">
-        <x:v>47</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D14" s="4" t="s">
-        <x:v>87</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="E14" s="7"/>
       <x:c r="F14" s="7"/>
       <x:c r="G14" s="4" t="s">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H14" s="7"/>
       <x:c r="I14" s="3"/>
@@ -1629,21 +1780,21 @@
     </x:row>
     <x:row r="15" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A15" s="4" t="s">
-        <x:v>87</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B15" s="13" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C15" s="7" t="s">
-        <x:v>4</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D15" s="4" t="s">
-        <x:v>48</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E15" s="6"/>
       <x:c r="F15" s="7"/>
       <x:c r="G15" s="6" t="s">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H15" s="7"/>
       <x:c r="I15" s="3"/>
@@ -1659,674 +1810,968 @@
     </x:row>
     <x:row r="16" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A16" s="4" t="s">
-        <x:v>48</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B16" s="12" t="s">
-        <x:v>43</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C16" s="8" t="s">
-        <x:v>35</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D16" s="4" t="s">
-        <x:v>60</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E16" s="8"/>
       <x:c r="F16" s="8"/>
       <x:c r="G16" s="6" t="s">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H16" s="8"/>
     </x:row>
     <x:row r="17" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A17" s="4" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="B17" s="13" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C17" s="9" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="D17" s="4" t="s">
         <x:v>60</x:v>
-      </x:c>
-      <x:c r="B17" s="13" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C17" s="9" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="D17" s="4" t="s">
-        <x:v>51</x:v>
       </x:c>
       <x:c r="E17" s="4"/>
       <x:c r="F17" s="8"/>
       <x:c r="G17" s="4" t="s">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H17" s="9"/>
     </x:row>
     <x:row r="18" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A18" s="4" t="s">
-        <x:v>51</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B18" s="12" t="s">
-        <x:v>43</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C18" s="9" t="s">
-        <x:v>44</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D18" s="4" t="s">
-        <x:v>49</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E18" s="8"/>
       <x:c r="F18" s="8"/>
       <x:c r="G18" s="4" t="s">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H18" s="9"/>
     </x:row>
     <x:row r="19" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A19" s="4" t="s">
-        <x:v>49</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B19" s="13" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C19" s="9" t="s">
-        <x:v>96</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D19" s="4" t="s">
-        <x:v>55</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E19" s="8"/>
       <x:c r="F19" s="8"/>
       <x:c r="G19" s="4" t="s">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H19" s="9"/>
     </x:row>
     <x:row r="20" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A20" s="4" t="s">
-        <x:v>55</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B20" s="12" t="s">
-        <x:v>43</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C20" s="9" t="s">
-        <x:v>23</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D20" s="4" t="s">
-        <x:v>61</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E20" s="8"/>
       <x:c r="F20" s="8"/>
       <x:c r="G20" s="4" t="s">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H20" s="9"/>
     </x:row>
     <x:row r="21" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A21" s="4" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B21" s="13" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C21" s="9" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D21" s="4" t="s">
         <x:v>61</x:v>
-      </x:c>
-      <x:c r="B21" s="13" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C21" s="9" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D21" s="4" t="s">
-        <x:v>52</x:v>
       </x:c>
       <x:c r="E21" s="8"/>
       <x:c r="F21" s="8"/>
       <x:c r="G21" s="4" t="s">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H21" s="9"/>
     </x:row>
     <x:row r="22" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A22" s="4" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B22" s="12" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="B22" s="12" t="s">
-        <x:v>43</x:v>
-      </x:c>
       <x:c r="C22" s="9" t="s">
-        <x:v>40</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D22" s="4" t="s">
-        <x:v>50</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E22" s="8"/>
       <x:c r="F22" s="8"/>
       <x:c r="G22" s="4" t="s">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H22" s="9"/>
     </x:row>
     <x:row r="23" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A23" s="4" t="s">
-        <x:v>50</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B23" s="12" t="s">
-        <x:v>43</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C23" s="9" t="s">
-        <x:v>22</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D23" s="4" t="s">
-        <x:v>70</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E23" s="8"/>
       <x:c r="F23" s="8"/>
       <x:c r="G23" s="4" t="s">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H23" s="9"/>
     </x:row>
     <x:row r="24" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A24" s="4" t="s">
-        <x:v>70</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B24" s="12" t="s">
-        <x:v>43</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C24" s="9" t="s">
-        <x:v>25</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D24" s="4" t="s">
-        <x:v>59</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E24" s="8"/>
       <x:c r="F24" s="8"/>
       <x:c r="G24" s="4" t="s">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H24" s="9"/>
     </x:row>
     <x:row r="25" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A25" s="4" t="s">
-        <x:v>59</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B25" s="12" t="s">
-        <x:v>43</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C25" s="9" t="s">
-        <x:v>26</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D25" s="4" t="s">
-        <x:v>65</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E25" s="8"/>
       <x:c r="F25" s="8"/>
       <x:c r="G25" s="4" t="s">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H25" s="9"/>
     </x:row>
     <x:row r="26" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A26" s="4" t="s">
-        <x:v>65</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B26" s="12" t="s">
-        <x:v>43</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C26" s="10" t="s">
-        <x:v>16</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D26" s="4" t="s">
-        <x:v>69</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E26" s="10"/>
       <x:c r="F26" s="10"/>
       <x:c r="G26" s="4" t="s">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H26" s="10"/>
     </x:row>
     <x:row r="27" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A27" s="4" t="s">
-        <x:v>69</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B27" s="13" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C27" s="10" t="s">
-        <x:v>8</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D27" s="4" t="s">
-        <x:v>67</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E27" s="10"/>
       <x:c r="F27" s="10"/>
       <x:c r="G27" s="4" t="s">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H27" s="10"/>
     </x:row>
     <x:row r="28" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A28" s="4" t="s">
-        <x:v>67</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B28" s="12" t="s">
-        <x:v>43</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C28" s="10" t="s">
-        <x:v>5</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D28" s="4" t="s">
-        <x:v>64</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E28" s="10"/>
       <x:c r="F28" s="10"/>
       <x:c r="G28" s="4" t="s">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H28" s="10"/>
     </x:row>
     <x:row r="29" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A29" s="4" t="s">
-        <x:v>64</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B29" s="13" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C29" s="10" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D29" s="4" t="s">
-        <x:v>66</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E29" s="6"/>
       <x:c r="F29" s="10"/>
       <x:c r="G29" s="6" t="s">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H29" s="10"/>
     </x:row>
     <x:row r="30" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A30" s="4" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B30" s="12" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C30" s="10" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="D30" s="4" t="s">
         <x:v>66</x:v>
-      </x:c>
-      <x:c r="B30" s="12" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="C30" s="10" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="D30" s="4" t="s">
-        <x:v>57</x:v>
       </x:c>
       <x:c r="E30" s="10"/>
       <x:c r="F30" s="10"/>
       <x:c r="G30" s="6" t="s">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H30" s="10"/>
     </x:row>
     <x:row r="31" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A31" s="4" t="s">
-        <x:v>57</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B31" s="13" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C31" s="10" t="s">
-        <x:v>18</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D31" s="4" t="s">
-        <x:v>63</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E31" s="4"/>
       <x:c r="F31" s="10"/>
       <x:c r="G31" s="4" t="s">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H31" s="10"/>
     </x:row>
     <x:row r="32" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A32" s="4" t="s">
-        <x:v>63</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B32" s="12" t="s">
-        <x:v>43</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C32" s="11" t="s">
-        <x:v>9</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D32" s="4" t="s">
-        <x:v>68</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E32" s="11"/>
       <x:c r="F32" s="11"/>
       <x:c r="G32" s="4" t="s">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H32" s="11"/>
     </x:row>
     <x:row r="33" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A33" s="4" t="s">
-        <x:v>68</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B33" s="13" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C33" s="11" t="s">
-        <x:v>30</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D33" s="4" t="s">
-        <x:v>53</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E33" s="11"/>
       <x:c r="F33" s="11"/>
       <x:c r="G33" s="4" t="s">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H33" s="11"/>
     </x:row>
     <x:row r="34" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A34" s="4" t="s">
-        <x:v>53</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B34" s="12" t="s">
-        <x:v>43</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C34" s="11" t="s">
-        <x:v>9</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D34" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E34" s="11"/>
       <x:c r="F34" s="11"/>
       <x:c r="G34" s="4" t="s">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H34" s="11"/>
     </x:row>
     <x:row r="35" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A35" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B35" s="13" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C35" s="11" t="s">
-        <x:v>46</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D35" s="4" t="s">
-        <x:v>75</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E35" s="11"/>
       <x:c r="F35" s="17"/>
       <x:c r="G35" s="4" t="s">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H35" s="11"/>
     </x:row>
     <x:row r="36" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A36" s="4" t="s">
-        <x:v>75</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B36" s="13" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C36" t="s">
-        <x:v>17</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D36" s="4" t="s">
-        <x:v>56</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="G36" s="4" t="s">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A37" s="4" t="s">
-        <x:v>56</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B37" s="13" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C37" t="s">
-        <x:v>29</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D37" s="4" t="s">
-        <x:v>74</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="G37" s="4" t="s">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A38" s="4" t="s">
-        <x:v>74</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B38" s="13" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C38" t="s">
-        <x:v>38</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D38" s="4" t="s">
-        <x:v>79</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="G38" s="4" t="s">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A39" s="4" t="s">
-        <x:v>79</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B39" s="12" t="s">
-        <x:v>43</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C39" t="s">
-        <x:v>92</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D39" s="4" t="s">
-        <x:v>80</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="G39" s="4" t="s">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A40" s="4" t="s">
-        <x:v>80</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B40" s="13" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C40" t="s">
-        <x:v>19</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D40" s="4" t="s">
-        <x:v>58</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="G40" s="4" t="s">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A41" s="4" t="s">
-        <x:v>58</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B41" s="13" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C41" t="s">
-        <x:v>41</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D41" s="4" t="s">
-        <x:v>73</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="G41" s="4" t="s">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A42" s="4" t="s">
-        <x:v>73</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B42" s="13" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C42" t="s">
-        <x:v>39</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D42" s="4" t="s">
-        <x:v>62</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="G42" s="4" t="s">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A43" s="4" t="s">
-        <x:v>62</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B43" s="13" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C43" t="s">
-        <x:v>28</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D43" s="4" t="s">
-        <x:v>72</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="G43" s="4" t="s">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A44" s="4" t="s">
-        <x:v>72</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B44" s="12" t="s">
-        <x:v>43</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C44" t="s">
-        <x:v>24</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D44" s="4" t="s">
-        <x:v>71</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="G44" s="4" t="s">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A45" s="4" t="s">
-        <x:v>71</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B45" s="13" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C45" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D45" s="4" t="s">
-        <x:v>78</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="G45" s="4" t="s">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A46" s="4" t="s">
-        <x:v>78</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B46" s="12" t="s">
-        <x:v>43</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C46" t="s">
-        <x:v>95</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D46" s="4" t="s">
-        <x:v>76</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="G46" s="4" t="s">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A47" s="4" t="s">
-        <x:v>76</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C47" t="s">
-        <x:v>27</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D47" s="4"/>
       <x:c r="G47" s="4" t="s">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A48" s="18" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="B48" s="13" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C48" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D48" s="18" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="G48" s="6" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A49" s="18" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="B49" s="13" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C49" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D49" s="18" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="G49" s="6" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A50" s="18" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="B50" s="13" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C50" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="D50" s="18" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="G50" s="4" t="s">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A51" s="18" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="B51" s="13" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C51" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D51" s="18" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="G51" s="4" t="s">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A52" s="18" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="B52" s="13" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C52" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="D52" s="18" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="G52" s="4" t="s">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A53" s="18" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="B53" s="13" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C53" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="D53" s="18" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="G53" s="4" t="s">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A54" s="18" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="B54" s="13" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C54" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="D54" s="18" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="G54" s="4" t="s">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A55" s="18" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="B55" s="12" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C55" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D55" s="18" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="G55" s="4" t="s">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A56" s="18" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="B56" s="13" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C56" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="D56" s="18" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="G56" s="4" t="s">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A57" s="18" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="B57" s="13" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C57" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="D57" s="18" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="G57" s="4" t="s">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A58" s="18" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="B58" s="12" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C58" t="s">
         <x:v>1</x:v>
       </x:c>
-    </x:row>
-    <x:row r="48" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A48" s="4"/>
-    </x:row>
-    <x:row r="49" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A49" s="4"/>
-    </x:row>
-    <x:row r="50" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A50" s="4"/>
-    </x:row>
-    <x:row r="51" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A51" s="4"/>
-    </x:row>
-    <x:row r="52" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A52" s="4"/>
-    </x:row>
-    <x:row r="53" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A53" s="4"/>
-    </x:row>
-    <x:row r="54" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A54" s="4"/>
-    </x:row>
-    <x:row r="55" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A55" s="4"/>
-    </x:row>
-    <x:row r="56" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A56" s="4"/>
-    </x:row>
-    <x:row r="57" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A57" s="4"/>
-    </x:row>
-    <x:row r="58" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A58" s="4"/>
-    </x:row>
-    <x:row r="59" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A59" s="4"/>
-    </x:row>
-    <x:row r="60" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A60" s="4"/>
-    </x:row>
-    <x:row r="61" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A61" s="4"/>
-    </x:row>
-    <x:row r="62" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A62" s="4"/>
-    </x:row>
-    <x:row r="63" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A63" s="4"/>
-    </x:row>
-    <x:row r="64" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A64" s="4"/>
-    </x:row>
-    <x:row r="65" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A65" s="4"/>
-    </x:row>
-    <x:row r="66" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A66" s="4"/>
-    </x:row>
-    <x:row r="67" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A67" s="4"/>
-    </x:row>
-    <x:row r="68" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A68" s="4"/>
-    </x:row>
-    <x:row r="69" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A69" s="4"/>
-    </x:row>
-    <x:row r="70" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A70" s="4"/>
-    </x:row>
-    <x:row r="71" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A71" s="4"/>
+      <x:c r="D58" s="18" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="G58" s="4" t="s">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A59" s="18" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="C59" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="G59" s="4" t="s">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A60" s="18" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="B60" s="12" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C60" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="G60" s="4" t="s">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A61" s="18" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="B61" s="13" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C61" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="G61" s="4" t="s">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A62" s="18" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="B62" s="12" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C62" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="G62" s="4" t="s">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A63" s="18" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="B63" s="13" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C63" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="G63" s="4" t="s">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A64" s="18" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="B64" s="13" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C64" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="G64" s="4" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A65" s="18" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="B65" s="12" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C65" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="G65" s="4" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A66" s="18" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="B66" s="13" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C66" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="G66" s="4" t="s">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A67" s="18" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="B67" s="13" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C67" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="G67" s="4" t="s">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A68" s="18" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="B68" s="13" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C68" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="G68" s="4" t="s">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A69" s="18" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="B69" s="12" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C69" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G69" s="4" t="s">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A70" s="18" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="B70" s="13" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C70" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="G70" s="4" t="s">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A71" s="18" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="B71" s="12" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C71" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G71" s="4" t="s">
+        <x:v>4</x:v>
+      </x:c>
     </x:row>
     <x:row r="72" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A72" s="4"/>

--- a/JsonConverter/ExcelFiles/MainDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/MainDialogue.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="149">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="150">
   <x:si>
     <x:t>측면에 있는 얼음과 숙성 버튼 중 필요한 걸 선택하면 돼.</x:t>
   </x:si>
@@ -461,6 +461,9 @@
   </x:si>
   <x:si>
     <x:t>그러니 너무 많이 넣으면, 손님이 빨리 취해버리게 될거야 잘 생각해서 넣어.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Texture2D/Character_Gillian_Smile</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -2615,6 +2618,9 @@
       <x:c r="C60" t="s">
         <x:v>143</x:v>
       </x:c>
+      <x:c r="D60" s="18" t="s">
+        <x:v>119</x:v>
+      </x:c>
       <x:c r="G60" s="4" t="s">
         <x:v>4</x:v>
       </x:c>
@@ -2629,8 +2635,11 @@
       <x:c r="C61" t="s">
         <x:v>144</x:v>
       </x:c>
+      <x:c r="D61" s="18" t="s">
+        <x:v>121</x:v>
+      </x:c>
       <x:c r="G61" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>149</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:7" ht="15.75" customHeight="1">
@@ -2643,6 +2652,9 @@
       <x:c r="C62" t="s">
         <x:v>142</x:v>
       </x:c>
+      <x:c r="D62" s="18" t="s">
+        <x:v>122</x:v>
+      </x:c>
       <x:c r="G62" s="4" t="s">
         <x:v>4</x:v>
       </x:c>
@@ -2657,6 +2669,9 @@
       <x:c r="C63" t="s">
         <x:v>112</x:v>
       </x:c>
+      <x:c r="D63" s="18" t="s">
+        <x:v>123</x:v>
+      </x:c>
       <x:c r="G63" s="4" t="s">
         <x:v>4</x:v>
       </x:c>
@@ -2671,6 +2686,9 @@
       <x:c r="C64" t="s">
         <x:v>24</x:v>
       </x:c>
+      <x:c r="D64" s="18" t="s">
+        <x:v>128</x:v>
+      </x:c>
       <x:c r="G64" s="4" t="s">
         <x:v>13</x:v>
       </x:c>
@@ -2685,6 +2703,9 @@
       <x:c r="C65" t="s">
         <x:v>116</x:v>
       </x:c>
+      <x:c r="D65" s="18" t="s">
+        <x:v>125</x:v>
+      </x:c>
       <x:c r="G65" s="4" t="s">
         <x:v>13</x:v>
       </x:c>
@@ -2699,6 +2720,9 @@
       <x:c r="C66" t="s">
         <x:v>110</x:v>
       </x:c>
+      <x:c r="D66" s="18" t="s">
+        <x:v>126</x:v>
+      </x:c>
       <x:c r="G66" s="4" t="s">
         <x:v>4</x:v>
       </x:c>
@@ -2713,6 +2737,9 @@
       <x:c r="C67" t="s">
         <x:v>111</x:v>
       </x:c>
+      <x:c r="D67" s="18" t="s">
+        <x:v>127</x:v>
+      </x:c>
       <x:c r="G67" s="4" t="s">
         <x:v>4</x:v>
       </x:c>
@@ -2727,6 +2754,9 @@
       <x:c r="C68" t="s">
         <x:v>148</x:v>
       </x:c>
+      <x:c r="D68" s="18" t="s">
+        <x:v>120</x:v>
+      </x:c>
       <x:c r="G68" s="4" t="s">
         <x:v>4</x:v>
       </x:c>
@@ -2741,6 +2771,9 @@
       <x:c r="C69" t="s">
         <x:v>7</x:v>
       </x:c>
+      <x:c r="D69" s="18" t="s">
+        <x:v>124</x:v>
+      </x:c>
       <x:c r="G69" s="4" t="s">
         <x:v>4</x:v>
       </x:c>
@@ -2754,6 +2787,9 @@
       </x:c>
       <x:c r="C70" t="s">
         <x:v>147</x:v>
+      </x:c>
+      <x:c r="D70" s="18" t="s">
+        <x:v>129</x:v>
       </x:c>
       <x:c r="G70" s="4" t="s">
         <x:v>4</x:v>

--- a/JsonConverter/ExcelFiles/MainDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/MainDialogue.xlsx
@@ -4,7 +4,7 @@
   <x:fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="25440" windowHeight="11190"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="20610" windowHeight="11190"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="DNTable_Weapon" sheetId="1" r:id="rId4"/>
@@ -14,276 +14,342 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="150">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="152">
+  <x:si>
+    <x:t>자, 충분히 오래 놀아줬지?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>미안, 무슨 말 했어?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그럼 이제 일을 시작하자고.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>내가 방금 한 말 들었어?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그래, 이제 막 끝났어.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>음..다른걸 만들어보자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NextDialogueId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CharacterDataId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그래. 잡아둬서 미안.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>...정말 오늘 일할 수 있는 거 맞아?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>내가 말했던 것들을 잘 떠올리면서 만들어!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그럼 문제없이 만들어 낼 수 있겠네!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SelectionDialogueIdList</x:t>
+  </x:si>
+  <x:si>
+    <x:t>character_gillian_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>괜찮아? 생각이 다른데 가있는 것 같은데.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>질!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>응?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그래.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>내가 너를 쥴스라고 부를 수 있게 허락해줄 때 쯤.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>음료는 "온더록스" 혹은 숙성을 요구하는지 확인해야 해.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(아, 그러고 보니 내 아파트 방바닥에 맥주 캔들이 엄청나게 널브러져 있었지. 또...)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>칵테일 조합법에 있는 탐색 막대를 이용해 레시피를 확인해 봐. 왼쪽 상단에 표시될거야.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>카모트린은 음료의 알콜 도수를 결정하지. 맛은 변화시키지 못하지만, 알콜의 효과는 그대로 가지고 있어.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>술을 섞고 삶을 바꿔줄 시간이군.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(게다가 포어에게 중성화 수술을 시켜주느라 지갑 속 마지막 동전 하나까지 다써버렸지. 월세를 한번만 더 미뤘다간 쫒겨날거야...)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그럼 우리 기초 과정부터 한번 다시 확인해 보자고. 괜찮지? 혹시 모르니까 말야</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그러고 난 다음, 섞기 버튼을 누르면 돼. 다시 눌러서 섞는 걸 멈출 수 있고.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아, 마지막 문장은 그렇게 신경쓰지 않아도 돼. 그냥 재밌는 뒷이야기 같은 거니까.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그러니 너무 많이 넣으면, 손님이 빨리 취해버리게 될거야 잘 생각해서 넣어.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이렇게 버튼을 누르면, 재료를 섞은 뒤에 기기가 자동으로 얼음을 추가시켜주지.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>나한테 다시 슈가러쉬나 피아노 맨을 만들어주면 더는 귀찮게 굴지 않을게.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>네가 피아노 맨을 만들 수 있을 정도 상태면, 나머지 과정은 생략할게. 그래도 웬만하면 잠깐참고 나랑 어울려줘, 괜찮지?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>길이 슈가 러쉬나 피아노 맨을 달라는군. 만약에 망쳤다면, 재시도 버튼을 눌러서 다시 하면 되겠지.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>만약에 레시피에 "카모트린 추가 가능"이라고 써져 있다면, 아예 넣지 않을 수도 잔 끝까지 채워 넣을 수도 있다는 의미야.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TexturePath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>알았다, 알았어...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자 그럼 시작해볼까?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이제 설명 끝났어?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VoicePath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string[]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아! 어서 와, 질.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>보스는 어디 있어?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아, 안녕 존.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>무슨 말 했어?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>또 맛이나 종류 기준으로 검색할 수 있어. "달콤한" 술이나 "남성적인" 술을 정렬시켜 볼 수 있다는 거야.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>리셋 버튼은 아무 때나 누를 수 있어. 셰이커가 움직이고 있을 때도 말이지. 부담 가지지 말고 원할 때 눌러.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>혹시 용어를 모를 수도 있으니 하는 말인데, "온더록스"는 "얼음"버튼을 눌러서 얼음을 넣어야 한다는 걸 의미해</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(삶의 기반도 흔들리게 됐는데, 정신까지 나가버릴 지경이라고.)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>길리안, 나 공식적인 BTC 교육을 받고 여기 온 거거든?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Texture2D/Character_Gillian_Smile</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Texture2D/Character_Gillian_Basic</x:t>
+  </x:si>
+  <x:si>
+    <x:t>음, 매월 30일에 월세를 내는게 엄청 스트레스거든, 그리고-</x:t>
+  </x:si>
   <x:si>
     <x:t>측면에 있는 얼음과 숙성 버튼 중 필요한 걸 선택하면 돼.</x:t>
   </x:si>
   <x:si>
-    <x:t>알았다, 알았어...</x:t>
+    <x:t>Texture2D/Character_Gillian_Dismay</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대체 언제쯤이면 네가 존같이 생겼다는 걸 인정할거야, 길?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(이틀 전에는 이곳이 폐쇄될 위기에 처했다는 것까지 알게됐지)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오른쪽 가운데에 있는 셰이커에 재료를 원하는 양만큼 클릭해서 넣어.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>했어. 너, 역시 딴 생각에 빠져 있는 것 같아. 그것도 아주 심하게.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>길에게 다시 슈가러쉬나 피아노 맨을 주자고. 이번엔 정확히 섞어보자.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>다 끝나면 서빙하기 버튼을 눌러서 손님에게 전해주면 돼. 그게 다야.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Texture2D/Character_Gillian_Surprise</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아, 만약 제조에 실패했다면 리셋 버튼을 눌러서 다시 시도할 수 있어.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(어제는 1시간 동안 혼자 떠들었다고 오해받는 일이 생기질않나.)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SelectionNameList</x:t>
   </x:si>
   <x:si>
     <x:t>이건...내가 원하던게 아니야.</x:t>
   </x:si>
   <x:si>
-    <x:t>TexturePath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Texture2D/Character_Gillian_Basic</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Texture2D/Character_Gillian_Dismay</x:t>
-  </x:si>
-  <x:si>
-    <x:t>자 그럼 시작해볼까?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이제 설명 끝났어?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>음..다른걸 만들어보자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CharacterDataId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>내가 방금 한 말 들었어?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>미안, 무슨 말 했어?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NextDialogueId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Texture2D/Character_Gillian_Surprise</x:t>
-  </x:si>
-  <x:si>
-    <x:t>길에게 다시 슈가러쉬나 피아노 맨을 주자고. 이번엔 정확히 섞어보자.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>질!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>character_gillian_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>...정말 오늘 일할 수 있는 거 맞아?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SelectionDialogueIdList</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그럼 문제없이 만들어 낼 수 있겠네!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>괜찮아? 생각이 다른데 가있는 것 같은데.</x:t>
+    <x:t>글쎄. 뭣 좀 사러 밖에 나갔...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>character_jill_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>우선 슈가 러쉬부터 시작해보자.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>별거 아니야 조금 생각할게 있어서.</x:t>
   </x:si>
   <x:si>
     <x:t>아, 그래! 잊기 전에 하나만 더!</x:t>
   </x:si>
   <x:si>
-    <x:t>(아, 그러고 보니 내 아파트 방바닥에 맥주 캔들이 엄청나게 널브러져 있었지. 또...)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>칵테일 조합법에 있는 탐색 막대를 이용해 레시피를 확인해 봐. 왼쪽 상단에 표시될거야.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그럼 우리 기초 과정부터 한번 다시 확인해 보자고. 괜찮지? 혹시 모르니까 말야</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그러고 난 다음, 섞기 버튼을 누르면 돼. 다시 눌러서 섞는 걸 멈출 수 있고.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>내가 너를 쥴스라고 부를 수 있게 허락해줄 때 쯤.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대체 언제쯤이면 네가 존같이 생겼다는 걸 인정할거야, 길?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(이틀 전에는 이곳이 폐쇄될 위기에 처했다는 것까지 알게됐지)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>음, 매월 30일에 월세를 내는게 엄청 스트레스거든, 그리고-</x:t>
-  </x:si>
-  <x:si>
-    <x:t>길리안, 나 공식적인 BTC 교육을 받고 여기 온 거거든?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(삶의 기반도 흔들리게 됐는데, 정신까지 나가버릴 지경이라고.)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(게다가 포어에게 중성화 수술을 시켜주느라 지갑 속 마지막 동전 하나까지 다써버렸지. 월세를 한번만 더 미뤘다간 쫒겨날거야...)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>길이 슈가 러쉬나 피아노 맨을 달라는군. 만약에 망쳤다면, 재시도 버튼을 눌러서 다시 하면 되겠지.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>리셋 버튼은 아무 때나 누를 수 있어. 셰이커가 움직이고 있을 때도 말이지. 부담 가지지 말고 원할 때 눌러.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>또 맛이나 종류 기준으로 검색할 수 있어. "달콤한" 술이나 "남성적인" 술을 정렬시켜 볼 수 있다는 거야.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>네가 피아노 맨을 만들 수 있을 정도 상태면, 나머지 과정은 생략할게. 그래도 웬만하면 잠깐참고 나랑 어울려줘, 괜찮지?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string[]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VoicePath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아! 어서 와, 질.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아, 안녕 존.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>무슨 말 했어?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>보스는 어디 있어?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>오른쪽 가운데에 있는 셰이커에 재료를 원하는 양만큼 클릭해서 넣어.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아, 만약 제조에 실패했다면 리셋 버튼을 눌러서 다시 시도할 수 있어.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(어제는 1시간 동안 혼자 떠들었다고 오해받는 일이 생기질않나.)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>다 끝나면 서빙하기 버튼을 눌러서 손님에게 전해주면 돼. 그게 다야.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>했어. 너, 역시 딴 생각에 빠져 있는 것 같아. 그것도 아주 심하게.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>character_jill_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>별거 아니야 조금 생각할게 있어서.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SelectionNameList</x:t>
-  </x:si>
-  <x:si>
-    <x:t>우선 슈가 러쉬부터 시작해보자.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>글쎄. 뭣 좀 사러 밖에 나갔...</x:t>
-  </x:si>
-  <x:si>
     <x:t>dialogue_tutorial_1_1_012</x:t>
   </x:si>
   <x:si>
+    <x:t>dialogue_tutorial_1_1_037</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_031</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_013</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_030</x:t>
+  </x:si>
+  <x:si>
     <x:t>dialogue_tutorial_1_1_015</x:t>
   </x:si>
   <x:si>
+    <x:t>dialogue_tutorial_1_1_027</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_025</x:t>
+  </x:si>
+  <x:si>
     <x:t>dialogue_tutorial_1_1_019</x:t>
   </x:si>
   <x:si>
+    <x:t>dialogue_tutorial_1_1_016</x:t>
+  </x:si>
+  <x:si>
     <x:t>dialogue_tutorial_1_1_014</x:t>
   </x:si>
   <x:si>
+    <x:t>dialogue_tutorial_1_1_033</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_039</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_017</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_021</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_028</x:t>
+  </x:si>
+  <x:si>
     <x:t>dialogue_tutorial_1_1_018</x:t>
   </x:si>
   <x:si>
-    <x:t>dialogue_tutorial_1_1_030</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_031</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_016</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_033</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_027</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_037</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_021</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_013</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_017</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_039</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_028</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_025</x:t>
+    <x:t>dialogue_tutorial_1_1_042</x:t>
   </x:si>
   <x:si>
     <x:t>dialogue_tutorial_1_1_022</x:t>
   </x:si>
   <x:si>
+    <x:t>dialogue_tutorial_1_1_023</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_024</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_020</x:t>
+  </x:si>
+  <x:si>
     <x:t>dialogue_tutorial_1_1_026</x:t>
   </x:si>
   <x:si>
-    <x:t>dialogue_tutorial_1_1_024</x:t>
+    <x:t>dialogue_tutorial_1_1_032</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_038</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_034</x:t>
   </x:si>
   <x:si>
     <x:t>dialogue_tutorial_1_1_029</x:t>
   </x:si>
   <x:si>
-    <x:t>dialogue_tutorial_1_1_023</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_020</x:t>
+    <x:t>dialogue_tutorial_1_1_035</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_036</x:t>
   </x:si>
   <x:si>
     <x:t>dialogue_tutorial_1_1_041</x:t>
   </x:si>
   <x:si>
+    <x:t>dialogue_tutorial_1_1_043</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_000</x:t>
+  </x:si>
+  <x:si>
     <x:t>dialogue_tutorial_1_1_040</x:t>
   </x:si>
   <x:si>
-    <x:t>dialogue_tutorial_1_1_038</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_034</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_032</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_043</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_042</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_035</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_036</x:t>
+    <x:t>dialogue_tutorial_1_1_011</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_008</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_010</x:t>
   </x:si>
   <x:si>
     <x:t>dialogue_tutorial_1_1_001</x:t>
@@ -292,178 +358,118 @@
     <x:t>dialogue_tutorial_1_1_002</x:t>
   </x:si>
   <x:si>
-    <x:t>dialogue_tutorial_1_1_010</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_008</x:t>
+    <x:t>dialogue_tutorial_1_1_007</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_006</x:t>
   </x:si>
   <x:si>
     <x:t>dialogue_tutorial_1_1_009</x:t>
   </x:si>
   <x:si>
-    <x:t>dialogue_tutorial_1_1_006</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_011</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_005</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_007</x:t>
+    <x:t>dialogue_tutorial_1_2_000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_3_007</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_3_008</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_3_005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_3_004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_3_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_3_011</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_3_000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_3_009</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_3_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_3_010</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_3_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_3_006</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_2_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_2_007</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_2_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_2_004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_2_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_2_008</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_2_009</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_2_005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_2_010</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_2_011</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_2_006</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_3_012</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그게 뭔데?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시끄러워.</x:t>
   </x:si>
   <x:si>
     <x:t>길...</x:t>
   </x:si>
   <x:si>
-    <x:t>시끄러워.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고유 ID</x:t>
+    <x:t>좋은 저녁.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>당연하지!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
   </x:si>
   <x:si>
     <x:t>하아...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그게 뭔데?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>좋은 저녁.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>당연하지!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>만약에 레시피에 "카모트린 추가 가능"이라고 써져 있다면, 아예 넣지 않을 수도 잔 끝까지 채워 넣을 수도 있다는 의미야.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>카모트린은 음료의 알콜 도수를 결정하지. 맛은 변화시키지 못하지만, 알콜의 효과는 그대로 가지고 있어.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그래.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>내가 말했던 것들을 잘 떠올리면서 만들어!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>음료는 "온더록스" 혹은 숙성을 요구하는지 확인해야 해.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>혹시 용어를 모를 수도 있으니 하는 말인데, "온더록스"는 "얼음"버튼을 눌러서 얼음을 넣어야 한다는 걸 의미해</x:t>
-  </x:si>
-  <x:si>
-    <x:t>응?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_2_000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아, 마지막 문장은 그렇게 신경쓰지 않아도 돼. 그냥 재밌는 뒷이야기 같은 거니까.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_3_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_3_009</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_3_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_3_003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_3_004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_3_010</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_3_006</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_3_007</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_3_008</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_3_005</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_3_011</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_3_000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_2_003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_2_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_2_004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_2_011</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_2_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_2_006</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_2_005</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_2_007</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_2_010</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_2_008</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_2_009</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그럼 이제 일을 시작하자고.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>자, 충분히 오래 놀아줬지?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그래. 잡아둬서 미안.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이렇게 버튼을 누르면, 재료를 섞은 뒤에 기기가 자동으로 얼음을 추가시켜주지.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>나한테 다시 슈가러쉬나 피아노 맨을 만들어주면 더는 귀찮게 굴지 않을게.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그래, 이제 막 끝났어.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그러니 너무 많이 넣으면, 손님이 빨리 취해버리게 될거야 잘 생각해서 넣어.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Texture2D/Character_Gillian_Smile</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1391,7 +1397,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1"/>
@@ -1403,51 +1409,51 @@
     </x:row>
     <x:row r="2" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A3" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
-        <x:v>9</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C3" s="2" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D3" s="2" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="E3" s="2" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="F3" s="2" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="E3" s="2" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="F3" s="2" t="s">
-        <x:v>21</x:v>
-      </x:c>
       <x:c r="G3" s="2" t="s">
-        <x:v>3</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="H3" s="2" t="s">
         <x:v>41</x:v>
@@ -1455,16 +1461,16 @@
     </x:row>
     <x:row r="4" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A4" s="4" t="s">
-        <x:v>86</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B4" s="14" t="s">
-        <x:v>52</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C4" s="4" t="s">
-        <x:v>107</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="D4" s="4" t="s">
-        <x:v>90</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="E4" s="12"/>
       <x:c r="F4" s="16"/>
@@ -1483,21 +1489,21 @@
     </x:row>
     <x:row r="5" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A5" s="4" t="s">
-        <x:v>90</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B5" s="15" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C5" s="4" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D5" s="4" t="s">
-        <x:v>91</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="E5" s="4"/>
       <x:c r="F5" s="4"/>
       <x:c r="G5" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="H5" s="4"/>
       <x:c r="I5" s="3"/>
@@ -1513,21 +1519,21 @@
     </x:row>
     <x:row r="6" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A6" s="4" t="s">
-        <x:v>91</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B6" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C6" s="4" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D6" s="4" t="s">
-        <x:v>97</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="E6" s="4"/>
       <x:c r="F6" s="4"/>
       <x:c r="G6" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="H6" s="4"/>
       <x:c r="I6" s="3"/>
@@ -1543,21 +1549,21 @@
     </x:row>
     <x:row r="7" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A7" s="4" t="s">
-        <x:v>97</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B7" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C7" s="4" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D7" s="4" t="s">
-        <x:v>99</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="E7" s="4"/>
       <x:c r="F7" s="4"/>
       <x:c r="G7" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="H7" s="4"/>
       <x:c r="I7" s="3"/>
@@ -1573,21 +1579,21 @@
     </x:row>
     <x:row r="8" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A8" s="4" t="s">
-        <x:v>99</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B8" s="13" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C8" s="6" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="C8" s="6" t="s">
-        <x:v>17</x:v>
-      </x:c>
       <x:c r="D8" s="4" t="s">
-        <x:v>98</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="E8" s="6"/>
       <x:c r="F8" s="6"/>
       <x:c r="G8" s="6" t="s">
-        <x:v>5</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H8" s="6"/>
       <x:c r="I8" s="3"/>
@@ -1603,21 +1609,21 @@
     </x:row>
     <x:row r="9" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A9" s="4" t="s">
-        <x:v>98</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B9" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C9" s="6" t="s">
-        <x:v>30</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D9" s="4" t="s">
-        <x:v>95</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="E9" s="6"/>
       <x:c r="F9" s="6"/>
       <x:c r="G9" s="6" t="s">
-        <x:v>5</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H9" s="4"/>
       <x:c r="I9" s="3"/>
@@ -1633,21 +1639,21 @@
     </x:row>
     <x:row r="10" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A10" s="4" t="s">
-        <x:v>95</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B10" s="13" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C10" s="7" t="s">
-        <x:v>29</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D10" s="4" t="s">
-        <x:v>100</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="E10" s="4"/>
       <x:c r="F10" s="7"/>
       <x:c r="G10" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="H10" s="7"/>
       <x:c r="I10" s="3"/>
@@ -1663,21 +1669,21 @@
     </x:row>
     <x:row r="11" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A11" s="4" t="s">
-        <x:v>100</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B11" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C11" s="7" t="s">
-        <x:v>102</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="D11" s="4" t="s">
-        <x:v>93</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="E11" s="7"/>
       <x:c r="F11" s="7"/>
       <x:c r="G11" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="H11" s="7"/>
       <x:c r="I11" s="3"/>
@@ -1693,21 +1699,21 @@
     </x:row>
     <x:row r="12" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A12" s="4" t="s">
-        <x:v>93</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B12" s="13" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C12" s="6" t="s">
-        <x:v>23</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D12" s="4" t="s">
-        <x:v>94</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="E12" s="6"/>
       <x:c r="F12" s="6"/>
       <x:c r="G12" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="H12" s="6"/>
       <x:c r="I12" s="3"/>
@@ -1723,21 +1729,21 @@
     </x:row>
     <x:row r="13" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A13" s="4" t="s">
-        <x:v>94</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B13" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C13" s="4" t="s">
-        <x:v>46</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D13" s="4" t="s">
-        <x:v>92</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E13" s="4"/>
       <x:c r="F13" s="4"/>
       <x:c r="G13" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="H13" s="4"/>
       <x:c r="I13" s="3"/>
@@ -1753,21 +1759,21 @@
     </x:row>
     <x:row r="14" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A14" s="4" t="s">
-        <x:v>92</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B14" s="13" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C14" s="7" t="s">
-        <x:v>56</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D14" s="4" t="s">
-        <x:v>96</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="E14" s="7"/>
       <x:c r="F14" s="7"/>
       <x:c r="G14" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="H14" s="7"/>
       <x:c r="I14" s="3"/>
@@ -1783,21 +1789,21 @@
     </x:row>
     <x:row r="15" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A15" s="4" t="s">
-        <x:v>96</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B15" s="13" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C15" s="7" t="s">
-        <x:v>10</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D15" s="4" t="s">
-        <x:v>57</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E15" s="6"/>
       <x:c r="F15" s="7"/>
       <x:c r="G15" s="6" t="s">
-        <x:v>5</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H15" s="7"/>
       <x:c r="I15" s="3"/>
@@ -1813,771 +1819,771 @@
     </x:row>
     <x:row r="16" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A16" s="4" t="s">
-        <x:v>57</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B16" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C16" s="8" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D16" s="4" t="s">
-        <x:v>69</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E16" s="8"/>
       <x:c r="F16" s="8"/>
       <x:c r="G16" s="6" t="s">
-        <x:v>5</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H16" s="8"/>
     </x:row>
     <x:row r="17" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A17" s="4" t="s">
-        <x:v>69</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B17" s="13" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C17" s="9" t="s">
-        <x:v>51</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D17" s="4" t="s">
-        <x:v>60</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E17" s="4"/>
       <x:c r="F17" s="8"/>
       <x:c r="G17" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="H17" s="9"/>
     </x:row>
     <x:row r="18" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A18" s="4" t="s">
-        <x:v>60</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B18" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C18" s="9" t="s">
-        <x:v>53</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D18" s="4" t="s">
-        <x:v>58</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E18" s="8"/>
       <x:c r="F18" s="8"/>
       <x:c r="G18" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="H18" s="9"/>
     </x:row>
     <x:row r="19" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A19" s="4" t="s">
-        <x:v>58</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B19" s="13" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C19" s="9" t="s">
-        <x:v>105</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="D19" s="4" t="s">
-        <x:v>64</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E19" s="8"/>
       <x:c r="F19" s="8"/>
       <x:c r="G19" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="H19" s="9"/>
     </x:row>
     <x:row r="20" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A20" s="4" t="s">
-        <x:v>64</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B20" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C20" s="9" t="s">
-        <x:v>32</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D20" s="4" t="s">
-        <x:v>70</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="E20" s="8"/>
       <x:c r="F20" s="8"/>
       <x:c r="G20" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="H20" s="9"/>
     </x:row>
     <x:row r="21" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A21" s="4" t="s">
-        <x:v>70</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B21" s="13" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C21" s="9" t="s">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D21" s="4" t="s">
-        <x:v>61</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E21" s="8"/>
       <x:c r="F21" s="8"/>
       <x:c r="G21" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="H21" s="9"/>
     </x:row>
     <x:row r="22" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A22" s="4" t="s">
-        <x:v>61</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B22" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C22" s="9" t="s">
-        <x:v>49</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D22" s="4" t="s">
-        <x:v>59</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E22" s="8"/>
       <x:c r="F22" s="8"/>
       <x:c r="G22" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="H22" s="9"/>
     </x:row>
     <x:row r="23" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A23" s="4" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B23" s="12" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C23" s="9" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="B23" s="12" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C23" s="9" t="s">
-        <x:v>31</x:v>
-      </x:c>
       <x:c r="D23" s="4" t="s">
-        <x:v>79</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E23" s="8"/>
       <x:c r="F23" s="8"/>
       <x:c r="G23" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="H23" s="9"/>
     </x:row>
     <x:row r="24" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A24" s="4" t="s">
-        <x:v>79</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B24" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C24" s="9" t="s">
-        <x:v>34</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D24" s="4" t="s">
-        <x:v>68</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E24" s="8"/>
       <x:c r="F24" s="8"/>
       <x:c r="G24" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="H24" s="9"/>
     </x:row>
     <x:row r="25" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A25" s="4" t="s">
-        <x:v>68</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B25" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C25" s="9" t="s">
-        <x:v>35</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D25" s="4" t="s">
-        <x:v>74</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E25" s="8"/>
       <x:c r="F25" s="8"/>
       <x:c r="G25" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="H25" s="9"/>
     </x:row>
     <x:row r="26" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A26" s="4" t="s">
-        <x:v>74</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B26" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C26" s="10" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D26" s="4" t="s">
-        <x:v>78</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="E26" s="10"/>
       <x:c r="F26" s="10"/>
       <x:c r="G26" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="H26" s="10"/>
     </x:row>
     <x:row r="27" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A27" s="4" t="s">
-        <x:v>78</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B27" s="13" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C27" s="10" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D27" s="4" t="s">
-        <x:v>76</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="E27" s="10"/>
       <x:c r="F27" s="10"/>
       <x:c r="G27" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="H27" s="10"/>
     </x:row>
     <x:row r="28" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A28" s="4" t="s">
-        <x:v>76</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B28" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C28" s="10" t="s">
-        <x:v>11</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D28" s="4" t="s">
-        <x:v>73</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E28" s="10"/>
       <x:c r="F28" s="10"/>
       <x:c r="G28" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="H28" s="10"/>
     </x:row>
     <x:row r="29" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A29" s="4" t="s">
-        <x:v>73</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B29" s="13" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C29" s="10" t="s">
-        <x:v>20</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D29" s="4" t="s">
-        <x:v>75</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="E29" s="6"/>
       <x:c r="F29" s="10"/>
       <x:c r="G29" s="6" t="s">
-        <x:v>5</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H29" s="10"/>
     </x:row>
     <x:row r="30" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A30" s="4" t="s">
-        <x:v>75</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B30" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C30" s="10" t="s">
-        <x:v>109</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="D30" s="4" t="s">
-        <x:v>66</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E30" s="10"/>
       <x:c r="F30" s="10"/>
       <x:c r="G30" s="6" t="s">
-        <x:v>5</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H30" s="10"/>
     </x:row>
     <x:row r="31" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A31" s="4" t="s">
-        <x:v>66</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B31" s="13" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C31" s="10" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D31" s="4" t="s">
-        <x:v>72</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E31" s="4"/>
       <x:c r="F31" s="10"/>
       <x:c r="G31" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="H31" s="10"/>
     </x:row>
     <x:row r="32" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A32" s="4" t="s">
-        <x:v>72</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B32" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C32" s="11" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D32" s="4" t="s">
-        <x:v>77</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E32" s="11"/>
       <x:c r="F32" s="11"/>
       <x:c r="G32" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="H32" s="11"/>
     </x:row>
     <x:row r="33" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A33" s="4" t="s">
-        <x:v>77</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B33" s="13" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C33" s="11" t="s">
-        <x:v>39</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D33" s="4" t="s">
-        <x:v>62</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E33" s="11"/>
       <x:c r="F33" s="11"/>
       <x:c r="G33" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="H33" s="11"/>
     </x:row>
     <x:row r="34" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A34" s="4" t="s">
-        <x:v>62</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B34" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C34" s="11" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D34" s="4" t="s">
-        <x:v>63</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E34" s="11"/>
       <x:c r="F34" s="11"/>
       <x:c r="G34" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="H34" s="11"/>
     </x:row>
     <x:row r="35" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A35" s="4" t="s">
-        <x:v>63</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B35" s="13" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C35" s="11" t="s">
-        <x:v>55</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D35" s="4" t="s">
-        <x:v>84</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="E35" s="11"/>
       <x:c r="F35" s="17"/>
       <x:c r="G35" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="H35" s="11"/>
     </x:row>
     <x:row r="36" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A36" s="4" t="s">
-        <x:v>84</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B36" s="13" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C36" t="s">
-        <x:v>26</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D36" s="4" t="s">
-        <x:v>65</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="G36" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A37" s="4" t="s">
-        <x:v>65</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B37" s="13" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C37" t="s">
-        <x:v>38</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D37" s="4" t="s">
-        <x:v>83</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="G37" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A38" s="4" t="s">
-        <x:v>83</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B38" s="13" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C38" t="s">
-        <x:v>47</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D38" s="4" t="s">
-        <x:v>88</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="G38" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A39" s="4" t="s">
-        <x:v>88</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B39" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C39" t="s">
-        <x:v>101</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="D39" s="4" t="s">
-        <x:v>89</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="G39" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A40" s="4" t="s">
-        <x:v>89</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B40" s="13" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C40" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D40" s="4" t="s">
-        <x:v>67</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="G40" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A41" s="4" t="s">
-        <x:v>67</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B41" s="13" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C41" t="s">
-        <x:v>50</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D41" s="4" t="s">
-        <x:v>82</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="G41" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A42" s="4" t="s">
-        <x:v>82</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B42" s="13" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C42" t="s">
-        <x:v>48</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D42" s="4" t="s">
-        <x:v>71</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="G42" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A43" s="4" t="s">
-        <x:v>71</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B43" s="13" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C43" t="s">
-        <x:v>37</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D43" s="4" t="s">
-        <x:v>81</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="G43" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A44" s="4" t="s">
-        <x:v>81</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B44" s="12" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C44" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C44" t="s">
-        <x:v>33</x:v>
-      </x:c>
       <x:c r="D44" s="4" t="s">
-        <x:v>80</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="G44" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A45" s="4" t="s">
-        <x:v>80</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B45" s="13" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C45" t="s">
-        <x:v>22</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D45" s="4" t="s">
-        <x:v>87</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="G45" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A46" s="4" t="s">
-        <x:v>87</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B46" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C46" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="D46" s="4" t="s">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="D46" s="4" t="s">
-        <x:v>85</x:v>
-      </x:c>
       <x:c r="G46" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A47" s="4" t="s">
-        <x:v>85</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C47" t="s">
-        <x:v>36</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D47" s="4"/>
       <x:c r="G47" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A48" s="18" t="s">
-        <x:v>117</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B48" s="13" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C48" t="s">
-        <x:v>2</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D48" s="18" t="s">
-        <x:v>132</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="G48" s="6" t="s">
-        <x:v>5</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A49" s="18" t="s">
-        <x:v>132</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B49" s="13" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C49" t="s">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D49" s="18" t="s">
-        <x:v>135</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="G49" s="6" t="s">
-        <x:v>5</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A50" s="18" t="s">
-        <x:v>135</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="B50" s="13" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C50" t="s">
-        <x:v>114</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D50" s="18" t="s">
-        <x:v>131</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="G50" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A51" s="18" t="s">
-        <x:v>131</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="B51" s="13" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C51" t="s">
-        <x:v>0</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D51" s="18" t="s">
-        <x:v>133</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="G51" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A52" s="18" t="s">
-        <x:v>133</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="B52" s="13" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C52" t="s">
-        <x:v>115</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D52" s="18" t="s">
-        <x:v>137</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="G52" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A53" s="18" t="s">
-        <x:v>137</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="B53" s="13" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C53" t="s">
-        <x:v>145</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D53" s="18" t="s">
-        <x:v>136</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="G53" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A54" s="18" t="s">
-        <x:v>136</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="B54" s="13" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C54" t="s">
-        <x:v>118</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D54" s="18" t="s">
-        <x:v>138</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="G54" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A55" s="18" t="s">
-        <x:v>138</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B55" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C55" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D55" s="18" t="s">
-        <x:v>140</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="G55" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A56" s="18" t="s">
-        <x:v>140</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="B56" s="13" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C56" t="s">
-        <x:v>146</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D56" s="18" t="s">
-        <x:v>141</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="G56" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A57" s="18" t="s">
-        <x:v>141</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="B57" s="13" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C57" t="s">
-        <x:v>113</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D57" s="18" t="s">
         <x:v>139</x:v>
       </x:c>
       <x:c r="G57" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:7" ht="15.75" customHeight="1">
@@ -2585,232 +2591,246 @@
         <x:v>139</x:v>
       </x:c>
       <x:c r="B58" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C58" t="s">
-        <x:v>1</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D58" s="18" t="s">
-        <x:v>134</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="G58" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A59" s="18" t="s">
-        <x:v>134</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="C59" t="s">
-        <x:v>14</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G59" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A60" s="18" t="s">
-        <x:v>130</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B60" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C60" t="s">
-        <x:v>143</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D60" s="18" t="s">
-        <x:v>119</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="G60" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A61" s="18" t="s">
-        <x:v>119</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="B61" s="13" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C61" t="s">
-        <x:v>144</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D61" s="18" t="s">
-        <x:v>121</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="G61" s="4" t="s">
-        <x:v>149</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A62" s="18" t="s">
-        <x:v>121</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B62" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C62" t="s">
-        <x:v>142</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D62" s="18" t="s">
-        <x:v>122</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="G62" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A63" s="18" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="B63" s="13" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C63" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D63" s="18" t="s">
         <x:v>122</x:v>
       </x:c>
-      <x:c r="B63" s="13" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C63" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="D63" s="18" t="s">
-        <x:v>123</x:v>
-      </x:c>
       <x:c r="G63" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A64" s="18" t="s">
-        <x:v>123</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B64" s="13" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C64" t="s">
-        <x:v>24</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D64" s="18" t="s">
-        <x:v>128</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="G64" s="4" t="s">
-        <x:v>13</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A65" s="18" t="s">
-        <x:v>128</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B65" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C65" t="s">
-        <x:v>116</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D65" s="18" t="s">
-        <x:v>125</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="G65" s="4" t="s">
-        <x:v>13</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A66" s="18" t="s">
-        <x:v>125</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B66" s="13" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C66" t="s">
-        <x:v>110</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D66" s="18" t="s">
-        <x:v>126</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="G66" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A67" s="18" t="s">
-        <x:v>126</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B67" s="13" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C67" t="s">
-        <x:v>111</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D67" s="18" t="s">
-        <x:v>127</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="G67" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A68" s="18" t="s">
-        <x:v>127</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B68" s="13" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C68" t="s">
-        <x:v>148</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D68" s="18" t="s">
-        <x:v>120</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="G68" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A69" s="18" t="s">
-        <x:v>120</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B69" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C69" t="s">
-        <x:v>7</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D69" s="18" t="s">
-        <x:v>124</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="G69" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A70" s="18" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="B70" s="13" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C70" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D70" s="18" t="s">
         <x:v>124</x:v>
       </x:c>
-      <x:c r="B70" s="13" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C70" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="D70" s="18" t="s">
-        <x:v>129</x:v>
-      </x:c>
       <x:c r="G70" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A71" s="18" t="s">
-        <x:v>129</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B71" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C71" t="s">
-        <x:v>6</x:v>
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D71" s="18" t="s">
+        <x:v>142</x:v>
       </x:c>
       <x:c r="G71" s="4" t="s">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="72" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A72" s="4"/>
+        <x:v>54</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A72" s="18" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="B72" s="12" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C72" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G72" s="4" t="s">
+        <x:v>54</x:v>
+      </x:c>
     </x:row>
     <x:row r="73" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A73" s="4"/>

--- a/JsonConverter/ExcelFiles/MainDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/MainDialogue.xlsx
@@ -4,7 +4,7 @@
   <x:fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="20610" windowHeight="11190"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="23760" windowHeight="9180"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="DNTable_Weapon" sheetId="1" r:id="rId4"/>
@@ -14,198 +14,330 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="152">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="256">
+  <x:si>
+    <x:t>여기요</x:t>
+  </x:si>
+  <x:si>
+    <x:t>거기 너! 맥주 한잔 줘</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아! 물론이죠, 곧 나갑니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아- 알겠습니다...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그러니 너무 많이 넣으면, 손님이 빨리 취해버리게 될거야 잘 생각해서 넣어.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이렇게 버튼을 누르면, 재료를 섞은 뒤에 기기가 자동으로 얼음을 추가시켜주지.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>나한테 다시 슈가러쉬나 피아노 맨을 만들어주면 더는 귀찮게 굴지 않을게.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어떤걸로 드릴까요, 어, 성함이..?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이제 좀 낫나요?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>네? 아, 미안해요. 너무 편안해서 쓰고 있다는걸 자주 까먹어요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>길에게 다시 슈가러쉬나 피아노 맨을 주자고. 이번엔 정확히 섞어보자.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>제가 원하는 음료는 아닌것 같아요...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(게다가 포어에게 중성화 수술을 시켜주느라 지갑 속 마지막 동전 하나까지 다써버렸지. 월세를 한번만 더 미뤘다간 쫒겨날거야...)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_1_2_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>제길, 질. 정신차려. 손님은 맥주를 원해! 맥.주!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_1_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_1_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_1_004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_1_005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_1_009</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_1_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_1_006</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어떤걸로 드릴까요, 세이?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>길리안, 나 공식적인 BTC 교육을 받고 여기 온 거거든?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Texture2D/Character_Gillian_Smile</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(이틀 전에는 이곳이 폐쇄될 위기에 처했다는 것까지 알게됐지)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Texture2D/Character_Gillian_Basic</x:t>
+  </x:si>
+  <x:si>
+    <x:t>음, 매월 30일에 월세를 내는게 엄청 스트레스거든, 그리고-</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대체 언제쯤이면 네가 존같이 생겼다는 걸 인정할거야, 길?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(삶의 기반도 흔들리게 됐는데, 정신까지 나가버릴 지경이라고.)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>측면에 있는 얼음과 숙성 버튼 중 필요한 걸 선택하면 돼.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Texture2D/Character_Gillian_Dismay</x:t>
+  </x:si>
+  <x:si>
+    <x:t>발키리 군단 소속이라고 하셨죠? 그럼 폭동 진압 같은 일들을 하시나요?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>다 끝나면 서빙하기 버튼을 눌러서 손님에게 전해주면 돼. 그게 다야.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>너는 어그멘티드 아이의 편집장이자 소유주인 도노반 D.도슨님과 대화를 나누고 있는 거라고.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>맥주를 원하는군. 덩치가 꽤 커보이는데.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>응?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그래.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>질!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>음료는 "온더록스" 혹은 숙성을 요구하는지 확인해야 해.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>내가 너를 쥴스라고 부를 수 있게 허락해줄 때 쯤.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>내가 말했던 것들을 잘 떠올리면서 만들어!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그럼 문제없이 만들어 낼 수 있겠네!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>괜찮아? 생각이 다른데 가있는 것 같은데.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>character_gillian_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>...정말 오늘 일할 수 있는 거 맞아?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SelectionDialogueIdList</x:t>
+  </x:si>
+  <x:si>
+    <x:t>character_jill_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>우선 슈가 러쉬부터 시작해보자.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SelectionNameList</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아, 그래! 잊기 전에 하나만 더!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>술을 섞고 삶을 바꿔줄 시간이군.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>별거 아니야 조금 생각할게 있어서.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이건...내가 원하던게 아니야.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>글쎄. 뭣 좀 사러 밖에 나갔...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>음...작고, 달콤하고, 차가운..문블라스트가 좋겠네요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_1_2_000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_1_000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_1_2_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_1_011</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_1_007</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_1_008</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(참 흥미로운 손님으로 하루를 시작하게 됐는걸.)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화이트 나이츠 손님은 그리 많지 않은데 말이죠, 사실 제대로 기억나는건 한명 뿐이지만요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>안녕하세-...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>칵테일 조합법에 있는 탐색 막대를 이용해 레시피를 확인해 봐. 왼쪽 상단에 표시될거야.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(아, 그러고 보니 내 아파트 방바닥에 맥주 캔들이 엄청나게 널브러져 있었지. 또...)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"우리는 가장 어두운 시기에 타오르는 빛이자, 범죄의 희생양들을 도와주는 자!"</x:t>
+  </x:si>
+  <x:si>
+    <x:t>저 헬멧은 벗어주시지 않을래요?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>길이 슈가 러쉬나 피아노 맨을 달라는군. 만약에 망쳤다면, 재시도 버튼을 눌러서 다시 하면 되겠지.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>리셋 버튼은 아무 때나 누를 수 있어. 셰이커가 움직이고 있을 때도 말이지. 부담 가지지 말고 원할 때 눌러.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>혹시 용어를 모를 수도 있으니 하는 말인데, "온더록스"는 "얼음"버튼을 눌러서 얼음을 넣어야 한다는 걸 의미해</x:t>
+  </x:si>
+  <x:si>
+    <x:t>또 맛이나 종류 기준으로 검색할 수 있어. "달콤한" 술이나 "남성적인" 술을 정렬시켜 볼 수 있다는 거야.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아아 좋아, 딱 제가 원했던 거예요. 감사합니다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>네가 피아노 맨을 만들 수 있을 정도 상태면, 나머지 과정은 생략할게. 그래도 웬만하면 잠깐참고 나랑 어울려줘, 괜찮지?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오른쪽 가운데에 있는 셰이커에 재료를 원하는 양만큼 클릭해서 넣어.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>했어. 너, 역시 딴 생각에 빠져 있는 것 같아. 그것도 아주 심하게.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그럼 우리 기초 과정부터 한번 다시 확인해 보자고. 괜찮지? 혹시 모르니까 말야</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그러고 난 다음, 섞기 버튼을 누르면 돼. 다시 눌러서 섞는 걸 멈출 수 있고.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아, 마지막 문장은 그렇게 신경쓰지 않아도 돼. 그냥 재밌는 뒷이야기 같은 거니까.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>카모트린은 음료의 알콜 도수를 결정하지. 맛은 변화시키지 못하지만, 알콜의 효과는 그대로 가지고 있어.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>애송아, 나는 남자야. 성인이라고. 내가 취할 생각이 없었다면, 대체 뭐하러 술집에 왔을거라고 생각하나?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>만약에 레시피에 "카모트린 추가 가능"이라고 써져 있다면, 아예 넣지 않을 수도 잔 끝까지 채워 넣을 수도 있다는 의미야.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>내가 이 동네에서 미팅이 있었다는 사실에 감사하도록 해, 이딴 개떡 같은 곳은 나같은 분의 존재 자체로도 도움이 될테니까.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>알았다, 알았어...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아, 안녕 존.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TexturePath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이제 설명 끝났어?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자 그럼 시작해볼까?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>보스는 어디 있어?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아! 어서 와, 질.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VoicePath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string[]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>무슨 말 했어?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>음..다른걸 만들어보자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>미안, 무슨 말 했어?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그래. 잡아둬서 미안.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그럼 이제 일을 시작하자고.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NextDialogueId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>내가 방금 한 말 들었어?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CharacterDataId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그래, 이제 막 끝났어.</x:t>
+  </x:si>
   <x:si>
     <x:t>자, 충분히 오래 놀아줬지?</x:t>
   </x:si>
   <x:si>
-    <x:t>미안, 무슨 말 했어?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그럼 이제 일을 시작하자고.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>내가 방금 한 말 들었어?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그래, 이제 막 끝났어.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>음..다른걸 만들어보자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NextDialogueId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CharacterDataId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그래. 잡아둬서 미안.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>...정말 오늘 일할 수 있는 거 맞아?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>내가 말했던 것들을 잘 떠올리면서 만들어!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그럼 문제없이 만들어 낼 수 있겠네!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SelectionDialogueIdList</x:t>
-  </x:si>
-  <x:si>
-    <x:t>character_gillian_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>괜찮아? 생각이 다른데 가있는 것 같은데.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>질!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>응?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그래.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>내가 너를 쥴스라고 부를 수 있게 허락해줄 때 쯤.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>음료는 "온더록스" 혹은 숙성을 요구하는지 확인해야 해.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(아, 그러고 보니 내 아파트 방바닥에 맥주 캔들이 엄청나게 널브러져 있었지. 또...)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>칵테일 조합법에 있는 탐색 막대를 이용해 레시피를 확인해 봐. 왼쪽 상단에 표시될거야.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>카모트린은 음료의 알콜 도수를 결정하지. 맛은 변화시키지 못하지만, 알콜의 효과는 그대로 가지고 있어.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>술을 섞고 삶을 바꿔줄 시간이군.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(게다가 포어에게 중성화 수술을 시켜주느라 지갑 속 마지막 동전 하나까지 다써버렸지. 월세를 한번만 더 미뤘다간 쫒겨날거야...)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그럼 우리 기초 과정부터 한번 다시 확인해 보자고. 괜찮지? 혹시 모르니까 말야</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그러고 난 다음, 섞기 버튼을 누르면 돼. 다시 눌러서 섞는 걸 멈출 수 있고.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아, 마지막 문장은 그렇게 신경쓰지 않아도 돼. 그냥 재밌는 뒷이야기 같은 거니까.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그러니 너무 많이 넣으면, 손님이 빨리 취해버리게 될거야 잘 생각해서 넣어.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이렇게 버튼을 누르면, 재료를 섞은 뒤에 기기가 자동으로 얼음을 추가시켜주지.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>나한테 다시 슈가러쉬나 피아노 맨을 만들어주면 더는 귀찮게 굴지 않을게.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>네가 피아노 맨을 만들 수 있을 정도 상태면, 나머지 과정은 생략할게. 그래도 웬만하면 잠깐참고 나랑 어울려줘, 괜찮지?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>길이 슈가 러쉬나 피아노 맨을 달라는군. 만약에 망쳤다면, 재시도 버튼을 눌러서 다시 하면 되겠지.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>만약에 레시피에 "카모트린 추가 가능"이라고 써져 있다면, 아예 넣지 않을 수도 잔 끝까지 채워 넣을 수도 있다는 의미야.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TexturePath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>알았다, 알았어...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>자 그럼 시작해볼까?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이제 설명 끝났어?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VoicePath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string[]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아! 어서 와, 질.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>보스는 어디 있어?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아, 안녕 존.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>무슨 말 했어?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>또 맛이나 종류 기준으로 검색할 수 있어. "달콤한" 술이나 "남성적인" 술을 정렬시켜 볼 수 있다는 거야.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>리셋 버튼은 아무 때나 누를 수 있어. 셰이커가 움직이고 있을 때도 말이지. 부담 가지지 말고 원할 때 눌러.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>혹시 용어를 모를 수도 있으니 하는 말인데, "온더록스"는 "얼음"버튼을 눌러서 얼음을 넣어야 한다는 걸 의미해</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(삶의 기반도 흔들리게 됐는데, 정신까지 나가버릴 지경이라고.)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>길리안, 나 공식적인 BTC 교육을 받고 여기 온 거거든?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Texture2D/Character_Gillian_Smile</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Texture2D/Character_Gillian_Basic</x:t>
-  </x:si>
-  <x:si>
-    <x:t>음, 매월 30일에 월세를 내는게 엄청 스트레스거든, 그리고-</x:t>
-  </x:si>
-  <x:si>
-    <x:t>측면에 있는 얼음과 숙성 버튼 중 필요한 걸 선택하면 돼.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Texture2D/Character_Gillian_Dismay</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대체 언제쯤이면 네가 존같이 생겼다는 걸 인정할거야, 길?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(이틀 전에는 이곳이 폐쇄될 위기에 처했다는 것까지 알게됐지)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>오른쪽 가운데에 있는 셰이커에 재료를 원하는 양만큼 클릭해서 넣어.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>했어. 너, 역시 딴 생각에 빠져 있는 것 같아. 그것도 아주 심하게.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>길에게 다시 슈가러쉬나 피아노 맨을 주자고. 이번엔 정확히 섞어보자.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>다 끝나면 서빙하기 버튼을 눌러서 손님에게 전해주면 돼. 그게 다야.</x:t>
+    <x:t>(어제는 1시간 동안 혼자 떠들었다고 오해받는 일이 생기질않나.)</x:t>
   </x:si>
   <x:si>
     <x:t>Texture2D/Character_Gillian_Surprise</x:t>
@@ -214,67 +346,94 @@
     <x:t>아, 만약 제조에 실패했다면 리셋 버튼을 눌러서 다시 시도할 수 있어.</x:t>
   </x:si>
   <x:si>
-    <x:t>(어제는 1시간 동안 혼자 떠들었다고 오해받는 일이 생기질않나.)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SelectionNameList</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이건...내가 원하던게 아니야.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>글쎄. 뭣 좀 사러 밖에 나갔...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>character_jill_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>우선 슈가 러쉬부터 시작해보자.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>별거 아니야 조금 생각할게 있어서.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아, 그래! 잊기 전에 하나만 더!</x:t>
+    <x:t>네, 맞아요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>character_donoban_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시끄러워.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>길...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>당연하지!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>좋은 저녁.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하아...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그게 뭔데?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_037</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_015</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_027</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_019</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_031</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_025</x:t>
   </x:si>
   <x:si>
     <x:t>dialogue_tutorial_1_1_012</x:t>
   </x:si>
   <x:si>
-    <x:t>dialogue_tutorial_1_1_037</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_031</x:t>
+    <x:t>dialogue_tutorial_1_1_030</x:t>
   </x:si>
   <x:si>
     <x:t>dialogue_tutorial_1_1_013</x:t>
   </x:si>
   <x:si>
-    <x:t>dialogue_tutorial_1_1_030</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_015</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_027</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_019</x:t>
+    <x:t>dialogue_tutorial_1_1_039</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_014</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_033</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_020</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_028</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_042</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_024</x:t>
   </x:si>
   <x:si>
     <x:t>dialogue_tutorial_1_1_016</x:t>
   </x:si>
   <x:si>
-    <x:t>dialogue_tutorial_1_1_014</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_033</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_039</x:t>
+    <x:t>dialogue_tutorial_1_1_018</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_022</x:t>
   </x:si>
   <x:si>
     <x:t>dialogue_tutorial_1_1_017</x:t>
@@ -283,27 +442,9 @@
     <x:t>dialogue_tutorial_1_1_021</x:t>
   </x:si>
   <x:si>
-    <x:t>dialogue_tutorial_1_1_028</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_018</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_042</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_022</x:t>
-  </x:si>
-  <x:si>
     <x:t>dialogue_tutorial_1_1_023</x:t>
   </x:si>
   <x:si>
-    <x:t>dialogue_tutorial_1_1_024</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_020</x:t>
-  </x:si>
-  <x:si>
     <x:t>dialogue_tutorial_1_1_026</x:t>
   </x:si>
   <x:si>
@@ -313,163 +454,334 @@
     <x:t>dialogue_tutorial_1_1_038</x:t>
   </x:si>
   <x:si>
+    <x:t>dialogue_tutorial_1_1_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_043</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_029</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_002</x:t>
+  </x:si>
+  <x:si>
     <x:t>dialogue_tutorial_1_1_034</x:t>
   </x:si>
   <x:si>
-    <x:t>dialogue_tutorial_1_1_029</x:t>
+    <x:t>dialogue_tutorial_1_1_011</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_040</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_041</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_007</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_036</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_003</x:t>
   </x:si>
   <x:si>
     <x:t>dialogue_tutorial_1_1_035</x:t>
   </x:si>
   <x:si>
-    <x:t>dialogue_tutorial_1_1_036</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_041</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_043</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_040</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_011</x:t>
-  </x:si>
-  <x:si>
     <x:t>dialogue_tutorial_1_1_008</x:t>
   </x:si>
   <x:si>
-    <x:t>dialogue_tutorial_1_1_004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_003</x:t>
-  </x:si>
-  <x:si>
     <x:t>dialogue_tutorial_1_1_010</x:t>
   </x:si>
   <x:si>
-    <x:t>dialogue_tutorial_1_1_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_007</x:t>
-  </x:si>
-  <x:si>
     <x:t>dialogue_tutorial_1_1_005</x:t>
   </x:si>
   <x:si>
+    <x:t>dialogue_tutorial_1_3_005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_3_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_2_000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_3_008</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_3_000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_3_004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_3_007</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_3_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_3_009</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_3_010</x:t>
+  </x:si>
+  <x:si>
     <x:t>dialogue_tutorial_1_1_006</x:t>
   </x:si>
   <x:si>
     <x:t>dialogue_tutorial_1_1_009</x:t>
   </x:si>
   <x:si>
-    <x:t>dialogue_tutorial_1_2_000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_3_007</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_3_008</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_3_005</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_3_004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_3_003</x:t>
-  </x:si>
-  <x:si>
     <x:t>dialogue_tutorial_1_3_011</x:t>
   </x:si>
   <x:si>
-    <x:t>dialogue_tutorial_1_3_000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_3_009</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_3_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_3_010</x:t>
-  </x:si>
-  <x:si>
     <x:t>dialogue_tutorial_1_3_001</x:t>
   </x:si>
   <x:si>
     <x:t>dialogue_tutorial_1_3_006</x:t>
   </x:si>
   <x:si>
+    <x:t>dialogue_tutorial_1_2_010</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_2_006</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_3_012</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_2_007</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_2_011</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_2_005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_2_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_2_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_2_008</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_2_009</x:t>
+  </x:si>
+  <x:si>
     <x:t>dialogue_tutorial_1_2_002</x:t>
   </x:si>
   <x:si>
-    <x:t>dialogue_tutorial_1_2_007</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_2_003</x:t>
-  </x:si>
-  <x:si>
     <x:t>dialogue_tutorial_1_2_004</x:t>
   </x:si>
   <x:si>
-    <x:t>dialogue_tutorial_1_2_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_2_008</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_2_009</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_2_005</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_2_010</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_2_011</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_2_006</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_3_012</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그게 뭔데?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시끄러워.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>길...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>좋은 저녁.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>당연하지!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하아...</x:t>
+    <x:t>dialogue_mainDialogue_2_3_000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>무슨말이죠?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_1_3_004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_1_3_005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_1_3_009</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어ᄄᅠᆫ 기사도 내 손길이 닿지 않고 발간될 수는 없지.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_1_3_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_1_3_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_1_3_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_1_3_007</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_1_3_008</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_1_3_000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_1_3_006</x:t>
+  </x:si>
+  <x:si>
+    <x:t>안녕하세요!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>여기있습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오히려, 그들의 뒷처리를 맡는 부대라고 할 수 있겠네요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>음...방금 그건 뭐였죠?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_3_013</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_3_006</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_3_008</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_3_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_3_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_3_004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_3_010</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_3_011</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_3_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_3_007</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_3_012</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_3_005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_3_009</x:t>
+  </x:si>
+  <x:si>
+    <x:t>음...이건 너무 길죠, 그냥 세이라고 불러주세요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_1_1_000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어떤 일을 하시나요, 손님? 성함이...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>으음.. 너 덕분에 잘 마시고 간다고.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_1_010</x:t>
+  </x:si>
+  <x:si>
+    <x:t>다시한번 세이에게 문블라스트를 만들어주자. 문블라스트!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_2_000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_1_2_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_1_2_005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_1_2_004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>미안해요. 아까 그건 우리의 복무신조 비슷한거에요. 매일 아침에 복창하는거죠.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>다시 해보자고. 맥주 한잔 줘. 보리 맥, 술 주. 맥.주.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>흐음...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"구조하라, 치료하라, 보호하라! 우리는 적습으로 고통받는 자들에게 위안을 주는 천사들일지어니!"</x:t>
+  </x:si>
+  <x:si>
+    <x:t>네, 고맙습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_1_1_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_1_1_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>폭동...? 아! 아뇨아뇨아뇨... 그건 아마 블리츠크리그 군단일거에요. 엄청 큰 갑옷 입은 부대 말하는 거죠?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아뇨, 그쪽이랑은 달라요. 음...정말 완전히 다른 부대라고요. 우리는 폭동 진압 같은 일은 전혀 하지 않아요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>음..뭐, 감사합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Texture2D/Character_Donoban_Smail</x:t>
+  </x:si>
+  <x:si>
+    <x:t>음료 맛있었어요.. 다음에 또 올게요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>여기요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그래, 이거 좋군. 정말 괜찮아. 아주 잘 했다 이거야.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_2_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_2_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_2_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_2_004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>발키리 군단 제 765부대 소속 특수 상등병, 세이 P 아사기리 대령했습니다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>character_sei_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>다시 만들어주셨으면 좋겠어요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"우리는 감시하고, 또한 수호한다!"</x:t>
+  </x:si>
+  <x:si>
+    <x:t>음...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Texture2D/Character_Donoban_Basic</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Texture2D/Character_Donoban_Dismay</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Texture2D/Character_Sai_Meka</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -666,7 +978,7 @@
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="19">
+  <x:cellXfs count="20">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
@@ -723,6 +1035,9 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -1382,7 +1697,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:R101"/>
+  <x:dimension ref="A1:R122"/>
   <x:sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1"/>
   <x:cols>
     <x:col min="1" max="1" width="26.36328125" customWidth="1"/>
@@ -1397,7 +1712,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>143</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1"/>
@@ -1409,68 +1724,68 @@
     </x:row>
     <x:row r="2" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s">
-        <x:v>149</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>150</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>150</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>150</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>150</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>150</x:v>
+        <x:v>117</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A3" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
-        <x:v>7</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C3" s="2" t="s">
-        <x:v>47</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D3" s="2" t="s">
-        <x:v>6</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="E3" s="2" t="s">
-        <x:v>67</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F3" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="G3" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="H3" s="2" t="s">
-        <x:v>41</x:v>
+        <x:v>94</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A4" s="4" t="s">
-        <x:v>105</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="B4" s="14" t="s">
-        <x:v>70</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C4" s="4" t="s">
-        <x:v>147</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D4" s="4" t="s">
-        <x:v>112</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="E4" s="12"/>
       <x:c r="F4" s="16"/>
@@ -1489,21 +1804,21 @@
     </x:row>
     <x:row r="5" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A5" s="4" t="s">
-        <x:v>112</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="B5" s="15" t="s">
-        <x:v>13</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C5" s="4" t="s">
-        <x:v>43</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D5" s="4" t="s">
-        <x:v>113</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="E5" s="4"/>
       <x:c r="F5" s="4"/>
       <x:c r="G5" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H5" s="4"/>
       <x:c r="I5" s="3"/>
@@ -1519,21 +1834,21 @@
     </x:row>
     <x:row r="6" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A6" s="4" t="s">
-        <x:v>113</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="B6" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C6" s="4" t="s">
-        <x:v>19</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D6" s="4" t="s">
-        <x:v>110</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="E6" s="4"/>
       <x:c r="F6" s="4"/>
       <x:c r="G6" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H6" s="4"/>
       <x:c r="I6" s="3"/>
@@ -1549,21 +1864,21 @@
     </x:row>
     <x:row r="7" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A7" s="4" t="s">
-        <x:v>110</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="B7" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C7" s="4" t="s">
-        <x:v>45</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D7" s="4" t="s">
-        <x:v>109</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="E7" s="4"/>
       <x:c r="F7" s="4"/>
       <x:c r="G7" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H7" s="4"/>
       <x:c r="I7" s="3"/>
@@ -1579,21 +1894,21 @@
     </x:row>
     <x:row r="8" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A8" s="4" t="s">
-        <x:v>109</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="B8" s="13" t="s">
-        <x:v>13</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C8" s="6" t="s">
-        <x:v>19</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D8" s="4" t="s">
-        <x:v>115</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="E8" s="6"/>
       <x:c r="F8" s="6"/>
       <x:c r="G8" s="6" t="s">
-        <x:v>57</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="H8" s="6"/>
       <x:c r="I8" s="3"/>
@@ -1609,21 +1924,21 @@
     </x:row>
     <x:row r="9" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A9" s="4" t="s">
-        <x:v>115</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="B9" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C9" s="6" t="s">
-        <x:v>58</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D9" s="4" t="s">
-        <x:v>116</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="E9" s="6"/>
       <x:c r="F9" s="6"/>
       <x:c r="G9" s="6" t="s">
-        <x:v>57</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="H9" s="4"/>
       <x:c r="I9" s="3"/>
@@ -1639,21 +1954,21 @@
     </x:row>
     <x:row r="10" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A10" s="4" t="s">
-        <x:v>116</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="B10" s="13" t="s">
-        <x:v>13</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C10" s="7" t="s">
-        <x:v>21</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D10" s="4" t="s">
-        <x:v>114</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="E10" s="4"/>
       <x:c r="F10" s="7"/>
       <x:c r="G10" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H10" s="7"/>
       <x:c r="I10" s="3"/>
@@ -1669,21 +1984,21 @@
     </x:row>
     <x:row r="11" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A11" s="4" t="s">
-        <x:v>114</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="B11" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C11" s="7" t="s">
-        <x:v>145</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D11" s="4" t="s">
-        <x:v>108</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="E11" s="7"/>
       <x:c r="F11" s="7"/>
       <x:c r="G11" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H11" s="7"/>
       <x:c r="I11" s="3"/>
@@ -1699,21 +2014,21 @@
     </x:row>
     <x:row r="12" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A12" s="4" t="s">
-        <x:v>108</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="B12" s="13" t="s">
-        <x:v>13</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C12" s="6" t="s">
-        <x:v>14</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D12" s="4" t="s">
-        <x:v>117</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="E12" s="6"/>
       <x:c r="F12" s="6"/>
       <x:c r="G12" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H12" s="6"/>
       <x:c r="I12" s="3"/>
@@ -1729,21 +2044,21 @@
     </x:row>
     <x:row r="13" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A13" s="4" t="s">
-        <x:v>117</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="B13" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C13" s="4" t="s">
-        <x:v>44</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D13" s="4" t="s">
-        <x:v>111</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="E13" s="4"/>
       <x:c r="F13" s="4"/>
       <x:c r="G13" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H13" s="4"/>
       <x:c r="I13" s="3"/>
@@ -1759,21 +2074,21 @@
     </x:row>
     <x:row r="14" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A14" s="4" t="s">
-        <x:v>111</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="B14" s="13" t="s">
-        <x:v>13</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C14" s="7" t="s">
-        <x:v>69</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D14" s="4" t="s">
-        <x:v>107</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="E14" s="7"/>
       <x:c r="F14" s="7"/>
       <x:c r="G14" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H14" s="7"/>
       <x:c r="I14" s="3"/>
@@ -1789,21 +2104,21 @@
     </x:row>
     <x:row r="15" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A15" s="4" t="s">
-        <x:v>107</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="B15" s="13" t="s">
-        <x:v>13</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C15" s="7" t="s">
-        <x:v>3</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D15" s="4" t="s">
-        <x:v>74</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="E15" s="6"/>
       <x:c r="F15" s="7"/>
       <x:c r="G15" s="6" t="s">
-        <x:v>57</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="H15" s="7"/>
       <x:c r="I15" s="3"/>
@@ -1819,1127 +2134,1637 @@
     </x:row>
     <x:row r="16" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A16" s="4" t="s">
-        <x:v>74</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B16" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C16" s="8" t="s">
-        <x:v>46</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D16" s="4" t="s">
-        <x:v>77</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="E16" s="8"/>
       <x:c r="F16" s="8"/>
       <x:c r="G16" s="6" t="s">
-        <x:v>57</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="H16" s="8"/>
     </x:row>
     <x:row r="17" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A17" s="4" t="s">
-        <x:v>77</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="B17" s="13" t="s">
-        <x:v>13</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C17" s="9" t="s">
-        <x:v>61</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D17" s="4" t="s">
-        <x:v>84</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="E17" s="4"/>
       <x:c r="F17" s="8"/>
       <x:c r="G17" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H17" s="9"/>
     </x:row>
     <x:row r="18" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A18" s="4" t="s">
-        <x:v>84</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="B18" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C18" s="9" t="s">
-        <x:v>72</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D18" s="4" t="s">
-        <x:v>79</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="E18" s="8"/>
       <x:c r="F18" s="8"/>
       <x:c r="G18" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H18" s="9"/>
     </x:row>
     <x:row r="19" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A19" s="4" t="s">
-        <x:v>79</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B19" s="13" t="s">
-        <x:v>13</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C19" s="9" t="s">
-        <x:v>144</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="D19" s="4" t="s">
-        <x:v>83</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="E19" s="8"/>
       <x:c r="F19" s="8"/>
       <x:c r="G19" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H19" s="9"/>
     </x:row>
     <x:row r="20" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A20" s="4" t="s">
-        <x:v>83</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="B20" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C20" s="9" t="s">
-        <x:v>55</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D20" s="4" t="s">
-        <x:v>87</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="E20" s="8"/>
       <x:c r="F20" s="8"/>
       <x:c r="G20" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H20" s="9"/>
     </x:row>
     <x:row r="21" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A21" s="4" t="s">
-        <x:v>87</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B21" s="13" t="s">
-        <x:v>13</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C21" s="9" t="s">
-        <x:v>20</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D21" s="4" t="s">
-        <x:v>90</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="E21" s="8"/>
       <x:c r="F21" s="8"/>
       <x:c r="G21" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H21" s="9"/>
     </x:row>
     <x:row r="22" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A22" s="4" t="s">
-        <x:v>90</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="B22" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C22" s="9" t="s">
-        <x:v>66</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D22" s="4" t="s">
-        <x:v>82</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="E22" s="8"/>
       <x:c r="F22" s="8"/>
       <x:c r="G22" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H22" s="9"/>
     </x:row>
     <x:row r="23" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A23" s="4" t="s">
-        <x:v>82</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B23" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C23" s="9" t="s">
-        <x:v>59</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D23" s="4" t="s">
-        <x:v>95</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="E23" s="8"/>
       <x:c r="F23" s="8"/>
       <x:c r="G23" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H23" s="9"/>
     </x:row>
     <x:row r="24" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A24" s="4" t="s">
-        <x:v>95</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="B24" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C24" s="9" t="s">
-        <x:v>51</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D24" s="4" t="s">
-        <x:v>88</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="E24" s="8"/>
       <x:c r="F24" s="8"/>
       <x:c r="G24" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H24" s="9"/>
     </x:row>
     <x:row r="25" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A25" s="4" t="s">
-        <x:v>88</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="B25" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C25" s="9" t="s">
-        <x:v>27</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D25" s="4" t="s">
-        <x:v>92</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="E25" s="8"/>
       <x:c r="F25" s="8"/>
       <x:c r="G25" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H25" s="9"/>
     </x:row>
     <x:row r="26" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A26" s="4" t="s">
-        <x:v>92</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="B26" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C26" s="10" t="s">
-        <x:v>23</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D26" s="4" t="s">
-        <x:v>93</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="E26" s="10"/>
       <x:c r="F26" s="10"/>
       <x:c r="G26" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H26" s="10"/>
     </x:row>
     <x:row r="27" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A27" s="4" t="s">
-        <x:v>93</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="B27" s="13" t="s">
-        <x:v>13</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C27" s="10" t="s">
-        <x:v>15</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D27" s="4" t="s">
-        <x:v>94</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="E27" s="10"/>
       <x:c r="F27" s="10"/>
       <x:c r="G27" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H27" s="10"/>
     </x:row>
     <x:row r="28" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A28" s="4" t="s">
-        <x:v>94</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="B28" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C28" s="10" t="s">
-        <x:v>1</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D28" s="4" t="s">
-        <x:v>81</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="E28" s="10"/>
       <x:c r="F28" s="10"/>
       <x:c r="G28" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H28" s="10"/>
     </x:row>
     <x:row r="29" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A29" s="4" t="s">
-        <x:v>81</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B29" s="13" t="s">
-        <x:v>13</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C29" s="10" t="s">
-        <x:v>9</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D29" s="4" t="s">
-        <x:v>96</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="E29" s="6"/>
       <x:c r="F29" s="10"/>
       <x:c r="G29" s="6" t="s">
-        <x:v>57</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="H29" s="10"/>
     </x:row>
     <x:row r="30" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A30" s="4" t="s">
-        <x:v>96</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="B30" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C30" s="10" t="s">
-        <x:v>148</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D30" s="4" t="s">
-        <x:v>80</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="E30" s="10"/>
       <x:c r="F30" s="10"/>
       <x:c r="G30" s="6" t="s">
-        <x:v>57</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="H30" s="10"/>
     </x:row>
     <x:row r="31" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A31" s="4" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="B31" s="13" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C31" s="10" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="B31" s="13" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C31" s="10" t="s">
-        <x:v>28</x:v>
-      </x:c>
       <x:c r="D31" s="4" t="s">
-        <x:v>89</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="E31" s="4"/>
       <x:c r="F31" s="10"/>
       <x:c r="G31" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H31" s="10"/>
     </x:row>
     <x:row r="32" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A32" s="4" t="s">
-        <x:v>89</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="B32" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C32" s="11" t="s">
-        <x:v>19</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D32" s="4" t="s">
-        <x:v>100</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="E32" s="11"/>
       <x:c r="F32" s="11"/>
       <x:c r="G32" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H32" s="11"/>
     </x:row>
     <x:row r="33" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A33" s="4" t="s">
-        <x:v>100</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="B33" s="13" t="s">
-        <x:v>13</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C33" s="11" t="s">
-        <x:v>34</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D33" s="4" t="s">
-        <x:v>78</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="E33" s="11"/>
       <x:c r="F33" s="11"/>
       <x:c r="G33" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H33" s="11"/>
     </x:row>
     <x:row r="34" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A34" s="4" t="s">
-        <x:v>78</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="B34" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C34" s="11" t="s">
-        <x:v>19</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D34" s="4" t="s">
-        <x:v>76</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E34" s="11"/>
       <x:c r="F34" s="11"/>
       <x:c r="G34" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H34" s="11"/>
     </x:row>
     <x:row r="35" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A35" s="4" t="s">
-        <x:v>76</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B35" s="13" t="s">
-        <x:v>13</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C35" s="11" t="s">
-        <x:v>71</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D35" s="4" t="s">
-        <x:v>97</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="E35" s="11"/>
       <x:c r="F35" s="17"/>
       <x:c r="G35" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H35" s="11"/>
     </x:row>
     <x:row r="36" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A36" s="4" t="s">
-        <x:v>97</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="B36" s="13" t="s">
-        <x:v>13</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C36" t="s">
-        <x:v>24</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D36" s="4" t="s">
-        <x:v>85</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="G36" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A37" s="4" t="s">
-        <x:v>85</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B37" s="13" t="s">
-        <x:v>13</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C37" t="s">
-        <x:v>48</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D37" s="4" t="s">
-        <x:v>99</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="G37" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A38" s="4" t="s">
-        <x:v>99</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="B38" s="13" t="s">
-        <x:v>13</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C38" t="s">
-        <x:v>60</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D38" s="4" t="s">
-        <x:v>101</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="G38" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A39" s="4" t="s">
-        <x:v>101</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="B39" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C39" t="s">
-        <x:v>146</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="D39" s="4" t="s">
-        <x:v>102</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="G39" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A40" s="4" t="s">
-        <x:v>102</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="B40" s="13" t="s">
-        <x:v>13</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C40" t="s">
-        <x:v>29</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D40" s="4" t="s">
-        <x:v>75</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="G40" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A41" s="4" t="s">
-        <x:v>75</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B41" s="13" t="s">
-        <x:v>13</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C41" t="s">
-        <x:v>63</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D41" s="4" t="s">
-        <x:v>98</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="G41" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A42" s="4" t="s">
-        <x:v>98</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="B42" s="13" t="s">
-        <x:v>13</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C42" t="s">
-        <x:v>65</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="D42" s="4" t="s">
-        <x:v>86</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="G42" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A43" s="4" t="s">
-        <x:v>86</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B43" s="13" t="s">
-        <x:v>13</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C43" t="s">
-        <x:v>49</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D43" s="4" t="s">
-        <x:v>106</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="G43" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A44" s="4" t="s">
-        <x:v>106</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="B44" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C44" t="s">
-        <x:v>52</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D44" s="4" t="s">
-        <x:v>103</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="G44" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A45" s="4" t="s">
-        <x:v>103</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="B45" s="13" t="s">
-        <x:v>13</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C45" t="s">
-        <x:v>11</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D45" s="4" t="s">
-        <x:v>91</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="G45" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A46" s="4" t="s">
-        <x:v>91</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B46" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C46" t="s">
-        <x:v>151</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D46" s="4" t="s">
-        <x:v>104</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="G46" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A47" s="4" t="s">
-        <x:v>104</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="C47" t="s">
-        <x:v>35</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D47" s="4"/>
       <x:c r="G47" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A48" s="18" t="s">
-        <x:v>118</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="B48" s="13" t="s">
-        <x:v>13</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C48" t="s">
-        <x:v>68</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D48" s="18" t="s">
-        <x:v>135</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="G48" s="6" t="s">
-        <x:v>57</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A49" s="18" t="s">
-        <x:v>135</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="B49" s="13" t="s">
-        <x:v>13</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C49" t="s">
-        <x:v>5</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D49" s="18" t="s">
-        <x:v>131</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="G49" s="6" t="s">
-        <x:v>57</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A50" s="18" t="s">
-        <x:v>131</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="B50" s="13" t="s">
-        <x:v>13</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C50" t="s">
-        <x:v>22</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D50" s="18" t="s">
-        <x:v>133</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="G50" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A51" s="18" t="s">
-        <x:v>133</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="B51" s="13" t="s">
-        <x:v>13</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C51" t="s">
-        <x:v>56</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D51" s="18" t="s">
-        <x:v>134</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="G51" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A52" s="18" t="s">
-        <x:v>134</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="B52" s="13" t="s">
-        <x:v>13</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C52" t="s">
-        <x:v>50</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D52" s="18" t="s">
-        <x:v>138</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="G52" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A53" s="18" t="s">
-        <x:v>138</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="B53" s="13" t="s">
-        <x:v>13</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C53" t="s">
-        <x:v>32</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D53" s="18" t="s">
-        <x:v>141</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="G53" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A54" s="18" t="s">
-        <x:v>141</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="B54" s="13" t="s">
-        <x:v>13</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C54" t="s">
-        <x:v>30</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D54" s="18" t="s">
-        <x:v>132</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="G54" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A55" s="18" t="s">
-        <x:v>132</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="B55" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C55" t="s">
-        <x:v>19</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D55" s="18" t="s">
-        <x:v>136</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="G55" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A56" s="18" t="s">
-        <x:v>136</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="B56" s="13" t="s">
-        <x:v>13</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C56" t="s">
-        <x:v>33</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D56" s="18" t="s">
-        <x:v>137</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="G56" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A57" s="18" t="s">
-        <x:v>137</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="B57" s="13" t="s">
-        <x:v>13</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C57" t="s">
-        <x:v>10</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D57" s="18" t="s">
-        <x:v>139</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="G57" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A58" s="18" t="s">
-        <x:v>139</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="B58" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C58" t="s">
-        <x:v>38</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D58" s="18" t="s">
-        <x:v>140</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="G58" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A59" s="18" t="s">
-        <x:v>140</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="C59" t="s">
-        <x:v>62</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G59" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A60" s="18" t="s">
-        <x:v>125</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="B60" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C60" t="s">
-        <x:v>0</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D60" s="18" t="s">
-        <x:v>129</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="G60" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A61" s="18" t="s">
-        <x:v>129</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="B61" s="13" t="s">
-        <x:v>13</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C61" t="s">
-        <x:v>8</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D61" s="18" t="s">
-        <x:v>127</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="G61" s="4" t="s">
-        <x:v>53</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A62" s="18" t="s">
-        <x:v>127</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="B62" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C62" t="s">
-        <x:v>2</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D62" s="18" t="s">
-        <x:v>123</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="G62" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A63" s="18" t="s">
-        <x:v>123</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="B63" s="13" t="s">
-        <x:v>13</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C63" t="s">
-        <x:v>18</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D63" s="18" t="s">
-        <x:v>122</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="G63" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A64" s="18" t="s">
-        <x:v>122</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="B64" s="13" t="s">
-        <x:v>13</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C64" t="s">
-        <x:v>73</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D64" s="18" t="s">
-        <x:v>121</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="G64" s="4" t="s">
-        <x:v>64</x:v>
+        <x:v>108</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A65" s="18" t="s">
-        <x:v>121</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="B65" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C65" t="s">
-        <x:v>16</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D65" s="18" t="s">
-        <x:v>130</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="G65" s="4" t="s">
-        <x:v>64</x:v>
+        <x:v>108</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A66" s="18" t="s">
-        <x:v>130</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="B66" s="13" t="s">
-        <x:v>13</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C66" t="s">
-        <x:v>36</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D66" s="18" t="s">
-        <x:v>119</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="G66" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A67" s="18" t="s">
-        <x:v>119</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="B67" s="13" t="s">
-        <x:v>13</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C67" t="s">
-        <x:v>25</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D67" s="18" t="s">
-        <x:v>120</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="G67" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A68" s="18" t="s">
-        <x:v>120</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="B68" s="13" t="s">
-        <x:v>13</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C68" t="s">
-        <x:v>31</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D68" s="18" t="s">
-        <x:v>126</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="G68" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A69" s="18" t="s">
-        <x:v>126</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="B69" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C69" t="s">
-        <x:v>40</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D69" s="18" t="s">
-        <x:v>128</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="G69" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A70" s="18" t="s">
-        <x:v>128</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="B70" s="13" t="s">
-        <x:v>13</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C70" t="s">
-        <x:v>4</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D70" s="18" t="s">
-        <x:v>124</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="G70" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A71" s="18" t="s">
-        <x:v>124</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="B71" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C71" t="s">
-        <x:v>39</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D71" s="18" t="s">
-        <x:v>142</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="G71" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A72" s="18" t="s">
-        <x:v>142</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="B72" s="12" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C72" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="G72" s="4"/>
+    </x:row>
+    <x:row r="73" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A73" s="4" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="B73" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="C73" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G73" s="4" t="s">
+        <x:v>253</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A74" s="4" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="B74" s="19" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C74" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G74" s="4" t="s">
+        <x:v>253</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A75" s="4" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="B75" s="12"/>
+      <x:c r="C75" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="G75" s="4" t="s">
+        <x:v>253</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A76" s="4" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B76" s="12" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C76" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G76" s="4" t="s">
+        <x:v>253</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A77" s="4" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B77" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="C77" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="G77" s="4" t="s">
+        <x:v>254</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A78" s="4" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B78" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="C78" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="G78" s="4" t="s">
+        <x:v>254</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A79" s="4" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="B79" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="C79" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="G79" s="4" t="s">
+        <x:v>253</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A80" s="4" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="B80" s="12" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C80" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G80" s="4" t="s">
+        <x:v>253</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A81" s="4" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="B81" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="C81" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="G81" s="4" t="s">
+        <x:v>253</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A82" s="4" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="B82" s="12" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C82" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G82" s="4" t="s">
+        <x:v>253</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A83" s="4" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="B83" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="C83" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="G83" s="4" t="s">
+        <x:v>240</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A84" s="4" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="B84" s="12" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C84" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="G84" s="4" t="s">
+        <x:v>240</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A85" s="4" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="B85" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="C85" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="G85" s="4" t="s">
+        <x:v>240</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A86" s="4" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="B86" s="12" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C86" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="G86" s="4" t="s">
+        <x:v>240</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A87" s="4" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="B87" s="12" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C87" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="G87" s="4" t="s">
+        <x:v>240</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A88" s="4" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="B88" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="C88" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="G88" s="4" t="s">
+        <x:v>253</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A89" s="4" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="B89" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="C89" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="G89" s="4" t="s">
+        <x:v>253</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A90" s="4" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="B90" s="12" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C90" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="G90" s="4" t="s">
+        <x:v>253</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A91" s="4" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="B91" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="C91" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="G91" s="4" t="s">
+        <x:v>253</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A92" s="4" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B92" s="12" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="C92" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="G92" s="4" t="s">
+        <x:v>255</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A93" s="4" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B93" s="12" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C93" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="G93" s="4" t="s">
+        <x:v>255</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A94" s="4" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B94" s="12" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C94" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="G94" s="4" t="s">
+        <x:v>255</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A95" s="4" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B95" s="12" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C95" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="G95" s="4" t="s">
+        <x:v>255</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A96" s="4" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B96" s="12" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="C96" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="G96" s="4" t="s">
+        <x:v>255</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="A97" s="4" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B97" s="12" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="C97" t="s">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="A98" s="4" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B98" s="12" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C98" t="s">
+        <x:v>234</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="A99" s="4" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="B99" s="12" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C99" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="A100" s="4" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B100" s="12" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="C100" t="s">
+        <x:v>248</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="A101" s="4" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B101" s="12" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="C101" t="s">
+        <x:v>220</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="A102" s="4" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="B102" s="12" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C102" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="A103" s="4" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B103" s="12" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="C103" t="s">
+        <x:v>58</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="A104" s="4" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="B104" s="12" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C104" t="s">
+        <x:v>242</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="A105" s="4" t="s">
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="B105" s="12" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="C105" t="s">
+        <x:v>252</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="A106" s="4" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="B106" s="12" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="C106" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="A107" s="4" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="B107" s="12" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="C107" t="s">
+        <x:v>250</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="A108" s="4" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="B108" s="12" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C108" t="s">
+        <x:v>225</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="A109" s="4" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="B109" s="12" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="C109" t="s">
+        <x:v>76</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="A110" s="4" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="B110" s="12" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C110" t="s">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="A111" s="4" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="B111" s="12" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C111" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="A112" s="4" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="B112" s="12" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="C112" t="s">
+        <x:v>237</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="A113" s="4" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="B113" s="12" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C113" t="s">
+        <x:v>110</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="A114" s="4" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="B114" s="12" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="C114" t="s">
+        <x:v>238</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="A115" s="4" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="B115" s="12" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="C115" t="s">
+        <x:v>205</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="A116" s="4" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="B116" s="12" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C116" t="s">
+        <x:v>191</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="A117" s="4" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="B117" s="12" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="C117" t="s">
+        <x:v>233</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="A118" s="4" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="B118" s="12" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="C118" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="C72" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="G72" s="4" t="s">
-        <x:v>54</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="73" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A73" s="4"/>
-    </x:row>
-    <x:row r="74" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A74" s="4"/>
-    </x:row>
-    <x:row r="75" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A75" s="4"/>
-    </x:row>
-    <x:row r="76" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A76" s="4"/>
-    </x:row>
-    <x:row r="77" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A77" s="4"/>
-    </x:row>
-    <x:row r="78" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A78" s="4"/>
-    </x:row>
-    <x:row r="79" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A79" s="4"/>
-    </x:row>
-    <x:row r="80" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A80" s="4"/>
-    </x:row>
-    <x:row r="81" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A81" s="4"/>
-    </x:row>
-    <x:row r="82" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A82" s="4"/>
-    </x:row>
-    <x:row r="83" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A83" s="4"/>
-    </x:row>
-    <x:row r="84" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A84" s="4"/>
-    </x:row>
-    <x:row r="85" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A85" s="4"/>
-    </x:row>
-    <x:row r="86" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A86" s="4"/>
-    </x:row>
-    <x:row r="87" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A87" s="4"/>
-    </x:row>
-    <x:row r="88" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A88" s="4"/>
-    </x:row>
-    <x:row r="89" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A89" s="4"/>
-    </x:row>
-    <x:row r="90" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A90" s="4"/>
-    </x:row>
-    <x:row r="91" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A91" s="4"/>
-    </x:row>
-    <x:row r="92" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A92" s="4"/>
-    </x:row>
-    <x:row r="93" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A93" s="4"/>
-    </x:row>
-    <x:row r="94" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A94" s="4"/>
-    </x:row>
-    <x:row r="95" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A95" s="4"/>
-    </x:row>
-    <x:row r="96" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A96" s="4"/>
-    </x:row>
-    <x:row r="97" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A97" s="4"/>
-    </x:row>
-    <x:row r="98" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A98" s="4"/>
-    </x:row>
-    <x:row r="99" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A99" s="4"/>
-    </x:row>
-    <x:row r="100" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A100" s="4"/>
-    </x:row>
-    <x:row r="101" spans="1:1" ht="15.75" customHeight="1">
-      <x:c r="A101" s="12"/>
-    </x:row>
-    <x:row r="102" ht="15.75" customHeight="1"/>
-    <x:row r="103" ht="15.75" customHeight="1"/>
-    <x:row r="104" ht="15.75" customHeight="1"/>
-    <x:row r="105" ht="15.75" customHeight="1"/>
-    <x:row r="106" ht="15.75" customHeight="1"/>
-    <x:row r="107" ht="15.75" customHeight="1"/>
-    <x:row r="108" ht="15.75" customHeight="1"/>
-    <x:row r="109" ht="15.75" customHeight="1"/>
-    <x:row r="110" ht="15.75" customHeight="1"/>
-    <x:row r="111" ht="15.75" customHeight="1"/>
-    <x:row r="112" ht="15.75" customHeight="1"/>
-    <x:row r="113" ht="15.75" customHeight="1"/>
-    <x:row r="114" ht="15.75" customHeight="1"/>
-    <x:row r="115" ht="15.75" customHeight="1"/>
-    <x:row r="116" ht="15.75" customHeight="1"/>
-    <x:row r="117" ht="15.75" customHeight="1"/>
-    <x:row r="118" ht="15.75" customHeight="1"/>
-    <x:row r="119" ht="15.75" customHeight="1"/>
-    <x:row r="120" ht="15.75" customHeight="1"/>
-    <x:row r="121" ht="15.75" customHeight="1"/>
-    <x:row r="122" ht="15.75" customHeight="1"/>
+    </x:row>
+    <x:row r="119" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="A119" s="4" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="B119" s="12" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="C119" t="s">
+        <x:v>251</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="A120" s="4" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="B120" s="12" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C120" t="s">
+        <x:v>206</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="A121" s="4" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="B121" s="12" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="C121" t="s">
+        <x:v>230</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="A122" s="4" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="B122" s="12" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="C122" t="s">
+        <x:v>241</x:v>
+      </x:c>
+    </x:row>
     <x:row r="123" ht="15.75" customHeight="1"/>
     <x:row r="124" ht="15.75" customHeight="1"/>
     <x:row r="125" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/MainDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/MainDialogue.xlsx
@@ -4,7 +4,7 @@
   <x:fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="23760" windowHeight="9180"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="22575" windowHeight="13110"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="DNTable_Weapon" sheetId="1" r:id="rId4"/>
@@ -14,774 +14,783 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="256">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="598" uniqueCount="259">
+  <x:si>
+    <x:t>애송아, 나는 남자야. 성인이라고. 내가 취할 생각이 없었다면, 대체 뭐하러 술집에 왔을거라고 생각하나?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>카모트린은 음료의 알콜 도수를 결정하지. 맛은 변화시키지 못하지만, 알콜의 효과는 그대로 가지고 있어.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>술을 섞고 삶을 바꿔줄 시간이군.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아! 물론이죠, 곧 나갑니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>별거 아니야 조금 생각할게 있어서.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SelectionNameList</x:t>
+  </x:si>
+  <x:si>
+    <x:t>우선 슈가 러쉬부터 시작해보자.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>character_jill_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>글쎄. 뭣 좀 사러 밖에 나갔...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>저 헬멧은 벗어주시지 않을래요?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아, 그래! 잊기 전에 하나만 더!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이건...내가 원하던게 아니야.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>다시 만들어주셨으면 좋겠어요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>character_donoban_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_1_3_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>내가 너를 쥴스라고 부를 수 있게 허락해줄 때 쯤.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_1_3_008</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_1_3_004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_1_3_005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>음료는 "온더록스" 혹은 숙성을 요구하는지 확인해야 해.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오히려, 그들의 뒷처리를 맡는 부대라고 할 수 있겠네요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_1_3_009</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_1_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>음...작고, 달콤하고, 차가운..문블라스트가 좋겠네요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_1_3_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_1_2_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_1_009</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_1_3_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_1_008</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_1_3_007</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_3_000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Texture2D/Character_Sei_Basic</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_1_007</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_1_006</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_1_005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_1_000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>제길, 질. 정신차려. 손님은 맥주를 원해! 맥.주!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_3_013</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_1_2_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_1_011</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_1_004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_1_3_000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_1_3_006</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_1_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_1_2_000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_3_011</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_3_008</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_3_010</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_1_010</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_3_012</x:t>
+  </x:si>
+  <x:si>
+    <x:t>음...이건 너무 길죠, 그냥 세이라고 불러주세요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_2_000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_3_006</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_1_1_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_3_007</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_2_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>다시한번 세이에게 문블라스트를 만들어주자. 문블라스트!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Texture2D/Character_Sei_Smile</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_2_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_3_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_3_005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_3_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_3_009</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_3_004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_1_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_1_2_005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_1_2_004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_2_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_1_1_000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Texture2D/Character_Sei_Meka</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_3_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_2_004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_1_1_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_1_2_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그래, 이거 좋군. 정말 괜찮아. 아주 잘 했다 이거야.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어떤기사도 내 손길이 닿지 않고 발간될 수는 없지.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>응?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>질!</x:t>
+  </x:si>
   <x:si>
     <x:t>여기요</x:t>
   </x:si>
   <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그래.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(삶의 기반도 흔들리게 됐는데, 정신까지 나가버릴 지경이라고.)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>측면에 있는 얼음과 숙성 버튼 중 필요한 걸 선택하면 돼.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(이틀 전에는 이곳이 폐쇄될 위기에 처했다는 것까지 알게됐지)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Texture2D/Character_Gillian_Dismay</x:t>
+  </x:si>
+  <x:si>
+    <x:t>음, 매월 30일에 월세를 내는게 엄청 스트레스거든, 그리고-</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Texture2D/Character_Gillian_Smile</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Texture2D/Character_Donoban_Smile</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Texture2D/Character_Donoban_Dismay</x:t>
+  </x:si>
+  <x:si>
+    <x:t>길리안, 나 공식적인 BTC 교육을 받고 여기 온 거거든?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대체 언제쯤이면 네가 존같이 생겼다는 걸 인정할거야, 길?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Texture2D/Character_Donoban_Basic</x:t>
+  </x:si>
+  <x:si>
+    <x:t>다시 해보자고. 맥주 한잔 줘. 보리 맥, 술 주. 맥.주.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Texture2D/Character_Gillian_Basic</x:t>
+  </x:si>
+  <x:si>
+    <x:t>너는 어그멘티드 아이의 편집장이자 소유주인 도노반 D.도슨님과 대화를 나누고 있는 거라고.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(아, 그러고 보니 내 아파트 방바닥에 맥주 캔들이 엄청나게 널브러져 있었지. 또...)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>칵테일 조합법에 있는 탐색 막대를 이용해 레시피를 확인해 봐. 왼쪽 상단에 표시될거야.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화이트 나이츠 손님은 그리 많지 않은데 말이죠, 사실 제대로 기억나는건 한명 뿐이지만요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아, 만약 제조에 실패했다면 리셋 버튼을 눌러서 다시 시도할 수 있어.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>네? 아, 미안해요. 너무 편안해서 쓰고 있다는걸 자주 까먹어요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오른쪽 가운데에 있는 셰이커에 재료를 원하는 양만큼 클릭해서 넣어.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(어제는 1시간 동안 혼자 떠들었다고 오해받는 일이 생기질않나.)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>발키리 군단 소속이라고 하셨죠? 그럼 폭동 진압 같은 일들을 하시나요?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>길에게 다시 슈가러쉬나 피아노 맨을 주자고. 이번엔 정확히 섞어보자.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>했어. 너, 역시 딴 생각에 빠져 있는 것 같아. 그것도 아주 심하게.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>다 끝나면 서빙하기 버튼을 눌러서 손님에게 전해주면 돼. 그게 다야.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Texture2D/Character_Gillian_Surprise</x:t>
+  </x:si>
+  <x:si>
+    <x:t>길이 슈가 러쉬나 피아노 맨을 달라는군. 만약에 망쳤다면, 재시도 버튼을 눌러서 다시 하면 되겠지.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"구조하라, 치료하라, 보호하라! 우리는 적습으로 고통받는 자들에게 위안을 주는 천사들일지어니!"</x:t>
+  </x:si>
+  <x:si>
+    <x:t>내가 이 동네에서 미팅이 있었다는 사실에 감사하도록 해, 이딴 개떡 같은 곳은 나같은 분의 존재 자체로도 도움이 될테니까.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>만약에 레시피에 "카모트린 추가 가능"이라고 써져 있다면, 아예 넣지 않을 수도 잔 끝까지 채워 넣을 수도 있다는 의미야.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>네가 피아노 맨을 만들 수 있을 정도 상태면, 나머지 과정은 생략할게. 그래도 웬만하면 잠깐참고 나랑 어울려줘, 괜찮지?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그럼 우리 기초 과정부터 한번 다시 확인해 보자고. 괜찮지? 혹시 모르니까 말야</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"우리는 가장 어두운 시기에 타오르는 빛이자, 범죄의 희생양들을 도와주는 자!"</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그러고 난 다음, 섞기 버튼을 누르면 돼. 다시 눌러서 섞는 걸 멈출 수 있고.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아, 마지막 문장은 그렇게 신경쓰지 않아도 돼. 그냥 재밌는 뒷이야기 같은 거니까.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(게다가 포어에게 중성화 수술을 시켜주느라 지갑 속 마지막 동전 하나까지 다써버렸지. 월세를 한번만 더 미뤘다간 쫒겨날거야...)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>폭동...? 아! 아뇨아뇨아뇨... 그건 아마 블리츠크리그 군단일거에요. 엄청 큰 갑옷 입은 부대 말하는 거죠?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아뇨, 그쪽이랑은 달라요. 음...정말 완전히 다른 부대라고요. 우리는 폭동 진압 같은 일은 전혀 하지 않아요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>혹시 용어를 모를 수도 있으니 하는 말인데, "온더록스"는 "얼음"버튼을 눌러서 얼음을 넣어야 한다는 걸 의미해</x:t>
+  </x:si>
+  <x:si>
+    <x:t>또 맛이나 종류 기준으로 검색할 수 있어. "달콤한" 술이나 "남성적인" 술을 정렬시켜 볼 수 있다는 거야.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>리셋 버튼은 아무 때나 누를 수 있어. 셰이커가 움직이고 있을 때도 말이지. 부담 가지지 말고 원할 때 눌러.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>미안해요. 아까 그건 우리의 복무신조 비슷한거에요. 매일 아침에 복창하는거죠.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그러니 너무 많이 넣으면, 손님이 빨리 취해버리게 될거야 잘 생각해서 넣어.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이렇게 버튼을 누르면, 재료를 섞은 뒤에 기기가 자동으로 얼음을 추가시켜주지.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>나한테 다시 슈가러쉬나 피아노 맨을 만들어주면 더는 귀찮게 굴지 않을게.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>발키리 군단 제 765부대 소속 특수 상등병, 세이 P 아사기리 대령했습니다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그럼 이제 일을 시작하자고.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CharacterDataId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>미안, 무슨 말 했어?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어떤걸로 드릴까요, 세이?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그래. 잡아둬서 미안.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그래, 이제 막 끝났어.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>음..뭐, 감사합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>음...방금 그건 뭐였죠?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NextDialogueId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자, 충분히 오래 놀아줬지?</x:t>
+  </x:si>
+  <x:si>
     <x:t>거기 너! 맥주 한잔 줘</x:t>
   </x:si>
   <x:si>
-    <x:t>아! 물론이죠, 곧 나갑니다.</x:t>
+    <x:t>내가 방금 한 말 들었어?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>음..다른걸 만들어보자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>character_sei_1</x:t>
   </x:si>
   <x:si>
     <x:t>아- 알겠습니다...</x:t>
   </x:si>
   <x:si>
-    <x:t>그러니 너무 많이 넣으면, 손님이 빨리 취해버리게 될거야 잘 생각해서 넣어.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이렇게 버튼을 누르면, 재료를 섞은 뒤에 기기가 자동으로 얼음을 추가시켜주지.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>나한테 다시 슈가러쉬나 피아노 맨을 만들어주면 더는 귀찮게 굴지 않을게.</x:t>
+    <x:t>이제 좀 낫나요?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>안녕하세-...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이제 설명 끝났어?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VoicePath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>보스는 어디 있어?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>알았다, 알았어...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string[]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>네, 고맙습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>무슨 말 했어?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자 그럼 시작해볼까?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아! 어서 와, 질.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아, 안녕 존.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TexturePath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_019</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_012</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_037</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_028</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_042</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_027</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_033</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아아 좋아, 딱 제가 원했던 거예요. 감사합니다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_039</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(참 흥미로운 손님으로 하루를 시작하게 됐는걸.)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_020</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_015</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_014</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_024</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_031</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_030</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_022</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_038</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_021</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_013</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_029</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_032</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_016</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_011</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_034</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_017</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_007</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_3_000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_2_000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_3_008</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_036</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_3_004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_040</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_3_005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_023</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_018</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_008</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_043</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_3_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_035</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_2_010</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_010</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_3_009</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_009</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_3_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_041</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_3_007</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_2_005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_3_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_3_006</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_2_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_3_011</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_2_007</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_2_011</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_006</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_3_012</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Texture2D/Character_Sei_Sad</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_3_010</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_2_008</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_2_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_2_006</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_2_004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_2_009</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_2_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>여기요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시끄러워.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>당연하지!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>흐음...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>길...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>여기있습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>음...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그게 뭔데?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>안녕하세요!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>좋은 저녁.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하아...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>네, 맞아요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>무슨말이죠?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그럼 문제없이 만들어 낼 수 있겠네!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>으음.. 너 덕분에 잘 마시고 간다고.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>내가 말했던 것들을 잘 떠올리면서 만들어!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>character_gillian_01</x:t>
   </x:si>
   <x:si>
     <x:t>어떤걸로 드릴까요, 어, 성함이..?</x:t>
   </x:si>
   <x:si>
-    <x:t>이제 좀 낫나요?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>네? 아, 미안해요. 너무 편안해서 쓰고 있다는걸 자주 까먹어요.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>길에게 다시 슈가러쉬나 피아노 맨을 주자고. 이번엔 정확히 섞어보자.</x:t>
+    <x:t>SelectionDialogueIdList</x:t>
   </x:si>
   <x:si>
     <x:t>제가 원하는 음료는 아닌것 같아요...</x:t>
   </x:si>
   <x:si>
-    <x:t>(게다가 포어에게 중성화 수술을 시켜주느라 지갑 속 마지막 동전 하나까지 다써버렸지. 월세를 한번만 더 미뤘다간 쫒겨날거야...)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_1_2_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>제길, 질. 정신차려. 손님은 맥주를 원해! 맥.주!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_1_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_1_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_1_004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_1_005</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_1_009</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_1_003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_1_006</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어떤걸로 드릴까요, 세이?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>길리안, 나 공식적인 BTC 교육을 받고 여기 온 거거든?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Texture2D/Character_Gillian_Smile</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(이틀 전에는 이곳이 폐쇄될 위기에 처했다는 것까지 알게됐지)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Texture2D/Character_Gillian_Basic</x:t>
-  </x:si>
-  <x:si>
-    <x:t>음, 매월 30일에 월세를 내는게 엄청 스트레스거든, 그리고-</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대체 언제쯤이면 네가 존같이 생겼다는 걸 인정할거야, 길?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(삶의 기반도 흔들리게 됐는데, 정신까지 나가버릴 지경이라고.)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>측면에 있는 얼음과 숙성 버튼 중 필요한 걸 선택하면 돼.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Texture2D/Character_Gillian_Dismay</x:t>
-  </x:si>
-  <x:si>
-    <x:t>발키리 군단 소속이라고 하셨죠? 그럼 폭동 진압 같은 일들을 하시나요?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>다 끝나면 서빙하기 버튼을 눌러서 손님에게 전해주면 돼. 그게 다야.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>너는 어그멘티드 아이의 편집장이자 소유주인 도노반 D.도슨님과 대화를 나누고 있는 거라고.</x:t>
-  </x:si>
-  <x:si>
     <x:t>맥주를 원하는군. 덩치가 꽤 커보이는데.</x:t>
   </x:si>
   <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>응?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그래.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>질!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>음료는 "온더록스" 혹은 숙성을 요구하는지 확인해야 해.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>내가 너를 쥴스라고 부를 수 있게 허락해줄 때 쯤.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>내가 말했던 것들을 잘 떠올리면서 만들어!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그럼 문제없이 만들어 낼 수 있겠네!</x:t>
+    <x:t>"우리는 감시하고, 또한 수호한다!"</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어떤 일을 하시나요, 손님? 성함이...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>...정말 오늘 일할 수 있는 거 맞아?</x:t>
   </x:si>
   <x:si>
     <x:t>괜찮아? 생각이 다른데 가있는 것 같은데.</x:t>
   </x:si>
   <x:si>
-    <x:t>character_gillian_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>...정말 오늘 일할 수 있는 거 맞아?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SelectionDialogueIdList</x:t>
-  </x:si>
-  <x:si>
-    <x:t>character_jill_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>우선 슈가 러쉬부터 시작해보자.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SelectionNameList</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아, 그래! 잊기 전에 하나만 더!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>술을 섞고 삶을 바꿔줄 시간이군.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>별거 아니야 조금 생각할게 있어서.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이건...내가 원하던게 아니야.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>글쎄. 뭣 좀 사러 밖에 나갔...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>음...작고, 달콤하고, 차가운..문블라스트가 좋겠네요.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_1_2_000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_1_000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_1_2_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_1_011</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_1_007</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_1_008</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(참 흥미로운 손님으로 하루를 시작하게 됐는걸.)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>화이트 나이츠 손님은 그리 많지 않은데 말이죠, 사실 제대로 기억나는건 한명 뿐이지만요.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>안녕하세-...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>칵테일 조합법에 있는 탐색 막대를 이용해 레시피를 확인해 봐. 왼쪽 상단에 표시될거야.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(아, 그러고 보니 내 아파트 방바닥에 맥주 캔들이 엄청나게 널브러져 있었지. 또...)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"우리는 가장 어두운 시기에 타오르는 빛이자, 범죄의 희생양들을 도와주는 자!"</x:t>
-  </x:si>
-  <x:si>
-    <x:t>저 헬멧은 벗어주시지 않을래요?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>길이 슈가 러쉬나 피아노 맨을 달라는군. 만약에 망쳤다면, 재시도 버튼을 눌러서 다시 하면 되겠지.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>리셋 버튼은 아무 때나 누를 수 있어. 셰이커가 움직이고 있을 때도 말이지. 부담 가지지 말고 원할 때 눌러.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>혹시 용어를 모를 수도 있으니 하는 말인데, "온더록스"는 "얼음"버튼을 눌러서 얼음을 넣어야 한다는 걸 의미해</x:t>
-  </x:si>
-  <x:si>
-    <x:t>또 맛이나 종류 기준으로 검색할 수 있어. "달콤한" 술이나 "남성적인" 술을 정렬시켜 볼 수 있다는 거야.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아아 좋아, 딱 제가 원했던 거예요. 감사합니다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>네가 피아노 맨을 만들 수 있을 정도 상태면, 나머지 과정은 생략할게. 그래도 웬만하면 잠깐참고 나랑 어울려줘, 괜찮지?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>오른쪽 가운데에 있는 셰이커에 재료를 원하는 양만큼 클릭해서 넣어.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>했어. 너, 역시 딴 생각에 빠져 있는 것 같아. 그것도 아주 심하게.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그럼 우리 기초 과정부터 한번 다시 확인해 보자고. 괜찮지? 혹시 모르니까 말야</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그러고 난 다음, 섞기 버튼을 누르면 돼. 다시 눌러서 섞는 걸 멈출 수 있고.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아, 마지막 문장은 그렇게 신경쓰지 않아도 돼. 그냥 재밌는 뒷이야기 같은 거니까.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>카모트린은 음료의 알콜 도수를 결정하지. 맛은 변화시키지 못하지만, 알콜의 효과는 그대로 가지고 있어.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>애송아, 나는 남자야. 성인이라고. 내가 취할 생각이 없었다면, 대체 뭐하러 술집에 왔을거라고 생각하나?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>만약에 레시피에 "카모트린 추가 가능"이라고 써져 있다면, 아예 넣지 않을 수도 잔 끝까지 채워 넣을 수도 있다는 의미야.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>내가 이 동네에서 미팅이 있었다는 사실에 감사하도록 해, 이딴 개떡 같은 곳은 나같은 분의 존재 자체로도 도움이 될테니까.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>알았다, 알았어...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아, 안녕 존.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TexturePath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이제 설명 끝났어?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>자 그럼 시작해볼까?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>보스는 어디 있어?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아! 어서 와, 질.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VoicePath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string[]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>무슨 말 했어?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>음..다른걸 만들어보자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>미안, 무슨 말 했어?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그래. 잡아둬서 미안.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그럼 이제 일을 시작하자고.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NextDialogueId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>내가 방금 한 말 들었어?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CharacterDataId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그래, 이제 막 끝났어.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>자, 충분히 오래 놀아줬지?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(어제는 1시간 동안 혼자 떠들었다고 오해받는 일이 생기질않나.)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Texture2D/Character_Gillian_Surprise</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아, 만약 제조에 실패했다면 리셋 버튼을 눌러서 다시 시도할 수 있어.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>네, 맞아요.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>character_donoban_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시끄러워.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>길...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>당연하지!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>좋은 저녁.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하아...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그게 뭔데?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_037</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_015</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_027</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_019</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_031</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_012</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_030</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_013</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_039</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_014</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_033</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_020</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_028</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_042</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_024</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_016</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_018</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_022</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_017</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_021</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_023</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_032</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_038</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_043</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_029</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_034</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_011</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_040</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_041</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_007</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_036</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_035</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_008</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_010</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_005</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_3_005</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_3_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_2_000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_3_008</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_3_000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_3_004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_3_007</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_3_003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_3_009</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_3_010</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_006</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_009</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_3_011</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_3_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_3_006</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_2_010</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_2_006</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_3_012</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_2_007</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_2_011</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_2_005</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_2_003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_2_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_2_008</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_2_009</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_2_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_2_004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_3_000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>무슨말이죠?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_1_3_004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_1_3_005</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_1_3_009</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어ᄄᅠᆫ 기사도 내 손길이 닿지 않고 발간될 수는 없지.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_1_3_003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_1_3_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_1_3_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_1_3_007</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_1_3_008</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_1_3_000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_1_3_006</x:t>
-  </x:si>
-  <x:si>
-    <x:t>안녕하세요!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>여기있습니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>오히려, 그들의 뒷처리를 맡는 부대라고 할 수 있겠네요.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>음...방금 그건 뭐였죠?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_3_013</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_3_006</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_3_008</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_3_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_3_003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_3_004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_3_010</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_3_011</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_3_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_3_007</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_3_012</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_3_005</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_3_009</x:t>
-  </x:si>
-  <x:si>
-    <x:t>음...이건 너무 길죠, 그냥 세이라고 불러주세요.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_1_1_000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어떤 일을 하시나요, 손님? 성함이...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>으음.. 너 덕분에 잘 마시고 간다고.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_1_010</x:t>
-  </x:si>
-  <x:si>
-    <x:t>다시한번 세이에게 문블라스트를 만들어주자. 문블라스트!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_2_000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_1_2_003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_1_2_005</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_1_2_004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>미안해요. 아까 그건 우리의 복무신조 비슷한거에요. 매일 아침에 복창하는거죠.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>다시 해보자고. 맥주 한잔 줘. 보리 맥, 술 주. 맥.주.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>흐음...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"구조하라, 치료하라, 보호하라! 우리는 적습으로 고통받는 자들에게 위안을 주는 천사들일지어니!"</x:t>
-  </x:si>
-  <x:si>
-    <x:t>네, 고맙습니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_1_1_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_1_1_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>폭동...? 아! 아뇨아뇨아뇨... 그건 아마 블리츠크리그 군단일거에요. 엄청 큰 갑옷 입은 부대 말하는 거죠?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아뇨, 그쪽이랑은 달라요. 음...정말 완전히 다른 부대라고요. 우리는 폭동 진압 같은 일은 전혀 하지 않아요.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>음..뭐, 감사합니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Texture2D/Character_Donoban_Smail</x:t>
-  </x:si>
-  <x:si>
     <x:t>음료 맛있었어요.. 다음에 또 올게요.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>여기요.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그래, 이거 좋군. 정말 괜찮아. 아주 잘 했다 이거야.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_2_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_2_003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_2_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_2_004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>발키리 군단 제 765부대 소속 특수 상등병, 세이 P 아사기리 대령했습니다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>character_sei_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>다시 만들어주셨으면 좋겠어요.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"우리는 감시하고, 또한 수호한다!"</x:t>
-  </x:si>
-  <x:si>
-    <x:t>음...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Texture2D/Character_Donoban_Basic</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Texture2D/Character_Donoban_Dismay</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Texture2D/Character_Sai_Meka</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1712,7 +1721,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1"/>
@@ -1724,68 +1733,68 @@
     </x:row>
     <x:row r="2" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>230</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A3" s="2" t="s">
-        <x:v>36</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
-        <x:v>104</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C3" s="2" t="s">
-        <x:v>97</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="D3" s="2" t="s">
-        <x:v>102</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="E3" s="2" t="s">
-        <x:v>52</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F3" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="G3" s="2" t="s">
-        <x:v>89</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="H3" s="2" t="s">
-        <x:v>94</x:v>
+        <x:v>148</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A4" s="4" t="s">
-        <x:v>152</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="B4" s="14" t="s">
-        <x:v>50</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C4" s="4" t="s">
-        <x:v>118</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="D4" s="4" t="s">
-        <x:v>146</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="E4" s="12"/>
       <x:c r="F4" s="16"/>
@@ -1804,21 +1813,21 @@
     </x:row>
     <x:row r="5" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A5" s="4" t="s">
-        <x:v>146</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="B5" s="15" t="s">
-        <x:v>47</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="C5" s="4" t="s">
-        <x:v>93</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="D5" s="4" t="s">
-        <x:v>149</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="E5" s="4"/>
       <x:c r="F5" s="4"/>
       <x:c r="G5" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="H5" s="4"/>
       <x:c r="I5" s="3"/>
@@ -1834,21 +1843,21 @@
     </x:row>
     <x:row r="6" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A6" s="4" t="s">
-        <x:v>149</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="B6" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C6" s="4" t="s">
-        <x:v>40</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D6" s="4" t="s">
-        <x:v>158</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="E6" s="4"/>
       <x:c r="F6" s="4"/>
       <x:c r="G6" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="H6" s="4"/>
       <x:c r="I6" s="3"/>
@@ -1864,21 +1873,21 @@
     </x:row>
     <x:row r="7" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A7" s="4" t="s">
-        <x:v>158</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="B7" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C7" s="4" t="s">
-        <x:v>88</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="D7" s="4" t="s">
-        <x:v>155</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="E7" s="4"/>
       <x:c r="F7" s="4"/>
       <x:c r="G7" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="H7" s="4"/>
       <x:c r="I7" s="3"/>
@@ -1894,21 +1903,21 @@
     </x:row>
     <x:row r="8" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A8" s="4" t="s">
-        <x:v>155</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="B8" s="13" t="s">
-        <x:v>47</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="C8" s="6" t="s">
-        <x:v>40</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D8" s="4" t="s">
-        <x:v>162</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="E8" s="6"/>
       <x:c r="F8" s="6"/>
       <x:c r="G8" s="6" t="s">
-        <x:v>31</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="H8" s="6"/>
       <x:c r="I8" s="3"/>
@@ -1924,21 +1933,21 @@
     </x:row>
     <x:row r="9" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A9" s="4" t="s">
-        <x:v>162</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="B9" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C9" s="6" t="s">
-        <x:v>28</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D9" s="4" t="s">
-        <x:v>173</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="E9" s="6"/>
       <x:c r="F9" s="6"/>
       <x:c r="G9" s="6" t="s">
-        <x:v>31</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="H9" s="4"/>
       <x:c r="I9" s="3"/>
@@ -1954,21 +1963,21 @@
     </x:row>
     <x:row r="10" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A10" s="4" t="s">
-        <x:v>173</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="B10" s="13" t="s">
-        <x:v>47</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="C10" s="7" t="s">
-        <x:v>43</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D10" s="4" t="s">
-        <x:v>156</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="E10" s="4"/>
       <x:c r="F10" s="7"/>
       <x:c r="G10" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="H10" s="7"/>
       <x:c r="I10" s="3"/>
@@ -1984,21 +1993,21 @@
     </x:row>
     <x:row r="11" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A11" s="4" t="s">
-        <x:v>156</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="B11" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C11" s="7" t="s">
-        <x:v>113</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="D11" s="4" t="s">
-        <x:v>160</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="E11" s="7"/>
       <x:c r="F11" s="7"/>
       <x:c r="G11" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="H11" s="7"/>
       <x:c r="I11" s="3"/>
@@ -2014,21 +2023,21 @@
     </x:row>
     <x:row r="12" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A12" s="4" t="s">
-        <x:v>160</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="B12" s="13" t="s">
-        <x:v>47</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="C12" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="D12" s="4" t="s">
-        <x:v>174</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="E12" s="6"/>
       <x:c r="F12" s="6"/>
       <x:c r="G12" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="H12" s="6"/>
       <x:c r="I12" s="3"/>
@@ -2044,21 +2053,21 @@
     </x:row>
     <x:row r="13" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A13" s="4" t="s">
-        <x:v>174</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="B13" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C13" s="4" t="s">
-        <x:v>92</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="D13" s="4" t="s">
-        <x:v>161</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="E13" s="4"/>
       <x:c r="F13" s="4"/>
       <x:c r="G13" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="H13" s="4"/>
       <x:c r="I13" s="3"/>
@@ -2074,21 +2083,21 @@
     </x:row>
     <x:row r="14" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A14" s="4" t="s">
-        <x:v>161</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="B14" s="13" t="s">
-        <x:v>47</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="C14" s="7" t="s">
-        <x:v>57</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D14" s="4" t="s">
-        <x:v>151</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="E14" s="7"/>
       <x:c r="F14" s="7"/>
       <x:c r="G14" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="H14" s="7"/>
       <x:c r="I14" s="3"/>
@@ -2104,21 +2113,21 @@
     </x:row>
     <x:row r="15" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A15" s="4" t="s">
-        <x:v>151</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="B15" s="13" t="s">
-        <x:v>47</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="C15" s="7" t="s">
-        <x:v>103</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="D15" s="4" t="s">
-        <x:v>127</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="E15" s="6"/>
       <x:c r="F15" s="7"/>
       <x:c r="G15" s="6" t="s">
-        <x:v>31</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="H15" s="7"/>
       <x:c r="I15" s="3"/>
@@ -2134,881 +2143,881 @@
     </x:row>
     <x:row r="16" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A16" s="4" t="s">
-        <x:v>127</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="B16" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C16" s="8" t="s">
-        <x:v>96</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="D16" s="4" t="s">
-        <x:v>129</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="E16" s="8"/>
       <x:c r="F16" s="8"/>
       <x:c r="G16" s="6" t="s">
-        <x:v>31</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="H16" s="8"/>
     </x:row>
     <x:row r="17" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A17" s="4" t="s">
-        <x:v>129</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="B17" s="13" t="s">
-        <x:v>47</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="C17" s="9" t="s">
-        <x:v>79</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D17" s="4" t="s">
-        <x:v>131</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="E17" s="4"/>
       <x:c r="F17" s="8"/>
       <x:c r="G17" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="H17" s="9"/>
     </x:row>
     <x:row r="18" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A18" s="4" t="s">
-        <x:v>131</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="B18" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C18" s="9" t="s">
-        <x:v>55</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D18" s="4" t="s">
-        <x:v>122</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="E18" s="8"/>
       <x:c r="F18" s="8"/>
       <x:c r="G18" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="H18" s="9"/>
     </x:row>
     <x:row r="19" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A19" s="4" t="s">
-        <x:v>122</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="B19" s="13" t="s">
-        <x:v>47</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="C19" s="9" t="s">
-        <x:v>120</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="D19" s="4" t="s">
-        <x:v>137</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="E19" s="8"/>
       <x:c r="F19" s="8"/>
       <x:c r="G19" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="H19" s="9"/>
     </x:row>
     <x:row r="20" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A20" s="4" t="s">
-        <x:v>137</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="B20" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C20" s="9" t="s">
-        <x:v>27</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D20" s="4" t="s">
-        <x:v>140</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="E20" s="8"/>
       <x:c r="F20" s="8"/>
       <x:c r="G20" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="H20" s="9"/>
     </x:row>
     <x:row r="21" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A21" s="4" t="s">
-        <x:v>140</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="B21" s="13" t="s">
-        <x:v>47</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="C21" s="9" t="s">
-        <x:v>37</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D21" s="4" t="s">
-        <x:v>138</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="E21" s="8"/>
       <x:c r="F21" s="8"/>
       <x:c r="G21" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="H21" s="9"/>
     </x:row>
     <x:row r="22" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A22" s="4" t="s">
-        <x:v>138</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="B22" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C22" s="9" t="s">
-        <x:v>107</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D22" s="4" t="s">
-        <x:v>124</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="E22" s="8"/>
       <x:c r="F22" s="8"/>
       <x:c r="G22" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="H22" s="9"/>
     </x:row>
     <x:row r="23" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A23" s="4" t="s">
-        <x:v>124</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="B23" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C23" s="9" t="s">
-        <x:v>25</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D23" s="4" t="s">
-        <x:v>133</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="E23" s="8"/>
       <x:c r="F23" s="8"/>
       <x:c r="G23" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="H23" s="9"/>
     </x:row>
     <x:row r="24" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A24" s="4" t="s">
-        <x:v>133</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="B24" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C24" s="9" t="s">
-        <x:v>29</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D24" s="4" t="s">
-        <x:v>141</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="E24" s="8"/>
       <x:c r="F24" s="8"/>
       <x:c r="G24" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="H24" s="9"/>
     </x:row>
     <x:row r="25" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A25" s="4" t="s">
-        <x:v>141</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="B25" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C25" s="9" t="s">
-        <x:v>12</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D25" s="4" t="s">
-        <x:v>139</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="E25" s="8"/>
       <x:c r="F25" s="8"/>
       <x:c r="G25" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="H25" s="9"/>
     </x:row>
     <x:row r="26" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A26" s="4" t="s">
-        <x:v>139</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="B26" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C26" s="10" t="s">
-        <x:v>69</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D26" s="4" t="s">
-        <x:v>142</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="E26" s="10"/>
       <x:c r="F26" s="10"/>
       <x:c r="G26" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="H26" s="10"/>
     </x:row>
     <x:row r="27" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A27" s="4" t="s">
-        <x:v>142</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="B27" s="13" t="s">
-        <x:v>47</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="C27" s="10" t="s">
-        <x:v>41</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D27" s="4" t="s">
-        <x:v>136</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="E27" s="10"/>
       <x:c r="F27" s="10"/>
       <x:c r="G27" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="H27" s="10"/>
     </x:row>
     <x:row r="28" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A28" s="4" t="s">
-        <x:v>136</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="B28" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C28" s="10" t="s">
-        <x:v>99</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="D28" s="4" t="s">
-        <x:v>126</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="E28" s="10"/>
       <x:c r="F28" s="10"/>
       <x:c r="G28" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="H28" s="10"/>
     </x:row>
     <x:row r="29" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A29" s="4" t="s">
-        <x:v>126</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="B29" s="13" t="s">
-        <x:v>47</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="C29" s="10" t="s">
-        <x:v>48</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="D29" s="4" t="s">
-        <x:v>143</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="E29" s="6"/>
       <x:c r="F29" s="10"/>
       <x:c r="G29" s="6" t="s">
-        <x:v>31</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="H29" s="10"/>
     </x:row>
     <x:row r="30" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A30" s="4" t="s">
-        <x:v>143</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="B30" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C30" s="10" t="s">
-        <x:v>115</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="D30" s="4" t="s">
-        <x:v>123</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="E30" s="10"/>
       <x:c r="F30" s="10"/>
       <x:c r="G30" s="6" t="s">
-        <x:v>31</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="H30" s="10"/>
     </x:row>
     <x:row r="31" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A31" s="4" t="s">
-        <x:v>123</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="B31" s="13" t="s">
-        <x:v>47</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="C31" s="10" t="s">
-        <x:v>80</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="D31" s="4" t="s">
-        <x:v>134</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="E31" s="4"/>
       <x:c r="F31" s="10"/>
       <x:c r="G31" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="H31" s="10"/>
     </x:row>
     <x:row r="32" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A32" s="4" t="s">
-        <x:v>134</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="B32" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C32" s="11" t="s">
-        <x:v>40</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D32" s="4" t="s">
-        <x:v>148</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="E32" s="11"/>
       <x:c r="F32" s="11"/>
       <x:c r="G32" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="H32" s="11"/>
     </x:row>
     <x:row r="33" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A33" s="4" t="s">
-        <x:v>148</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="B33" s="13" t="s">
-        <x:v>47</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="C33" s="11" t="s">
-        <x:v>77</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D33" s="4" t="s">
-        <x:v>128</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="E33" s="11"/>
       <x:c r="F33" s="11"/>
       <x:c r="G33" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="H33" s="11"/>
     </x:row>
     <x:row r="34" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A34" s="4" t="s">
-        <x:v>128</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="B34" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C34" s="11" t="s">
-        <x:v>40</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D34" s="4" t="s">
-        <x:v>125</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="E34" s="11"/>
       <x:c r="F34" s="11"/>
       <x:c r="G34" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="H34" s="11"/>
     </x:row>
     <x:row r="35" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A35" s="4" t="s">
-        <x:v>125</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="B35" s="13" t="s">
-        <x:v>47</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="C35" s="11" t="s">
-        <x:v>51</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D35" s="4" t="s">
-        <x:v>144</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="E35" s="11"/>
       <x:c r="F35" s="17"/>
       <x:c r="G35" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="H35" s="11"/>
     </x:row>
     <x:row r="36" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A36" s="4" t="s">
-        <x:v>144</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="B36" s="13" t="s">
-        <x:v>47</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="C36" t="s">
-        <x:v>68</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D36" s="4" t="s">
-        <x:v>132</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="G36" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A37" s="4" t="s">
-        <x:v>132</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="B37" s="13" t="s">
-        <x:v>47</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="C37" t="s">
-        <x:v>75</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="D37" s="4" t="s">
-        <x:v>150</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="G37" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A38" s="4" t="s">
-        <x:v>150</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="B38" s="13" t="s">
-        <x:v>47</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="C38" t="s">
-        <x:v>78</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D38" s="4" t="s">
-        <x:v>159</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="G38" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A39" s="4" t="s">
-        <x:v>159</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="B39" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C39" t="s">
-        <x:v>114</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="D39" s="4" t="s">
-        <x:v>157</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="G39" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A40" s="4" t="s">
-        <x:v>157</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="B40" s="13" t="s">
-        <x:v>47</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="C40" t="s">
-        <x:v>81</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="D40" s="4" t="s">
-        <x:v>121</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="G40" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A41" s="4" t="s">
-        <x:v>121</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="B41" s="13" t="s">
-        <x:v>47</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="C41" t="s">
-        <x:v>33</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D41" s="4" t="s">
-        <x:v>145</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="G41" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A42" s="4" t="s">
-        <x:v>145</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="B42" s="13" t="s">
-        <x:v>47</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="C42" t="s">
-        <x:v>109</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D42" s="4" t="s">
-        <x:v>130</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="G42" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A43" s="4" t="s">
-        <x:v>130</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="B43" s="13" t="s">
-        <x:v>47</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="C43" t="s">
-        <x:v>73</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="D43" s="4" t="s">
-        <x:v>153</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="G43" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A44" s="4" t="s">
-        <x:v>153</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="B44" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C44" t="s">
-        <x:v>23</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D44" s="4" t="s">
-        <x:v>154</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="G44" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A45" s="4" t="s">
-        <x:v>154</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="B45" s="13" t="s">
-        <x:v>47</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="C45" t="s">
-        <x:v>45</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="D45" s="4" t="s">
-        <x:v>135</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="G45" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A46" s="4" t="s">
-        <x:v>135</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="B46" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C46" t="s">
-        <x:v>119</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="D46" s="4" t="s">
-        <x:v>147</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="G46" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A47" s="4" t="s">
-        <x:v>147</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="C47" t="s">
-        <x:v>72</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="D47" s="4"/>
       <x:c r="G47" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A48" s="18" t="s">
-        <x:v>165</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="B48" s="13" t="s">
-        <x:v>47</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="C48" t="s">
-        <x:v>56</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D48" s="18" t="s">
-        <x:v>185</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="G48" s="6" t="s">
-        <x:v>31</x:v>
+        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A49" s="18" t="s">
-        <x:v>185</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="B49" s="13" t="s">
-        <x:v>47</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="C49" t="s">
-        <x:v>98</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="D49" s="18" t="s">
-        <x:v>188</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="G49" s="6" t="s">
-        <x:v>31</x:v>
+        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A50" s="18" t="s">
-        <x:v>188</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="B50" s="13" t="s">
-        <x:v>47</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="C50" t="s">
-        <x:v>42</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D50" s="18" t="s">
-        <x:v>184</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="G50" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A51" s="18" t="s">
-        <x:v>184</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="B51" s="13" t="s">
-        <x:v>47</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="C51" t="s">
-        <x:v>30</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D51" s="18" t="s">
-        <x:v>189</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="G51" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A52" s="18" t="s">
-        <x:v>189</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="B52" s="13" t="s">
-        <x:v>47</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="C52" t="s">
-        <x:v>74</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="D52" s="18" t="s">
-        <x:v>183</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="G52" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A53" s="18" t="s">
-        <x:v>183</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="B53" s="13" t="s">
-        <x:v>47</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="C53" t="s">
-        <x:v>5</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="D53" s="18" t="s">
-        <x:v>179</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="G53" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A54" s="18" t="s">
-        <x:v>179</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="B54" s="13" t="s">
-        <x:v>47</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="C54" t="s">
-        <x:v>82</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D54" s="18" t="s">
-        <x:v>181</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="G54" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A55" s="18" t="s">
-        <x:v>181</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="B55" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C55" t="s">
-        <x:v>40</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D55" s="18" t="s">
-        <x:v>186</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="G55" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A56" s="18" t="s">
-        <x:v>186</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="B56" s="13" t="s">
-        <x:v>47</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="C56" t="s">
-        <x:v>6</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="D56" s="18" t="s">
-        <x:v>187</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="G56" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A57" s="18" t="s">
-        <x:v>187</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="B57" s="13" t="s">
-        <x:v>47</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="C57" t="s">
-        <x:v>44</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="D57" s="18" t="s">
-        <x:v>178</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="G57" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A58" s="18" t="s">
-        <x:v>178</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="B58" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C58" t="s">
-        <x:v>87</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="D58" s="18" t="s">
-        <x:v>182</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="G58" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A59" s="18" t="s">
-        <x:v>182</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="C59" t="s">
-        <x:v>10</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="G59" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A60" s="18" t="s">
-        <x:v>167</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="B60" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C60" t="s">
-        <x:v>106</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="D60" s="18" t="s">
-        <x:v>176</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="G60" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A61" s="18" t="s">
-        <x:v>176</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="B61" s="13" t="s">
-        <x:v>47</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="C61" t="s">
-        <x:v>100</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="D61" s="18" t="s">
-        <x:v>164</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="G61" s="4" t="s">
-        <x:v>24</x:v>
+        <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A62" s="18" t="s">
-        <x:v>164</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="B62" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C62" t="s">
-        <x:v>101</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="D62" s="18" t="s">
-        <x:v>170</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="G62" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A63" s="18" t="s">
-        <x:v>170</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="B63" s="13" t="s">
-        <x:v>47</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="C63" t="s">
-        <x:v>39</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D63" s="18" t="s">
-        <x:v>168</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="G63" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A64" s="18" t="s">
-        <x:v>168</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="B64" s="13" t="s">
-        <x:v>47</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="C64" t="s">
-        <x:v>53</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D64" s="18" t="s">
-        <x:v>163</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="G64" s="4" t="s">
         <x:v>108</x:v>
@@ -3016,16 +3025,16 @@
     </x:row>
     <x:row r="65" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A65" s="18" t="s">
-        <x:v>163</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="B65" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C65" t="s">
-        <x:v>38</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D65" s="18" t="s">
-        <x:v>177</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="G65" s="4" t="s">
         <x:v>108</x:v>
@@ -3033,736 +3042,947 @@
     </x:row>
     <x:row r="66" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A66" s="18" t="s">
-        <x:v>177</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="B66" s="13" t="s">
-        <x:v>47</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="C66" t="s">
-        <x:v>85</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D66" s="18" t="s">
-        <x:v>169</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="G66" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A67" s="18" t="s">
-        <x:v>169</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="B67" s="13" t="s">
-        <x:v>47</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="C67" t="s">
-        <x:v>83</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D67" s="18" t="s">
-        <x:v>166</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="G67" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A68" s="18" t="s">
-        <x:v>166</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="B68" s="13" t="s">
-        <x:v>47</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="C68" t="s">
-        <x:v>4</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="D68" s="18" t="s">
-        <x:v>171</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="G68" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A69" s="18" t="s">
-        <x:v>171</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="B69" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C69" t="s">
-        <x:v>90</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="D69" s="18" t="s">
-        <x:v>172</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="G69" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A70" s="18" t="s">
-        <x:v>172</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="B70" s="13" t="s">
-        <x:v>47</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="C70" t="s">
-        <x:v>105</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="D70" s="18" t="s">
-        <x:v>175</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="G70" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A71" s="18" t="s">
-        <x:v>175</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="B71" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C71" t="s">
-        <x:v>91</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="D71" s="18" t="s">
-        <x:v>180</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="G71" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A72" s="18" t="s">
-        <x:v>180</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="B72" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C72" t="s">
-        <x:v>54</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G72" s="4"/>
     </x:row>
     <x:row r="73" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A73" s="4" t="s">
-        <x:v>221</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B73" t="s">
-        <x:v>111</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C73" t="s">
-        <x:v>1</x:v>
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="D73" s="4" t="s">
+        <x:v>72</x:v>
       </x:c>
       <x:c r="G73" s="4" t="s">
-        <x:v>253</x:v>
+        <x:v>93</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A74" s="4" t="s">
-        <x:v>236</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B74" s="19" t="s">
-        <x:v>50</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C74" t="s">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D74" s="4" t="s">
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G74" s="4" t="s">
-        <x:v>253</x:v>
+        <x:v>93</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A75" s="4" t="s">
-        <x:v>235</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B75" s="12"/>
       <x:c r="C75" t="s">
-        <x:v>35</x:v>
-      </x:c>
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="D75" s="4"/>
       <x:c r="G75" s="4" t="s">
-        <x:v>253</x:v>
+        <x:v>93</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A76" s="4" t="s">
-        <x:v>59</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B76" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C76" t="s">
-        <x:v>0</x:v>
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D76" s="4" t="s">
+        <x:v>25</x:v>
       </x:c>
       <x:c r="G76" s="4" t="s">
-        <x:v>253</x:v>
+        <x:v>93</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A77" s="4" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B77" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B77" t="s">
-        <x:v>111</x:v>
-      </x:c>
       <x:c r="C77" t="s">
-        <x:v>40</x:v>
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="D77" s="4" t="s">
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G77" s="4" t="s">
-        <x:v>254</x:v>
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A78" s="4" t="s">
-        <x:v>61</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B78" t="s">
-        <x:v>111</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C78" t="s">
-        <x:v>84</x:v>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D78" s="4" t="s">
+        <x:v>73</x:v>
       </x:c>
       <x:c r="G78" s="4" t="s">
-        <x:v>254</x:v>
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A79" s="4" t="s">
-        <x:v>227</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B79" t="s">
-        <x:v>111</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C79" t="s">
-        <x:v>231</x:v>
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="D79" s="4" t="s">
+        <x:v>66</x:v>
       </x:c>
       <x:c r="G79" s="4" t="s">
-        <x:v>253</x:v>
+        <x:v>93</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A80" s="4" t="s">
-        <x:v>229</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B80" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C80" t="s">
-        <x:v>3</x:v>
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="D80" s="4" t="s">
+        <x:v>65</x:v>
       </x:c>
       <x:c r="G80" s="4" t="s">
-        <x:v>253</x:v>
+        <x:v>93</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A81" s="4" t="s">
-        <x:v>228</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B81" t="s">
-        <x:v>111</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C81" t="s">
-        <x:v>14</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="G81" s="4" t="s">
-        <x:v>253</x:v>
+        <x:v>93</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A82" s="4" t="s">
-        <x:v>201</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B82" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C82" t="s">
-        <x:v>204</x:v>
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="D82" t="s">
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G82" s="4" t="s">
-        <x:v>253</x:v>
+        <x:v>93</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A83" s="4" t="s">
-        <x:v>197</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B83" t="s">
-        <x:v>111</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C83" t="s">
-        <x:v>243</x:v>
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="D83" t="s">
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G83" s="4" t="s">
-        <x:v>240</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A84" s="4" t="s">
-        <x:v>198</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B84" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C84" t="s">
-        <x:v>239</x:v>
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="D84" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G84" s="4" t="s">
-        <x:v>240</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A85" s="4" t="s">
-        <x:v>196</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B85" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C85" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="C85" t="s">
-        <x:v>86</x:v>
+      <x:c r="D85" t="s">
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G85" s="4" t="s">
-        <x:v>240</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A86" s="4" t="s">
-        <x:v>192</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B86" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C86" t="s">
-        <x:v>232</x:v>
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="D86" t="s">
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G86" s="4" t="s">
-        <x:v>240</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A87" s="4" t="s">
-        <x:v>193</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B87" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C87" t="s">
-        <x:v>222</x:v>
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="D87" t="s">
+        <x:v>42</x:v>
       </x:c>
       <x:c r="G87" s="4" t="s">
-        <x:v>240</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A88" s="4" t="s">
-        <x:v>202</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B88" t="s">
-        <x:v>111</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C88" t="s">
-        <x:v>34</x:v>
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D88" t="s">
+        <x:v>29</x:v>
       </x:c>
       <x:c r="G88" s="4" t="s">
-        <x:v>253</x:v>
+        <x:v>93</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A89" s="4" t="s">
-        <x:v>199</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B89" t="s">
-        <x:v>111</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C89" t="s">
-        <x:v>195</x:v>
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="D89" t="s">
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G89" s="4" t="s">
-        <x:v>253</x:v>
+        <x:v>93</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A90" s="4" t="s">
-        <x:v>200</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B90" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C90" t="s">
-        <x:v>65</x:v>
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="D90" t="s">
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G90" s="4" t="s">
-        <x:v>253</x:v>
+        <x:v>93</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A91" s="4" t="s">
-        <x:v>194</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B91" t="s">
-        <x:v>111</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C91" t="s">
-        <x:v>223</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="G91" s="4" t="s">
-        <x:v>253</x:v>
+        <x:v>93</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A92" s="4" t="s">
-        <x:v>60</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B92" s="12" t="s">
-        <x:v>249</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C92" t="s">
-        <x:v>203</x:v>
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="D92" t="s">
+        <x:v>22</x:v>
       </x:c>
       <x:c r="G92" s="4" t="s">
-        <x:v>255</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A93" s="4" t="s">
-        <x:v>15</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B93" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C93" t="s">
-        <x:v>67</x:v>
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="D93" t="s">
+        <x:v>64</x:v>
       </x:c>
       <x:c r="G93" s="4" t="s">
-        <x:v>255</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A94" s="4" t="s">
-        <x:v>16</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B94" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C94" t="s">
-        <x:v>40</x:v>
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="D94" t="s">
+        <x:v>43</x:v>
       </x:c>
       <x:c r="G94" s="4" t="s">
-        <x:v>255</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A95" s="4" t="s">
-        <x:v>20</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B95" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C95" t="s">
-        <x:v>71</x:v>
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D95" t="s">
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G95" s="4" t="s">
-        <x:v>255</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A96" s="4" t="s">
-        <x:v>17</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B96" s="12" t="s">
-        <x:v>249</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C96" t="s">
-        <x:v>9</x:v>
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="D96" t="s">
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G96" s="4" t="s">
-        <x:v>255</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="97" spans="1:3" ht="15.75" customHeight="1">
+        <x:v>69</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A97" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B97" s="12" t="s">
-        <x:v>249</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C97" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="98" spans="1:3" ht="15.75" customHeight="1">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="D97" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G97" s="4" t="s">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A98" s="4" t="s">
-        <x:v>21</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B98" s="12" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C98" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="D98" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G98" s="4" t="s">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A99" s="4" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B99" s="12" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C99" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="D99" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="G99" s="4" t="s">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A100" s="4" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B100" s="12" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="C100" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="D100" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G100" s="4" t="s">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A101" s="4" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B101" s="12" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="C101" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="C98" t="s">
-        <x:v>234</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="99" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A99" s="4" t="s">
+      <x:c r="D101" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="G101" s="4" t="s">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A102" s="4" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B102" s="12" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C102" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="D102" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="G102" s="4" t="s">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A103" s="4" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B103" s="12" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="C103" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G103" s="4" t="s">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A104" s="4" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B104" s="12" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C104" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="D104" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="G104" s="18" t="s">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A105" s="4" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B105" s="12" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="C105" t="s">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="D105" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="G105" s="4" t="s">
+        <x:v>222</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A106" s="4" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B106" s="12" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="C106" t="s">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="D106" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="G106" s="4" t="s">
+        <x:v>222</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A107" s="4" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="B107" s="12" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="C107" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D107" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="G107" s="4" t="s">
+        <x:v>222</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A108" s="4" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="B108" s="12" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C108" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="G108" s="4" t="s">
+        <x:v>222</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A109" s="4" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B109" s="12" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="C109" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="D109" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="G109" s="18" t="s">
+        <x:v>57</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A110" s="4" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B110" s="12" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C110" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D110" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="G110" s="18" t="s">
+        <x:v>57</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A111" s="4" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B111" s="12" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C111" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="D111" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="G111" s="18" t="s">
+        <x:v>57</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A112" s="4" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B112" s="12" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="C112" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="D112" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="B99" s="12" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C99" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="100" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A100" s="4" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="B100" s="12" t="s">
-        <x:v>249</x:v>
-      </x:c>
-      <x:c r="C100" t="s">
-        <x:v>248</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="101" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A101" s="4" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="B101" s="12" t="s">
-        <x:v>249</x:v>
-      </x:c>
-      <x:c r="C101" t="s">
-        <x:v>220</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="102" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A102" s="4" t="s">
-        <x:v>224</x:v>
-      </x:c>
-      <x:c r="B102" s="12" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C102" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="103" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A103" s="4" t="s">
+      <x:c r="G112" s="18" t="s">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A113" s="4" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="B113" s="12" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C113" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="D113" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="G113" s="18" t="s">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A114" s="4" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B114" s="12" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="C114" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="D114" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="G114" s="18" t="s">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A115" s="4" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B115" s="12" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="C115" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D115" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="G115" s="18" t="s">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A116" s="4" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B116" s="12" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C116" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="D116" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="G116" s="18" t="s">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A117" s="4" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B117" s="12" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="C117" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="D117" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="B103" s="12" t="s">
-        <x:v>249</x:v>
-      </x:c>
-      <x:c r="C103" t="s">
-        <x:v>58</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="104" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A104" s="4" t="s">
-        <x:v>226</x:v>
-      </x:c>
-      <x:c r="B104" s="12" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C104" t="s">
-        <x:v>242</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="105" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A105" s="4" t="s">
-        <x:v>246</x:v>
-      </x:c>
-      <x:c r="B105" s="12" t="s">
-        <x:v>249</x:v>
-      </x:c>
-      <x:c r="C105" t="s">
-        <x:v>252</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="106" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A106" s="4" t="s">
-        <x:v>244</x:v>
-      </x:c>
-      <x:c r="B106" s="12" t="s">
-        <x:v>249</x:v>
-      </x:c>
-      <x:c r="C106" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="107" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A107" s="4" t="s">
-        <x:v>245</x:v>
-      </x:c>
-      <x:c r="B107" s="12" t="s">
-        <x:v>249</x:v>
-      </x:c>
-      <x:c r="C107" t="s">
-        <x:v>250</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="108" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A108" s="4" t="s">
-        <x:v>247</x:v>
-      </x:c>
-      <x:c r="B108" s="12" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C108" t="s">
-        <x:v>225</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="109" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A109" s="4" t="s">
-        <x:v>190</x:v>
-      </x:c>
-      <x:c r="B109" s="12" t="s">
-        <x:v>249</x:v>
-      </x:c>
-      <x:c r="C109" t="s">
-        <x:v>76</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="110" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A110" s="4" t="s">
-        <x:v>215</x:v>
-      </x:c>
-      <x:c r="B110" s="12" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C110" t="s">
-        <x:v>66</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="111" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A111" s="4" t="s">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="B111" s="12" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C111" t="s">
-        <x:v>32</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="112" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A112" s="4" t="s">
-        <x:v>211</x:v>
-      </x:c>
-      <x:c r="B112" s="12" t="s">
-        <x:v>249</x:v>
-      </x:c>
-      <x:c r="C112" t="s">
-        <x:v>237</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="113" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A113" s="4" t="s">
-        <x:v>212</x:v>
-      </x:c>
-      <x:c r="B113" s="12" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C113" t="s">
-        <x:v>110</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="114" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A114" s="4" t="s">
-        <x:v>218</x:v>
-      </x:c>
-      <x:c r="B114" s="12" t="s">
-        <x:v>249</x:v>
-      </x:c>
-      <x:c r="C114" t="s">
-        <x:v>238</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="115" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A115" s="4" t="s">
-        <x:v>208</x:v>
-      </x:c>
-      <x:c r="B115" s="12" t="s">
-        <x:v>249</x:v>
-      </x:c>
-      <x:c r="C115" t="s">
-        <x:v>205</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="116" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A116" s="4" t="s">
-        <x:v>216</x:v>
-      </x:c>
-      <x:c r="B116" s="12" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C116" t="s">
-        <x:v>191</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="117" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A117" s="4" t="s">
-        <x:v>209</x:v>
-      </x:c>
-      <x:c r="B117" s="12" t="s">
-        <x:v>249</x:v>
-      </x:c>
-      <x:c r="C117" t="s">
-        <x:v>233</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="118" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="G117" s="18" t="s">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A118" s="4" t="s">
-        <x:v>219</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B118" s="12" t="s">
-        <x:v>249</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C118" t="s">
-        <x:v>70</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="119" spans="1:3" ht="15.75" customHeight="1">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="D118" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="G118" s="18" t="s">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A119" s="4" t="s">
-        <x:v>213</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B119" s="12" t="s">
-        <x:v>249</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C119" t="s">
-        <x:v>251</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="120" spans="1:3" ht="15.75" customHeight="1">
+        <x:v>254</x:v>
+      </x:c>
+      <x:c r="D119" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="G119" s="18" t="s">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A120" s="4" t="s">
-        <x:v>214</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B120" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C120" t="s">
-        <x:v>206</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="121" spans="1:3" ht="15.75" customHeight="1">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="D120" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="G120" s="18" t="s">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A121" s="4" t="s">
-        <x:v>217</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B121" s="12" t="s">
-        <x:v>249</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C121" t="s">
-        <x:v>230</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="122" spans="1:3" ht="15.75" customHeight="1">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="D121" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G121" s="18" t="s">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A122" s="4" t="s">
-        <x:v>207</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B122" s="12" t="s">
-        <x:v>249</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C122" t="s">
-        <x:v>241</x:v>
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="G122" s="18" t="s">
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="123" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/MainDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/MainDialogue.xlsx
@@ -16,6 +16,9 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="598" uniqueCount="259">
   <x:si>
+    <x:t>character_donoban_01</x:t>
+  </x:si>
+  <x:si>
     <x:t>애송아, 나는 남자야. 성인이라고. 내가 취할 생각이 없었다면, 대체 뭐하러 술집에 왔을거라고 생각하나?</x:t>
   </x:si>
   <x:si>
@@ -55,9 +58,6 @@
     <x:t>다시 만들어주셨으면 좋겠어요.</x:t>
   </x:si>
   <x:si>
-    <x:t>character_donoban_1</x:t>
-  </x:si>
-  <x:si>
     <x:t>dialogue_mainDialogue_1_3_003</x:t>
   </x:si>
   <x:si>
@@ -265,6 +265,9 @@
     <x:t>그래.</x:t>
   </x:si>
   <x:si>
+    <x:t>character_sei_01</x:t>
+  </x:si>
+  <x:si>
     <x:t>(삶의 기반도 흔들리게 됐는데, 정신까지 나가버릴 지경이라고.)</x:t>
   </x:si>
   <x:si>
@@ -440,9 +443,6 @@
   </x:si>
   <x:si>
     <x:t>음..다른걸 만들어보자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>character_sei_1</x:t>
   </x:si>
   <x:si>
     <x:t>아- 알겠습니다...</x:t>
@@ -1762,16 +1762,16 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
-        <x:v>130</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="C3" s="2" t="s">
         <x:v>145</x:v>
       </x:c>
       <x:c r="D3" s="2" t="s">
-        <x:v>137</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="E3" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F3" s="2" t="s">
         <x:v>251</x:v>
@@ -1788,7 +1788,7 @@
         <x:v>187</x:v>
       </x:c>
       <x:c r="B4" s="14" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C4" s="4" t="s">
         <x:v>240</x:v>
@@ -1827,7 +1827,7 @@
       <x:c r="E5" s="4"/>
       <x:c r="F5" s="4"/>
       <x:c r="G5" s="4" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="H5" s="4"/>
       <x:c r="I5" s="3"/>
@@ -1846,7 +1846,7 @@
         <x:v>184</x:v>
       </x:c>
       <x:c r="B6" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C6" s="4" t="s">
         <x:v>78</x:v>
@@ -1857,7 +1857,7 @@
       <x:c r="E6" s="4"/>
       <x:c r="F6" s="4"/>
       <x:c r="G6" s="4" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="H6" s="4"/>
       <x:c r="I6" s="3"/>
@@ -1876,7 +1876,7 @@
         <x:v>204</x:v>
       </x:c>
       <x:c r="B7" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C7" s="4" t="s">
         <x:v>156</x:v>
@@ -1887,7 +1887,7 @@
       <x:c r="E7" s="4"/>
       <x:c r="F7" s="4"/>
       <x:c r="G7" s="4" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="H7" s="4"/>
       <x:c r="I7" s="3"/>
@@ -1917,7 +1917,7 @@
       <x:c r="E8" s="6"/>
       <x:c r="F8" s="6"/>
       <x:c r="G8" s="6" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="H8" s="6"/>
       <x:c r="I8" s="3"/>
@@ -1936,10 +1936,10 @@
         <x:v>202</x:v>
       </x:c>
       <x:c r="B9" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C9" s="6" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D9" s="4" t="s">
         <x:v>220</x:v>
@@ -1947,7 +1947,7 @@
       <x:c r="E9" s="6"/>
       <x:c r="F9" s="6"/>
       <x:c r="G9" s="6" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="H9" s="4"/>
       <x:c r="I9" s="3"/>
@@ -1977,7 +1977,7 @@
       <x:c r="E10" s="4"/>
       <x:c r="F10" s="7"/>
       <x:c r="G10" s="4" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="H10" s="7"/>
       <x:c r="I10" s="3"/>
@@ -1996,7 +1996,7 @@
         <x:v>189</x:v>
       </x:c>
       <x:c r="B11" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C11" s="7" t="s">
         <x:v>232</x:v>
@@ -2007,7 +2007,7 @@
       <x:c r="E11" s="7"/>
       <x:c r="F11" s="7"/>
       <x:c r="G11" s="4" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="H11" s="7"/>
       <x:c r="I11" s="3"/>
@@ -2037,7 +2037,7 @@
       <x:c r="E12" s="6"/>
       <x:c r="F12" s="6"/>
       <x:c r="G12" s="4" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="H12" s="6"/>
       <x:c r="I12" s="3"/>
@@ -2056,7 +2056,7 @@
         <x:v>209</x:v>
       </x:c>
       <x:c r="B13" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C13" s="4" t="s">
         <x:v>149</x:v>
@@ -2067,7 +2067,7 @@
       <x:c r="E13" s="4"/>
       <x:c r="F13" s="4"/>
       <x:c r="G13" s="4" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="H13" s="4"/>
       <x:c r="I13" s="3"/>
@@ -2089,7 +2089,7 @@
         <x:v>249</x:v>
       </x:c>
       <x:c r="C14" s="7" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D14" s="4" t="s">
         <x:v>185</x:v>
@@ -2097,7 +2097,7 @@
       <x:c r="E14" s="7"/>
       <x:c r="F14" s="7"/>
       <x:c r="G14" s="4" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="H14" s="7"/>
       <x:c r="I14" s="3"/>
@@ -2119,7 +2119,7 @@
         <x:v>249</x:v>
       </x:c>
       <x:c r="C15" s="7" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="D15" s="4" t="s">
         <x:v>159</x:v>
@@ -2127,7 +2127,7 @@
       <x:c r="E15" s="6"/>
       <x:c r="F15" s="7"/>
       <x:c r="G15" s="6" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="H15" s="7"/>
       <x:c r="I15" s="3"/>
@@ -2146,7 +2146,7 @@
         <x:v>159</x:v>
       </x:c>
       <x:c r="B16" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C16" s="8" t="s">
         <x:v>153</x:v>
@@ -2157,7 +2157,7 @@
       <x:c r="E16" s="8"/>
       <x:c r="F16" s="8"/>
       <x:c r="G16" s="6" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="H16" s="8"/>
     </x:row>
@@ -2169,7 +2169,7 @@
         <x:v>249</x:v>
       </x:c>
       <x:c r="C17" s="9" t="s">
-        <x:v>106</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D17" s="4" t="s">
         <x:v>171</x:v>
@@ -2177,7 +2177,7 @@
       <x:c r="E17" s="4"/>
       <x:c r="F17" s="8"/>
       <x:c r="G17" s="4" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="H17" s="9"/>
     </x:row>
@@ -2186,10 +2186,10 @@
         <x:v>171</x:v>
       </x:c>
       <x:c r="B18" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C18" s="9" t="s">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D18" s="4" t="s">
         <x:v>170</x:v>
@@ -2197,7 +2197,7 @@
       <x:c r="E18" s="8"/>
       <x:c r="F18" s="8"/>
       <x:c r="G18" s="4" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="H18" s="9"/>
     </x:row>
@@ -2217,7 +2217,7 @@
       <x:c r="E19" s="8"/>
       <x:c r="F19" s="8"/>
       <x:c r="G19" s="4" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="H19" s="9"/>
     </x:row>
@@ -2226,10 +2226,10 @@
         <x:v>183</x:v>
       </x:c>
       <x:c r="B20" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C20" s="9" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D20" s="4" t="s">
         <x:v>188</x:v>
@@ -2237,7 +2237,7 @@
       <x:c r="E20" s="8"/>
       <x:c r="F20" s="8"/>
       <x:c r="G20" s="4" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="H20" s="9"/>
     </x:row>
@@ -2257,7 +2257,7 @@
       <x:c r="E21" s="8"/>
       <x:c r="F21" s="8"/>
       <x:c r="G21" s="4" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="H21" s="9"/>
     </x:row>
@@ -2266,10 +2266,10 @@
         <x:v>199</x:v>
       </x:c>
       <x:c r="B22" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C22" s="9" t="s">
-        <x:v>103</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D22" s="4" t="s">
         <x:v>158</x:v>
@@ -2277,7 +2277,7 @@
       <x:c r="E22" s="8"/>
       <x:c r="F22" s="8"/>
       <x:c r="G22" s="4" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="H22" s="9"/>
     </x:row>
@@ -2286,10 +2286,10 @@
         <x:v>158</x:v>
       </x:c>
       <x:c r="B23" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C23" s="9" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D23" s="4" t="s">
         <x:v>169</x:v>
@@ -2297,7 +2297,7 @@
       <x:c r="E23" s="8"/>
       <x:c r="F23" s="8"/>
       <x:c r="G23" s="4" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="H23" s="9"/>
     </x:row>
@@ -2306,10 +2306,10 @@
         <x:v>169</x:v>
       </x:c>
       <x:c r="B24" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C24" s="9" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D24" s="4" t="s">
         <x:v>178</x:v>
@@ -2317,7 +2317,7 @@
       <x:c r="E24" s="8"/>
       <x:c r="F24" s="8"/>
       <x:c r="G24" s="4" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="H24" s="9"/>
     </x:row>
@@ -2326,10 +2326,10 @@
         <x:v>178</x:v>
       </x:c>
       <x:c r="B25" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C25" s="9" t="s">
-        <x:v>118</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D25" s="4" t="s">
         <x:v>175</x:v>
@@ -2337,7 +2337,7 @@
       <x:c r="E25" s="8"/>
       <x:c r="F25" s="8"/>
       <x:c r="G25" s="4" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="H25" s="9"/>
     </x:row>
@@ -2346,10 +2346,10 @@
         <x:v>175</x:v>
       </x:c>
       <x:c r="B26" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C26" s="10" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D26" s="4" t="s">
         <x:v>198</x:v>
@@ -2357,7 +2357,7 @@
       <x:c r="E26" s="10"/>
       <x:c r="F26" s="10"/>
       <x:c r="G26" s="4" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="H26" s="10"/>
     </x:row>
@@ -2377,7 +2377,7 @@
       <x:c r="E27" s="10"/>
       <x:c r="F27" s="10"/>
       <x:c r="G27" s="4" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="H27" s="10"/>
     </x:row>
@@ -2386,10 +2386,10 @@
         <x:v>172</x:v>
       </x:c>
       <x:c r="B28" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C28" s="10" t="s">
-        <x:v>131</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="D28" s="4" t="s">
         <x:v>167</x:v>
@@ -2397,7 +2397,7 @@
       <x:c r="E28" s="10"/>
       <x:c r="F28" s="10"/>
       <x:c r="G28" s="4" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="H28" s="10"/>
     </x:row>
@@ -2417,7 +2417,7 @@
       <x:c r="E29" s="6"/>
       <x:c r="F29" s="10"/>
       <x:c r="G29" s="6" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="H29" s="10"/>
     </x:row>
@@ -2426,7 +2426,7 @@
         <x:v>181</x:v>
       </x:c>
       <x:c r="B30" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C30" s="10" t="s">
         <x:v>233</x:v>
@@ -2437,7 +2437,7 @@
       <x:c r="E30" s="10"/>
       <x:c r="F30" s="10"/>
       <x:c r="G30" s="6" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="H30" s="10"/>
     </x:row>
@@ -2449,7 +2449,7 @@
         <x:v>249</x:v>
       </x:c>
       <x:c r="C31" s="10" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D31" s="4" t="s">
         <x:v>161</x:v>
@@ -2457,7 +2457,7 @@
       <x:c r="E31" s="4"/>
       <x:c r="F31" s="10"/>
       <x:c r="G31" s="4" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="H31" s="10"/>
     </x:row>
@@ -2466,7 +2466,7 @@
         <x:v>161</x:v>
       </x:c>
       <x:c r="B32" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C32" s="11" t="s">
         <x:v>78</x:v>
@@ -2477,7 +2477,7 @@
       <x:c r="E32" s="11"/>
       <x:c r="F32" s="11"/>
       <x:c r="G32" s="4" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="H32" s="11"/>
     </x:row>
@@ -2489,7 +2489,7 @@
         <x:v>249</x:v>
       </x:c>
       <x:c r="C33" s="11" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="D33" s="4" t="s">
         <x:v>174</x:v>
@@ -2497,7 +2497,7 @@
       <x:c r="E33" s="11"/>
       <x:c r="F33" s="11"/>
       <x:c r="G33" s="4" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="H33" s="11"/>
     </x:row>
@@ -2506,7 +2506,7 @@
         <x:v>174</x:v>
       </x:c>
       <x:c r="B34" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C34" s="11" t="s">
         <x:v>78</x:v>
@@ -2517,7 +2517,7 @@
       <x:c r="E34" s="11"/>
       <x:c r="F34" s="11"/>
       <x:c r="G34" s="4" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="H34" s="11"/>
     </x:row>
@@ -2529,7 +2529,7 @@
         <x:v>249</x:v>
       </x:c>
       <x:c r="C35" s="11" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D35" s="4" t="s">
         <x:v>182</x:v>
@@ -2537,7 +2537,7 @@
       <x:c r="E35" s="11"/>
       <x:c r="F35" s="17"/>
       <x:c r="G35" s="4" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="H35" s="11"/>
     </x:row>
@@ -2549,13 +2549,13 @@
         <x:v>249</x:v>
       </x:c>
       <x:c r="C36" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D36" s="4" t="s">
         <x:v>164</x:v>
       </x:c>
       <x:c r="G36" s="4" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:7" ht="15.75" customHeight="1">
@@ -2566,13 +2566,13 @@
         <x:v>249</x:v>
       </x:c>
       <x:c r="C37" t="s">
-        <x:v>122</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="D37" s="4" t="s">
         <x:v>186</x:v>
       </x:c>
       <x:c r="G37" s="4" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:7" ht="15.75" customHeight="1">
@@ -2583,13 +2583,13 @@
         <x:v>249</x:v>
       </x:c>
       <x:c r="C38" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D38" s="4" t="s">
         <x:v>205</x:v>
       </x:c>
       <x:c r="G38" s="4" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:7" ht="15.75" customHeight="1">
@@ -2597,7 +2597,7 @@
         <x:v>205</x:v>
       </x:c>
       <x:c r="B39" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C39" t="s">
         <x:v>235</x:v>
@@ -2606,7 +2606,7 @@
         <x:v>194</x:v>
       </x:c>
       <x:c r="G39" s="4" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:7" ht="15.75" customHeight="1">
@@ -2617,13 +2617,13 @@
         <x:v>249</x:v>
       </x:c>
       <x:c r="C40" t="s">
-        <x:v>116</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D40" s="4" t="s">
         <x:v>160</x:v>
       </x:c>
       <x:c r="G40" s="4" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:7" ht="15.75" customHeight="1">
@@ -2634,13 +2634,13 @@
         <x:v>249</x:v>
       </x:c>
       <x:c r="C41" t="s">
-        <x:v>107</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D41" s="4" t="s">
         <x:v>176</x:v>
       </x:c>
       <x:c r="G41" s="4" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:7" ht="15.75" customHeight="1">
@@ -2651,13 +2651,13 @@
         <x:v>249</x:v>
       </x:c>
       <x:c r="C42" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D42" s="4" t="s">
         <x:v>166</x:v>
       </x:c>
       <x:c r="G42" s="4" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:7" ht="15.75" customHeight="1">
@@ -2668,13 +2668,13 @@
         <x:v>249</x:v>
       </x:c>
       <x:c r="C43" t="s">
-        <x:v>123</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D43" s="4" t="s">
         <x:v>196</x:v>
       </x:c>
       <x:c r="G43" s="4" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:7" ht="15.75" customHeight="1">
@@ -2682,16 +2682,16 @@
         <x:v>196</x:v>
       </x:c>
       <x:c r="B44" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C44" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D44" s="4" t="s">
         <x:v>211</x:v>
       </x:c>
       <x:c r="G44" s="4" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:7" ht="15.75" customHeight="1">
@@ -2708,7 +2708,7 @@
         <x:v>162</x:v>
       </x:c>
       <x:c r="G45" s="4" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:7" ht="15.75" customHeight="1">
@@ -2716,7 +2716,7 @@
         <x:v>162</x:v>
       </x:c>
       <x:c r="B46" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C46" t="s">
         <x:v>242</x:v>
@@ -2725,7 +2725,7 @@
         <x:v>201</x:v>
       </x:c>
       <x:c r="G46" s="4" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:7" ht="15.75" customHeight="1">
@@ -2733,11 +2733,11 @@
         <x:v>201</x:v>
       </x:c>
       <x:c r="C47" t="s">
-        <x:v>109</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D47" s="4"/>
       <x:c r="G47" s="4" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:7" ht="15.75" customHeight="1">
@@ -2748,13 +2748,13 @@
         <x:v>249</x:v>
       </x:c>
       <x:c r="C48" t="s">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D48" s="18" t="s">
         <x:v>229</x:v>
       </x:c>
       <x:c r="G48" s="6" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:7" ht="15.75" customHeight="1">
@@ -2765,13 +2765,13 @@
         <x:v>249</x:v>
       </x:c>
       <x:c r="C49" t="s">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D49" s="18" t="s">
         <x:v>225</x:v>
       </x:c>
       <x:c r="G49" s="6" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:7" ht="15.75" customHeight="1">
@@ -2788,7 +2788,7 @@
         <x:v>216</x:v>
       </x:c>
       <x:c r="G50" s="4" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:7" ht="15.75" customHeight="1">
@@ -2799,13 +2799,13 @@
         <x:v>249</x:v>
       </x:c>
       <x:c r="C51" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D51" s="18" t="s">
         <x:v>227</x:v>
       </x:c>
       <x:c r="G51" s="4" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:7" ht="15.75" customHeight="1">
@@ -2816,13 +2816,13 @@
         <x:v>249</x:v>
       </x:c>
       <x:c r="C52" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="D52" s="18" t="s">
         <x:v>213</x:v>
       </x:c>
       <x:c r="G52" s="4" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:7" ht="15.75" customHeight="1">
@@ -2833,13 +2833,13 @@
         <x:v>249</x:v>
       </x:c>
       <x:c r="C53" t="s">
-        <x:v>126</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="D53" s="18" t="s">
         <x:v>226</x:v>
       </x:c>
       <x:c r="G53" s="4" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:7" ht="15.75" customHeight="1">
@@ -2850,13 +2850,13 @@
         <x:v>249</x:v>
       </x:c>
       <x:c r="C54" t="s">
-        <x:v>117</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D54" s="18" t="s">
         <x:v>218</x:v>
       </x:c>
       <x:c r="G54" s="4" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:7" ht="15.75" customHeight="1">
@@ -2864,7 +2864,7 @@
         <x:v>218</x:v>
       </x:c>
       <x:c r="B55" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C55" t="s">
         <x:v>78</x:v>
@@ -2873,7 +2873,7 @@
         <x:v>224</x:v>
       </x:c>
       <x:c r="G55" s="4" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:7" ht="15.75" customHeight="1">
@@ -2884,13 +2884,13 @@
         <x:v>249</x:v>
       </x:c>
       <x:c r="C56" t="s">
-        <x:v>127</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="D56" s="18" t="s">
         <x:v>228</x:v>
       </x:c>
       <x:c r="G56" s="4" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:7" ht="15.75" customHeight="1">
@@ -2907,7 +2907,7 @@
         <x:v>206</x:v>
       </x:c>
       <x:c r="G57" s="4" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:7" ht="15.75" customHeight="1">
@@ -2915,7 +2915,7 @@
         <x:v>206</x:v>
       </x:c>
       <x:c r="B58" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C58" t="s">
         <x:v>150</x:v>
@@ -2924,7 +2924,7 @@
         <x:v>219</x:v>
       </x:c>
       <x:c r="G58" s="4" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:7" ht="15.75" customHeight="1">
@@ -2932,10 +2932,10 @@
         <x:v>219</x:v>
       </x:c>
       <x:c r="C59" t="s">
-        <x:v>105</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="G59" s="4" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:7" ht="15.75" customHeight="1">
@@ -2943,16 +2943,16 @@
         <x:v>191</x:v>
       </x:c>
       <x:c r="B60" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C60" t="s">
-        <x:v>138</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="D60" s="18" t="s">
         <x:v>214</x:v>
       </x:c>
       <x:c r="G60" s="4" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:7" ht="15.75" customHeight="1">
@@ -2963,13 +2963,13 @@
         <x:v>249</x:v>
       </x:c>
       <x:c r="C61" t="s">
-        <x:v>133</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="D61" s="18" t="s">
         <x:v>203</x:v>
       </x:c>
       <x:c r="G61" s="4" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:7" ht="15.75" customHeight="1">
@@ -2977,16 +2977,16 @@
         <x:v>203</x:v>
       </x:c>
       <x:c r="B62" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C62" t="s">
-        <x:v>129</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="D62" s="18" t="s">
         <x:v>210</x:v>
       </x:c>
       <x:c r="G62" s="4" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:7" ht="15.75" customHeight="1">
@@ -3003,7 +3003,7 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="G63" s="4" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:7" ht="15.75" customHeight="1">
@@ -3014,13 +3014,13 @@
         <x:v>249</x:v>
       </x:c>
       <x:c r="C64" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D64" s="18" t="s">
         <x:v>197</x:v>
       </x:c>
       <x:c r="G64" s="4" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:7" ht="15.75" customHeight="1">
@@ -3028,7 +3028,7 @@
         <x:v>197</x:v>
       </x:c>
       <x:c r="B65" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C65" t="s">
         <x:v>76</x:v>
@@ -3037,7 +3037,7 @@
         <x:v>215</x:v>
       </x:c>
       <x:c r="G65" s="4" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:7" ht="15.75" customHeight="1">
@@ -3048,13 +3048,13 @@
         <x:v>249</x:v>
       </x:c>
       <x:c r="C66" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D66" s="18" t="s">
         <x:v>212</x:v>
       </x:c>
       <x:c r="G66" s="4" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:7" ht="15.75" customHeight="1">
@@ -3065,13 +3065,13 @@
         <x:v>249</x:v>
       </x:c>
       <x:c r="C67" t="s">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D67" s="18" t="s">
         <x:v>193</x:v>
       </x:c>
       <x:c r="G67" s="4" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:7" ht="15.75" customHeight="1">
@@ -3082,13 +3082,13 @@
         <x:v>249</x:v>
       </x:c>
       <x:c r="C68" t="s">
-        <x:v>125</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="D68" s="18" t="s">
         <x:v>208</x:v>
       </x:c>
       <x:c r="G68" s="4" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:7" ht="15.75" customHeight="1">
@@ -3096,7 +3096,7 @@
         <x:v>208</x:v>
       </x:c>
       <x:c r="B69" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C69" t="s">
         <x:v>147</x:v>
@@ -3105,7 +3105,7 @@
         <x:v>223</x:v>
       </x:c>
       <x:c r="G69" s="4" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:7" ht="15.75" customHeight="1">
@@ -3116,13 +3116,13 @@
         <x:v>249</x:v>
       </x:c>
       <x:c r="C70" t="s">
-        <x:v>134</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="D70" s="18" t="s">
         <x:v>217</x:v>
       </x:c>
       <x:c r="G70" s="4" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:7" ht="15.75" customHeight="1">
@@ -3130,7 +3130,7 @@
         <x:v>217</x:v>
       </x:c>
       <x:c r="B71" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C71" t="s">
         <x:v>154</x:v>
@@ -3139,7 +3139,7 @@
         <x:v>221</x:v>
       </x:c>
       <x:c r="G71" s="4" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:7" ht="15.75" customHeight="1">
@@ -3147,10 +3147,10 @@
         <x:v>221</x:v>
       </x:c>
       <x:c r="B72" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C72" t="s">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G72" s="4"/>
     </x:row>
@@ -3159,16 +3159,16 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="B73" t="s">
-        <x:v>13</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C73" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="D73" s="4" t="s">
         <x:v>72</x:v>
       </x:c>
       <x:c r="G73" s="4" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:7" ht="15.75" customHeight="1">
@@ -3176,16 +3176,16 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="B74" s="19" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C74" t="s">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D74" s="4" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="G74" s="4" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:7" ht="15.75" customHeight="1">
@@ -3198,7 +3198,7 @@
       </x:c>
       <x:c r="D75" s="4"/>
       <x:c r="G75" s="4" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:7" ht="15.75" customHeight="1">
@@ -3206,7 +3206,7 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B76" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C76" t="s">
         <x:v>80</x:v>
@@ -3215,7 +3215,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="G76" s="4" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:7" ht="15.75" customHeight="1">
@@ -3223,7 +3223,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B77" t="s">
-        <x:v>13</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C77" t="s">
         <x:v>78</x:v>
@@ -3232,7 +3232,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="G77" s="4" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:7" ht="15.75" customHeight="1">
@@ -3240,16 +3240,16 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B78" t="s">
-        <x:v>13</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C78" t="s">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D78" s="4" t="s">
         <x:v>73</x:v>
       </x:c>
       <x:c r="G78" s="4" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:7" ht="15.75" customHeight="1">
@@ -3257,16 +3257,16 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="B79" t="s">
-        <x:v>13</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C79" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D79" s="4" t="s">
         <x:v>66</x:v>
       </x:c>
       <x:c r="G79" s="4" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:7" ht="15.75" customHeight="1">
@@ -3274,7 +3274,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B80" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C80" t="s">
         <x:v>143</x:v>
@@ -3283,7 +3283,7 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="G80" s="4" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:7" ht="15.75" customHeight="1">
@@ -3291,13 +3291,13 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="B81" t="s">
-        <x:v>13</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C81" t="s">
         <x:v>36</x:v>
       </x:c>
       <x:c r="G81" s="4" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:7" ht="15.75" customHeight="1">
@@ -3305,7 +3305,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B82" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C82" t="s">
         <x:v>236</x:v>
@@ -3314,7 +3314,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="G82" s="4" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:7" ht="15.75" customHeight="1">
@@ -3322,7 +3322,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B83" t="s">
-        <x:v>13</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C83" t="s">
         <x:v>74</x:v>
@@ -3331,7 +3331,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="G83" s="4" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:7" ht="15.75" customHeight="1">
@@ -3339,16 +3339,16 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B84" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C84" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="D84" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="G84" s="4" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:7" ht="15.75" customHeight="1">
@@ -3356,16 +3356,16 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B85" t="s">
-        <x:v>13</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C85" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D85" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="G85" s="4" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:7" ht="15.75" customHeight="1">
@@ -3373,7 +3373,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B86" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C86" t="s">
         <x:v>234</x:v>
@@ -3382,7 +3382,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="G86" s="4" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:7" ht="15.75" customHeight="1">
@@ -3390,7 +3390,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B87" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C87" t="s">
         <x:v>255</x:v>
@@ -3399,7 +3399,7 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="G87" s="4" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:7" ht="15.75" customHeight="1">
@@ -3407,16 +3407,16 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B88" t="s">
-        <x:v>13</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C88" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D88" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="G88" s="4" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:7" ht="15.75" customHeight="1">
@@ -3424,7 +3424,7 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B89" t="s">
-        <x:v>13</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C89" t="s">
         <x:v>75</x:v>
@@ -3433,7 +3433,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="G89" s="4" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:7" ht="15.75" customHeight="1">
@@ -3441,7 +3441,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B90" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C90" t="s">
         <x:v>168</x:v>
@@ -3450,7 +3450,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="G90" s="4" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:7" ht="15.75" customHeight="1">
@@ -3458,13 +3458,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B91" t="s">
-        <x:v>13</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C91" t="s">
         <x:v>247</x:v>
       </x:c>
       <x:c r="G91" s="4" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:7" ht="15.75" customHeight="1">
@@ -3472,7 +3472,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B92" s="12" t="s">
-        <x:v>142</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C92" t="s">
         <x:v>239</x:v>
@@ -3489,7 +3489,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B93" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C93" t="s">
         <x:v>146</x:v>
@@ -3506,7 +3506,7 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="B94" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C94" t="s">
         <x:v>78</x:v>
@@ -3523,10 +3523,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B95" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C95" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D95" t="s">
         <x:v>40</x:v>
@@ -3540,10 +3540,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B96" s="12" t="s">
-        <x:v>142</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C96" t="s">
-        <x:v>101</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D96" t="s">
         <x:v>34</x:v>
@@ -3557,7 +3557,7 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B97" s="12" t="s">
-        <x:v>142</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C97" t="s">
         <x:v>144</x:v>
@@ -3574,7 +3574,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B98" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C98" t="s">
         <x:v>152</x:v>
@@ -3591,7 +3591,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B99" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C99" t="s">
         <x:v>250</x:v>
@@ -3608,10 +3608,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B100" s="12" t="s">
-        <x:v>142</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C100" t="s">
-        <x:v>128</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="D100" t="s">
         <x:v>26</x:v>
@@ -3625,7 +3625,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B101" s="12" t="s">
-        <x:v>142</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C101" t="s">
         <x:v>50</x:v>
@@ -3642,10 +3642,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B102" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C102" t="s">
-        <x:v>132</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="D102" t="s">
         <x:v>39</x:v>
@@ -3659,7 +3659,7 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B103" s="12" t="s">
-        <x:v>142</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C103" t="s">
         <x:v>23</x:v>
@@ -3673,7 +3673,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B104" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C104" t="s">
         <x:v>231</x:v>
@@ -3690,7 +3690,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B105" s="12" t="s">
-        <x:v>142</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C105" t="s">
         <x:v>237</x:v>
@@ -3707,7 +3707,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B106" s="12" t="s">
-        <x:v>142</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C106" t="s">
         <x:v>252</x:v>
@@ -3724,10 +3724,10 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="B107" s="12" t="s">
-        <x:v>142</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C107" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D107" t="s">
         <x:v>71</x:v>
@@ -3741,7 +3741,7 @@
         <x:v>71</x:v>
       </x:c>
       <x:c r="B108" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C108" t="s">
         <x:v>56</x:v>
@@ -3755,7 +3755,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B109" s="12" t="s">
-        <x:v>142</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C109" t="s">
         <x:v>165</x:v>
@@ -3772,10 +3772,10 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B110" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C110" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D110" t="s">
         <x:v>70</x:v>
@@ -3789,10 +3789,10 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="B111" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C111" t="s">
-        <x:v>104</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D111" t="s">
         <x:v>59</x:v>
@@ -3806,10 +3806,10 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B112" s="12" t="s">
-        <x:v>142</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C112" t="s">
-        <x:v>119</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="D112" t="s">
         <x:v>63</x:v>
@@ -3823,7 +3823,7 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="B113" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C113" t="s">
         <x:v>243</x:v>
@@ -3840,10 +3840,10 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B114" s="12" t="s">
-        <x:v>142</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C114" t="s">
-        <x:v>120</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="D114" t="s">
         <x:v>52</x:v>
@@ -3857,7 +3857,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B115" s="12" t="s">
-        <x:v>142</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C115" t="s">
         <x:v>20</x:v>
@@ -3874,7 +3874,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B116" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C116" t="s">
         <x:v>244</x:v>
@@ -3891,10 +3891,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B117" s="12" t="s">
-        <x:v>142</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C117" t="s">
-        <x:v>110</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="D117" t="s">
         <x:v>62</x:v>
@@ -3908,10 +3908,10 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="B118" s="12" t="s">
-        <x:v>142</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C118" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="D118" t="s">
         <x:v>47</x:v>
@@ -3925,7 +3925,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B119" s="12" t="s">
-        <x:v>142</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C119" t="s">
         <x:v>254</x:v>
@@ -3942,10 +3942,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B120" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C120" t="s">
-        <x:v>136</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="D120" t="s">
         <x:v>49</x:v>
@@ -3959,10 +3959,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B121" s="12" t="s">
-        <x:v>142</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C121" t="s">
-        <x:v>124</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="D121" t="s">
         <x:v>37</x:v>
@@ -3976,7 +3976,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B122" s="12" t="s">
-        <x:v>142</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C122" t="s">
         <x:v>258</x:v>

--- a/JsonConverter/ExcelFiles/MainDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/MainDialogue.xlsx
@@ -14,783 +14,855 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="598" uniqueCount="259">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="283">
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_3_016</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_3_014</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_3_017</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_3_019</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_3_015</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_3_022</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_3_021</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_3_025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_3_024</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_3_018</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_3_020</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_3_023</x:t>
+  </x:si>
+  <x:si>
+    <x:t>우선 슈가 러쉬부터 시작해보자.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>글쎄. 뭣 좀 사러 밖에 나갔...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>술을 섞고 삶을 바꿔줄 시간이군.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>character_sei_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>별거 아니야 조금 생각할게 있어서.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아, 그래! 잊기 전에 하나만 더!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이건...내가 원하던게 아니야.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>character_jill_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>다시 만들어주셨으면 좋겠어요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아! 물론이죠, 곧 나갑니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>저 헬멧은 벗어주시지 않을래요?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SelectionNameList</x:t>
+  </x:si>
+  <x:si>
+    <x:t>저기 보스, 제가 "보스"라고 부르면 좀 차갑게 들리나요?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>음, 매월 30일에 월세를 내는게 엄청 스트레스거든, 그리고-</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Texture2D/Character_Gillian_Smile</x:t>
+  </x:si>
+  <x:si>
+    <x:t>길리안, 나 공식적인 BTC 교육을 받고 여기 온 거거든?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대체 언제쯤이면 네가 존같이 생겼다는 걸 인정할거야, 길?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(이틀 전에는 이곳이 폐쇄될 위기에 처했다는 것까지 알게됐지)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Texture2D/Character_Gillian_Dismay</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Texture2D/Character_Donoban_Smile</x:t>
+  </x:si>
+  <x:si>
+    <x:t>다시 해보자고. 맥주 한잔 줘. 보리 맥, 술 주. 맥.주.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Texture2D/Character_Donoban_Dismay</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Texture2D/Character_Donoban_Basic</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Texture2D/Character_Gillian_Basic</x:t>
+  </x:si>
+  <x:si>
+    <x:t>측면에 있는 얼음과 숙성 버튼 중 필요한 걸 선택하면 돼.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(삶의 기반도 흔들리게 됐는데, 정신까지 나가버릴 지경이라고.)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>애송아, 나는 남자야. 성인이라고. 내가 취할 생각이 없었다면, 대체 뭐하러 술집에 왔을거라고 생각하나?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>카모트린은 음료의 알콜 도수를 결정하지. 맛은 변화시키지 못하지만, 알콜의 효과는 그대로 가지고 있어.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_1_2_004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_2_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>응?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>여기요</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그래.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>질!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감사합니다. 다음에 또 오세요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>음? 별로, 아냐.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그럼 우리 기초 과정부터 한번 다시 확인해 보자고. 괜찮지? 혹시 모르니까 말야</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그러고 난 다음, 섞기 버튼을 누르면 돼. 다시 눌러서 섞는 걸 멈출 수 있고.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아, 마지막 문장은 그렇게 신경쓰지 않아도 돼. 그냥 재밌는 뒷이야기 같은 거니까.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"우리는 가장 어두운 시기에 타오르는 빛이자, 범죄의 희생양들을 도와주는 자!"</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(아, 그러고 보니 내 아파트 방바닥에 맥주 캔들이 엄청나게 널브러져 있었지. 또...)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>너는 어그멘티드 아이의 편집장이자 소유주인 도노반 D.도슨님과 대화를 나누고 있는 거라고.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>칵테일 조합법에 있는 탐색 막대를 이용해 레시피를 확인해 봐. 왼쪽 상단에 표시될거야.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화이트 나이츠 손님은 그리 많지 않은데 말이죠, 사실 제대로 기억나는건 한명 뿐이지만요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그런 것 같아요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(게다가 포어에게 중성화 수술을 시켜주느라 지갑 속 마지막 동전 하나까지 다써버렸지. 월세를 한번만 더 미뤘다간 쫒겨날거야...)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>내가 어색해서 그렇게 부르는게 아니라, 그냥 습관적으로 그렇게 부르는거잖아.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>내가 이 동네에서 미팅이 있었다는 사실에 감사하도록 해, 이딴 개떡 같은 곳은 나같은 분의 존재 자체로도 도움이 될테니까.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>만약에 레시피에 "카모트린 추가 가능"이라고 써져 있다면, 아예 넣지 않을 수도 잔 끝까지 채워 넣을 수도 있다는 의미야.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"구조하라, 치료하라, 보호하라! 우리는 적습으로 고통받는 자들에게 위안을 주는 천사들일지어니!"</x:t>
+  </x:si>
+  <x:si>
+    <x:t>길이 슈가 러쉬나 피아노 맨을 달라는군. 만약에 망쳤다면, 재시도 버튼을 눌러서 다시 하면 되겠지.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이렇게 버튼을 누르면, 재료를 섞은 뒤에 기기가 자동으로 얼음을 추가시켜주지.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그러니 너무 많이 넣으면, 손님이 빨리 취해버리게 될거야 잘 생각해서 넣어.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>미안해요. 아까 그건 우리의 복무신조 비슷한거에요. 매일 아침에 복창하는거죠.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>나한테 다시 슈가러쉬나 피아노 맨을 만들어주면 더는 귀찮게 굴지 않을게.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>발키리 군단 제 765부대 소속 특수 상등병, 세이 P 아사기리 대령했습니다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>네가 피아노 맨을 만들 수 있을 정도 상태면, 나머지 과정은 생략할게. 그래도 웬만하면 잠깐참고 나랑 어울려줘, 괜찮지?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아뇨, 그쪽이랑은 달라요. 음...정말 완전히 다른 부대라고요. 우리는 폭동 진압 같은 일은 전혀 하지 않아요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>혹시 용어를 모를 수도 있으니 하는 말인데, "온더록스"는 "얼음"버튼을 눌러서 얼음을 넣어야 한다는 걸 의미해</x:t>
+  </x:si>
+  <x:si>
+    <x:t>폭동...? 아! 아뇨아뇨아뇨... 그건 아마 블리츠크리그 군단일거에요. 엄청 큰 갑옷 입은 부대 말하는 거죠?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>리셋 버튼은 아무 때나 누를 수 있어. 셰이커가 움직이고 있을 때도 말이지. 부담 가지지 말고 원할 때 눌러.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>또 맛이나 종류 기준으로 검색할 수 있어. "달콤한" 술이나 "남성적인" 술을 정렬시켜 볼 수 있다는 거야.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>네? 아, 미안해요. 너무 편안해서 쓰고 있다는걸 자주 까먹어요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>길에게 다시 슈가러쉬나 피아노 맨을 주자고. 이번엔 정확히 섞어보자.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>다 끝나면 서빙하기 버튼을 눌러서 손님에게 전해주면 돼. 그게 다야.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오른쪽 가운데에 있는 셰이커에 재료를 원하는 양만큼 클릭해서 넣어.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아, 만약 제조에 실패했다면 리셋 버튼을 눌러서 다시 시도할 수 있어.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>발키리 군단 소속이라고 하셨죠? 그럼 폭동 진압 같은 일들을 하시나요?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(어제는 1시간 동안 혼자 떠들었다고 오해받는 일이 생기질않나.)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Texture2D/Character_Gillian_Surprise</x:t>
+  </x:si>
+  <x:si>
+    <x:t>했어. 너, 역시 딴 생각에 빠져 있는 것 같아. 그것도 아주 심하게.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_1_1_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_1_1_000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어떤기사도 내 손길이 닿지 않고 발간될 수는 없지.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_2_004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_1_2_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Texture2D/Character_Sei_Meka</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그래, 이거 좋군. 정말 괜찮아. 아주 잘 했다 이거야.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_3_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오늘자 봉급은 계좌로 넣어줄게.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어찌됐건, 유리잔들 설거지 끝나고 나면 가도 좋아.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_1_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>음...이건 너무 길죠, 그냥 세이라고 불러주세요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_1_2_000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_3_008</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_3_010</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_3_012</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_3_007</x:t>
+  </x:si>
+  <x:si>
+    <x:t>다시한번 세이에게 문블라스트를 만들어주자. 문블라스트!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_3_011</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_1_3_006</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Texture2D/Character_Sei_Smile</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_2_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_1_3_000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_3_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_3_009</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_3_004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_1_2_005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_2_000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_3_005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_3_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_3_006</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_1_1_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_1_010</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_2_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_1_004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_1_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이제 좀 낫나요?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아- 알겠습니다...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>안녕하세-...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이제 설명 끝났어?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>알았다, 알았어...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아, 안녕 존.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VoicePath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>무슨 말 했어?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자 그럼 시작해볼까?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TexturePath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string[]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>네, 고맙습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>보스는 어디 있어?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아! 어서 와, 질.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_1_2_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>내가 너를 쥴스라고 부를 수 있게 허락해줄 때 쯤.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_1_000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_1_3_005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_1_3_007</x:t>
+  </x:si>
+  <x:si>
+    <x:t>음료는 "온더록스" 혹은 숙성을 요구하는지 확인해야 해.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_1_3_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_1_3_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_1_3_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_1_3_008</x:t>
+  </x:si>
+  <x:si>
+    <x:t>음...작고, 달콤하고, 차가운..문블라스트가 좋겠네요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_3_000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_1_011</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_1_3_004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오히려, 그들의 뒷처리를 맡는 부대라고 할 수 있겠네요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_1_2_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_1_008</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_1_005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_1_009</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_1_3_009</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_1_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Texture2D/Character_Sei_Basic</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_1_007</x:t>
+  </x:si>
+  <x:si>
+    <x:t>제길, 질. 정신차려. 손님은 맥주를 원해! 맥.주!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_1_006</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_3_013</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Texture2D/Character_Boss_Basic</x:t>
+  </x:si>
+  <x:si>
+    <x:t>미안, 무슨 말 했어?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그래, 이제 막 끝났어.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CharacterDataId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자, 충분히 오래 놀아줬지?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>내가 방금 한 말 들었어?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그래. 잡아둬서 미안.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>음...방금 그건 뭐였죠?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NextDialogueId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>음..다른걸 만들어보자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>음..뭐, 감사합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>거기 너! 맥주 한잔 줘</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어떤걸로 드릴까요, 세이?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그럼 이제 일을 시작하자고.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>무슨말이죠?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>네, 맞아요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>여기요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그게 뭔데?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>음...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>당연하지!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하아...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>흐음...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시끄러워.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>안녕하세요!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>좋은 저녁.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>길...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>여기있습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_024</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_020</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_028</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_042</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_037</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_027</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_012</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아아 좋아, 딱 제가 원했던 거예요. 감사합니다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_015</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_033</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_019</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_039</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(참 흥미로운 손님으로 하루를 시작하게 됐는걸.)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_014</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_032</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_030</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_038</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_034</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_011</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_016</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_021</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_013</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_029</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_022</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_017</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_031</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_023</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_018</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_3_008</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_3_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_043</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_040</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_2_000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_007</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_3_005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_3_000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_3_004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_008</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_036</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_2_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_041</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_3_011</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_2_007</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_2_005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_2_011</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_006</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_010</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_3_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_3_007</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_009</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_3_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_035</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_2_010</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_3_009</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_3_006</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_2_004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_2_009</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_2_006</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_2_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_3_010</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_2_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_2_008</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Texture2D/Character_Sei_Sad</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_3_012</x:t>
+  </x:si>
+  <x:si>
+    <x:t>제가 원하는 음료는 아닌것 같아요...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>character_gillian_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>...정말 오늘 일할 수 있는 거 맞아?</x:t>
+  </x:si>
   <x:si>
     <x:t>character_donoban_01</x:t>
   </x:si>
   <x:si>
-    <x:t>애송아, 나는 남자야. 성인이라고. 내가 취할 생각이 없었다면, 대체 뭐하러 술집에 왔을거라고 생각하나?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>카모트린은 음료의 알콜 도수를 결정하지. 맛은 변화시키지 못하지만, 알콜의 효과는 그대로 가지고 있어.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>술을 섞고 삶을 바꿔줄 시간이군.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아! 물론이죠, 곧 나갑니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>별거 아니야 조금 생각할게 있어서.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SelectionNameList</x:t>
-  </x:si>
-  <x:si>
-    <x:t>우선 슈가 러쉬부터 시작해보자.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>character_jill_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>글쎄. 뭣 좀 사러 밖에 나갔...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>저 헬멧은 벗어주시지 않을래요?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아, 그래! 잊기 전에 하나만 더!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이건...내가 원하던게 아니야.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>다시 만들어주셨으면 좋겠어요.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_1_3_003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>내가 너를 쥴스라고 부를 수 있게 허락해줄 때 쯤.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_1_3_008</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_1_3_004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_1_3_005</x:t>
-  </x:si>
-  <x:si>
-    <x:t>음료는 "온더록스" 혹은 숙성을 요구하는지 확인해야 해.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>오히려, 그들의 뒷처리를 맡는 부대라고 할 수 있겠네요.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_1_3_009</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_1_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>음...작고, 달콤하고, 차가운..문블라스트가 좋겠네요.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_1_3_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_1_2_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_1_009</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_1_3_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_1_008</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_1_3_007</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_3_000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Texture2D/Character_Sei_Basic</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_1_007</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_1_006</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_1_005</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_1_000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>제길, 질. 정신차려. 손님은 맥주를 원해! 맥.주!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_3_013</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_1_2_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_1_011</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_1_004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_1_3_000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_1_3_006</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_1_003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_1_2_000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_3_011</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_3_008</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_3_010</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_1_010</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_3_012</x:t>
-  </x:si>
-  <x:si>
-    <x:t>음...이건 너무 길죠, 그냥 세이라고 불러주세요.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_2_000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_3_006</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_1_1_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_3_007</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_2_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>다시한번 세이에게 문블라스트를 만들어주자. 문블라스트!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Texture2D/Character_Sei_Smile</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_2_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_3_003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_3_005</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_3_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_3_009</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_3_004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_1_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_1_2_005</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_1_2_004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_2_003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_1_1_000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Texture2D/Character_Sei_Meka</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_3_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_2_004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_1_1_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_1_2_003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그래, 이거 좋군. 정말 괜찮아. 아주 잘 했다 이거야.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어떤기사도 내 손길이 닿지 않고 발간될 수는 없지.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>응?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>질!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>여기요</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그래.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>character_sei_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(삶의 기반도 흔들리게 됐는데, 정신까지 나가버릴 지경이라고.)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>측면에 있는 얼음과 숙성 버튼 중 필요한 걸 선택하면 돼.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(이틀 전에는 이곳이 폐쇄될 위기에 처했다는 것까지 알게됐지)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Texture2D/Character_Gillian_Dismay</x:t>
-  </x:si>
-  <x:si>
-    <x:t>음, 매월 30일에 월세를 내는게 엄청 스트레스거든, 그리고-</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Texture2D/Character_Gillian_Smile</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Texture2D/Character_Donoban_Smile</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Texture2D/Character_Donoban_Dismay</x:t>
-  </x:si>
-  <x:si>
-    <x:t>길리안, 나 공식적인 BTC 교육을 받고 여기 온 거거든?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대체 언제쯤이면 네가 존같이 생겼다는 걸 인정할거야, 길?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Texture2D/Character_Donoban_Basic</x:t>
-  </x:si>
-  <x:si>
-    <x:t>다시 해보자고. 맥주 한잔 줘. 보리 맥, 술 주. 맥.주.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Texture2D/Character_Gillian_Basic</x:t>
-  </x:si>
-  <x:si>
-    <x:t>너는 어그멘티드 아이의 편집장이자 소유주인 도노반 D.도슨님과 대화를 나누고 있는 거라고.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(아, 그러고 보니 내 아파트 방바닥에 맥주 캔들이 엄청나게 널브러져 있었지. 또...)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>칵테일 조합법에 있는 탐색 막대를 이용해 레시피를 확인해 봐. 왼쪽 상단에 표시될거야.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>화이트 나이츠 손님은 그리 많지 않은데 말이죠, 사실 제대로 기억나는건 한명 뿐이지만요.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아, 만약 제조에 실패했다면 리셋 버튼을 눌러서 다시 시도할 수 있어.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>네? 아, 미안해요. 너무 편안해서 쓰고 있다는걸 자주 까먹어요.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>오른쪽 가운데에 있는 셰이커에 재료를 원하는 양만큼 클릭해서 넣어.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(어제는 1시간 동안 혼자 떠들었다고 오해받는 일이 생기질않나.)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>발키리 군단 소속이라고 하셨죠? 그럼 폭동 진압 같은 일들을 하시나요?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>길에게 다시 슈가러쉬나 피아노 맨을 주자고. 이번엔 정확히 섞어보자.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>했어. 너, 역시 딴 생각에 빠져 있는 것 같아. 그것도 아주 심하게.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>다 끝나면 서빙하기 버튼을 눌러서 손님에게 전해주면 돼. 그게 다야.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Texture2D/Character_Gillian_Surprise</x:t>
-  </x:si>
-  <x:si>
-    <x:t>길이 슈가 러쉬나 피아노 맨을 달라는군. 만약에 망쳤다면, 재시도 버튼을 눌러서 다시 하면 되겠지.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"구조하라, 치료하라, 보호하라! 우리는 적습으로 고통받는 자들에게 위안을 주는 천사들일지어니!"</x:t>
-  </x:si>
-  <x:si>
-    <x:t>내가 이 동네에서 미팅이 있었다는 사실에 감사하도록 해, 이딴 개떡 같은 곳은 나같은 분의 존재 자체로도 도움이 될테니까.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>만약에 레시피에 "카모트린 추가 가능"이라고 써져 있다면, 아예 넣지 않을 수도 잔 끝까지 채워 넣을 수도 있다는 의미야.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>네가 피아노 맨을 만들 수 있을 정도 상태면, 나머지 과정은 생략할게. 그래도 웬만하면 잠깐참고 나랑 어울려줘, 괜찮지?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그럼 우리 기초 과정부터 한번 다시 확인해 보자고. 괜찮지? 혹시 모르니까 말야</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"우리는 가장 어두운 시기에 타오르는 빛이자, 범죄의 희생양들을 도와주는 자!"</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그러고 난 다음, 섞기 버튼을 누르면 돼. 다시 눌러서 섞는 걸 멈출 수 있고.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아, 마지막 문장은 그렇게 신경쓰지 않아도 돼. 그냥 재밌는 뒷이야기 같은 거니까.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(게다가 포어에게 중성화 수술을 시켜주느라 지갑 속 마지막 동전 하나까지 다써버렸지. 월세를 한번만 더 미뤘다간 쫒겨날거야...)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>폭동...? 아! 아뇨아뇨아뇨... 그건 아마 블리츠크리그 군단일거에요. 엄청 큰 갑옷 입은 부대 말하는 거죠?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아뇨, 그쪽이랑은 달라요. 음...정말 완전히 다른 부대라고요. 우리는 폭동 진압 같은 일은 전혀 하지 않아요.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>혹시 용어를 모를 수도 있으니 하는 말인데, "온더록스"는 "얼음"버튼을 눌러서 얼음을 넣어야 한다는 걸 의미해</x:t>
-  </x:si>
-  <x:si>
-    <x:t>또 맛이나 종류 기준으로 검색할 수 있어. "달콤한" 술이나 "남성적인" 술을 정렬시켜 볼 수 있다는 거야.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>리셋 버튼은 아무 때나 누를 수 있어. 셰이커가 움직이고 있을 때도 말이지. 부담 가지지 말고 원할 때 눌러.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>미안해요. 아까 그건 우리의 복무신조 비슷한거에요. 매일 아침에 복창하는거죠.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그러니 너무 많이 넣으면, 손님이 빨리 취해버리게 될거야 잘 생각해서 넣어.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이렇게 버튼을 누르면, 재료를 섞은 뒤에 기기가 자동으로 얼음을 추가시켜주지.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>나한테 다시 슈가러쉬나 피아노 맨을 만들어주면 더는 귀찮게 굴지 않을게.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>발키리 군단 제 765부대 소속 특수 상등병, 세이 P 아사기리 대령했습니다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그럼 이제 일을 시작하자고.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CharacterDataId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>미안, 무슨 말 했어?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어떤걸로 드릴까요, 세이?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그래. 잡아둬서 미안.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그래, 이제 막 끝났어.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>음..뭐, 감사합니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>음...방금 그건 뭐였죠?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NextDialogueId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>자, 충분히 오래 놀아줬지?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>거기 너! 맥주 한잔 줘</x:t>
-  </x:si>
-  <x:si>
-    <x:t>내가 방금 한 말 들었어?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>음..다른걸 만들어보자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아- 알겠습니다...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이제 좀 낫나요?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>안녕하세-...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이제 설명 끝났어?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VoicePath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>보스는 어디 있어?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>알았다, 알았어...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string[]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>네, 고맙습니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>무슨 말 했어?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>자 그럼 시작해볼까?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아! 어서 와, 질.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아, 안녕 존.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TexturePath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_019</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_012</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_037</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_028</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_042</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_027</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_033</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아아 좋아, 딱 제가 원했던 거예요. 감사합니다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_039</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(참 흥미로운 손님으로 하루를 시작하게 됐는걸.)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_020</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_015</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_014</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_024</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_031</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_030</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_022</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_038</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_021</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_013</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_029</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_032</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_016</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_011</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_034</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_017</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_007</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_3_000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_2_000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_3_008</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_036</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_3_004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_040</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_3_005</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_023</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_018</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_008</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_043</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_005</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_3_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_035</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_2_010</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_010</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_3_009</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_009</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_3_003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_041</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_3_007</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_2_005</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_3_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_3_006</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_2_003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_3_011</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_2_007</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_2_011</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_006</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_3_012</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Texture2D/Character_Sei_Sad</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_3_010</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_2_008</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_2_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_2_006</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_2_004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_2_009</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_2_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>여기요.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시끄러워.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>당연하지!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>흐음...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>길...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>여기있습니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>음...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그게 뭔데?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>안녕하세요!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>좋은 저녁.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하아...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>네, 맞아요.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>무슨말이죠?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
+    <x:t>어떤 일을 하시나요, 손님? 성함이...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>음료 맛있었어요.. 다음에 또 올게요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"우리는 감시하고, 또한 수호한다!"</x:t>
   </x:si>
   <x:si>
     <x:t>그럼 문제없이 만들어 낼 수 있겠네!</x:t>
   </x:si>
   <x:si>
+    <x:t>어떤걸로 드릴까요, 어, 성함이..?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>맥주를 원하는군. 덩치가 꽤 커보이는데.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>내가 말했던 것들을 잘 떠올리면서 만들어!</x:t>
+  </x:si>
+  <x:si>
     <x:t>으음.. 너 덕분에 잘 마시고 간다고.</x:t>
   </x:si>
   <x:si>
-    <x:t>내가 말했던 것들을 잘 떠올리면서 만들어!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>character_gillian_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어떤걸로 드릴까요, 어, 성함이..?</x:t>
-  </x:si>
-  <x:si>
     <x:t>SelectionDialogueIdList</x:t>
   </x:si>
   <x:si>
-    <x:t>제가 원하는 음료는 아닌것 같아요...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>맥주를 원하는군. 덩치가 꽤 커보이는데.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"우리는 감시하고, 또한 수호한다!"</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어떤 일을 하시나요, 손님? 성함이...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>...정말 오늘 일할 수 있는 거 맞아?</x:t>
-  </x:si>
-  <x:si>
     <x:t>괜찮아? 생각이 다른데 가있는 것 같은데.</x:t>
   </x:si>
   <x:si>
-    <x:t>음료 맛있었어요.. 다음에 또 올게요.</x:t>
+    <x:t>character_boss_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이렇게 하루가 끝났군.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오늘 밤은 여기까지인가?</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1706,7 +1778,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:R122"/>
+  <x:dimension ref="A1:R137"/>
   <x:sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1"/>
   <x:cols>
     <x:col min="1" max="1" width="26.36328125" customWidth="1"/>
@@ -1721,7 +1793,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>241</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1"/>
@@ -1733,68 +1805,68 @@
     </x:row>
     <x:row r="2" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s">
-        <x:v>245</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>230</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>230</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>230</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>230</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>230</x:v>
+        <x:v>180</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A3" s="2" t="s">
-        <x:v>81</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
-        <x:v>131</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="C3" s="2" t="s">
-        <x:v>145</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D3" s="2" t="s">
-        <x:v>138</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="E3" s="2" t="s">
-        <x:v>6</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F3" s="2" t="s">
-        <x:v>251</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="G3" s="2" t="s">
-        <x:v>157</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="H3" s="2" t="s">
-        <x:v>148</x:v>
+        <x:v>130</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A4" s="4" t="s">
-        <x:v>187</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="B4" s="14" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C4" s="4" t="s">
-        <x:v>240</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="D4" s="4" t="s">
-        <x:v>177</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="E4" s="12"/>
       <x:c r="F4" s="16"/>
@@ -1813,21 +1885,21 @@
     </x:row>
     <x:row r="5" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A5" s="4" t="s">
-        <x:v>177</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="B5" s="15" t="s">
-        <x:v>249</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="C5" s="4" t="s">
-        <x:v>155</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="D5" s="4" t="s">
-        <x:v>184</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="E5" s="4"/>
       <x:c r="F5" s="4"/>
       <x:c r="G5" s="4" t="s">
-        <x:v>96</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H5" s="4"/>
       <x:c r="I5" s="3"/>
@@ -1843,21 +1915,21 @@
     </x:row>
     <x:row r="6" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A6" s="4" t="s">
-        <x:v>184</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="B6" s="12" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C6" s="4" t="s">
-        <x:v>78</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D6" s="4" t="s">
-        <x:v>204</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="E6" s="4"/>
       <x:c r="F6" s="4"/>
       <x:c r="G6" s="4" t="s">
-        <x:v>96</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H6" s="4"/>
       <x:c r="I6" s="3"/>
@@ -1873,21 +1945,21 @@
     </x:row>
     <x:row r="7" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A7" s="4" t="s">
-        <x:v>204</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="B7" s="12" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C7" s="4" t="s">
-        <x:v>156</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="D7" s="4" t="s">
-        <x:v>190</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="E7" s="4"/>
       <x:c r="F7" s="4"/>
       <x:c r="G7" s="4" t="s">
-        <x:v>96</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H7" s="4"/>
       <x:c r="I7" s="3"/>
@@ -1903,21 +1975,21 @@
     </x:row>
     <x:row r="8" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A8" s="4" t="s">
-        <x:v>190</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="B8" s="13" t="s">
-        <x:v>249</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="C8" s="6" t="s">
-        <x:v>78</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D8" s="4" t="s">
-        <x:v>202</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="E8" s="6"/>
       <x:c r="F8" s="6"/>
       <x:c r="G8" s="6" t="s">
-        <x:v>87</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="H8" s="6"/>
       <x:c r="I8" s="3"/>
@@ -1933,21 +2005,21 @@
     </x:row>
     <x:row r="9" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A9" s="4" t="s">
-        <x:v>202</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="B9" s="12" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C9" s="6" t="s">
-        <x:v>93</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D9" s="4" t="s">
-        <x:v>220</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="E9" s="6"/>
       <x:c r="F9" s="6"/>
       <x:c r="G9" s="6" t="s">
-        <x:v>87</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="H9" s="4"/>
       <x:c r="I9" s="3"/>
@@ -1963,21 +2035,21 @@
     </x:row>
     <x:row r="10" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A10" s="4" t="s">
-        <x:v>220</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="B10" s="13" t="s">
-        <x:v>249</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="C10" s="7" t="s">
-        <x:v>15</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="D10" s="4" t="s">
-        <x:v>189</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="E10" s="4"/>
       <x:c r="F10" s="7"/>
       <x:c r="G10" s="4" t="s">
-        <x:v>96</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H10" s="7"/>
       <x:c r="I10" s="3"/>
@@ -1993,21 +2065,21 @@
     </x:row>
     <x:row r="11" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A11" s="4" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="B11" s="12" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C11" s="7" t="s">
         <x:v>189</x:v>
       </x:c>
-      <x:c r="B11" s="12" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C11" s="7" t="s">
-        <x:v>232</x:v>
-      </x:c>
       <x:c r="D11" s="4" t="s">
-        <x:v>200</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="E11" s="7"/>
       <x:c r="F11" s="7"/>
       <x:c r="G11" s="4" t="s">
-        <x:v>96</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H11" s="7"/>
       <x:c r="I11" s="3"/>
@@ -2023,21 +2095,21 @@
     </x:row>
     <x:row r="12" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A12" s="4" t="s">
-        <x:v>200</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="B12" s="13" t="s">
-        <x:v>249</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="C12" s="6" t="s">
-        <x:v>257</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="D12" s="4" t="s">
-        <x:v>209</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="E12" s="6"/>
       <x:c r="F12" s="6"/>
       <x:c r="G12" s="4" t="s">
-        <x:v>96</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H12" s="6"/>
       <x:c r="I12" s="3"/>
@@ -2053,21 +2125,21 @@
     </x:row>
     <x:row r="13" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A13" s="4" t="s">
-        <x:v>209</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="B13" s="12" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C13" s="4" t="s">
-        <x:v>149</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="D13" s="4" t="s">
-        <x:v>207</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="E13" s="4"/>
       <x:c r="F13" s="4"/>
       <x:c r="G13" s="4" t="s">
-        <x:v>96</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H13" s="4"/>
       <x:c r="I13" s="3"/>
@@ -2083,21 +2155,21 @@
     </x:row>
     <x:row r="14" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A14" s="4" t="s">
-        <x:v>207</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="B14" s="13" t="s">
-        <x:v>249</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="C14" s="7" t="s">
-        <x:v>9</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D14" s="4" t="s">
-        <x:v>185</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="E14" s="7"/>
       <x:c r="F14" s="7"/>
       <x:c r="G14" s="4" t="s">
-        <x:v>96</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H14" s="7"/>
       <x:c r="I14" s="3"/>
@@ -2113,21 +2185,21 @@
     </x:row>
     <x:row r="15" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A15" s="4" t="s">
-        <x:v>185</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="B15" s="13" t="s">
-        <x:v>249</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="C15" s="7" t="s">
-        <x:v>141</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="D15" s="4" t="s">
-        <x:v>159</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="E15" s="6"/>
       <x:c r="F15" s="7"/>
       <x:c r="G15" s="6" t="s">
-        <x:v>87</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="H15" s="7"/>
       <x:c r="I15" s="3"/>
@@ -2143,1863 +2215,2052 @@
     </x:row>
     <x:row r="16" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A16" s="4" t="s">
-        <x:v>159</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="B16" s="12" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C16" s="8" t="s">
-        <x:v>153</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="D16" s="4" t="s">
-        <x:v>179</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="E16" s="8"/>
       <x:c r="F16" s="8"/>
       <x:c r="G16" s="6" t="s">
-        <x:v>87</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="H16" s="8"/>
     </x:row>
     <x:row r="17" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A17" s="4" t="s">
-        <x:v>179</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="B17" s="13" t="s">
-        <x:v>249</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="C17" s="9" t="s">
-        <x:v>107</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D17" s="4" t="s">
-        <x:v>171</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="E17" s="4"/>
       <x:c r="F17" s="8"/>
       <x:c r="G17" s="4" t="s">
-        <x:v>96</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H17" s="9"/>
     </x:row>
     <x:row r="18" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A18" s="4" t="s">
-        <x:v>171</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="B18" s="12" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C18" s="9" t="s">
-        <x:v>5</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D18" s="4" t="s">
-        <x:v>170</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="E18" s="8"/>
       <x:c r="F18" s="8"/>
       <x:c r="G18" s="4" t="s">
-        <x:v>96</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H18" s="9"/>
     </x:row>
     <x:row r="19" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A19" s="4" t="s">
-        <x:v>170</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="B19" s="13" t="s">
-        <x:v>249</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="C19" s="9" t="s">
-        <x:v>238</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="D19" s="4" t="s">
-        <x:v>183</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="E19" s="8"/>
       <x:c r="F19" s="8"/>
       <x:c r="G19" s="4" t="s">
-        <x:v>96</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H19" s="9"/>
     </x:row>
     <x:row r="20" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A20" s="4" t="s">
-        <x:v>183</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="B20" s="12" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C20" s="9" t="s">
-        <x:v>88</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D20" s="4" t="s">
-        <x:v>188</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="E20" s="8"/>
       <x:c r="F20" s="8"/>
       <x:c r="G20" s="4" t="s">
-        <x:v>96</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H20" s="9"/>
     </x:row>
     <x:row r="21" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A21" s="4" t="s">
-        <x:v>188</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="B21" s="13" t="s">
-        <x:v>249</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="C21" s="9" t="s">
-        <x:v>77</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D21" s="4" t="s">
-        <x:v>199</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="E21" s="8"/>
       <x:c r="F21" s="8"/>
       <x:c r="G21" s="4" t="s">
-        <x:v>96</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H21" s="9"/>
     </x:row>
     <x:row r="22" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A22" s="4" t="s">
-        <x:v>199</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="B22" s="12" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C22" s="9" t="s">
-        <x:v>104</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D22" s="4" t="s">
-        <x:v>158</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="E22" s="8"/>
       <x:c r="F22" s="8"/>
       <x:c r="G22" s="4" t="s">
-        <x:v>96</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H22" s="9"/>
     </x:row>
     <x:row r="23" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A23" s="4" t="s">
-        <x:v>158</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="B23" s="12" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C23" s="9" t="s">
-        <x:v>86</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D23" s="4" t="s">
-        <x:v>169</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E23" s="8"/>
       <x:c r="F23" s="8"/>
       <x:c r="G23" s="4" t="s">
-        <x:v>96</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H23" s="9"/>
     </x:row>
     <x:row r="24" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A24" s="4" t="s">
-        <x:v>169</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="B24" s="12" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C24" s="9" t="s">
-        <x:v>84</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D24" s="4" t="s">
-        <x:v>178</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="E24" s="8"/>
       <x:c r="F24" s="8"/>
       <x:c r="G24" s="4" t="s">
-        <x:v>96</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H24" s="9"/>
     </x:row>
     <x:row r="25" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A25" s="4" t="s">
-        <x:v>178</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="B25" s="12" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C25" s="9" t="s">
-        <x:v>119</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D25" s="4" t="s">
-        <x:v>175</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="E25" s="8"/>
       <x:c r="F25" s="8"/>
       <x:c r="G25" s="4" t="s">
-        <x:v>96</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H25" s="9"/>
     </x:row>
     <x:row r="26" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A26" s="4" t="s">
-        <x:v>175</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="B26" s="12" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C26" s="10" t="s">
-        <x:v>98</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D26" s="4" t="s">
-        <x:v>198</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="E26" s="10"/>
       <x:c r="F26" s="10"/>
       <x:c r="G26" s="4" t="s">
-        <x:v>96</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H26" s="10"/>
     </x:row>
     <x:row r="27" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A27" s="4" t="s">
-        <x:v>198</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="B27" s="13" t="s">
-        <x:v>249</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="C27" s="10" t="s">
-        <x:v>79</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D27" s="4" t="s">
-        <x:v>172</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="E27" s="10"/>
       <x:c r="F27" s="10"/>
       <x:c r="G27" s="4" t="s">
-        <x:v>96</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H27" s="10"/>
     </x:row>
     <x:row r="28" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A28" s="4" t="s">
-        <x:v>172</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="B28" s="12" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C28" s="10" t="s">
-        <x:v>132</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="D28" s="4" t="s">
-        <x:v>167</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="E28" s="10"/>
       <x:c r="F28" s="10"/>
       <x:c r="G28" s="4" t="s">
-        <x:v>96</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H28" s="10"/>
     </x:row>
     <x:row r="29" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A29" s="4" t="s">
-        <x:v>167</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="B29" s="13" t="s">
-        <x:v>249</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="C29" s="10" t="s">
-        <x:v>256</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="D29" s="4" t="s">
-        <x:v>181</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="E29" s="6"/>
       <x:c r="F29" s="10"/>
       <x:c r="G29" s="6" t="s">
-        <x:v>87</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="H29" s="10"/>
     </x:row>
     <x:row r="30" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A30" s="4" t="s">
-        <x:v>181</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="B30" s="12" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C30" s="10" t="s">
-        <x:v>233</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="D30" s="4" t="s">
-        <x:v>163</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="E30" s="10"/>
       <x:c r="F30" s="10"/>
       <x:c r="G30" s="6" t="s">
-        <x:v>87</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="H30" s="10"/>
     </x:row>
     <x:row r="31" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A31" s="4" t="s">
-        <x:v>163</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="B31" s="13" t="s">
-        <x:v>249</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="C31" s="10" t="s">
-        <x:v>115</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D31" s="4" t="s">
-        <x:v>161</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="E31" s="4"/>
       <x:c r="F31" s="10"/>
       <x:c r="G31" s="4" t="s">
-        <x:v>96</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H31" s="10"/>
     </x:row>
     <x:row r="32" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A32" s="4" t="s">
-        <x:v>161</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="B32" s="12" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C32" s="11" t="s">
-        <x:v>78</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D32" s="4" t="s">
-        <x:v>180</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="E32" s="11"/>
       <x:c r="F32" s="11"/>
       <x:c r="G32" s="4" t="s">
-        <x:v>96</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H32" s="11"/>
     </x:row>
     <x:row r="33" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A33" s="4" t="s">
-        <x:v>180</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="B33" s="13" t="s">
-        <x:v>249</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="C33" s="11" t="s">
-        <x:v>114</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D33" s="4" t="s">
-        <x:v>174</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="E33" s="11"/>
       <x:c r="F33" s="11"/>
       <x:c r="G33" s="4" t="s">
-        <x:v>96</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H33" s="11"/>
     </x:row>
     <x:row r="34" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A34" s="4" t="s">
-        <x:v>174</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="B34" s="12" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C34" s="11" t="s">
-        <x:v>78</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D34" s="4" t="s">
-        <x:v>173</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="E34" s="11"/>
       <x:c r="F34" s="11"/>
       <x:c r="G34" s="4" t="s">
-        <x:v>96</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H34" s="11"/>
     </x:row>
     <x:row r="35" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A35" s="4" t="s">
-        <x:v>173</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="B35" s="13" t="s">
-        <x:v>249</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="C35" s="11" t="s">
-        <x:v>7</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D35" s="4" t="s">
-        <x:v>182</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="E35" s="11"/>
       <x:c r="F35" s="17"/>
       <x:c r="G35" s="4" t="s">
-        <x:v>96</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H35" s="11"/>
     </x:row>
     <x:row r="36" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A36" s="4" t="s">
-        <x:v>182</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="B36" s="13" t="s">
-        <x:v>249</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="C36" t="s">
-        <x:v>99</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D36" s="4" t="s">
-        <x:v>164</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="G36" s="4" t="s">
-        <x:v>96</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A37" s="4" t="s">
-        <x:v>164</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="B37" s="13" t="s">
-        <x:v>249</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="C37" t="s">
-        <x:v>123</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D37" s="4" t="s">
-        <x:v>186</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="G37" s="4" t="s">
-        <x:v>96</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A38" s="4" t="s">
-        <x:v>186</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="B38" s="13" t="s">
-        <x:v>249</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="C38" t="s">
-        <x:v>103</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D38" s="4" t="s">
-        <x:v>205</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="G38" s="4" t="s">
-        <x:v>96</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A39" s="4" t="s">
-        <x:v>205</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="B39" s="12" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C39" t="s">
-        <x:v>235</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="D39" s="4" t="s">
-        <x:v>194</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="G39" s="4" t="s">
-        <x:v>96</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A40" s="4" t="s">
-        <x:v>194</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="B40" s="13" t="s">
-        <x:v>249</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="C40" t="s">
-        <x:v>117</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D40" s="4" t="s">
-        <x:v>160</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="G40" s="4" t="s">
-        <x:v>96</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A41" s="4" t="s">
-        <x:v>160</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="B41" s="13" t="s">
-        <x:v>249</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="C41" t="s">
-        <x:v>108</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D41" s="4" t="s">
-        <x:v>176</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="G41" s="4" t="s">
-        <x:v>96</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A42" s="4" t="s">
-        <x:v>176</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="B42" s="13" t="s">
-        <x:v>249</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="C42" t="s">
-        <x:v>101</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D42" s="4" t="s">
-        <x:v>166</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="G42" s="4" t="s">
-        <x:v>96</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A43" s="4" t="s">
-        <x:v>166</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="B43" s="13" t="s">
-        <x:v>249</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="C43" t="s">
-        <x:v>124</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D43" s="4" t="s">
-        <x:v>196</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="G43" s="4" t="s">
-        <x:v>96</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A44" s="4" t="s">
-        <x:v>196</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="B44" s="12" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C44" t="s">
-        <x:v>92</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D44" s="4" t="s">
-        <x:v>211</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="G44" s="4" t="s">
-        <x:v>96</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A45" s="4" t="s">
-        <x:v>211</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="B45" s="13" t="s">
-        <x:v>249</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="C45" t="s">
-        <x:v>246</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="D45" s="4" t="s">
-        <x:v>162</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="G45" s="4" t="s">
-        <x:v>96</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A46" s="4" t="s">
-        <x:v>162</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="B46" s="12" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C46" t="s">
-        <x:v>242</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="D46" s="4" t="s">
-        <x:v>201</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="G46" s="4" t="s">
-        <x:v>96</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A47" s="4" t="s">
-        <x:v>201</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="C47" t="s">
-        <x:v>110</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D47" s="4"/>
       <x:c r="G47" s="4" t="s">
-        <x:v>96</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A48" s="18" t="s">
-        <x:v>192</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="B48" s="13" t="s">
-        <x:v>249</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="C48" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D48" s="18" t="s">
-        <x:v>229</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="G48" s="6" t="s">
-        <x:v>87</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A49" s="18" t="s">
-        <x:v>229</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="B49" s="13" t="s">
-        <x:v>249</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="C49" t="s">
-        <x:v>142</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="D49" s="18" t="s">
-        <x:v>225</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="G49" s="6" t="s">
-        <x:v>87</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A50" s="18" t="s">
-        <x:v>225</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="B50" s="13" t="s">
-        <x:v>249</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="C50" t="s">
-        <x:v>19</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="D50" s="18" t="s">
-        <x:v>216</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="G50" s="4" t="s">
-        <x:v>96</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A51" s="18" t="s">
-        <x:v>216</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="B51" s="13" t="s">
-        <x:v>249</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="C51" t="s">
-        <x:v>85</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D51" s="18" t="s">
-        <x:v>227</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="G51" s="4" t="s">
-        <x:v>96</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A52" s="18" t="s">
-        <x:v>227</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="B52" s="13" t="s">
-        <x:v>249</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="C52" t="s">
-        <x:v>122</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D52" s="18" t="s">
-        <x:v>213</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="G52" s="4" t="s">
-        <x:v>96</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A53" s="18" t="s">
-        <x:v>213</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="B53" s="13" t="s">
-        <x:v>249</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="C53" t="s">
-        <x:v>127</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D53" s="18" t="s">
-        <x:v>226</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="G53" s="4" t="s">
-        <x:v>96</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A54" s="18" t="s">
-        <x:v>226</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="B54" s="13" t="s">
-        <x:v>249</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="C54" t="s">
-        <x:v>118</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D54" s="18" t="s">
-        <x:v>218</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="G54" s="4" t="s">
-        <x:v>96</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A55" s="18" t="s">
-        <x:v>218</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="B55" s="12" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C55" t="s">
-        <x:v>78</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D55" s="18" t="s">
-        <x:v>224</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="G55" s="4" t="s">
-        <x:v>96</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A56" s="18" t="s">
-        <x:v>224</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="B56" s="13" t="s">
-        <x:v>249</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="C56" t="s">
-        <x:v>128</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D56" s="18" t="s">
-        <x:v>228</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="G56" s="4" t="s">
-        <x:v>96</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A57" s="18" t="s">
-        <x:v>228</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="B57" s="13" t="s">
-        <x:v>249</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="C57" t="s">
-        <x:v>248</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="D57" s="18" t="s">
-        <x:v>206</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="G57" s="4" t="s">
-        <x:v>96</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A58" s="18" t="s">
-        <x:v>206</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="B58" s="12" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C58" t="s">
-        <x:v>150</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="D58" s="18" t="s">
-        <x:v>219</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="G58" s="4" t="s">
-        <x:v>96</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A59" s="18" t="s">
-        <x:v>219</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="C59" t="s">
-        <x:v>106</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="G59" s="4" t="s">
-        <x:v>96</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A60" s="18" t="s">
-        <x:v>191</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="B60" s="12" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C60" t="s">
-        <x:v>139</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="D60" s="18" t="s">
-        <x:v>214</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="G60" s="4" t="s">
-        <x:v>96</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A61" s="18" t="s">
-        <x:v>214</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="B61" s="13" t="s">
-        <x:v>249</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="C61" t="s">
-        <x:v>134</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="D61" s="18" t="s">
-        <x:v>203</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="G61" s="4" t="s">
-        <x:v>89</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A62" s="18" t="s">
-        <x:v>203</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="B62" s="12" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C62" t="s">
-        <x:v>130</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="D62" s="18" t="s">
-        <x:v>210</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="G62" s="4" t="s">
-        <x:v>96</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A63" s="18" t="s">
-        <x:v>210</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="B63" s="13" t="s">
-        <x:v>249</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="C63" t="s">
-        <x:v>82</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D63" s="18" t="s">
-        <x:v>195</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="G63" s="4" t="s">
-        <x:v>96</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A64" s="18" t="s">
-        <x:v>195</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="B64" s="13" t="s">
-        <x:v>249</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="C64" t="s">
-        <x:v>11</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D64" s="18" t="s">
-        <x:v>197</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="G64" s="4" t="s">
-        <x:v>109</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A65" s="18" t="s">
-        <x:v>197</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="B65" s="12" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C65" t="s">
-        <x:v>76</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D65" s="18" t="s">
-        <x:v>215</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="G65" s="4" t="s">
-        <x:v>109</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A66" s="18" t="s">
-        <x:v>215</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B66" s="13" t="s">
-        <x:v>249</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="C66" t="s">
-        <x:v>113</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D66" s="18" t="s">
-        <x:v>212</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="G66" s="4" t="s">
-        <x:v>96</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A67" s="18" t="s">
-        <x:v>212</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="B67" s="13" t="s">
-        <x:v>249</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="C67" t="s">
-        <x:v>2</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D67" s="18" t="s">
-        <x:v>193</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="G67" s="4" t="s">
-        <x:v>96</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A68" s="18" t="s">
-        <x:v>193</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="B68" s="13" t="s">
-        <x:v>249</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="C68" t="s">
-        <x:v>126</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D68" s="18" t="s">
-        <x:v>208</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="G68" s="4" t="s">
-        <x:v>96</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A69" s="18" t="s">
-        <x:v>208</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="B69" s="12" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C69" t="s">
-        <x:v>147</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="D69" s="18" t="s">
-        <x:v>223</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="G69" s="4" t="s">
-        <x:v>96</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A70" s="18" t="s">
-        <x:v>223</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="B70" s="13" t="s">
-        <x:v>249</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="C70" t="s">
-        <x:v>135</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="D70" s="18" t="s">
-        <x:v>217</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="G70" s="4" t="s">
-        <x:v>96</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A71" s="18" t="s">
-        <x:v>217</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="B71" s="12" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C71" t="s">
-        <x:v>154</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="D71" s="18" t="s">
-        <x:v>221</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="G71" s="4" t="s">
-        <x:v>96</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A72" s="18" t="s">
-        <x:v>221</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="B72" s="12" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C72" t="s">
-        <x:v>3</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G72" s="4"/>
     </x:row>
     <x:row r="73" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A73" s="4" t="s">
-        <x:v>68</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B73" t="s">
-        <x:v>0</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="C73" t="s">
-        <x:v>140</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="D73" s="4" t="s">
-        <x:v>72</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="G73" s="4" t="s">
-        <x:v>94</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A74" s="4" t="s">
-        <x:v>72</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B74" s="19" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C74" t="s">
-        <x:v>4</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D74" s="4" t="s">
-        <x:v>53</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="G74" s="4" t="s">
-        <x:v>94</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A75" s="4" t="s">
-        <x:v>53</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B75" s="12"/>
       <x:c r="C75" t="s">
-        <x:v>253</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="D75" s="4"/>
       <x:c r="G75" s="4" t="s">
-        <x:v>94</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A76" s="4" t="s">
-        <x:v>44</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B76" s="12" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C76" t="s">
-        <x:v>80</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D76" s="4" t="s">
-        <x:v>25</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="G76" s="4" t="s">
-        <x:v>94</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A77" s="4" t="s">
-        <x:v>25</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="B77" t="s">
-        <x:v>0</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="C77" t="s">
-        <x:v>78</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D77" s="4" t="s">
-        <x:v>38</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="G77" s="4" t="s">
-        <x:v>91</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A78" s="4" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="B78" t="s">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="C78" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="B78" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C78" t="s">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="D78" s="4" t="s">
-        <x:v>73</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="G78" s="4" t="s">
-        <x:v>91</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A79" s="4" t="s">
-        <x:v>73</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B79" t="s">
-        <x:v>0</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="C79" t="s">
-        <x:v>95</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D79" s="4" t="s">
-        <x:v>66</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G79" s="4" t="s">
-        <x:v>94</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A80" s="4" t="s">
-        <x:v>66</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B80" s="12" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C80" t="s">
-        <x:v>143</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="D80" s="4" t="s">
-        <x:v>65</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="G80" s="4" t="s">
-        <x:v>94</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A81" s="4" t="s">
-        <x:v>65</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B81" t="s">
-        <x:v>0</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="C81" t="s">
-        <x:v>36</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="G81" s="4" t="s">
-        <x:v>94</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A82" s="4" t="s">
-        <x:v>41</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B82" s="12" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C82" t="s">
-        <x:v>236</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="D82" t="s">
-        <x:v>24</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="G82" s="4" t="s">
-        <x:v>94</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A83" s="4" t="s">
-        <x:v>24</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="B83" t="s">
-        <x:v>0</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="C83" t="s">
-        <x:v>74</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D83" t="s">
-        <x:v>27</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="G83" s="4" t="s">
-        <x:v>90</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A84" s="4" t="s">
-        <x:v>27</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="B84" s="12" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C84" t="s">
-        <x:v>136</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="D84" t="s">
-        <x:v>14</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="G84" s="4" t="s">
-        <x:v>90</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A85" s="4" t="s">
-        <x:v>14</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="B85" t="s">
-        <x:v>0</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="C85" t="s">
-        <x:v>112</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D85" t="s">
-        <x:v>17</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="G85" s="4" t="s">
-        <x:v>90</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A86" s="4" t="s">
-        <x:v>17</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="B86" s="12" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C86" t="s">
-        <x:v>234</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="D86" t="s">
-        <x:v>18</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="G86" s="4" t="s">
-        <x:v>90</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A87" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="B87" s="12" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C87" t="s">
-        <x:v>255</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="D87" t="s">
-        <x:v>42</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="G87" s="4" t="s">
-        <x:v>90</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A88" s="4" t="s">
-        <x:v>42</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B88" t="s">
-        <x:v>0</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="C88" t="s">
-        <x:v>97</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D88" t="s">
-        <x:v>29</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="G88" s="4" t="s">
-        <x:v>94</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A89" s="4" t="s">
-        <x:v>29</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="B89" t="s">
-        <x:v>0</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="C89" t="s">
-        <x:v>75</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D89" t="s">
-        <x:v>16</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="G89" s="4" t="s">
-        <x:v>94</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A90" s="4" t="s">
-        <x:v>16</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="B90" s="12" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C90" t="s">
-        <x:v>168</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="D90" t="s">
-        <x:v>21</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="G90" s="4" t="s">
-        <x:v>94</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A91" s="4" t="s">
-        <x:v>21</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="B91" t="s">
-        <x:v>0</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="C91" t="s">
-        <x:v>247</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="G91" s="4" t="s">
-        <x:v>94</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A92" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B92" s="12" t="s">
-        <x:v>83</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C92" t="s">
-        <x:v>239</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="D92" t="s">
-        <x:v>22</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="G92" s="4" t="s">
-        <x:v>69</x:v>
+        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A93" s="4" t="s">
-        <x:v>22</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="B93" s="12" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C93" t="s">
-        <x:v>146</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="D93" t="s">
-        <x:v>64</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="G93" s="4" t="s">
-        <x:v>69</x:v>
+        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A94" s="4" t="s">
-        <x:v>64</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B94" s="12" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C94" t="s">
-        <x:v>78</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D94" t="s">
-        <x:v>43</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="G94" s="4" t="s">
-        <x:v>69</x:v>
+        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A95" s="4" t="s">
-        <x:v>43</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B95" s="12" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C95" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D95" t="s">
-        <x:v>40</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="G95" s="4" t="s">
-        <x:v>69</x:v>
+        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A96" s="4" t="s">
-        <x:v>40</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B96" s="12" t="s">
-        <x:v>83</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C96" t="s">
-        <x:v>102</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D96" t="s">
-        <x:v>34</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="G96" s="4" t="s">
-        <x:v>69</x:v>
+        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A97" s="4" t="s">
-        <x:v>34</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="B97" s="12" t="s">
-        <x:v>83</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C97" t="s">
-        <x:v>144</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="D97" t="s">
-        <x:v>33</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="G97" s="4" t="s">
-        <x:v>31</x:v>
+        <x:v>159</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A98" s="4" t="s">
-        <x:v>33</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="B98" s="12" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C98" t="s">
-        <x:v>152</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="D98" t="s">
-        <x:v>32</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="G98" s="4" t="s">
-        <x:v>31</x:v>
+        <x:v>159</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A99" s="4" t="s">
-        <x:v>32</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="B99" s="12" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C99" t="s">
-        <x:v>250</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="D99" t="s">
-        <x:v>28</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="G99" s="4" t="s">
-        <x:v>31</x:v>
+        <x:v>159</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A100" s="4" t="s">
-        <x:v>28</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="B100" s="12" t="s">
-        <x:v>83</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C100" t="s">
-        <x:v>129</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D100" t="s">
-        <x:v>26</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="G100" s="4" t="s">
-        <x:v>31</x:v>
+        <x:v>159</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A101" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="B101" s="12" t="s">
-        <x:v>83</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C101" t="s">
-        <x:v>50</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D101" t="s">
-        <x:v>48</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="G101" s="4" t="s">
-        <x:v>31</x:v>
+        <x:v>159</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A102" s="4" t="s">
-        <x:v>48</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B102" s="12" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C102" t="s">
-        <x:v>133</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="D102" t="s">
-        <x:v>39</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="G102" s="4" t="s">
-        <x:v>31</x:v>
+        <x:v>159</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A103" s="4" t="s">
-        <x:v>39</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="B103" s="12" t="s">
-        <x:v>83</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C103" t="s">
-        <x:v>23</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="G103" s="4" t="s">
-        <x:v>31</x:v>
+        <x:v>159</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A104" s="4" t="s">
-        <x:v>51</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B104" s="12" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C104" t="s">
-        <x:v>231</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="D104" t="s">
-        <x:v>58</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="G104" s="18" t="s">
-        <x:v>31</x:v>
+        <x:v>159</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A105" s="4" t="s">
-        <x:v>58</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B105" s="12" t="s">
-        <x:v>83</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C105" t="s">
-        <x:v>237</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="D105" t="s">
-        <x:v>55</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="G105" s="4" t="s">
-        <x:v>222</x:v>
+        <x:v>264</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A106" s="4" t="s">
-        <x:v>55</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B106" s="12" t="s">
-        <x:v>83</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C106" t="s">
-        <x:v>252</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="D106" t="s">
-        <x:v>67</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G106" s="4" t="s">
-        <x:v>222</x:v>
+        <x:v>264</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A107" s="4" t="s">
-        <x:v>67</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B107" s="12" t="s">
-        <x:v>83</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C107" t="s">
-        <x:v>13</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D107" t="s">
-        <x:v>71</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="G107" s="4" t="s">
-        <x:v>222</x:v>
+        <x:v>264</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A108" s="4" t="s">
-        <x:v>71</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B108" s="12" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C108" t="s">
-        <x:v>56</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="G108" s="4" t="s">
-        <x:v>222</x:v>
+        <x:v>264</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A109" s="4" t="s">
-        <x:v>30</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="B109" s="12" t="s">
-        <x:v>83</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C109" t="s">
-        <x:v>165</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="D109" t="s">
-        <x:v>61</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="G109" s="18" t="s">
-        <x:v>57</x:v>
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A110" s="4" t="s">
-        <x:v>61</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B110" s="12" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C110" t="s">
-        <x:v>100</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D110" t="s">
-        <x:v>70</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="G110" s="18" t="s">
-        <x:v>57</x:v>
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A111" s="4" t="s">
-        <x:v>70</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B111" s="12" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C111" t="s">
-        <x:v>105</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D111" t="s">
-        <x:v>59</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="G111" s="18" t="s">
-        <x:v>57</x:v>
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A112" s="4" t="s">
-        <x:v>59</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B112" s="12" t="s">
-        <x:v>83</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C112" t="s">
-        <x:v>120</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D112" t="s">
-        <x:v>63</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="G112" s="18" t="s">
-        <x:v>31</x:v>
+        <x:v>159</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A113" s="4" t="s">
-        <x:v>63</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B113" s="12" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C113" t="s">
-        <x:v>243</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="D113" t="s">
-        <x:v>60</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="G113" s="18" t="s">
-        <x:v>31</x:v>
+        <x:v>159</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A114" s="4" t="s">
-        <x:v>60</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B114" s="12" t="s">
-        <x:v>83</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C114" t="s">
-        <x:v>121</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D114" t="s">
-        <x:v>52</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="G114" s="18" t="s">
-        <x:v>31</x:v>
+        <x:v>159</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A115" s="4" t="s">
-        <x:v>52</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B115" s="12" t="s">
-        <x:v>83</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C115" t="s">
-        <x:v>20</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="D115" t="s">
-        <x:v>54</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="G115" s="18" t="s">
-        <x:v>31</x:v>
+        <x:v>159</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A116" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B116" s="12" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C116" t="s">
-        <x:v>244</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="D116" t="s">
-        <x:v>46</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="G116" s="18" t="s">
-        <x:v>31</x:v>
+        <x:v>159</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A117" s="4" t="s">
-        <x:v>46</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B117" s="12" t="s">
-        <x:v>83</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C117" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="D117" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="D117" t="s">
-        <x:v>62</x:v>
-      </x:c>
       <x:c r="G117" s="18" t="s">
-        <x:v>31</x:v>
+        <x:v>159</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A118" s="4" t="s">
-        <x:v>62</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B118" s="12" t="s">
-        <x:v>83</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C118" t="s">
-        <x:v>116</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D118" t="s">
-        <x:v>47</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="G118" s="18" t="s">
-        <x:v>31</x:v>
+        <x:v>159</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A119" s="4" t="s">
-        <x:v>47</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B119" s="12" t="s">
-        <x:v>83</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C119" t="s">
-        <x:v>254</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="D119" t="s">
-        <x:v>45</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="G119" s="18" t="s">
-        <x:v>31</x:v>
+        <x:v>159</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A120" s="4" t="s">
-        <x:v>45</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B120" s="12" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C120" t="s">
-        <x:v>137</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="D120" t="s">
-        <x:v>49</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="G120" s="18" t="s">
-        <x:v>31</x:v>
+        <x:v>159</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A121" s="4" t="s">
-        <x:v>49</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B121" s="12" t="s">
-        <x:v>83</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C121" t="s">
-        <x:v>125</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D121" t="s">
-        <x:v>37</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="G121" s="18" t="s">
-        <x:v>31</x:v>
+        <x:v>159</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A122" s="4" t="s">
-        <x:v>37</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="B122" s="12" t="s">
-        <x:v>83</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C122" t="s">
-        <x:v>258</x:v>
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="D122" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G122" s="18" t="s">
-        <x:v>31</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="123" ht="15.75" customHeight="1"/>
-    <x:row r="124" ht="15.75" customHeight="1"/>
-    <x:row r="125" ht="15.75" customHeight="1"/>
-    <x:row r="126" ht="15.75" customHeight="1"/>
-    <x:row r="127" ht="15.75" customHeight="1"/>
-    <x:row r="128" ht="15.75" customHeight="1"/>
-    <x:row r="129" ht="15.75" customHeight="1"/>
-    <x:row r="130" ht="15.75" customHeight="1"/>
-    <x:row r="131" ht="15.75" customHeight="1"/>
-    <x:row r="132" ht="15.75" customHeight="1"/>
-    <x:row r="133" ht="15.75" customHeight="1"/>
-    <x:row r="134" ht="15.75" customHeight="1"/>
-    <x:row r="135" ht="15.75" customHeight="1"/>
-    <x:row r="136" ht="15.75" customHeight="1"/>
-    <x:row r="137" ht="15.75" customHeight="1"/>
+        <x:v>159</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123" spans="1:4" ht="15.75" customHeight="1">
+      <x:c r="A123" s="4" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B123" s="12" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C123" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D123" t="s">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124" spans="1:4" ht="15.75" customHeight="1">
+      <x:c r="A124" s="4" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B124" s="12" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C124" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="D124" t="s">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125" spans="1:4" ht="15.75" customHeight="1">
+      <x:c r="A125" s="4" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B125" s="12" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C125" t="s">
+        <x:v>281</x:v>
+      </x:c>
+      <x:c r="D125" t="s">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="126" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A126" s="4" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B126" s="12" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="C126" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="D126" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="G126" s="18" t="s">
+        <x:v>164</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="127" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A127" s="4" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B127" s="12" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C127" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="D127" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G127" s="18" t="s">
+        <x:v>164</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A128" s="4" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B128" s="12" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="C128" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="D128" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G128" s="18" t="s">
+        <x:v>164</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="129" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A129" s="4" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B129" s="12" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C129" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="D129" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G129" s="18" t="s">
+        <x:v>164</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="130" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A130" s="4" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B130" s="12" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="C130" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D130" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G130" s="18" t="s">
+        <x:v>164</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A131" s="4" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B131" s="12" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="C131" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="D131" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G131" s="18" t="s">
+        <x:v>164</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A132" s="4" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B132" s="12" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C132" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="D132" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="G132" s="18" t="s">
+        <x:v>164</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A133" s="4" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B133" s="12" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="C133" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D133" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G133" s="18" t="s">
+        <x:v>164</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="134" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A134" s="4" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B134" s="12" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="C134" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="G134" s="18" t="s">
+        <x:v>164</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="135" spans="1:1" ht="15.75" customHeight="1">
+      <x:c r="A135" s="4"/>
+    </x:row>
+    <x:row r="136" spans="1:1" ht="15.75" customHeight="1">
+      <x:c r="A136" s="4"/>
+    </x:row>
+    <x:row r="137" spans="1:1" ht="15.75" customHeight="1">
+      <x:c r="A137" s="4"/>
+    </x:row>
     <x:row r="138" ht="15.75" customHeight="1"/>
     <x:row r="139" ht="15.75" customHeight="1"/>
     <x:row r="140" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/MainDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/MainDialogue.xlsx
@@ -16,853 +16,853 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="283">
   <x:si>
+    <x:t>애송아, 나는 남자야. 성인이라고. 내가 취할 생각이 없었다면, 대체 뭐하러 술집에 왔을거라고 생각하나?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>카모트린은 음료의 알콜 도수를 결정하지. 맛은 변화시키지 못하지만, 알콜의 효과는 그대로 가지고 있어.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(게다가 포어에게 중성화 수술을 시켜주느라 지갑 속 마지막 동전 하나까지 다써버렸지. 월세를 한번만 더 미뤘다간 쫒겨날거야...)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>내가 방금 한 말 들었어?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그래. 잡아둬서 미안.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>거기 너! 맥주 한잔 줘</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그래, 이제 막 끝났어.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>음...방금 그건 뭐였죠?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NextDialogueId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>음..뭐, 감사합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어떤걸로 드릴까요, 세이?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>음..다른걸 만들어보자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>미안, 무슨 말 했어?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CharacterDataId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자, 충분히 오래 놀아줬지?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그럼 이제 일을 시작하자고.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오늘 밤은 여기까지인가?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이렇게 하루가 끝났군.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Texture2D/Character_Gillian_Smile</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Texture2D/Character_Gillian_Dismay</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Texture2D/Character_Donoban_Smile</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Texture2D/Character_Donoban_Basic</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Texture2D/Character_Gillian_Basic</x:t>
+  </x:si>
+  <x:si>
+    <x:t>다시 해보자고. 맥주 한잔 줘. 보리 맥, 술 주. 맥.주.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Texture2D/Character_Donoban_Dismay</x:t>
+  </x:si>
+  <x:si>
+    <x:t>길리안, 나 공식적인 BTC 교육을 받고 여기 온 거거든?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>음, 매월 30일에 월세를 내는게 엄청 스트레스거든, 그리고-</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대체 언제쯤이면 네가 존같이 생겼다는 걸 인정할거야, 길?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>저기 보스, 제가 "보스"라고 부르면 좀 차갑게 들리나요?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(이틀 전에는 이곳이 폐쇄될 위기에 처했다는 것까지 알게됐지)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>측면에 있는 얼음과 숙성 버튼 중 필요한 걸 선택하면 돼.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(삶의 기반도 흔들리게 됐는데, 정신까지 나가버릴 지경이라고.)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>제가 원하는 음료는 아닌것 같아요...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그럼 문제없이 만들어 낼 수 있겠네!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SelectionDialogueIdList</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어떤 일을 하시나요, 손님? 성함이...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>character_donoban_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>음료 맛있었어요.. 다음에 또 올게요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>character_gillian_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>괜찮아? 생각이 다른데 가있는 것 같은데.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>맥주를 원하는군. 덩치가 꽤 커보이는데.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>내가 말했던 것들을 잘 떠올리면서 만들어!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>으음.. 너 덕분에 잘 마시고 간다고.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어떤걸로 드릴까요, 어, 성함이..?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>...정말 오늘 일할 수 있는 거 맞아?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"우리는 감시하고, 또한 수호한다!"</x:t>
+  </x:si>
+  <x:si>
+    <x:t>응?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>여기요</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그래.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>질!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감사합니다. 다음에 또 오세요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오늘자 봉급은 계좌로 넣어줄게.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>character_boss_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>다시 만들어주셨으면 좋겠어요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>별거 아니야 조금 생각할게 있어서.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>글쎄. 뭣 좀 사러 밖에 나갔...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>character_sei_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>character_jill_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>저 헬멧은 벗어주시지 않을래요?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>술을 섞고 삶을 바꿔줄 시간이군.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아, 그래! 잊기 전에 하나만 더!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이건...내가 원하던게 아니야.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아! 물론이죠, 곧 나갑니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SelectionNameList</x:t>
+  </x:si>
+  <x:si>
+    <x:t>우선 슈가 러쉬부터 시작해보자.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>칵테일 조합법에 있는 탐색 막대를 이용해 레시피를 확인해 봐. 왼쪽 상단에 표시될거야.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>너는 어그멘티드 아이의 편집장이자 소유주인 도노반 D.도슨님과 대화를 나누고 있는 거라고.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(아, 그러고 보니 내 아파트 방바닥에 맥주 캔들이 엄청나게 널브러져 있었지. 또...)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화이트 나이츠 손님은 그리 많지 않은데 말이죠, 사실 제대로 기억나는건 한명 뿐이지만요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"우리는 가장 어두운 시기에 타오르는 빛이자, 범죄의 희생양들을 도와주는 자!"</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그러고 난 다음, 섞기 버튼을 누르면 돼. 다시 눌러서 섞는 걸 멈출 수 있고.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그럼 우리 기초 과정부터 한번 다시 확인해 보자고. 괜찮지? 혹시 모르니까 말야</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아, 마지막 문장은 그렇게 신경쓰지 않아도 돼. 그냥 재밌는 뒷이야기 같은 거니까.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_1_3_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_1_010</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_2_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_1_000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_1_3_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_1_3_004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오히려, 그들의 뒷처리를 맡는 부대라고 할 수 있겠네요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_1_2_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_1_008</x:t>
+  </x:si>
+  <x:si>
+    <x:t>내가 너를 쥴스라고 부를 수 있게 허락해줄 때 쯤.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_1_004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_1_005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_1_3_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_1_009</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_1_3_005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_1_3_009</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_3_006</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_1_1_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_1_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Texture2D/Character_Sei_Basic</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_3_000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_1_3_007</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_1_3_008</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_1_007</x:t>
+  </x:si>
+  <x:si>
+    <x:t>제길, 질. 정신차려. 손님은 맥주를 원해! 맥.주!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_1_006</x:t>
+  </x:si>
+  <x:si>
+    <x:t>음료는 "온더록스" 혹은 숙성을 요구하는지 확인해야 해.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_1_011</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_3_013</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_1_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_1_2_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>음...작고, 달콤하고, 차가운..문블라스트가 좋겠네요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Texture2D/Character_Boss_Basic</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_3_023</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_3_012</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_3_015</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_1_2_003</x:t>
+  </x:si>
+  <x:si>
     <x:t>dialogue_mainDialogue_2_3_016</x:t>
   </x:si>
   <x:si>
+    <x:t>dialogue_mainDialogue_1_2_004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_2_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어찌됐건, 유리잔들 설거지 끝나고 나면 가도 좋아.</x:t>
+  </x:si>
+  <x:si>
     <x:t>dialogue_mainDialogue_2_3_014</x:t>
   </x:si>
   <x:si>
+    <x:t>dialogue_mainDialogue_2_3_025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Texture2D/Character_Sei_Meka</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_3_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_2_004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>음...이건 너무 길죠, 그냥 세이라고 불러주세요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_1_2_000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_3_010</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_3_024</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어떤기사도 내 손길이 닿지 않고 발간될 수는 없지.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그래, 이거 좋군. 정말 괜찮아. 아주 잘 했다 이거야.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_3_007</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_3_022</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_3_021</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_3_018</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_1_1_000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_3_019</x:t>
+  </x:si>
+  <x:si>
+    <x:t>다시한번 세이에게 문블라스트를 만들어주자. 문블라스트!</x:t>
+  </x:si>
+  <x:si>
     <x:t>dialogue_mainDialogue_2_3_017</x:t>
   </x:si>
   <x:si>
-    <x:t>dialogue_mainDialogue_2_3_019</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_3_015</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_3_022</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_3_021</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_3_025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_3_024</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_3_018</x:t>
-  </x:si>
-  <x:si>
     <x:t>dialogue_mainDialogue_2_3_020</x:t>
   </x:si>
   <x:si>
-    <x:t>dialogue_mainDialogue_2_3_023</x:t>
-  </x:si>
-  <x:si>
-    <x:t>우선 슈가 러쉬부터 시작해보자.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>글쎄. 뭣 좀 사러 밖에 나갔...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>술을 섞고 삶을 바꿔줄 시간이군.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>character_sei_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>별거 아니야 조금 생각할게 있어서.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아, 그래! 잊기 전에 하나만 더!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이건...내가 원하던게 아니야.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>character_jill_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>다시 만들어주셨으면 좋겠어요.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아! 물론이죠, 곧 나갑니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>저 헬멧은 벗어주시지 않을래요?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SelectionNameList</x:t>
-  </x:si>
-  <x:si>
-    <x:t>저기 보스, 제가 "보스"라고 부르면 좀 차갑게 들리나요?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>음, 매월 30일에 월세를 내는게 엄청 스트레스거든, 그리고-</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Texture2D/Character_Gillian_Smile</x:t>
-  </x:si>
-  <x:si>
-    <x:t>길리안, 나 공식적인 BTC 교육을 받고 여기 온 거거든?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대체 언제쯤이면 네가 존같이 생겼다는 걸 인정할거야, 길?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(이틀 전에는 이곳이 폐쇄될 위기에 처했다는 것까지 알게됐지)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Texture2D/Character_Gillian_Dismay</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Texture2D/Character_Donoban_Smile</x:t>
-  </x:si>
-  <x:si>
-    <x:t>다시 해보자고. 맥주 한잔 줘. 보리 맥, 술 주. 맥.주.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Texture2D/Character_Donoban_Dismay</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Texture2D/Character_Donoban_Basic</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Texture2D/Character_Gillian_Basic</x:t>
-  </x:si>
-  <x:si>
-    <x:t>측면에 있는 얼음과 숙성 버튼 중 필요한 걸 선택하면 돼.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(삶의 기반도 흔들리게 됐는데, 정신까지 나가버릴 지경이라고.)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>애송아, 나는 남자야. 성인이라고. 내가 취할 생각이 없었다면, 대체 뭐하러 술집에 왔을거라고 생각하나?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>카모트린은 음료의 알콜 도수를 결정하지. 맛은 변화시키지 못하지만, 알콜의 효과는 그대로 가지고 있어.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_1_2_004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_2_003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>응?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>여기요</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그래.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>질!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감사합니다. 다음에 또 오세요.</x:t>
+    <x:t>dialogue_mainDialogue_1_1_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_1_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_3_008</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_3_005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_3_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_1_3_006</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_3_011</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Texture2D/Character_Sei_Smile</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_3_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_1_2_005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_3_009</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_1_3_000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_2_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_3_004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_2_000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>만약에 레시피에 "카모트린 추가 가능"이라고 써져 있다면, 아예 넣지 않을 수도 잔 끝까지 채워 넣을 수도 있다는 의미야.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>내가 이 동네에서 미팅이 있었다는 사실에 감사하도록 해, 이딴 개떡 같은 곳은 나같은 분의 존재 자체로도 도움이 될테니까.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"구조하라, 치료하라, 보호하라! 우리는 적습으로 고통받는 자들에게 위안을 주는 천사들일지어니!"</x:t>
+  </x:si>
+  <x:si>
+    <x:t>길이 슈가 러쉬나 피아노 맨을 달라는군. 만약에 망쳤다면, 재시도 버튼을 눌러서 다시 하면 되겠지.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>발키리 군단 제 765부대 소속 특수 상등병, 세이 P 아사기리 대령했습니다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>나한테 다시 슈가러쉬나 피아노 맨을 만들어주면 더는 귀찮게 굴지 않을게.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>미안해요. 아까 그건 우리의 복무신조 비슷한거에요. 매일 아침에 복창하는거죠.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그러니 너무 많이 넣으면, 손님이 빨리 취해버리게 될거야 잘 생각해서 넣어.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>내가 어색해서 그렇게 부르는게 아니라, 그냥 습관적으로 그렇게 부르는거잖아.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이렇게 버튼을 누르면, 재료를 섞은 뒤에 기기가 자동으로 얼음을 추가시켜주지.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>네가 피아노 맨을 만들 수 있을 정도 상태면, 나머지 과정은 생략할게. 그래도 웬만하면 잠깐참고 나랑 어울려줘, 괜찮지?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아뇨, 그쪽이랑은 달라요. 음...정말 완전히 다른 부대라고요. 우리는 폭동 진압 같은 일은 전혀 하지 않아요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>폭동...? 아! 아뇨아뇨아뇨... 그건 아마 블리츠크리그 군단일거에요. 엄청 큰 갑옷 입은 부대 말하는 거죠?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>리셋 버튼은 아무 때나 누를 수 있어. 셰이커가 움직이고 있을 때도 말이지. 부담 가지지 말고 원할 때 눌러.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>혹시 용어를 모를 수도 있으니 하는 말인데, "온더록스"는 "얼음"버튼을 눌러서 얼음을 넣어야 한다는 걸 의미해</x:t>
+  </x:si>
+  <x:si>
+    <x:t>또 맛이나 종류 기준으로 검색할 수 있어. "달콤한" 술이나 "남성적인" 술을 정렬시켜 볼 수 있다는 거야.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Texture2D/Character_Gillian_Surprise</x:t>
+  </x:si>
+  <x:si>
+    <x:t>했어. 너, 역시 딴 생각에 빠져 있는 것 같아. 그것도 아주 심하게.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>길에게 다시 슈가러쉬나 피아노 맨을 주자고. 이번엔 정확히 섞어보자.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아, 만약 제조에 실패했다면 리셋 버튼을 눌러서 다시 시도할 수 있어.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>발키리 군단 소속이라고 하셨죠? 그럼 폭동 진압 같은 일들을 하시나요?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>다 끝나면 서빙하기 버튼을 눌러서 손님에게 전해주면 돼. 그게 다야.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오른쪽 가운데에 있는 셰이커에 재료를 원하는 양만큼 클릭해서 넣어.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(어제는 1시간 동안 혼자 떠들었다고 오해받는 일이 생기질않나.)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>네? 아, 미안해요. 너무 편안해서 쓰고 있다는걸 자주 까먹어요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그런 것 같아요.</x:t>
   </x:si>
   <x:si>
     <x:t>음? 별로, 아냐.</x:t>
   </x:si>
   <x:si>
-    <x:t>그럼 우리 기초 과정부터 한번 다시 확인해 보자고. 괜찮지? 혹시 모르니까 말야</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그러고 난 다음, 섞기 버튼을 누르면 돼. 다시 눌러서 섞는 걸 멈출 수 있고.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아, 마지막 문장은 그렇게 신경쓰지 않아도 돼. 그냥 재밌는 뒷이야기 같은 거니까.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"우리는 가장 어두운 시기에 타오르는 빛이자, 범죄의 희생양들을 도와주는 자!"</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(아, 그러고 보니 내 아파트 방바닥에 맥주 캔들이 엄청나게 널브러져 있었지. 또...)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>너는 어그멘티드 아이의 편집장이자 소유주인 도노반 D.도슨님과 대화를 나누고 있는 거라고.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>칵테일 조합법에 있는 탐색 막대를 이용해 레시피를 확인해 봐. 왼쪽 상단에 표시될거야.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>화이트 나이츠 손님은 그리 많지 않은데 말이죠, 사실 제대로 기억나는건 한명 뿐이지만요.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그런 것 같아요.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(게다가 포어에게 중성화 수술을 시켜주느라 지갑 속 마지막 동전 하나까지 다써버렸지. 월세를 한번만 더 미뤘다간 쫒겨날거야...)</x:t>
+    <x:t>자 그럼 시작해볼까?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아- 알겠습니다...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이제 좀 낫나요?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>안녕하세-...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>알았다, 알았어...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아, 안녕 존.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VoicePath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이제 설명 끝났어?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>무슨 말 했어?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TexturePath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string[]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>보스는 어디 있어?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아! 어서 와, 질.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>네, 고맙습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아아 좋아, 딱 제가 원했던 거예요. 감사합니다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_015</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_012</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_033</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_037</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_024</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_028</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_042</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_027</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_020</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_021</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_039</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_038</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(참 흥미로운 손님으로 하루를 시작하게 됐는걸.)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_019</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_013</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_011</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_034</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_029</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_030</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_032</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_016</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_014</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_040</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_022</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_023</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_031</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_3_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_043</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_017</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_2_000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_007</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_3_005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_3_008</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_018</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_3_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_3_007</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_009</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_2_007</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_041</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_006</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_3_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_008</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_036</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_2_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_2_005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_3_000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_3_011</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_2_011</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_3_004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_010</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_035</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_3_006</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_2_009</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_2_006</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_2_010</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_3_010</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_2_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_2_004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_2_008</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_3_012</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_2_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Texture2D/Character_Sei_Sad</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_3_009</x:t>
   </x:si>
   <x:si>
     <x:t>아...</x:t>
   </x:si>
   <x:si>
-    <x:t>내가 어색해서 그렇게 부르는게 아니라, 그냥 습관적으로 그렇게 부르는거잖아.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>내가 이 동네에서 미팅이 있었다는 사실에 감사하도록 해, 이딴 개떡 같은 곳은 나같은 분의 존재 자체로도 도움이 될테니까.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>만약에 레시피에 "카모트린 추가 가능"이라고 써져 있다면, 아예 넣지 않을 수도 잔 끝까지 채워 넣을 수도 있다는 의미야.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"구조하라, 치료하라, 보호하라! 우리는 적습으로 고통받는 자들에게 위안을 주는 천사들일지어니!"</x:t>
-  </x:si>
-  <x:si>
-    <x:t>길이 슈가 러쉬나 피아노 맨을 달라는군. 만약에 망쳤다면, 재시도 버튼을 눌러서 다시 하면 되겠지.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이렇게 버튼을 누르면, 재료를 섞은 뒤에 기기가 자동으로 얼음을 추가시켜주지.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그러니 너무 많이 넣으면, 손님이 빨리 취해버리게 될거야 잘 생각해서 넣어.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>미안해요. 아까 그건 우리의 복무신조 비슷한거에요. 매일 아침에 복창하는거죠.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>나한테 다시 슈가러쉬나 피아노 맨을 만들어주면 더는 귀찮게 굴지 않을게.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>발키리 군단 제 765부대 소속 특수 상등병, 세이 P 아사기리 대령했습니다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>네가 피아노 맨을 만들 수 있을 정도 상태면, 나머지 과정은 생략할게. 그래도 웬만하면 잠깐참고 나랑 어울려줘, 괜찮지?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아뇨, 그쪽이랑은 달라요. 음...정말 완전히 다른 부대라고요. 우리는 폭동 진압 같은 일은 전혀 하지 않아요.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>혹시 용어를 모를 수도 있으니 하는 말인데, "온더록스"는 "얼음"버튼을 눌러서 얼음을 넣어야 한다는 걸 의미해</x:t>
-  </x:si>
-  <x:si>
-    <x:t>폭동...? 아! 아뇨아뇨아뇨... 그건 아마 블리츠크리그 군단일거에요. 엄청 큰 갑옷 입은 부대 말하는 거죠?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>리셋 버튼은 아무 때나 누를 수 있어. 셰이커가 움직이고 있을 때도 말이지. 부담 가지지 말고 원할 때 눌러.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>또 맛이나 종류 기준으로 검색할 수 있어. "달콤한" 술이나 "남성적인" 술을 정렬시켜 볼 수 있다는 거야.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>네? 아, 미안해요. 너무 편안해서 쓰고 있다는걸 자주 까먹어요.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>길에게 다시 슈가러쉬나 피아노 맨을 주자고. 이번엔 정확히 섞어보자.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>다 끝나면 서빙하기 버튼을 눌러서 손님에게 전해주면 돼. 그게 다야.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>오른쪽 가운데에 있는 셰이커에 재료를 원하는 양만큼 클릭해서 넣어.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아, 만약 제조에 실패했다면 리셋 버튼을 눌러서 다시 시도할 수 있어.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>발키리 군단 소속이라고 하셨죠? 그럼 폭동 진압 같은 일들을 하시나요?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(어제는 1시간 동안 혼자 떠들었다고 오해받는 일이 생기질않나.)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Texture2D/Character_Gillian_Surprise</x:t>
-  </x:si>
-  <x:si>
-    <x:t>했어. 너, 역시 딴 생각에 빠져 있는 것 같아. 그것도 아주 심하게.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_1_1_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_1_1_000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어떤기사도 내 손길이 닿지 않고 발간될 수는 없지.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_2_004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_1_2_003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Texture2D/Character_Sei_Meka</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그래, 이거 좋군. 정말 괜찮아. 아주 잘 했다 이거야.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_3_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>오늘자 봉급은 계좌로 넣어줄게.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어찌됐건, 유리잔들 설거지 끝나고 나면 가도 좋아.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_1_003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>음...이건 너무 길죠, 그냥 세이라고 불러주세요.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_1_2_000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_3_008</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_3_010</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_3_012</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_3_007</x:t>
-  </x:si>
-  <x:si>
-    <x:t>다시한번 세이에게 문블라스트를 만들어주자. 문블라스트!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_3_011</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_1_3_006</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Texture2D/Character_Sei_Smile</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_2_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_1_3_000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_3_003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_3_009</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_3_004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_1_2_005</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_2_000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_3_005</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_3_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_3_006</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_1_1_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_1_010</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_2_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_1_004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_1_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이제 좀 낫나요?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아- 알겠습니다...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>안녕하세-...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이제 설명 끝났어?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>알았다, 알았어...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아, 안녕 존.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VoicePath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>무슨 말 했어?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>자 그럼 시작해볼까?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TexturePath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string[]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>네, 고맙습니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>보스는 어디 있어?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아! 어서 와, 질.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_1_2_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>내가 너를 쥴스라고 부를 수 있게 허락해줄 때 쯤.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_1_000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_1_3_005</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_1_3_007</x:t>
-  </x:si>
-  <x:si>
-    <x:t>음료는 "온더록스" 혹은 숙성을 요구하는지 확인해야 해.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_1_3_003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_1_3_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_1_3_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_1_3_008</x:t>
-  </x:si>
-  <x:si>
-    <x:t>음...작고, 달콤하고, 차가운..문블라스트가 좋겠네요.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_3_000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_1_011</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_1_3_004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>오히려, 그들의 뒷처리를 맡는 부대라고 할 수 있겠네요.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_1_2_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_1_008</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_1_005</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_1_009</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_1_3_009</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_1_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Texture2D/Character_Sei_Basic</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_1_007</x:t>
-  </x:si>
-  <x:si>
-    <x:t>제길, 질. 정신차려. 손님은 맥주를 원해! 맥.주!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_1_006</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_3_013</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Texture2D/Character_Boss_Basic</x:t>
-  </x:si>
-  <x:si>
-    <x:t>미안, 무슨 말 했어?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그래, 이제 막 끝났어.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CharacterDataId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>자, 충분히 오래 놀아줬지?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>내가 방금 한 말 들었어?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그래. 잡아둬서 미안.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>음...방금 그건 뭐였죠?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NextDialogueId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>음..다른걸 만들어보자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>음..뭐, 감사합니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>거기 너! 맥주 한잔 줘</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어떤걸로 드릴까요, 세이?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그럼 이제 일을 시작하자고.</x:t>
+    <x:t>네, 맞아요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>여기요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하아...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>흐음...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시끄러워.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>안녕하세요!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>길...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>좋은 저녁.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>여기있습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>음...</x:t>
   </x:si>
   <x:si>
     <x:t>무슨말이죠?</x:t>
   </x:si>
   <x:si>
+    <x:t>그게 뭔데?</x:t>
+  </x:si>
+  <x:si>
     <x:t>(name)</x:t>
   </x:si>
   <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>네, 맞아요.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>여기요.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그게 뭔데?</x:t>
+    <x:t>당연하지!</x:t>
   </x:si>
   <x:si>
     <x:t>고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>음...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>당연하지!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하아...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>흐음...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시끄러워.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>안녕하세요!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>좋은 저녁.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>길...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>여기있습니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_024</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_020</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_028</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_042</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_037</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_027</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_012</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아아 좋아, 딱 제가 원했던 거예요. 감사합니다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_015</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_033</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_019</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_039</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(참 흥미로운 손님으로 하루를 시작하게 됐는걸.)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_014</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_032</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_030</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_038</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_034</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_011</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_016</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_021</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_013</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_029</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_022</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_017</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_031</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_023</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_018</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_005</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_3_008</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_3_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_043</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_040</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_2_000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_007</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_3_005</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_3_000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_3_004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_008</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_036</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_2_003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_041</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_3_011</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_2_007</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_2_005</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_2_011</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_006</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_010</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_3_003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_3_007</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_009</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_3_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_035</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_2_010</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_3_009</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_3_006</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_2_004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_2_009</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_2_006</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_2_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_3_010</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_2_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_2_008</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Texture2D/Character_Sei_Sad</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_3_012</x:t>
-  </x:si>
-  <x:si>
-    <x:t>제가 원하는 음료는 아닌것 같아요...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>character_gillian_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>...정말 오늘 일할 수 있는 거 맞아?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>character_donoban_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어떤 일을 하시나요, 손님? 성함이...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>음료 맛있었어요.. 다음에 또 올게요.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"우리는 감시하고, 또한 수호한다!"</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그럼 문제없이 만들어 낼 수 있겠네!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어떤걸로 드릴까요, 어, 성함이..?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>맥주를 원하는군. 덩치가 꽤 커보이는데.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>내가 말했던 것들을 잘 떠올리면서 만들어!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>으음.. 너 덕분에 잘 마시고 간다고.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SelectionDialogueIdList</x:t>
-  </x:si>
-  <x:si>
-    <x:t>괜찮아? 생각이 다른데 가있는 것 같은데.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>character_boss_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이렇게 하루가 끝났군.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>오늘 밤은 여기까지인가?</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1793,7 +1793,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>184</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1"/>
@@ -1805,68 +1805,68 @@
     </x:row>
     <x:row r="2" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s">
-        <x:v>179</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>273</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A3" s="2" t="s">
-        <x:v>44</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
-        <x:v>167</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C3" s="2" t="s">
-        <x:v>124</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="D3" s="2" t="s">
-        <x:v>172</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E3" s="2" t="s">
-        <x:v>23</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F3" s="2" t="s">
-        <x:v>278</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G3" s="2" t="s">
-        <x:v>133</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="H3" s="2" t="s">
-        <x:v>130</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A4" s="4" t="s">
-        <x:v>216</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="B4" s="14" t="s">
-        <x:v>19</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C4" s="4" t="s">
-        <x:v>191</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="D4" s="4" t="s">
-        <x:v>223</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="E4" s="12"/>
       <x:c r="F4" s="16"/>
@@ -1885,21 +1885,21 @@
     </x:row>
     <x:row r="5" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A5" s="4" t="s">
-        <x:v>223</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="B5" s="15" t="s">
-        <x:v>267</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C5" s="4" t="s">
-        <x:v>137</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="D5" s="4" t="s">
-        <x:v>219</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="E5" s="4"/>
       <x:c r="F5" s="4"/>
       <x:c r="G5" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H5" s="4"/>
       <x:c r="I5" s="3"/>
@@ -1915,21 +1915,21 @@
     </x:row>
     <x:row r="6" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A6" s="4" t="s">
-        <x:v>219</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="B6" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C6" s="4" t="s">
-        <x:v>45</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D6" s="4" t="s">
-        <x:v>234</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="E6" s="4"/>
       <x:c r="F6" s="4"/>
       <x:c r="G6" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H6" s="4"/>
       <x:c r="I6" s="3"/>
@@ -1945,21 +1945,21 @@
     </x:row>
     <x:row r="7" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A7" s="4" t="s">
-        <x:v>234</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="B7" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C7" s="4" t="s">
-        <x:v>129</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="D7" s="4" t="s">
-        <x:v>226</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="E7" s="4"/>
       <x:c r="F7" s="4"/>
       <x:c r="G7" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H7" s="4"/>
       <x:c r="I7" s="3"/>
@@ -1975,21 +1975,21 @@
     </x:row>
     <x:row r="8" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A8" s="4" t="s">
-        <x:v>226</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="B8" s="13" t="s">
-        <x:v>267</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C8" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D8" s="4" t="s">
-        <x:v>228</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="E8" s="6"/>
       <x:c r="F8" s="6"/>
       <x:c r="G8" s="6" t="s">
-        <x:v>30</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="H8" s="6"/>
       <x:c r="I8" s="3"/>
@@ -2005,21 +2005,21 @@
     </x:row>
     <x:row r="9" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A9" s="4" t="s">
-        <x:v>228</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="B9" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C9" s="6" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D9" s="4" t="s">
-        <x:v>247</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="E9" s="6"/>
       <x:c r="F9" s="6"/>
       <x:c r="G9" s="6" t="s">
-        <x:v>30</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="H9" s="4"/>
       <x:c r="I9" s="3"/>
@@ -2035,21 +2035,21 @@
     </x:row>
     <x:row r="10" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A10" s="4" t="s">
-        <x:v>247</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="B10" s="13" t="s">
-        <x:v>267</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C10" s="7" t="s">
-        <x:v>139</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D10" s="4" t="s">
-        <x:v>235</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="E10" s="4"/>
       <x:c r="F10" s="7"/>
       <x:c r="G10" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H10" s="7"/>
       <x:c r="I10" s="3"/>
@@ -2065,21 +2065,21 @@
     </x:row>
     <x:row r="11" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A11" s="4" t="s">
-        <x:v>235</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="B11" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C11" s="7" t="s">
-        <x:v>189</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="D11" s="4" t="s">
-        <x:v>239</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="E11" s="7"/>
       <x:c r="F11" s="7"/>
       <x:c r="G11" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H11" s="7"/>
       <x:c r="I11" s="3"/>
@@ -2095,21 +2095,21 @@
     </x:row>
     <x:row r="12" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A12" s="4" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="B12" s="13" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C12" s="6" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D12" s="4" t="s">
         <x:v>239</x:v>
-      </x:c>
-      <x:c r="B12" s="13" t="s">
-        <x:v>267</x:v>
-      </x:c>
-      <x:c r="C12" s="6" t="s">
-        <x:v>279</x:v>
-      </x:c>
-      <x:c r="D12" s="4" t="s">
-        <x:v>251</x:v>
       </x:c>
       <x:c r="E12" s="6"/>
       <x:c r="F12" s="6"/>
       <x:c r="G12" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H12" s="6"/>
       <x:c r="I12" s="3"/>
@@ -2125,21 +2125,21 @@
     </x:row>
     <x:row r="13" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A13" s="4" t="s">
-        <x:v>251</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="B13" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C13" s="4" t="s">
-        <x:v>136</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="D13" s="4" t="s">
-        <x:v>248</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="E13" s="4"/>
       <x:c r="F13" s="4"/>
       <x:c r="G13" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H13" s="4"/>
       <x:c r="I13" s="3"/>
@@ -2155,21 +2155,21 @@
     </x:row>
     <x:row r="14" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A14" s="4" t="s">
-        <x:v>248</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="B14" s="13" t="s">
-        <x:v>267</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C14" s="7" t="s">
-        <x:v>13</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D14" s="4" t="s">
-        <x:v>214</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="E14" s="7"/>
       <x:c r="F14" s="7"/>
       <x:c r="G14" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H14" s="7"/>
       <x:c r="I14" s="3"/>
@@ -2185,21 +2185,21 @@
     </x:row>
     <x:row r="15" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A15" s="4" t="s">
-        <x:v>214</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="B15" s="13" t="s">
-        <x:v>267</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C15" s="7" t="s">
-        <x:v>169</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D15" s="4" t="s">
-        <x:v>201</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="E15" s="6"/>
       <x:c r="F15" s="7"/>
       <x:c r="G15" s="6" t="s">
-        <x:v>30</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="H15" s="7"/>
       <x:c r="I15" s="3"/>
@@ -2215,373 +2215,373 @@
     </x:row>
     <x:row r="16" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A16" s="4" t="s">
-        <x:v>201</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="B16" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C16" s="8" t="s">
-        <x:v>131</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="D16" s="4" t="s">
-        <x:v>218</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="E16" s="8"/>
       <x:c r="F16" s="8"/>
       <x:c r="G16" s="6" t="s">
-        <x:v>30</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="H16" s="8"/>
     </x:row>
     <x:row r="17" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A17" s="4" t="s">
-        <x:v>218</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="B17" s="13" t="s">
-        <x:v>267</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C17" s="9" t="s">
-        <x:v>86</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="D17" s="4" t="s">
-        <x:v>208</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="E17" s="4"/>
       <x:c r="F17" s="8"/>
       <x:c r="G17" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H17" s="9"/>
     </x:row>
     <x:row r="18" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A18" s="4" t="s">
-        <x:v>208</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="B18" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C18" s="9" t="s">
-        <x:v>16</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D18" s="4" t="s">
-        <x:v>203</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E18" s="8"/>
       <x:c r="F18" s="8"/>
       <x:c r="G18" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H18" s="9"/>
     </x:row>
     <x:row r="19" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A19" s="4" t="s">
-        <x:v>203</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="B19" s="13" t="s">
-        <x:v>267</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C19" s="9" t="s">
-        <x:v>183</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="D19" s="4" t="s">
-        <x:v>215</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="E19" s="8"/>
       <x:c r="F19" s="8"/>
       <x:c r="G19" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H19" s="9"/>
     </x:row>
     <x:row r="20" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A20" s="4" t="s">
-        <x:v>215</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="B20" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C20" s="9" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D20" s="4" t="s">
-        <x:v>222</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="E20" s="8"/>
       <x:c r="F20" s="8"/>
       <x:c r="G20" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H20" s="9"/>
     </x:row>
     <x:row r="21" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A21" s="4" t="s">
-        <x:v>222</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="B21" s="13" t="s">
-        <x:v>267</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C21" s="9" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D21" s="4" t="s">
-        <x:v>227</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="E21" s="8"/>
       <x:c r="F21" s="8"/>
       <x:c r="G21" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H21" s="9"/>
     </x:row>
     <x:row r="22" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A22" s="4" t="s">
-        <x:v>227</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="B22" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C22" s="9" t="s">
-        <x:v>84</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="D22" s="4" t="s">
-        <x:v>205</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="E22" s="8"/>
       <x:c r="F22" s="8"/>
       <x:c r="G22" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H22" s="9"/>
     </x:row>
     <x:row r="23" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A23" s="4" t="s">
-        <x:v>205</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="B23" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C23" s="9" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D23" s="4" t="s">
-        <x:v>195</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="E23" s="8"/>
       <x:c r="F23" s="8"/>
       <x:c r="G23" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H23" s="9"/>
     </x:row>
     <x:row r="24" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A24" s="4" t="s">
-        <x:v>195</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="B24" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C24" s="9" t="s">
-        <x:v>37</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D24" s="4" t="s">
-        <x:v>217</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="E24" s="8"/>
       <x:c r="F24" s="8"/>
       <x:c r="G24" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H24" s="9"/>
     </x:row>
     <x:row r="25" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A25" s="4" t="s">
-        <x:v>217</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="B25" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C25" s="9" t="s">
-        <x:v>60</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D25" s="4" t="s">
-        <x:v>221</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="E25" s="8"/>
       <x:c r="F25" s="8"/>
       <x:c r="G25" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H25" s="9"/>
     </x:row>
     <x:row r="26" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A26" s="4" t="s">
-        <x:v>221</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="B26" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C26" s="10" t="s">
-        <x:v>55</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D26" s="4" t="s">
-        <x:v>225</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="E26" s="10"/>
       <x:c r="F26" s="10"/>
       <x:c r="G26" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H26" s="10"/>
     </x:row>
     <x:row r="27" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A27" s="4" t="s">
-        <x:v>225</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="B27" s="13" t="s">
-        <x:v>267</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C27" s="10" t="s">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D27" s="4" t="s">
-        <x:v>194</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="E27" s="10"/>
       <x:c r="F27" s="10"/>
       <x:c r="G27" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H27" s="10"/>
     </x:row>
     <x:row r="28" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A28" s="4" t="s">
-        <x:v>194</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="B28" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C28" s="10" t="s">
-        <x:v>165</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D28" s="4" t="s">
-        <x:v>196</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="E28" s="10"/>
       <x:c r="F28" s="10"/>
       <x:c r="G28" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H28" s="10"/>
     </x:row>
     <x:row r="29" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A29" s="4" t="s">
-        <x:v>196</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="B29" s="13" t="s">
-        <x:v>267</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C29" s="10" t="s">
-        <x:v>268</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D29" s="4" t="s">
-        <x:v>212</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="E29" s="6"/>
       <x:c r="F29" s="10"/>
       <x:c r="G29" s="6" t="s">
-        <x:v>30</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="H29" s="10"/>
     </x:row>
     <x:row r="30" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A30" s="4" t="s">
-        <x:v>212</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="B30" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C30" s="10" t="s">
-        <x:v>186</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="D30" s="4" t="s">
-        <x:v>200</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="E30" s="10"/>
       <x:c r="F30" s="10"/>
       <x:c r="G30" s="6" t="s">
-        <x:v>30</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="H30" s="10"/>
     </x:row>
     <x:row r="31" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A31" s="4" t="s">
-        <x:v>200</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="B31" s="13" t="s">
-        <x:v>267</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C31" s="10" t="s">
-        <x:v>51</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D31" s="4" t="s">
-        <x:v>197</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="E31" s="4"/>
       <x:c r="F31" s="10"/>
       <x:c r="G31" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H31" s="10"/>
     </x:row>
     <x:row r="32" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A32" s="4" t="s">
-        <x:v>197</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="B32" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C32" s="11" t="s">
-        <x:v>45</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D32" s="4" t="s">
-        <x:v>220</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="E32" s="11"/>
       <x:c r="F32" s="11"/>
       <x:c r="G32" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H32" s="11"/>
     </x:row>
     <x:row r="33" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A33" s="4" t="s">
-        <x:v>220</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="B33" s="13" t="s">
-        <x:v>267</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C33" s="11" t="s">
-        <x:v>72</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="D33" s="4" t="s">
-        <x:v>210</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="E33" s="11"/>
       <x:c r="F33" s="11"/>
       <x:c r="G33" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H33" s="11"/>
     </x:row>
     <x:row r="34" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A34" s="4" t="s">
-        <x:v>210</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="B34" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C34" s="11" t="s">
-        <x:v>45</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D34" s="4" t="s">
         <x:v>224</x:v>
@@ -2589,7 +2589,7 @@
       <x:c r="E34" s="11"/>
       <x:c r="F34" s="11"/>
       <x:c r="G34" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H34" s="11"/>
     </x:row>
@@ -2598,70 +2598,70 @@
         <x:v>224</x:v>
       </x:c>
       <x:c r="B35" s="13" t="s">
-        <x:v>267</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C35" s="11" t="s">
-        <x:v>12</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D35" s="4" t="s">
-        <x:v>209</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="E35" s="11"/>
       <x:c r="F35" s="17"/>
       <x:c r="G35" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H35" s="11"/>
     </x:row>
     <x:row r="36" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A36" s="4" t="s">
-        <x:v>209</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="B36" s="13" t="s">
-        <x:v>267</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C36" t="s">
-        <x:v>57</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D36" s="4" t="s">
-        <x:v>204</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="G36" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A37" s="4" t="s">
-        <x:v>204</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="B37" s="13" t="s">
-        <x:v>267</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C37" t="s">
-        <x:v>77</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="D37" s="4" t="s">
-        <x:v>213</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="G37" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A38" s="4" t="s">
-        <x:v>213</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="B38" s="13" t="s">
-        <x:v>267</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C38" t="s">
-        <x:v>81</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="D38" s="4" t="s">
         <x:v>253</x:v>
       </x:c>
       <x:c r="G38" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:7" ht="15.75" customHeight="1">
@@ -2669,67 +2669,67 @@
         <x:v>253</x:v>
       </x:c>
       <x:c r="B39" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C39" t="s">
-        <x:v>192</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="D39" s="4" t="s">
-        <x:v>240</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="G39" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A40" s="4" t="s">
-        <x:v>240</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="B40" s="13" t="s">
-        <x:v>267</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C40" t="s">
-        <x:v>52</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D40" s="4" t="s">
-        <x:v>199</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="G40" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A41" s="4" t="s">
-        <x:v>199</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="B41" s="13" t="s">
-        <x:v>267</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C41" t="s">
-        <x:v>80</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="D41" s="4" t="s">
-        <x:v>211</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="G41" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A42" s="4" t="s">
-        <x:v>211</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="B42" s="13" t="s">
-        <x:v>267</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C42" t="s">
-        <x:v>82</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="D42" s="4" t="s">
         <x:v>206</x:v>
       </x:c>
       <x:c r="G42" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:7" ht="15.75" customHeight="1">
@@ -2737,1038 +2737,1038 @@
         <x:v>206</x:v>
       </x:c>
       <x:c r="B43" s="13" t="s">
-        <x:v>267</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C43" t="s">
-        <x:v>76</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="D43" s="4" t="s">
-        <x:v>232</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="G43" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A44" s="4" t="s">
-        <x:v>232</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="B44" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C44" t="s">
-        <x:v>27</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D44" s="4" t="s">
-        <x:v>242</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="G44" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A45" s="4" t="s">
-        <x:v>242</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="B45" s="13" t="s">
-        <x:v>267</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C45" t="s">
-        <x:v>273</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D45" s="4" t="s">
-        <x:v>198</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="G45" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A46" s="4" t="s">
-        <x:v>198</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="B46" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C46" t="s">
-        <x:v>187</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="D46" s="4" t="s">
-        <x:v>231</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="G46" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A47" s="4" t="s">
-        <x:v>231</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="C47" t="s">
-        <x:v>66</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="D47" s="4"/>
       <x:c r="G47" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A48" s="18" t="s">
-        <x:v>233</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="B48" s="13" t="s">
-        <x:v>267</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C48" t="s">
-        <x:v>18</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D48" s="18" t="s">
-        <x:v>262</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="G48" s="6" t="s">
-        <x:v>30</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A49" s="18" t="s">
-        <x:v>262</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="B49" s="13" t="s">
-        <x:v>267</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C49" t="s">
-        <x:v>173</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D49" s="18" t="s">
-        <x:v>260</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="G49" s="6" t="s">
-        <x:v>30</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A50" s="18" t="s">
-        <x:v>260</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="B50" s="13" t="s">
-        <x:v>267</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C50" t="s">
-        <x:v>143</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D50" s="18" t="s">
-        <x:v>241</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="G50" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A51" s="18" t="s">
-        <x:v>241</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="B51" s="13" t="s">
-        <x:v>267</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C51" t="s">
-        <x:v>36</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D51" s="18" t="s">
-        <x:v>257</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="G51" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A52" s="18" t="s">
-        <x:v>257</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="B52" s="13" t="s">
-        <x:v>267</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C52" t="s">
-        <x:v>74</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="D52" s="18" t="s">
-        <x:v>245</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="G52" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A53" s="18" t="s">
-        <x:v>245</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="B53" s="13" t="s">
-        <x:v>267</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C53" t="s">
-        <x:v>67</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="D53" s="18" t="s">
-        <x:v>259</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="G53" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A54" s="18" t="s">
-        <x:v>259</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B54" s="13" t="s">
-        <x:v>267</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C54" t="s">
-        <x:v>53</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D54" s="18" t="s">
-        <x:v>244</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="G54" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A55" s="18" t="s">
-        <x:v>244</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="B55" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C55" t="s">
-        <x:v>45</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D55" s="18" t="s">
-        <x:v>263</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="G55" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A56" s="18" t="s">
-        <x:v>263</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="B56" s="13" t="s">
-        <x:v>267</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C56" t="s">
-        <x:v>70</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="D56" s="18" t="s">
-        <x:v>258</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="G56" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A57" s="18" t="s">
-        <x:v>258</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="B57" s="13" t="s">
-        <x:v>267</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C57" t="s">
-        <x:v>276</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D57" s="18" t="s">
-        <x:v>254</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="G57" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A58" s="18" t="s">
-        <x:v>254</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="B58" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C58" t="s">
-        <x:v>128</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="D58" s="18" t="s">
-        <x:v>246</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="G58" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A59" s="18" t="s">
-        <x:v>246</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="C59" t="s">
-        <x:v>79</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="G59" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A60" s="18" t="s">
-        <x:v>237</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="B60" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C60" t="s">
-        <x:v>168</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D60" s="18" t="s">
-        <x:v>252</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="G60" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A61" s="18" t="s">
-        <x:v>252</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="B61" s="13" t="s">
-        <x:v>267</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C61" t="s">
-        <x:v>170</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D61" s="18" t="s">
-        <x:v>230</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="G61" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A62" s="18" t="s">
-        <x:v>230</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="B62" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C62" t="s">
-        <x:v>177</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D62" s="18" t="s">
-        <x:v>249</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="G62" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A63" s="18" t="s">
-        <x:v>249</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="B63" s="13" t="s">
-        <x:v>267</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C63" t="s">
-        <x:v>47</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D63" s="18" t="s">
-        <x:v>238</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="G63" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A64" s="18" t="s">
-        <x:v>238</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="B64" s="13" t="s">
-        <x:v>267</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C64" t="s">
-        <x:v>17</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D64" s="18" t="s">
-        <x:v>236</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="G64" s="4" t="s">
-        <x:v>85</x:v>
+        <x:v>168</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A65" s="18" t="s">
-        <x:v>236</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="B65" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C65" t="s">
-        <x:v>42</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D65" s="18" t="s">
-        <x:v>256</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="G65" s="4" t="s">
-        <x:v>85</x:v>
+        <x:v>168</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A66" s="18" t="s">
-        <x:v>256</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="B66" s="13" t="s">
-        <x:v>267</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C66" t="s">
-        <x:v>64</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="D66" s="18" t="s">
-        <x:v>250</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="G66" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A67" s="18" t="s">
-        <x:v>250</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="B67" s="13" t="s">
-        <x:v>267</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C67" t="s">
-        <x:v>39</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D67" s="18" t="s">
-        <x:v>229</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="G67" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A68" s="18" t="s">
-        <x:v>229</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="B68" s="13" t="s">
-        <x:v>267</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C68" t="s">
-        <x:v>68</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="D68" s="18" t="s">
-        <x:v>255</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="G68" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A69" s="18" t="s">
-        <x:v>255</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="B69" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C69" t="s">
-        <x:v>127</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="D69" s="18" t="s">
-        <x:v>261</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="G69" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A70" s="18" t="s">
-        <x:v>261</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="B70" s="13" t="s">
-        <x:v>267</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C70" t="s">
-        <x:v>166</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D70" s="18" t="s">
-        <x:v>243</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="G70" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A71" s="18" t="s">
-        <x:v>243</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="B71" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C71" t="s">
-        <x:v>132</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="D71" s="18" t="s">
-        <x:v>265</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="G71" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A72" s="18" t="s">
-        <x:v>265</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="B72" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C72" t="s">
-        <x:v>14</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G72" s="4"/>
     </x:row>
     <x:row r="73" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A73" s="4" t="s">
-        <x:v>88</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B73" t="s">
-        <x:v>269</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C73" t="s">
-        <x:v>175</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D73" s="4" t="s">
-        <x:v>87</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="G73" s="4" t="s">
-        <x:v>34</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A74" s="4" t="s">
-        <x:v>87</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="B74" s="19" t="s">
-        <x:v>19</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C74" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="D74" s="4" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="G74" s="4" t="s">
         <x:v>21</x:v>
-      </x:c>
-      <x:c r="D74" s="4" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="G74" s="4" t="s">
-        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A75" s="4" t="s">
-        <x:v>118</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B75" s="12"/>
       <x:c r="C75" t="s">
-        <x:v>275</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D75" s="4"/>
       <x:c r="G75" s="4" t="s">
-        <x:v>34</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A76" s="4" t="s">
-        <x:v>99</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B76" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C76" t="s">
-        <x:v>43</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D76" s="4" t="s">
-        <x:v>153</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="G76" s="4" t="s">
-        <x:v>34</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A77" s="4" t="s">
-        <x:v>153</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B77" t="s">
-        <x:v>269</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C77" t="s">
-        <x:v>45</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D77" s="4" t="s">
-        <x:v>138</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="G77" s="4" t="s">
-        <x:v>33</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A78" s="4" t="s">
-        <x:v>138</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B78" t="s">
-        <x:v>269</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C78" t="s">
-        <x:v>38</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D78" s="4" t="s">
-        <x:v>91</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="G78" s="4" t="s">
-        <x:v>33</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A79" s="4" t="s">
-        <x:v>91</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B79" t="s">
-        <x:v>269</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C79" t="s">
-        <x:v>32</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D79" s="4" t="s">
-        <x:v>40</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="G79" s="4" t="s">
-        <x:v>34</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A80" s="4" t="s">
-        <x:v>40</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B80" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C80" t="s">
-        <x:v>125</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="D80" s="4" t="s">
-        <x:v>113</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="G80" s="4" t="s">
-        <x:v>34</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A81" s="4" t="s">
-        <x:v>113</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="B81" t="s">
-        <x:v>269</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C81" t="s">
-        <x:v>161</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="G81" s="4" t="s">
-        <x:v>34</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A82" s="4" t="s">
-        <x:v>109</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="B82" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C82" t="s">
-        <x:v>193</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="D82" t="s">
-        <x:v>145</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="G82" s="4" t="s">
-        <x:v>34</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A83" s="4" t="s">
-        <x:v>145</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B83" t="s">
-        <x:v>269</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C83" t="s">
-        <x:v>93</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="D83" t="s">
-        <x:v>146</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="G83" s="4" t="s">
-        <x:v>31</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A84" s="4" t="s">
-        <x:v>146</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B84" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C84" t="s">
-        <x:v>174</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D84" t="s">
-        <x:v>144</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="G84" s="4" t="s">
-        <x:v>31</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A85" s="4" t="s">
-        <x:v>144</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B85" t="s">
-        <x:v>269</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C85" t="s">
-        <x:v>63</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="D85" t="s">
-        <x:v>151</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="G85" s="4" t="s">
-        <x:v>31</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A86" s="4" t="s">
-        <x:v>151</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B86" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C86" t="s">
-        <x:v>188</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="D86" t="s">
-        <x:v>141</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="G86" s="4" t="s">
-        <x:v>31</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A87" s="4" t="s">
-        <x:v>141</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B87" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C87" t="s">
-        <x:v>270</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D87" t="s">
-        <x:v>106</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="G87" s="4" t="s">
-        <x:v>31</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A88" s="4" t="s">
-        <x:v>106</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="B88" t="s">
-        <x:v>269</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C88" t="s">
-        <x:v>56</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D88" t="s">
-        <x:v>142</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="G88" s="4" t="s">
-        <x:v>34</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A89" s="4" t="s">
-        <x:v>142</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B89" t="s">
-        <x:v>269</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C89" t="s">
-        <x:v>89</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="D89" t="s">
-        <x:v>147</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="G89" s="4" t="s">
-        <x:v>34</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A90" s="4" t="s">
-        <x:v>147</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B90" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C90" t="s">
-        <x:v>207</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="D90" t="s">
-        <x:v>157</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="G90" s="4" t="s">
-        <x:v>34</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A91" s="4" t="s">
-        <x:v>157</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B91" t="s">
-        <x:v>269</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C91" t="s">
-        <x:v>277</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="G91" s="4" t="s">
-        <x:v>34</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A92" s="4" t="s">
-        <x:v>140</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B92" s="12" t="s">
-        <x:v>15</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C92" t="s">
-        <x:v>190</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="D92" t="s">
-        <x:v>158</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="G92" s="4" t="s">
-        <x:v>92</x:v>
+        <x:v>119</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A93" s="4" t="s">
-        <x:v>158</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B93" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C93" t="s">
-        <x:v>126</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="D93" t="s">
-        <x:v>122</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="G93" s="4" t="s">
-        <x:v>92</x:v>
+        <x:v>119</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A94" s="4" t="s">
-        <x:v>122</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B94" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C94" t="s">
-        <x:v>45</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D94" t="s">
-        <x:v>97</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="G94" s="4" t="s">
-        <x:v>92</x:v>
+        <x:v>119</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A95" s="4" t="s">
-        <x:v>97</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="B95" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C95" t="s">
-        <x:v>22</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D95" t="s">
-        <x:v>121</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="G95" s="4" t="s">
-        <x:v>92</x:v>
+        <x:v>119</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A96" s="4" t="s">
-        <x:v>121</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B96" s="12" t="s">
-        <x:v>15</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C96" t="s">
-        <x:v>78</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="D96" t="s">
-        <x:v>155</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="G96" s="4" t="s">
-        <x:v>92</x:v>
+        <x:v>119</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A97" s="4" t="s">
-        <x:v>155</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B97" s="12" t="s">
-        <x:v>15</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C97" t="s">
-        <x:v>123</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="D97" t="s">
-        <x:v>162</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="G97" s="4" t="s">
-        <x:v>159</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A98" s="4" t="s">
-        <x:v>162</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B98" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C98" t="s">
-        <x:v>135</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="D98" t="s">
-        <x:v>160</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="G98" s="4" t="s">
-        <x:v>159</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A99" s="4" t="s">
-        <x:v>160</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B99" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C99" t="s">
-        <x:v>274</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D99" t="s">
-        <x:v>154</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="G99" s="4" t="s">
-        <x:v>159</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A100" s="4" t="s">
-        <x:v>154</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B100" s="12" t="s">
-        <x:v>15</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C100" t="s">
-        <x:v>71</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="D100" t="s">
-        <x:v>156</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="G100" s="4" t="s">
-        <x:v>159</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A101" s="4" t="s">
-        <x:v>156</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B101" s="12" t="s">
-        <x:v>15</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C101" t="s">
-        <x:v>98</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="D101" t="s">
-        <x:v>119</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="G101" s="4" t="s">
-        <x:v>159</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A102" s="4" t="s">
-        <x:v>119</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B102" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C102" t="s">
-        <x:v>176</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D102" t="s">
-        <x:v>150</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="G102" s="4" t="s">
-        <x:v>159</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A103" s="4" t="s">
-        <x:v>150</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B103" s="12" t="s">
-        <x:v>15</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C103" t="s">
-        <x:v>148</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="G103" s="4" t="s">
-        <x:v>159</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A104" s="4" t="s">
-        <x:v>114</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="B104" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C104" t="s">
-        <x:v>182</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="D104" t="s">
-        <x:v>108</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="G104" s="18" t="s">
-        <x:v>159</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A105" s="4" t="s">
-        <x:v>108</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="B105" s="12" t="s">
-        <x:v>15</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C105" t="s">
-        <x:v>185</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="D105" t="s">
-        <x:v>120</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="G105" s="4" t="s">
         <x:v>264</x:v>
@@ -3776,16 +3776,16 @@
     </x:row>
     <x:row r="106" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A106" s="4" t="s">
-        <x:v>120</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B106" s="12" t="s">
-        <x:v>15</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C106" t="s">
-        <x:v>266</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D106" t="s">
-        <x:v>41</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="G106" s="4" t="s">
         <x:v>264</x:v>
@@ -3793,16 +3793,16 @@
     </x:row>
     <x:row r="107" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A107" s="4" t="s">
-        <x:v>41</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B107" s="12" t="s">
-        <x:v>15</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C107" t="s">
-        <x:v>20</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D107" t="s">
-        <x:v>90</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="G107" s="4" t="s">
         <x:v>264</x:v>
@@ -3810,13 +3810,13 @@
     </x:row>
     <x:row r="108" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A108" s="4" t="s">
-        <x:v>90</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B108" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C108" t="s">
-        <x:v>104</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="G108" s="4" t="s">
         <x:v>264</x:v>
@@ -3824,432 +3824,432 @@
     </x:row>
     <x:row r="109" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A109" s="4" t="s">
-        <x:v>149</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B109" s="12" t="s">
-        <x:v>15</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C109" t="s">
-        <x:v>202</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="D109" t="s">
-        <x:v>116</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="G109" s="18" t="s">
-        <x:v>107</x:v>
+        <x:v>144</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A110" s="4" t="s">
-        <x:v>116</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="B110" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C110" t="s">
-        <x:v>58</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D110" t="s">
-        <x:v>94</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="G110" s="18" t="s">
-        <x:v>107</x:v>
+        <x:v>144</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A111" s="4" t="s">
-        <x:v>94</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B111" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C111" t="s">
-        <x:v>83</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="D111" t="s">
-        <x:v>110</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="G111" s="18" t="s">
-        <x:v>107</x:v>
+        <x:v>144</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A112" s="4" t="s">
-        <x:v>110</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="B112" s="12" t="s">
-        <x:v>15</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C112" t="s">
-        <x:v>75</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="D112" t="s">
-        <x:v>112</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="G112" s="18" t="s">
-        <x:v>159</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A113" s="4" t="s">
-        <x:v>112</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="B113" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C113" t="s">
-        <x:v>181</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="D113" t="s">
-        <x:v>115</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="G113" s="18" t="s">
-        <x:v>159</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A114" s="4" t="s">
-        <x:v>115</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B114" s="12" t="s">
-        <x:v>15</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C114" t="s">
-        <x:v>73</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="D114" t="s">
-        <x:v>117</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="G114" s="18" t="s">
-        <x:v>159</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A115" s="4" t="s">
-        <x:v>117</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B115" s="12" t="s">
-        <x:v>15</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C115" t="s">
-        <x:v>152</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D115" t="s">
-        <x:v>103</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="G115" s="18" t="s">
-        <x:v>159</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A116" s="4" t="s">
-        <x:v>103</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="B116" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C116" t="s">
-        <x:v>178</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="D116" t="s">
-        <x:v>100</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="G116" s="18" t="s">
-        <x:v>159</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A117" s="4" t="s">
-        <x:v>100</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="B117" s="12" t="s">
-        <x:v>15</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C117" t="s">
-        <x:v>65</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="D117" t="s">
-        <x:v>111</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="G117" s="18" t="s">
-        <x:v>159</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A118" s="4" t="s">
-        <x:v>111</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="B118" s="12" t="s">
-        <x:v>15</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C118" t="s">
-        <x:v>54</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D118" t="s">
-        <x:v>101</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="G118" s="18" t="s">
-        <x:v>159</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A119" s="4" t="s">
-        <x:v>101</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B119" s="12" t="s">
-        <x:v>15</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C119" t="s">
-        <x:v>272</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D119" t="s">
-        <x:v>105</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="G119" s="18" t="s">
-        <x:v>159</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A120" s="4" t="s">
-        <x:v>105</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="B120" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C120" t="s">
-        <x:v>171</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D120" t="s">
-        <x:v>102</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="G120" s="18" t="s">
-        <x:v>159</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A121" s="4" t="s">
-        <x:v>102</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B121" s="12" t="s">
-        <x:v>15</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C121" t="s">
-        <x:v>69</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="D121" t="s">
-        <x:v>163</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="G121" s="18" t="s">
-        <x:v>159</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A122" s="4" t="s">
-        <x:v>163</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B122" s="12" t="s">
-        <x:v>15</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C122" t="s">
-        <x:v>271</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D122" t="s">
-        <x:v>1</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="G122" s="18" t="s">
-        <x:v>159</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:4" ht="15.75" customHeight="1">
       <x:c r="A123" s="4" t="s">
-        <x:v>1</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B123" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C123" t="s">
-        <x:v>49</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D123" t="s">
-        <x:v>4</x:v>
+        <x:v>111</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:4" ht="15.75" customHeight="1">
       <x:c r="A124" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B124" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C124" t="s">
-        <x:v>45</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D124" t="s">
-        <x:v>0</x:v>
+        <x:v>113</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:4" ht="15.75" customHeight="1">
       <x:c r="A125" s="4" t="s">
-        <x:v>0</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B125" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C125" t="s">
-        <x:v>281</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D125" t="s">
-        <x:v>2</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A126" s="4" t="s">
-        <x:v>2</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B126" s="12" t="s">
-        <x:v>280</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C126" t="s">
-        <x:v>282</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D126" t="s">
-        <x:v>9</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="G126" s="18" t="s">
-        <x:v>164</x:v>
+        <x:v>108</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A127" s="4" t="s">
-        <x:v>9</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="B127" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C127" t="s">
-        <x:v>59</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="D127" t="s">
-        <x:v>3</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="G127" s="18" t="s">
-        <x:v>164</x:v>
+        <x:v>108</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A128" s="4" t="s">
-        <x:v>3</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="B128" s="12" t="s">
-        <x:v>280</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C128" t="s">
-        <x:v>185</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="D128" t="s">
-        <x:v>10</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="G128" s="18" t="s">
-        <x:v>164</x:v>
+        <x:v>108</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A129" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="B129" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C129" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D129" t="s">
-        <x:v>6</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="G129" s="18" t="s">
-        <x:v>164</x:v>
+        <x:v>108</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A130" s="4" t="s">
-        <x:v>6</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B130" s="12" t="s">
-        <x:v>280</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C130" t="s">
-        <x:v>50</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="D130" t="s">
-        <x:v>5</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="G130" s="18" t="s">
-        <x:v>164</x:v>
+        <x:v>108</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A131" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="B131" s="12" t="s">
-        <x:v>280</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C131" t="s">
-        <x:v>62</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="D131" t="s">
-        <x:v>11</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="G131" s="18" t="s">
-        <x:v>164</x:v>
+        <x:v>108</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A132" s="4" t="s">
-        <x:v>11</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B132" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C132" t="s">
-        <x:v>61</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="D132" t="s">
-        <x:v>8</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="G132" s="18" t="s">
-        <x:v>164</x:v>
+        <x:v>108</x:v>
       </x:c>
     </x:row>
     <x:row r="133" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A133" s="4" t="s">
-        <x:v>8</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B133" s="12" t="s">
-        <x:v>280</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C133" t="s">
-        <x:v>96</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="D133" t="s">
-        <x:v>7</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="G133" s="18" t="s">
-        <x:v>164</x:v>
+        <x:v>108</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A134" s="4" t="s">
-        <x:v>7</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B134" s="12" t="s">
-        <x:v>280</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C134" t="s">
-        <x:v>95</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G134" s="18" t="s">
-        <x:v>164</x:v>
+        <x:v>108</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:1" ht="15.75" customHeight="1">
